--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A236C0-E229-47FA-BB97-C980C094582E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F862BD5-6CDF-4A44-BF04-5DE8AF0F5E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1637,7 +1637,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1676,7 +1676,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="8" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -2002,7 +2003,8 @@
     <col min="4" max="4" width="7.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="6.7109375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="16" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="17" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -2046,6 +2048,9 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
+      <c r="H2" s="17">
+        <v>53.333333333333336</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -2061,6 +2066,9 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
+      <c r="H3" s="17">
+        <v>86.666666666666671</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
@@ -2076,6 +2084,9 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
+      <c r="H4" s="17">
+        <v>66.666666666666657</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -2091,6 +2102,9 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
+      <c r="H5" s="17">
+        <v>26.666666666666668</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -2106,6 +2120,9 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
+      <c r="H6" s="17">
+        <v>43.333333333333336</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
@@ -2121,6 +2138,9 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
+      <c r="H7" s="17">
+        <v>53.333333333333336</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -2136,6 +2156,9 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
+      <c r="H8" s="17">
+        <v>73.333333333333329</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
@@ -2151,6 +2174,9 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
+      <c r="H9" s="17">
+        <v>50</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
@@ -2166,6 +2192,9 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
+      <c r="H10" s="17">
+        <v>96.666666666666671</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -2181,6 +2210,9 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
+      <c r="H11" s="17">
+        <v>73.333333333333329</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
@@ -2196,6 +2228,9 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
+      <c r="H12" s="17">
+        <v>36.666666666666664</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
@@ -2211,6 +2246,9 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
+      <c r="H13" s="17">
+        <v>80</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
@@ -2226,6 +2264,9 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
+      <c r="H14" s="17">
+        <v>60</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
@@ -2241,6 +2282,9 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
+      <c r="H15" s="17">
+        <v>80</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -2256,8 +2300,11 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>31</v>
       </c>
@@ -2271,8 +2318,11 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>33</v>
       </c>
@@ -2286,8 +2336,11 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="17">
+        <v>46.666666666666664</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>35</v>
       </c>
@@ -2301,8 +2354,11 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>37</v>
       </c>
@@ -2316,8 +2372,11 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>39</v>
       </c>
@@ -2331,8 +2390,11 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="17">
+        <v>73.333333333333329</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
@@ -2346,8 +2408,11 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" s="17">
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
@@ -2361,8 +2426,11 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>45</v>
       </c>
@@ -2376,8 +2444,11 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>47</v>
       </c>
@@ -2391,8 +2462,11 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" s="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>49</v>
       </c>
@@ -2406,8 +2480,11 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>51</v>
       </c>
@@ -2421,8 +2498,11 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27" s="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>53</v>
       </c>
@@ -2436,8 +2516,11 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H28" s="17">
+        <v>96.666666666666671</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>55</v>
       </c>
@@ -2451,8 +2534,11 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>57</v>
       </c>
@@ -2466,8 +2552,11 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H30" s="17">
+        <v>96.666666666666671</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2570,11 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H31" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>61</v>
       </c>
@@ -2496,8 +2588,11 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="17">
+        <v>36.666666666666664</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>63</v>
       </c>
@@ -2511,8 +2606,11 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>65</v>
       </c>
@@ -2526,8 +2624,11 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>67</v>
       </c>
@@ -2541,8 +2642,11 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H35" s="17">
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>69</v>
       </c>
@@ -2556,8 +2660,11 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>71</v>
       </c>
@@ -2571,8 +2678,11 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>73</v>
       </c>
@@ -2586,8 +2696,11 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" s="17">
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>75</v>
       </c>
@@ -2601,8 +2714,11 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>77</v>
       </c>
@@ -2616,8 +2732,11 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40" s="17">
+        <v>46.666666666666664</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>79</v>
       </c>
@@ -2631,8 +2750,11 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41" s="17">
+        <v>56.666666666666664</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>82</v>
       </c>
@@ -2646,8 +2768,11 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" s="17">
+        <v>13.333333333333334</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>84</v>
       </c>
@@ -2661,8 +2786,11 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43" s="17">
+        <v>53.333333333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>86</v>
       </c>
@@ -2676,8 +2804,11 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>88</v>
       </c>
@@ -2691,8 +2822,11 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H45" s="17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>90</v>
       </c>
@@ -2706,8 +2840,11 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46" s="17">
+        <v>73.333333333333329</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>92</v>
       </c>
@@ -2721,8 +2858,11 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47" s="17">
+        <v>53.333333333333336</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>94</v>
       </c>
@@ -2736,8 +2876,11 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>96</v>
       </c>
@@ -2751,8 +2894,11 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49" s="17">
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>98</v>
       </c>
@@ -2766,8 +2912,11 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50" s="17">
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>100</v>
       </c>
@@ -2781,8 +2930,11 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51" s="17">
+        <v>73.333333333333329</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>102</v>
       </c>
@@ -2796,8 +2948,11 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52" s="17">
+        <v>53.333333333333336</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>104</v>
       </c>
@@ -2811,8 +2966,11 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>106</v>
       </c>
@@ -2826,8 +2984,11 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54" s="17">
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>108</v>
       </c>
@@ -2841,8 +3002,11 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55" s="17">
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>110</v>
       </c>
@@ -2856,8 +3020,11 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56" s="17">
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>112</v>
       </c>
@@ -2871,8 +3038,11 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>114</v>
       </c>
@@ -2886,8 +3056,11 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58" s="17">
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>116</v>
       </c>
@@ -2901,8 +3074,11 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H59" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>118</v>
       </c>
@@ -2916,8 +3092,11 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60" s="17">
+        <v>53.333333333333336</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>120</v>
       </c>
@@ -2931,8 +3110,11 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H61" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>122</v>
       </c>
@@ -2946,8 +3128,11 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>124</v>
       </c>
@@ -2961,8 +3146,11 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H63" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>126</v>
       </c>
@@ -2976,8 +3164,11 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64" s="17">
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>128</v>
       </c>
@@ -2991,8 +3182,11 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>130</v>
       </c>
@@ -3006,8 +3200,11 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66" s="17">
+        <v>96.666666666666671</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>132</v>
       </c>
@@ -3021,8 +3218,11 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67" s="17">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>134</v>
       </c>
@@ -3036,8 +3236,11 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>136</v>
       </c>
@@ -3051,8 +3254,11 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69" s="17">
+        <v>73.333333333333329</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>138</v>
       </c>
@@ -3066,8 +3272,11 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70" s="17">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>140</v>
       </c>
@@ -3081,8 +3290,11 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71" s="17">
+        <v>53.333333333333336</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>142</v>
       </c>
@@ -3096,8 +3308,11 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72" s="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>144</v>
       </c>
@@ -3111,8 +3326,11 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H73" s="17">
+        <v>96.666666666666671</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>146</v>
       </c>
@@ -3126,8 +3344,11 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H74" s="17">
+        <v>23.333333333333332</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>148</v>
       </c>
@@ -3141,8 +3362,11 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H75" s="17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>150</v>
       </c>
@@ -3156,8 +3380,11 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H76" s="17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
         <v>152</v>
       </c>
@@ -3171,8 +3398,11 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H77" s="17">
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>154</v>
       </c>
@@ -3186,8 +3416,11 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H78" s="17">
+        <v>23.333333333333332</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
         <v>156</v>
       </c>
@@ -3201,8 +3434,11 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H79" s="17">
+        <v>43.333333333333336</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>158</v>
       </c>
@@ -3216,8 +3452,11 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H80" s="17">
+        <v>63.333333333333329</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
         <v>160</v>
       </c>
@@ -3231,8 +3470,11 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H81" s="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>162</v>
       </c>
@@ -3246,8 +3488,11 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H82" s="17">
+        <v>53.333333333333336</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>164</v>
       </c>
@@ -3261,8 +3506,11 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H83" s="17">
+        <v>63.333333333333329</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>166</v>
       </c>
@@ -3276,8 +3524,11 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H84" s="17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>168</v>
       </c>
@@ -3291,8 +3542,11 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H85" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>170</v>
       </c>
@@ -3306,8 +3560,11 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H86" s="17">
+        <v>36.666666666666664</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>172</v>
       </c>
@@ -3321,8 +3578,11 @@
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H87" s="17">
+        <v>43.333333333333336</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>174</v>
       </c>
@@ -3336,8 +3596,11 @@
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H88" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
         <v>176</v>
       </c>
@@ -3351,8 +3614,11 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H89" s="17">
+        <v>43.333333333333336</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>178</v>
       </c>
@@ -3366,8 +3632,11 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H90" s="17">
+        <v>23.333333333333332</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>180</v>
       </c>
@@ -3381,8 +3650,11 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H91" s="17">
+        <v>73.333333333333329</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>182</v>
       </c>
@@ -3396,8 +3668,11 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H92" s="17">
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>184</v>
       </c>
@@ -3411,8 +3686,11 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H93" s="17">
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>186</v>
       </c>
@@ -3426,8 +3704,11 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H94" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
         <v>188</v>
       </c>
@@ -3441,8 +3722,11 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H95" s="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
         <v>190</v>
       </c>
@@ -3456,8 +3740,11 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H96" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
         <v>192</v>
       </c>
@@ -3471,8 +3758,11 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H97" s="17">
+        <v>36.666666666666664</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
         <v>194</v>
       </c>
@@ -3486,8 +3776,11 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H98" s="17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
         <v>196</v>
       </c>
@@ -3501,8 +3794,11 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H99" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>198</v>
       </c>
@@ -3516,8 +3812,11 @@
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H100" s="17">
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
         <v>200</v>
       </c>
@@ -3531,8 +3830,11 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H101" s="17">
+        <v>63.333333333333329</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
         <v>202</v>
       </c>
@@ -3546,8 +3848,11 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H102" s="17">
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
         <v>204</v>
       </c>
@@ -3561,8 +3866,11 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H103" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>206</v>
       </c>
@@ -3576,8 +3884,11 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H104" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>208</v>
       </c>
@@ -3591,8 +3902,11 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H105" s="17">
+        <v>96.666666666666671</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>210</v>
       </c>
@@ -3606,8 +3920,11 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H106" s="17">
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
         <v>212</v>
       </c>
@@ -3621,8 +3938,11 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H107" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
         <v>214</v>
       </c>
@@ -3636,8 +3956,11 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H108" s="17">
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
         <v>216</v>
       </c>
@@ -3651,8 +3974,11 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H109" s="17">
+        <v>36.666666666666664</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
         <v>218</v>
       </c>
@@ -3666,8 +3992,11 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H110" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
         <v>220</v>
       </c>
@@ -3681,8 +4010,11 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H111" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
         <v>222</v>
       </c>
@@ -3696,8 +4028,11 @@
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H112" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
         <v>224</v>
       </c>
@@ -3711,8 +4046,11 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H113" s="17">
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
         <v>226</v>
       </c>
@@ -3726,8 +4064,11 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H114" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
         <v>228</v>
       </c>
@@ -3741,8 +4082,11 @@
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H115" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
         <v>230</v>
       </c>
@@ -3756,8 +4100,11 @@
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H116" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
         <v>232</v>
       </c>
@@ -3771,8 +4118,11 @@
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H117" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
         <v>234</v>
       </c>
@@ -3786,8 +4136,11 @@
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H118" s="17">
+        <v>96.666666666666671</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
         <v>236</v>
       </c>
@@ -3801,8 +4154,11 @@
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H119" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
         <v>238</v>
       </c>
@@ -3816,8 +4172,11 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H120" s="17">
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
         <v>240</v>
       </c>
@@ -3831,8 +4190,11 @@
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H121" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
         <v>242</v>
       </c>
@@ -3846,8 +4208,11 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H122" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
         <v>244</v>
       </c>
@@ -3861,8 +4226,11 @@
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H123" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
         <v>246</v>
       </c>
@@ -3876,8 +4244,11 @@
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H124" s="17">
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
         <v>248</v>
       </c>
@@ -3891,8 +4262,11 @@
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H125" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>250</v>
       </c>
@@ -3906,8 +4280,11 @@
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H126" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
         <v>252</v>
       </c>
@@ -3921,8 +4298,11 @@
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H127" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
         <v>254</v>
       </c>
@@ -3936,8 +4316,11 @@
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H128" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
         <v>256</v>
       </c>
@@ -3951,8 +4334,11 @@
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H129" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
         <v>258</v>
       </c>
@@ -3966,8 +4352,11 @@
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H130" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
         <v>260</v>
       </c>
@@ -3981,8 +4370,11 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H131" s="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
         <v>262</v>
       </c>
@@ -3996,8 +4388,11 @@
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H132" s="17">
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
         <v>264</v>
       </c>
@@ -4011,8 +4406,11 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H133" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
         <v>266</v>
       </c>
@@ -4026,8 +4424,11 @@
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H134" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
         <v>268</v>
       </c>
@@ -4041,8 +4442,11 @@
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H135" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>270</v>
       </c>
@@ -4056,8 +4460,11 @@
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H136" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
         <v>272</v>
       </c>
@@ -4071,8 +4478,11 @@
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H137" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
         <v>274</v>
       </c>
@@ -4086,8 +4496,11 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H138" s="17">
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
         <v>276</v>
       </c>
@@ -4101,8 +4514,11 @@
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H139" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
         <v>278</v>
       </c>
@@ -4116,8 +4532,11 @@
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H140" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>280</v>
       </c>
@@ -4131,8 +4550,11 @@
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H141" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
         <v>282</v>
       </c>
@@ -4146,8 +4568,11 @@
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H142" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
         <v>284</v>
       </c>
@@ -4161,8 +4586,11 @@
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H143" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
         <v>286</v>
       </c>
@@ -4176,8 +4604,11 @@
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H144" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
         <v>288</v>
       </c>
@@ -4191,8 +4622,11 @@
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H145" s="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>290</v>
       </c>
@@ -4206,8 +4640,11 @@
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H146" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
         <v>292</v>
       </c>
@@ -4221,8 +4658,11 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H147" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
         <v>294</v>
       </c>
@@ -4236,8 +4676,11 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H148" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
         <v>296</v>
       </c>
@@ -4251,8 +4694,11 @@
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H149" s="17">
+        <v>73.333333333333329</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
         <v>298</v>
       </c>
@@ -4266,8 +4712,11 @@
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H150" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
         <v>300</v>
       </c>
@@ -4281,8 +4730,11 @@
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H151" s="17">
+        <v>73.333333333333329</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>302</v>
       </c>
@@ -4296,8 +4748,11 @@
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H152" s="17">
+        <v>46.666666666666664</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
         <v>304</v>
       </c>
@@ -4311,8 +4766,11 @@
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H153" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
         <v>306</v>
       </c>
@@ -4326,8 +4784,11 @@
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H154" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
         <v>308</v>
       </c>
@@ -4341,8 +4802,11 @@
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H155" s="17">
+        <v>63.333333333333329</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>310</v>
       </c>
@@ -4356,8 +4820,11 @@
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H156" s="17">
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
         <v>312</v>
       </c>
@@ -4371,8 +4838,11 @@
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H157" s="17">
+        <v>56.666666666666664</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>314</v>
       </c>
@@ -4386,8 +4856,11 @@
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H158" s="17">
+        <v>63.333333333333329</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
         <v>316</v>
       </c>
@@ -4401,8 +4874,11 @@
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H159" s="17">
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
         <v>318</v>
       </c>
@@ -4416,8 +4892,11 @@
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H160" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
         <v>320</v>
       </c>
@@ -4431,8 +4910,11 @@
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H161" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
         <v>322</v>
       </c>
@@ -4446,8 +4928,11 @@
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H162" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
         <v>324</v>
       </c>
@@ -4461,8 +4946,11 @@
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H163" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
         <v>326</v>
       </c>
@@ -4476,8 +4964,11 @@
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H164" s="17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
         <v>328</v>
       </c>
@@ -4491,8 +4982,11 @@
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H165" s="17">
+        <v>63.333333333333329</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>330</v>
       </c>
@@ -4506,8 +5000,11 @@
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H166" s="17">
+        <v>36.666666666666664</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
         <v>332</v>
       </c>
@@ -4521,8 +5018,11 @@
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H167" s="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
         <v>334</v>
       </c>
@@ -4536,8 +5036,11 @@
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H168" s="17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
         <v>336</v>
       </c>
@@ -4551,8 +5054,11 @@
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H169" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
         <v>338</v>
       </c>
@@ -4566,8 +5072,11 @@
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H170" s="17">
+        <v>16.666666666666664</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
         <v>340</v>
       </c>
@@ -4581,8 +5090,11 @@
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H171" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
         <v>342</v>
       </c>
@@ -4596,8 +5108,11 @@
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H172" s="17">
+        <v>26.666666666666668</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
         <v>344</v>
       </c>
@@ -4611,8 +5126,11 @@
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H173" s="17">
+        <v>16.666666666666664</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
         <v>346</v>
       </c>
@@ -4626,8 +5144,11 @@
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H174" s="17">
+        <v>76.666666666666671</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
         <v>348</v>
       </c>
@@ -4641,8 +5162,11 @@
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H175" s="17">
+        <v>26.666666666666668</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>350</v>
       </c>
@@ -4656,8 +5180,11 @@
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H176" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
         <v>352</v>
       </c>
@@ -4671,8 +5198,11 @@
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H177" s="17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
         <v>354</v>
       </c>
@@ -4686,8 +5216,11 @@
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H178" s="17">
+        <v>96.666666666666671</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
         <v>356</v>
       </c>
@@ -4701,8 +5234,11 @@
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H179" s="17">
+        <v>96.666666666666671</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
         <v>358</v>
       </c>
@@ -4716,8 +5252,11 @@
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H180" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
         <v>360</v>
       </c>
@@ -4731,8 +5270,11 @@
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H181" s="17">
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
         <v>362</v>
       </c>
@@ -4746,8 +5288,11 @@
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H182" s="17">
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
         <v>364</v>
       </c>
@@ -4761,8 +5306,11 @@
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H183" s="17">
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
         <v>366</v>
       </c>
@@ -4776,8 +5324,11 @@
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H184" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
         <v>368</v>
       </c>
@@ -4791,8 +5342,11 @@
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H185" s="17">
+        <v>73.333333333333329</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>370</v>
       </c>
@@ -4806,8 +5360,11 @@
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H186" s="17">
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
         <v>372</v>
       </c>
@@ -4821,8 +5378,11 @@
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H187" s="17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
         <v>374</v>
       </c>
@@ -4837,7 +5397,7 @@
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
         <v>376</v>
       </c>
@@ -4852,7 +5412,7 @@
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
         <v>378</v>
       </c>
@@ -4867,7 +5427,7 @@
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
         <v>380</v>
       </c>
@@ -4882,7 +5442,7 @@
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
         <v>382</v>
       </c>
@@ -5678,21 +6238,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C7DC5809443B914698F205EDCFE14C5C" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="910dd8289e79bf7e3b2db69aaa037196">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2592cbe8-961e-4422-8c47-4737933d0fe0" xmlns:ns3="7af58a8f-2f6f-405a-b238-befdc3c227d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecb9083a17ae33be0a7009b46db9eab7" ns2:_="" ns3:_="">
     <xsd:import namespace="2592cbe8-961e-4422-8c47-4737933d0fe0"/>
@@ -5869,24 +6414,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70AE5412-3087-4F96-A882-A7717BC45E52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5903,4 +6446,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theva\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F862BD5-6CDF-4A44-BF04-5DE8AF0F5E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F69514-2D53-4F50-A70A-2BE0D90A1A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1580,7 +1580,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1603,41 +1603,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1672,12 +1644,16 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1698,9 +1674,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1738,7 +1714,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1844,7 +1820,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1986,7 +1962,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2004,33 +1980,33 @@
     <col min="5" max="5" width="7.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="6.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="17" customWidth="1"/>
+    <col min="8" max="8" width="16" style="14" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>480</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="17" t="s">
         <v>485</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="18" t="s">
         <v>486</v>
       </c>
     </row>
@@ -2047,8 +2023,10 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="17">
+      <c r="G2" s="15">
+        <v>38</v>
+      </c>
+      <c r="H2" s="19">
         <v>53.333333333333336</v>
       </c>
     </row>
@@ -2065,8 +2043,8 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="17">
+      <c r="G3" s="15"/>
+      <c r="H3" s="19">
         <v>86.666666666666671</v>
       </c>
     </row>
@@ -2083,8 +2061,10 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="17">
+      <c r="G4" s="15">
+        <v>78</v>
+      </c>
+      <c r="H4" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -2101,8 +2081,10 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="17">
+      <c r="G5" s="15">
+        <v>46</v>
+      </c>
+      <c r="H5" s="19">
         <v>26.666666666666668</v>
       </c>
     </row>
@@ -2119,8 +2101,10 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="17">
+      <c r="G6" s="15">
+        <v>40</v>
+      </c>
+      <c r="H6" s="19">
         <v>43.333333333333336</v>
       </c>
     </row>
@@ -2137,8 +2121,8 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="17">
+      <c r="G7" s="15"/>
+      <c r="H7" s="19">
         <v>53.333333333333336</v>
       </c>
     </row>
@@ -2155,8 +2139,8 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="17">
+      <c r="G8" s="15"/>
+      <c r="H8" s="19">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -2173,8 +2157,10 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="17">
+      <c r="G9" s="15">
+        <v>46</v>
+      </c>
+      <c r="H9" s="19">
         <v>50</v>
       </c>
     </row>
@@ -2191,8 +2177,8 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="17">
+      <c r="G10" s="15"/>
+      <c r="H10" s="19">
         <v>96.666666666666671</v>
       </c>
     </row>
@@ -2209,8 +2195,8 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="17">
+      <c r="G11" s="15"/>
+      <c r="H11" s="19">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -2227,8 +2213,10 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="17">
+      <c r="G12" s="15">
+        <v>35</v>
+      </c>
+      <c r="H12" s="19">
         <v>36.666666666666664</v>
       </c>
     </row>
@@ -2245,8 +2233,8 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="17">
+      <c r="G13" s="15"/>
+      <c r="H13" s="19">
         <v>80</v>
       </c>
     </row>
@@ -2263,8 +2251,10 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="17">
+      <c r="G14" s="15">
+        <v>86</v>
+      </c>
+      <c r="H14" s="19">
         <v>60</v>
       </c>
     </row>
@@ -2281,8 +2271,8 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="17">
+      <c r="G15" s="15"/>
+      <c r="H15" s="19">
         <v>80</v>
       </c>
     </row>
@@ -2299,8 +2289,8 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="17">
+      <c r="G16" s="15"/>
+      <c r="H16" s="19">
         <v>80</v>
       </c>
     </row>
@@ -2317,8 +2307,8 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="17">
+      <c r="G17" s="15"/>
+      <c r="H17" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -2335,8 +2325,10 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="17">
+      <c r="G18" s="15">
+        <v>71</v>
+      </c>
+      <c r="H18" s="19">
         <v>46.666666666666664</v>
       </c>
     </row>
@@ -2353,8 +2345,8 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="17">
+      <c r="G19" s="15"/>
+      <c r="H19" s="19">
         <v>60</v>
       </c>
     </row>
@@ -2371,8 +2363,10 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="17">
+      <c r="G20" s="15">
+        <v>71</v>
+      </c>
+      <c r="H20" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -2389,8 +2383,8 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="17">
+      <c r="G21" s="15"/>
+      <c r="H21" s="19">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -2407,8 +2401,8 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="17">
+      <c r="G22" s="15"/>
+      <c r="H22" s="19">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -2425,8 +2419,8 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="17">
+      <c r="G23" s="15"/>
+      <c r="H23" s="19">
         <v>70</v>
       </c>
     </row>
@@ -2443,8 +2437,8 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="17">
+      <c r="G24" s="15"/>
+      <c r="H24" s="19">
         <v>70</v>
       </c>
     </row>
@@ -2461,8 +2455,8 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="17">
+      <c r="G25" s="15"/>
+      <c r="H25" s="19">
         <v>90</v>
       </c>
     </row>
@@ -2479,8 +2473,8 @@
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="17">
+      <c r="G26" s="15"/>
+      <c r="H26" s="19">
         <v>80</v>
       </c>
     </row>
@@ -2497,8 +2491,8 @@
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="17">
+      <c r="G27" s="15"/>
+      <c r="H27" s="19">
         <v>90</v>
       </c>
     </row>
@@ -2515,8 +2509,8 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="17">
+      <c r="G28" s="15"/>
+      <c r="H28" s="19">
         <v>96.666666666666671</v>
       </c>
     </row>
@@ -2533,8 +2527,8 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="17">
+      <c r="G29" s="15"/>
+      <c r="H29" s="19">
         <v>70</v>
       </c>
     </row>
@@ -2551,8 +2545,8 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="17">
+      <c r="G30" s="15"/>
+      <c r="H30" s="19">
         <v>96.666666666666671</v>
       </c>
     </row>
@@ -2569,8 +2563,8 @@
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="17">
+      <c r="G31" s="15"/>
+      <c r="H31" s="19">
         <v>20</v>
       </c>
     </row>
@@ -2587,8 +2581,10 @@
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="17">
+      <c r="G32" s="15">
+        <v>68</v>
+      </c>
+      <c r="H32" s="19">
         <v>36.666666666666664</v>
       </c>
     </row>
@@ -2605,8 +2601,8 @@
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="17">
+      <c r="G33" s="15"/>
+      <c r="H33" s="19">
         <v>70</v>
       </c>
     </row>
@@ -2623,8 +2619,8 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="17">
+      <c r="G34" s="15"/>
+      <c r="H34" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -2641,8 +2637,8 @@
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="17">
+      <c r="G35" s="15"/>
+      <c r="H35" s="19">
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -2659,8 +2655,8 @@
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="17">
+      <c r="G36" s="15"/>
+      <c r="H36" s="19">
         <v>80</v>
       </c>
     </row>
@@ -2677,8 +2673,8 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="17">
+      <c r="G37" s="15"/>
+      <c r="H37" s="19">
         <v>80</v>
       </c>
     </row>
@@ -2695,8 +2691,8 @@
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="17">
+      <c r="G38" s="15"/>
+      <c r="H38" s="19">
         <v>86.666666666666671</v>
       </c>
     </row>
@@ -2713,8 +2709,8 @@
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="17">
+      <c r="G39" s="15"/>
+      <c r="H39" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -2731,8 +2727,10 @@
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="17">
+      <c r="G40" s="15">
+        <v>54</v>
+      </c>
+      <c r="H40" s="19">
         <v>46.666666666666664</v>
       </c>
     </row>
@@ -2749,8 +2747,10 @@
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="17">
+      <c r="G41" s="15">
+        <v>34</v>
+      </c>
+      <c r="H41" s="19">
         <v>56.666666666666664</v>
       </c>
     </row>
@@ -2767,8 +2767,10 @@
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="17">
+      <c r="G42" s="15">
+        <v>46</v>
+      </c>
+      <c r="H42" s="19">
         <v>13.333333333333334</v>
       </c>
     </row>
@@ -2785,8 +2787,10 @@
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="17">
+      <c r="G43" s="15">
+        <v>73</v>
+      </c>
+      <c r="H43" s="19">
         <v>53.333333333333336</v>
       </c>
     </row>
@@ -2803,8 +2807,8 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="17">
+      <c r="G44" s="15"/>
+      <c r="H44" s="19">
         <v>80</v>
       </c>
     </row>
@@ -2821,8 +2825,10 @@
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="17">
+      <c r="G45" s="15">
+        <v>56</v>
+      </c>
+      <c r="H45" s="19">
         <v>50</v>
       </c>
     </row>
@@ -2839,8 +2845,8 @@
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="17">
+      <c r="G46" s="15"/>
+      <c r="H46" s="19">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -2857,8 +2863,10 @@
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="17">
+      <c r="G47" s="15">
+        <v>51</v>
+      </c>
+      <c r="H47" s="19">
         <v>53.333333333333336</v>
       </c>
     </row>
@@ -2875,8 +2883,10 @@
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="17">
+      <c r="G48" s="15">
+        <v>55</v>
+      </c>
+      <c r="H48" s="19">
         <v>0</v>
       </c>
     </row>
@@ -2893,8 +2903,8 @@
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="17">
+      <c r="G49" s="15"/>
+      <c r="H49" s="19">
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -2911,8 +2921,8 @@
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="17">
+      <c r="G50" s="15"/>
+      <c r="H50" s="19">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -2929,8 +2939,8 @@
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="17">
+      <c r="G51" s="15"/>
+      <c r="H51" s="19">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -2947,8 +2957,10 @@
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="17">
+      <c r="G52" s="15">
+        <v>56</v>
+      </c>
+      <c r="H52" s="19">
         <v>53.333333333333336</v>
       </c>
     </row>
@@ -2965,8 +2977,8 @@
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="17">
+      <c r="G53" s="15"/>
+      <c r="H53" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -2983,8 +2995,8 @@
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="17">
+      <c r="G54" s="15"/>
+      <c r="H54" s="19">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -3001,8 +3013,8 @@
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="17">
+      <c r="G55" s="15"/>
+      <c r="H55" s="19">
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -3019,8 +3031,8 @@
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="17">
+      <c r="G56" s="15"/>
+      <c r="H56" s="19">
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -3037,8 +3049,10 @@
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="17">
+      <c r="G57" s="15">
+        <v>54</v>
+      </c>
+      <c r="H57" s="19">
         <v>60</v>
       </c>
     </row>
@@ -3055,8 +3069,8 @@
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="17">
+      <c r="G58" s="15"/>
+      <c r="H58" s="19">
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -3073,8 +3087,8 @@
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="17">
+      <c r="G59" s="15"/>
+      <c r="H59" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -3091,8 +3105,10 @@
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="17">
+      <c r="G60" s="15">
+        <v>52</v>
+      </c>
+      <c r="H60" s="19">
         <v>53.333333333333336</v>
       </c>
     </row>
@@ -3109,8 +3125,8 @@
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="17">
+      <c r="G61" s="15"/>
+      <c r="H61" s="19">
         <v>80</v>
       </c>
     </row>
@@ -3127,8 +3143,8 @@
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="17">
+      <c r="G62" s="15"/>
+      <c r="H62" s="19">
         <v>70</v>
       </c>
     </row>
@@ -3145,8 +3161,8 @@
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="17">
+      <c r="G63" s="15"/>
+      <c r="H63" s="19">
         <v>100</v>
       </c>
     </row>
@@ -3163,8 +3179,8 @@
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="17">
+      <c r="G64" s="15"/>
+      <c r="H64" s="19">
         <v>86.666666666666671</v>
       </c>
     </row>
@@ -3181,8 +3197,8 @@
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="17">
+      <c r="G65" s="15"/>
+      <c r="H65" s="19">
         <v>70</v>
       </c>
     </row>
@@ -3199,8 +3215,8 @@
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="17">
+      <c r="G66" s="15"/>
+      <c r="H66" s="19">
         <v>96.666666666666671</v>
       </c>
     </row>
@@ -3217,8 +3233,10 @@
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="17">
+      <c r="G67" s="15">
+        <v>49</v>
+      </c>
+      <c r="H67" s="19">
         <v>30</v>
       </c>
     </row>
@@ -3235,8 +3253,10 @@
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="17">
+      <c r="G68" s="15">
+        <v>59</v>
+      </c>
+      <c r="H68" s="19">
         <v>20</v>
       </c>
     </row>
@@ -3253,8 +3273,8 @@
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="17">
+      <c r="G69" s="15"/>
+      <c r="H69" s="19">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -3271,8 +3291,10 @@
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="17">
+      <c r="G70" s="15">
+        <v>40</v>
+      </c>
+      <c r="H70" s="19">
         <v>30</v>
       </c>
     </row>
@@ -3289,8 +3311,10 @@
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="17">
+      <c r="G71" s="15">
+        <v>50</v>
+      </c>
+      <c r="H71" s="19">
         <v>53.333333333333336</v>
       </c>
     </row>
@@ -3307,8 +3331,8 @@
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="17">
+      <c r="G72" s="15"/>
+      <c r="H72" s="19">
         <v>90</v>
       </c>
     </row>
@@ -3325,8 +3349,8 @@
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="17">
+      <c r="G73" s="15"/>
+      <c r="H73" s="19">
         <v>96.666666666666671</v>
       </c>
     </row>
@@ -3343,8 +3367,10 @@
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="17">
+      <c r="G74" s="15">
+        <v>35</v>
+      </c>
+      <c r="H74" s="19">
         <v>23.333333333333332</v>
       </c>
     </row>
@@ -3361,8 +3387,10 @@
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="17">
+      <c r="G75" s="15">
+        <v>48</v>
+      </c>
+      <c r="H75" s="19">
         <v>40</v>
       </c>
     </row>
@@ -3379,8 +3407,10 @@
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="17">
+      <c r="G76" s="15">
+        <v>37</v>
+      </c>
+      <c r="H76" s="19">
         <v>50</v>
       </c>
     </row>
@@ -3397,8 +3427,8 @@
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="17">
+      <c r="G77" s="15"/>
+      <c r="H77" s="19">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -3415,8 +3445,10 @@
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="17">
+      <c r="G78" s="15">
+        <v>54</v>
+      </c>
+      <c r="H78" s="19">
         <v>23.333333333333332</v>
       </c>
     </row>
@@ -3433,8 +3465,10 @@
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="17">
+      <c r="G79" s="15">
+        <v>42</v>
+      </c>
+      <c r="H79" s="19">
         <v>43.333333333333336</v>
       </c>
     </row>
@@ -3451,8 +3485,10 @@
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="17">
+      <c r="G80" s="15">
+        <v>63</v>
+      </c>
+      <c r="H80" s="19">
         <v>63.333333333333329</v>
       </c>
     </row>
@@ -3469,8 +3505,8 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="17">
+      <c r="G81" s="15"/>
+      <c r="H81" s="19">
         <v>90</v>
       </c>
     </row>
@@ -3487,8 +3523,10 @@
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="17">
+      <c r="G82" s="15">
+        <v>54</v>
+      </c>
+      <c r="H82" s="19">
         <v>53.333333333333336</v>
       </c>
     </row>
@@ -3505,8 +3543,10 @@
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="17">
+      <c r="G83" s="15">
+        <v>67</v>
+      </c>
+      <c r="H83" s="19">
         <v>63.333333333333329</v>
       </c>
     </row>
@@ -3523,8 +3563,10 @@
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="17">
+      <c r="G84" s="15">
+        <v>70</v>
+      </c>
+      <c r="H84" s="19">
         <v>50</v>
       </c>
     </row>
@@ -3541,8 +3583,8 @@
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="17">
+      <c r="G85" s="15"/>
+      <c r="H85" s="19">
         <v>60</v>
       </c>
     </row>
@@ -3559,8 +3601,10 @@
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="17">
+      <c r="G86" s="15">
+        <v>42</v>
+      </c>
+      <c r="H86" s="19">
         <v>36.666666666666664</v>
       </c>
     </row>
@@ -3577,8 +3621,10 @@
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="17">
+      <c r="G87" s="15">
+        <v>47</v>
+      </c>
+      <c r="H87" s="19">
         <v>43.333333333333336</v>
       </c>
     </row>
@@ -3595,8 +3641,8 @@
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="17">
+      <c r="G88" s="15"/>
+      <c r="H88" s="19">
         <v>80</v>
       </c>
     </row>
@@ -3613,8 +3659,10 @@
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="17">
+      <c r="G89" s="15">
+        <v>68</v>
+      </c>
+      <c r="H89" s="19">
         <v>43.333333333333336</v>
       </c>
     </row>
@@ -3631,8 +3679,10 @@
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="17">
+      <c r="G90" s="15">
+        <v>56</v>
+      </c>
+      <c r="H90" s="19">
         <v>23.333333333333332</v>
       </c>
     </row>
@@ -3649,8 +3699,8 @@
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="17">
+      <c r="G91" s="15"/>
+      <c r="H91" s="19">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -3667,8 +3717,8 @@
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="17">
+      <c r="G92" s="15"/>
+      <c r="H92" s="19">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -3685,8 +3735,8 @@
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="17">
+      <c r="G93" s="15"/>
+      <c r="H93" s="19">
         <v>86.666666666666671</v>
       </c>
     </row>
@@ -3703,8 +3753,10 @@
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="17">
+      <c r="G94" s="15">
+        <v>33</v>
+      </c>
+      <c r="H94" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -3721,8 +3773,8 @@
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="17">
+      <c r="G95" s="15"/>
+      <c r="H95" s="19">
         <v>90</v>
       </c>
     </row>
@@ -3739,8 +3791,10 @@
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="17">
+      <c r="G96" s="15">
+        <v>65</v>
+      </c>
+      <c r="H96" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -3757,8 +3811,10 @@
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="17">
+      <c r="G97" s="15">
+        <v>42</v>
+      </c>
+      <c r="H97" s="19">
         <v>36.666666666666664</v>
       </c>
     </row>
@@ -3775,8 +3831,10 @@
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="17">
+      <c r="G98" s="15">
+        <v>59</v>
+      </c>
+      <c r="H98" s="19">
         <v>50</v>
       </c>
     </row>
@@ -3793,8 +3851,8 @@
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="17">
+      <c r="G99" s="15"/>
+      <c r="H99" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -3811,8 +3869,8 @@
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="17">
+      <c r="G100" s="15"/>
+      <c r="H100" s="19">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -3829,8 +3887,10 @@
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="17">
+      <c r="G101" s="15">
+        <v>57</v>
+      </c>
+      <c r="H101" s="19">
         <v>63.333333333333329</v>
       </c>
     </row>
@@ -3847,8 +3907,8 @@
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="17">
+      <c r="G102" s="15"/>
+      <c r="H102" s="19">
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -3865,8 +3925,10 @@
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="17">
+      <c r="G103" s="15">
+        <v>31</v>
+      </c>
+      <c r="H103" s="19">
         <v>60</v>
       </c>
     </row>
@@ -3883,8 +3945,8 @@
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="17">
+      <c r="G104" s="15"/>
+      <c r="H104" s="19">
         <v>80</v>
       </c>
     </row>
@@ -3901,8 +3963,8 @@
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="17">
+      <c r="G105" s="15"/>
+      <c r="H105" s="19">
         <v>96.666666666666671</v>
       </c>
     </row>
@@ -3919,8 +3981,8 @@
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="17">
+      <c r="G106" s="15"/>
+      <c r="H106" s="19">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -3937,8 +3999,10 @@
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="17">
+      <c r="G107" s="15">
+        <v>57</v>
+      </c>
+      <c r="H107" s="19">
         <v>70</v>
       </c>
     </row>
@@ -3955,8 +4019,8 @@
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="17">
+      <c r="G108" s="15"/>
+      <c r="H108" s="19">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -3973,8 +4037,10 @@
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="17">
+      <c r="G109" s="15">
+        <v>66</v>
+      </c>
+      <c r="H109" s="19">
         <v>36.666666666666664</v>
       </c>
     </row>
@@ -3991,8 +4057,8 @@
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="17">
+      <c r="G110" s="15"/>
+      <c r="H110" s="19">
         <v>70</v>
       </c>
     </row>
@@ -4009,8 +4075,8 @@
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="17">
+      <c r="G111" s="15"/>
+      <c r="H111" s="19">
         <v>70</v>
       </c>
     </row>
@@ -4027,8 +4093,8 @@
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="17">
+      <c r="G112" s="15"/>
+      <c r="H112" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -4045,8 +4111,8 @@
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-      <c r="H113" s="17">
+      <c r="G113" s="15"/>
+      <c r="H113" s="19">
         <v>86.666666666666671</v>
       </c>
     </row>
@@ -4063,8 +4129,8 @@
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="17">
+      <c r="G114" s="15"/>
+      <c r="H114" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -4081,8 +4147,8 @@
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="17">
+      <c r="G115" s="15"/>
+      <c r="H115" s="19">
         <v>70</v>
       </c>
     </row>
@@ -4099,8 +4165,10 @@
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="17">
+      <c r="G116" s="15">
+        <v>57</v>
+      </c>
+      <c r="H116" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -4117,8 +4185,10 @@
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="17">
+      <c r="G117" s="15">
+        <v>43</v>
+      </c>
+      <c r="H117" s="19">
         <v>60</v>
       </c>
     </row>
@@ -4135,8 +4205,8 @@
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="17">
+      <c r="G118" s="15"/>
+      <c r="H118" s="19">
         <v>96.666666666666671</v>
       </c>
     </row>
@@ -4153,8 +4223,8 @@
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-      <c r="H119" s="17">
+      <c r="G119" s="15"/>
+      <c r="H119" s="19">
         <v>80</v>
       </c>
     </row>
@@ -4171,8 +4241,8 @@
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-      <c r="H120" s="17">
+      <c r="G120" s="15"/>
+      <c r="H120" s="19">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -4189,8 +4259,10 @@
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="17">
+      <c r="G121" s="15">
+        <v>50</v>
+      </c>
+      <c r="H121" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -4207,8 +4279,8 @@
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-      <c r="H122" s="17">
+      <c r="G122" s="15"/>
+      <c r="H122" s="19">
         <v>80</v>
       </c>
     </row>
@@ -4225,8 +4297,8 @@
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-      <c r="H123" s="17">
+      <c r="G123" s="15"/>
+      <c r="H123" s="19">
         <v>0</v>
       </c>
     </row>
@@ -4243,8 +4315,8 @@
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-      <c r="H124" s="17">
+      <c r="G124" s="15"/>
+      <c r="H124" s="19">
         <v>86.666666666666671</v>
       </c>
     </row>
@@ -4261,8 +4333,8 @@
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-      <c r="H125" s="17">
+      <c r="G125" s="15"/>
+      <c r="H125" s="19">
         <v>70</v>
       </c>
     </row>
@@ -4279,8 +4351,10 @@
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-      <c r="H126" s="17">
+      <c r="G126" s="15">
+        <v>67</v>
+      </c>
+      <c r="H126" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -4297,8 +4371,10 @@
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-      <c r="H127" s="17">
+      <c r="G127" s="15">
+        <v>56</v>
+      </c>
+      <c r="H127" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -4315,8 +4391,8 @@
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-      <c r="H128" s="17">
+      <c r="G128" s="15"/>
+      <c r="H128" s="19">
         <v>70</v>
       </c>
     </row>
@@ -4333,8 +4409,8 @@
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-      <c r="H129" s="17">
+      <c r="G129" s="15"/>
+      <c r="H129" s="19">
         <v>70</v>
       </c>
     </row>
@@ -4351,8 +4427,8 @@
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-      <c r="H130" s="17">
+      <c r="G130" s="15"/>
+      <c r="H130" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -4369,8 +4445,8 @@
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-      <c r="H131" s="17">
+      <c r="G131" s="15"/>
+      <c r="H131" s="19">
         <v>90</v>
       </c>
     </row>
@@ -4387,8 +4463,8 @@
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-      <c r="H132" s="17">
+      <c r="G132" s="15"/>
+      <c r="H132" s="19">
         <v>86.666666666666671</v>
       </c>
     </row>
@@ -4405,8 +4481,8 @@
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-      <c r="H133" s="17">
+      <c r="G133" s="15"/>
+      <c r="H133" s="19">
         <v>80</v>
       </c>
     </row>
@@ -4423,8 +4499,8 @@
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-      <c r="H134" s="17">
+      <c r="G134" s="15"/>
+      <c r="H134" s="19">
         <v>100</v>
       </c>
     </row>
@@ -4441,8 +4517,8 @@
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-      <c r="H135" s="17">
+      <c r="G135" s="15"/>
+      <c r="H135" s="19">
         <v>80</v>
       </c>
     </row>
@@ -4459,8 +4535,8 @@
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-      <c r="H136" s="17">
+      <c r="G136" s="15"/>
+      <c r="H136" s="19">
         <v>100</v>
       </c>
     </row>
@@ -4477,8 +4553,8 @@
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-      <c r="H137" s="17">
+      <c r="G137" s="15"/>
+      <c r="H137" s="19">
         <v>80</v>
       </c>
     </row>
@@ -4495,8 +4571,8 @@
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-      <c r="H138" s="17">
+      <c r="G138" s="15"/>
+      <c r="H138" s="19">
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -4513,8 +4589,8 @@
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-      <c r="H139" s="17">
+      <c r="G139" s="15"/>
+      <c r="H139" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -4531,8 +4607,8 @@
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-      <c r="H140" s="17">
+      <c r="G140" s="15"/>
+      <c r="H140" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -4549,8 +4625,10 @@
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
-      <c r="H141" s="17">
+      <c r="G141" s="15">
+        <v>37</v>
+      </c>
+      <c r="H141" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -4567,8 +4645,8 @@
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-      <c r="H142" s="17">
+      <c r="G142" s="15"/>
+      <c r="H142" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -4585,8 +4663,10 @@
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
-      <c r="G143" s="2"/>
-      <c r="H143" s="17">
+      <c r="G143" s="15">
+        <v>66</v>
+      </c>
+      <c r="H143" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -4603,8 +4683,8 @@
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-      <c r="H144" s="17">
+      <c r="G144" s="15"/>
+      <c r="H144" s="19">
         <v>80</v>
       </c>
     </row>
@@ -4621,8 +4701,8 @@
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-      <c r="H145" s="17">
+      <c r="G145" s="15"/>
+      <c r="H145" s="19">
         <v>90</v>
       </c>
     </row>
@@ -4639,8 +4719,8 @@
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
-      <c r="G146" s="2"/>
-      <c r="H146" s="17">
+      <c r="G146" s="15"/>
+      <c r="H146" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -4657,8 +4737,10 @@
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
-      <c r="G147" s="2"/>
-      <c r="H147" s="17">
+      <c r="G147" s="15">
+        <v>26</v>
+      </c>
+      <c r="H147" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -4675,8 +4757,8 @@
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
-      <c r="G148" s="2"/>
-      <c r="H148" s="17">
+      <c r="G148" s="15"/>
+      <c r="H148" s="19">
         <v>70</v>
       </c>
     </row>
@@ -4693,8 +4775,8 @@
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
-      <c r="G149" s="2"/>
-      <c r="H149" s="17">
+      <c r="G149" s="15"/>
+      <c r="H149" s="19">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -4711,8 +4793,10 @@
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-      <c r="H150" s="17">
+      <c r="G150" s="15">
+        <v>56</v>
+      </c>
+      <c r="H150" s="19">
         <v>60</v>
       </c>
     </row>
@@ -4729,8 +4813,8 @@
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
-      <c r="G151" s="2"/>
-      <c r="H151" s="17">
+      <c r="G151" s="15"/>
+      <c r="H151" s="19">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -4747,8 +4831,10 @@
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-      <c r="H152" s="17">
+      <c r="G152" s="15">
+        <v>41</v>
+      </c>
+      <c r="H152" s="19">
         <v>46.666666666666664</v>
       </c>
     </row>
@@ -4765,8 +4851,8 @@
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
-      <c r="G153" s="2"/>
-      <c r="H153" s="17">
+      <c r="G153" s="15"/>
+      <c r="H153" s="19">
         <v>70</v>
       </c>
     </row>
@@ -4783,8 +4869,10 @@
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-      <c r="H154" s="17">
+      <c r="G154" s="15">
+        <v>71</v>
+      </c>
+      <c r="H154" s="19">
         <v>20</v>
       </c>
     </row>
@@ -4801,8 +4889,10 @@
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
-      <c r="G155" s="2"/>
-      <c r="H155" s="17">
+      <c r="G155" s="15">
+        <v>55</v>
+      </c>
+      <c r="H155" s="19">
         <v>63.333333333333329</v>
       </c>
     </row>
@@ -4819,8 +4909,8 @@
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
-      <c r="G156" s="2"/>
-      <c r="H156" s="17">
+      <c r="G156" s="15"/>
+      <c r="H156" s="19">
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -4837,8 +4927,10 @@
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-      <c r="H157" s="17">
+      <c r="G157" s="15">
+        <v>54</v>
+      </c>
+      <c r="H157" s="19">
         <v>56.666666666666664</v>
       </c>
     </row>
@@ -4855,8 +4947,10 @@
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
-      <c r="H158" s="17">
+      <c r="G158" s="15">
+        <v>55</v>
+      </c>
+      <c r="H158" s="19">
         <v>63.333333333333329</v>
       </c>
     </row>
@@ -4873,8 +4967,8 @@
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-      <c r="H159" s="17">
+      <c r="G159" s="15"/>
+      <c r="H159" s="19">
         <v>86.666666666666671</v>
       </c>
     </row>
@@ -4891,8 +4985,8 @@
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-      <c r="H160" s="17">
+      <c r="G160" s="15"/>
+      <c r="H160" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -4909,8 +5003,10 @@
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
-      <c r="G161" s="2"/>
-      <c r="H161" s="17">
+      <c r="G161" s="15">
+        <v>45</v>
+      </c>
+      <c r="H161" s="19">
         <v>60</v>
       </c>
     </row>
@@ -4927,8 +5023,8 @@
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-      <c r="H162" s="17">
+      <c r="G162" s="15"/>
+      <c r="H162" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -4945,8 +5041,10 @@
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
-      <c r="G163" s="2"/>
-      <c r="H163" s="17">
+      <c r="G163" s="15">
+        <v>46</v>
+      </c>
+      <c r="H163" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -4963,8 +5061,10 @@
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-      <c r="H164" s="17">
+      <c r="G164" s="15">
+        <v>78</v>
+      </c>
+      <c r="H164" s="19">
         <v>50</v>
       </c>
     </row>
@@ -4981,8 +5081,10 @@
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
-      <c r="G165" s="2"/>
-      <c r="H165" s="17">
+      <c r="G165" s="15">
+        <v>50</v>
+      </c>
+      <c r="H165" s="19">
         <v>63.333333333333329</v>
       </c>
     </row>
@@ -4999,8 +5101,10 @@
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
-      <c r="G166" s="2"/>
-      <c r="H166" s="17">
+      <c r="G166" s="15">
+        <v>63</v>
+      </c>
+      <c r="H166" s="19">
         <v>36.666666666666664</v>
       </c>
     </row>
@@ -5017,8 +5121,10 @@
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
-      <c r="G167" s="2"/>
-      <c r="H167" s="17">
+      <c r="G167" s="15">
+        <v>78</v>
+      </c>
+      <c r="H167" s="19">
         <v>90</v>
       </c>
     </row>
@@ -5035,8 +5141,8 @@
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
-      <c r="H168" s="17">
+      <c r="G168" s="15"/>
+      <c r="H168" s="19">
         <v>50</v>
       </c>
     </row>
@@ -5053,8 +5159,8 @@
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
-      <c r="G169" s="2"/>
-      <c r="H169" s="17">
+      <c r="G169" s="15"/>
+      <c r="H169" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -5071,8 +5177,10 @@
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
-      <c r="G170" s="2"/>
-      <c r="H170" s="17">
+      <c r="G170" s="15">
+        <v>40</v>
+      </c>
+      <c r="H170" s="19">
         <v>16.666666666666664</v>
       </c>
     </row>
@@ -5089,8 +5197,10 @@
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
-      <c r="G171" s="2"/>
-      <c r="H171" s="17">
+      <c r="G171" s="15">
+        <v>41</v>
+      </c>
+      <c r="H171" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -5107,8 +5217,8 @@
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
-      <c r="H172" s="17">
+      <c r="G172" s="15"/>
+      <c r="H172" s="19">
         <v>26.666666666666668</v>
       </c>
     </row>
@@ -5125,8 +5235,10 @@
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-      <c r="H173" s="17">
+      <c r="G173" s="15">
+        <v>48</v>
+      </c>
+      <c r="H173" s="19">
         <v>16.666666666666664</v>
       </c>
     </row>
@@ -5143,8 +5255,8 @@
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-      <c r="H174" s="17">
+      <c r="G174" s="15"/>
+      <c r="H174" s="19">
         <v>76.666666666666671</v>
       </c>
     </row>
@@ -5161,8 +5273,10 @@
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
-      <c r="G175" s="2"/>
-      <c r="H175" s="17">
+      <c r="G175" s="15">
+        <v>29</v>
+      </c>
+      <c r="H175" s="19">
         <v>26.666666666666668</v>
       </c>
     </row>
@@ -5179,8 +5293,10 @@
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
-      <c r="G176" s="2"/>
-      <c r="H176" s="17">
+      <c r="G176" s="15">
+        <v>55</v>
+      </c>
+      <c r="H176" s="19">
         <v>60</v>
       </c>
     </row>
@@ -5197,8 +5313,8 @@
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
-      <c r="G177" s="2"/>
-      <c r="H177" s="17">
+      <c r="G177" s="15"/>
+      <c r="H177" s="19">
         <v>80</v>
       </c>
     </row>
@@ -5215,8 +5331,8 @@
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
-      <c r="G178" s="2"/>
-      <c r="H178" s="17">
+      <c r="G178" s="15"/>
+      <c r="H178" s="19">
         <v>96.666666666666671</v>
       </c>
     </row>
@@ -5233,8 +5349,10 @@
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
-      <c r="G179" s="2"/>
-      <c r="H179" s="17">
+      <c r="G179" s="15">
+        <v>37</v>
+      </c>
+      <c r="H179" s="19">
         <v>96.666666666666671</v>
       </c>
     </row>
@@ -5251,8 +5369,10 @@
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
-      <c r="G180" s="2"/>
-      <c r="H180" s="17">
+      <c r="G180" s="15">
+        <v>42</v>
+      </c>
+      <c r="H180" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -5269,8 +5389,8 @@
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
-      <c r="G181" s="2"/>
-      <c r="H181" s="17">
+      <c r="G181" s="15"/>
+      <c r="H181" s="19">
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -5287,8 +5407,8 @@
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
-      <c r="G182" s="2"/>
-      <c r="H182" s="17">
+      <c r="G182" s="15"/>
+      <c r="H182" s="19">
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -5305,8 +5425,8 @@
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
-      <c r="G183" s="2"/>
-      <c r="H183" s="17">
+      <c r="G183" s="15"/>
+      <c r="H183" s="19">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -5323,8 +5443,10 @@
       <c r="D184" s="2"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
-      <c r="G184" s="2"/>
-      <c r="H184" s="17">
+      <c r="G184" s="15">
+        <v>67</v>
+      </c>
+      <c r="H184" s="19">
         <v>100</v>
       </c>
     </row>
@@ -5341,8 +5463,8 @@
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
-      <c r="G185" s="2"/>
-      <c r="H185" s="17">
+      <c r="G185" s="15"/>
+      <c r="H185" s="19">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -5359,8 +5481,8 @@
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
-      <c r="G186" s="2"/>
-      <c r="H186" s="17">
+      <c r="G186" s="15"/>
+      <c r="H186" s="19">
         <v>86.666666666666671</v>
       </c>
     </row>
@@ -5377,8 +5499,8 @@
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-      <c r="H187" s="17">
+      <c r="G187" s="15"/>
+      <c r="H187" s="19">
         <v>50</v>
       </c>
     </row>
@@ -5395,7 +5517,10 @@
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
+      <c r="G188" s="15">
+        <v>42</v>
+      </c>
+      <c r="H188" s="19"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
@@ -5410,7 +5535,8 @@
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
-      <c r="G189" s="2"/>
+      <c r="G189" s="15"/>
+      <c r="H189" s="19"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
@@ -5425,7 +5551,8 @@
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
-      <c r="G190" s="2"/>
+      <c r="G190" s="15"/>
+      <c r="H190" s="19"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
@@ -5440,7 +5567,8 @@
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
-      <c r="G191" s="2"/>
+      <c r="G191" s="15"/>
+      <c r="H191" s="19"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -5455,9 +5583,10 @@
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G192" s="15"/>
+      <c r="H192" s="19"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
         <v>384</v>
       </c>
@@ -5470,9 +5599,10 @@
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G193" s="15"/>
+      <c r="H193" s="19"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
         <v>386</v>
       </c>
@@ -5485,9 +5615,10 @@
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G194" s="15"/>
+      <c r="H194" s="19"/>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
         <v>388</v>
       </c>
@@ -5500,9 +5631,10 @@
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G195" s="15"/>
+      <c r="H195" s="19"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
         <v>390</v>
       </c>
@@ -5515,9 +5647,10 @@
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G196" s="15"/>
+      <c r="H196" s="19"/>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
         <v>392</v>
       </c>
@@ -5530,9 +5663,10 @@
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
-      <c r="G197" s="2"/>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G197" s="15"/>
+      <c r="H197" s="19"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
         <v>394</v>
       </c>
@@ -5545,9 +5679,10 @@
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G198" s="15"/>
+      <c r="H198" s="19"/>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
         <v>396</v>
       </c>
@@ -5560,9 +5695,10 @@
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G199" s="15"/>
+      <c r="H199" s="19"/>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
         <v>398</v>
       </c>
@@ -5575,9 +5711,10 @@
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G200" s="15"/>
+      <c r="H200" s="19"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
         <v>400</v>
       </c>
@@ -5590,9 +5727,10 @@
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
-      <c r="G201" s="2"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G201" s="15"/>
+      <c r="H201" s="19"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
         <v>402</v>
       </c>
@@ -5605,9 +5743,10 @@
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
-      <c r="G202" s="2"/>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G202" s="15"/>
+      <c r="H202" s="19"/>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
         <v>404</v>
       </c>
@@ -5620,9 +5759,10 @@
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
-      <c r="G203" s="2"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G203" s="15"/>
+      <c r="H203" s="19"/>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
         <v>406</v>
       </c>
@@ -5635,9 +5775,10 @@
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G204" s="15"/>
+      <c r="H204" s="19"/>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
         <v>408</v>
       </c>
@@ -5650,9 +5791,10 @@
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G205" s="15"/>
+      <c r="H205" s="19"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
         <v>410</v>
       </c>
@@ -5665,9 +5807,10 @@
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
-      <c r="G206" s="2"/>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G206" s="15"/>
+      <c r="H206" s="19"/>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
         <v>412</v>
       </c>
@@ -5680,9 +5823,10 @@
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
-      <c r="G207" s="2"/>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G207" s="15"/>
+      <c r="H207" s="19"/>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
         <v>414</v>
       </c>
@@ -5695,9 +5839,10 @@
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
-      <c r="G208" s="2"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G208" s="15"/>
+      <c r="H208" s="19"/>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
         <v>416</v>
       </c>
@@ -5710,9 +5855,10 @@
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
-      <c r="G209" s="2"/>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G209" s="15"/>
+      <c r="H209" s="19"/>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
         <v>418</v>
       </c>
@@ -5725,9 +5871,10 @@
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G210" s="15"/>
+      <c r="H210" s="19"/>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
         <v>420</v>
       </c>
@@ -5740,9 +5887,10 @@
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
-      <c r="G211" s="2"/>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G211" s="15"/>
+      <c r="H211" s="19"/>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
         <v>422</v>
       </c>
@@ -5755,9 +5903,10 @@
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
-      <c r="G212" s="2"/>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G212" s="15"/>
+      <c r="H212" s="19"/>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
         <v>424</v>
       </c>
@@ -5770,9 +5919,10 @@
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
-      <c r="G213" s="2"/>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G213" s="15"/>
+      <c r="H213" s="19"/>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
         <v>426</v>
       </c>
@@ -5785,9 +5935,10 @@
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
-      <c r="G214" s="2"/>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G214" s="15"/>
+      <c r="H214" s="19"/>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
         <v>428</v>
       </c>
@@ -5800,9 +5951,10 @@
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
-      <c r="G215" s="2"/>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G215" s="15"/>
+      <c r="H215" s="19"/>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
         <v>430</v>
       </c>
@@ -5815,9 +5967,10 @@
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
-      <c r="G216" s="2"/>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G216" s="15"/>
+      <c r="H216" s="19"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
         <v>432</v>
       </c>
@@ -5830,9 +5983,10 @@
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G217" s="15"/>
+      <c r="H217" s="19"/>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
         <v>434</v>
       </c>
@@ -5845,9 +5999,10 @@
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
-      <c r="G218" s="2"/>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G218" s="15"/>
+      <c r="H218" s="19"/>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
         <v>436</v>
       </c>
@@ -5860,9 +6015,10 @@
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
-      <c r="G219" s="2"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G219" s="15"/>
+      <c r="H219" s="19"/>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="8" t="s">
         <v>438</v>
       </c>
@@ -5875,9 +6031,10 @@
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
-      <c r="G220" s="2"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G220" s="15"/>
+      <c r="H220" s="19"/>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
         <v>440</v>
       </c>
@@ -5890,9 +6047,10 @@
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
-      <c r="G221" s="2"/>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G221" s="15"/>
+      <c r="H221" s="19"/>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
         <v>442</v>
       </c>
@@ -5905,9 +6063,10 @@
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
       <c r="F222" s="2"/>
-      <c r="G222" s="2"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G222" s="15"/>
+      <c r="H222" s="19"/>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
         <v>444</v>
       </c>
@@ -5920,9 +6079,10 @@
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G223" s="15"/>
+      <c r="H223" s="19"/>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
         <v>446</v>
       </c>
@@ -5935,9 +6095,10 @@
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
-      <c r="G224" s="2"/>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G224" s="15"/>
+      <c r="H224" s="19"/>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
         <v>448</v>
       </c>
@@ -5950,9 +6111,10 @@
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
-      <c r="G225" s="2"/>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G225" s="15"/>
+      <c r="H225" s="19"/>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
         <v>450</v>
       </c>
@@ -5965,9 +6127,10 @@
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
-      <c r="G226" s="2"/>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G226" s="15"/>
+      <c r="H226" s="19"/>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
         <v>452</v>
       </c>
@@ -5980,9 +6143,10 @@
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
-      <c r="G227" s="2"/>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G227" s="15"/>
+      <c r="H227" s="19"/>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
         <v>454</v>
       </c>
@@ -5995,9 +6159,10 @@
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
-      <c r="G228" s="2"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G228" s="15"/>
+      <c r="H228" s="19"/>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
         <v>456</v>
       </c>
@@ -6010,9 +6175,10 @@
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
-      <c r="G229" s="2"/>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G229" s="15"/>
+      <c r="H229" s="19"/>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
         <v>458</v>
       </c>
@@ -6025,9 +6191,10 @@
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G230" s="15"/>
+      <c r="H230" s="19"/>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
         <v>460</v>
       </c>
@@ -6040,9 +6207,10 @@
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
-      <c r="G231" s="2"/>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G231" s="15"/>
+      <c r="H231" s="19"/>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
         <v>462</v>
       </c>
@@ -6055,9 +6223,10 @@
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
-      <c r="G232" s="2"/>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G232" s="15"/>
+      <c r="H232" s="19"/>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
         <v>464</v>
       </c>
@@ -6070,9 +6239,10 @@
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
-      <c r="G233" s="2"/>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G233" s="15"/>
+      <c r="H233" s="19"/>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
         <v>466</v>
       </c>
@@ -6085,9 +6255,10 @@
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G234" s="15"/>
+      <c r="H234" s="19"/>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
         <v>468</v>
       </c>
@@ -6100,9 +6271,10 @@
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G235" s="15"/>
+      <c r="H235" s="19"/>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
         <v>470</v>
       </c>
@@ -6115,9 +6287,10 @@
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
-      <c r="G236" s="2"/>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G236" s="15"/>
+      <c r="H236" s="19"/>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
         <v>472</v>
       </c>
@@ -6130,9 +6303,10 @@
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
-      <c r="G237" s="2"/>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G237" s="15"/>
+      <c r="H237" s="19"/>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
         <v>474</v>
       </c>
@@ -6145,9 +6319,10 @@
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G238" s="15"/>
+      <c r="H238" s="19"/>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
         <v>476</v>
       </c>
@@ -6160,9 +6335,10 @@
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G239" s="15"/>
+      <c r="H239" s="19"/>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
         <v>478</v>
       </c>
@@ -6175,7 +6351,8 @@
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
-      <c r="G240" s="2"/>
+      <c r="G240" s="15"/>
+      <c r="H240" s="19"/>
     </row>
     <row r="241" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A241" s="10"/>
@@ -6238,6 +6415,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C7DC5809443B914698F205EDCFE14C5C" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="910dd8289e79bf7e3b2db69aaa037196">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2592cbe8-961e-4422-8c47-4737933d0fe0" xmlns:ns3="7af58a8f-2f6f-405a-b238-befdc3c227d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecb9083a17ae33be0a7009b46db9eab7" ns2:_="" ns3:_="">
     <xsd:import namespace="2592cbe8-961e-4422-8c47-4737933d0fe0"/>
@@ -6414,15 +6600,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -6430,6 +6607,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70AE5412-3087-4F96-A882-A7717BC45E52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6448,14 +6633,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
   <ds:schemaRefs>

--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F69514-2D53-4F50-A70A-2BE0D90A1A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B87042-3F4D-43B4-8A1C-EFE2BD14DAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
@@ -5349,9 +5349,7 @@
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
-      <c r="G179" s="15">
-        <v>37</v>
-      </c>
+      <c r="G179" s="15"/>
       <c r="H179" s="19">
         <v>96.666666666666671</v>
       </c>
@@ -5499,7 +5497,9 @@
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
-      <c r="G187" s="15"/>
+      <c r="G187" s="15">
+        <v>37</v>
+      </c>
       <c r="H187" s="19">
         <v>50</v>
       </c>
@@ -6415,15 +6415,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C7DC5809443B914698F205EDCFE14C5C" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="910dd8289e79bf7e3b2db69aaa037196">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2592cbe8-961e-4422-8c47-4737933d0fe0" xmlns:ns3="7af58a8f-2f6f-405a-b238-befdc3c227d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecb9083a17ae33be0a7009b46db9eab7" ns2:_="" ns3:_="">
     <xsd:import namespace="2592cbe8-961e-4422-8c47-4737933d0fe0"/>
@@ -6600,6 +6591,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -6607,14 +6607,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70AE5412-3087-4F96-A882-A7717BC45E52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6633,6 +6625,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
   <ds:schemaRefs>

--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B87042-3F4D-43B4-8A1C-EFE2BD14DAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30EC971-B752-4234-AF53-A6057C79772F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="487">
   <si>
     <t>Name</t>
   </si>
@@ -5535,7 +5535,9 @@
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
-      <c r="G189" s="15"/>
+      <c r="G189" s="15">
+        <v>55</v>
+      </c>
       <c r="H189" s="19"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -5551,7 +5553,9 @@
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
-      <c r="G190" s="15"/>
+      <c r="G190" s="15" t="s">
+        <v>81</v>
+      </c>
       <c r="H190" s="19"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -5567,7 +5571,9 @@
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
-      <c r="G191" s="15"/>
+      <c r="G191" s="15">
+        <v>57</v>
+      </c>
       <c r="H191" s="19"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -5583,7 +5589,9 @@
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
-      <c r="G192" s="15"/>
+      <c r="G192" s="15">
+        <v>44</v>
+      </c>
       <c r="H192" s="19"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -5599,7 +5607,9 @@
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
-      <c r="G193" s="15"/>
+      <c r="G193" s="15">
+        <v>44</v>
+      </c>
       <c r="H193" s="19"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -5615,7 +5625,9 @@
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
-      <c r="G194" s="15"/>
+      <c r="G194" s="15">
+        <v>61</v>
+      </c>
       <c r="H194" s="19"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -5631,7 +5643,9 @@
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
-      <c r="G195" s="15"/>
+      <c r="G195" s="15">
+        <v>76</v>
+      </c>
       <c r="H195" s="19"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -5647,7 +5661,9 @@
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
-      <c r="G196" s="15"/>
+      <c r="G196" s="15">
+        <v>56</v>
+      </c>
       <c r="H196" s="19"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -5663,7 +5679,9 @@
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
-      <c r="G197" s="15"/>
+      <c r="G197" s="15">
+        <v>73</v>
+      </c>
       <c r="H197" s="19"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -5679,7 +5697,9 @@
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
-      <c r="G198" s="15"/>
+      <c r="G198" s="15">
+        <v>42</v>
+      </c>
       <c r="H198" s="19"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -5695,7 +5715,9 @@
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
-      <c r="G199" s="15"/>
+      <c r="G199" s="15">
+        <v>45</v>
+      </c>
       <c r="H199" s="19"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -5711,7 +5733,9 @@
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
-      <c r="G200" s="15"/>
+      <c r="G200" s="15">
+        <v>53</v>
+      </c>
       <c r="H200" s="19"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -5727,7 +5751,9 @@
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
-      <c r="G201" s="15"/>
+      <c r="G201" s="15">
+        <v>37</v>
+      </c>
       <c r="H201" s="19"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -5743,7 +5769,9 @@
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
-      <c r="G202" s="15"/>
+      <c r="G202" s="15">
+        <v>69</v>
+      </c>
       <c r="H202" s="19"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -5759,7 +5787,9 @@
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
-      <c r="G203" s="15"/>
+      <c r="G203" s="15">
+        <v>51</v>
+      </c>
       <c r="H203" s="19"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -5775,7 +5805,9 @@
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
-      <c r="G204" s="15"/>
+      <c r="G204" s="15">
+        <v>55</v>
+      </c>
       <c r="H204" s="19"/>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -5791,7 +5823,9 @@
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
-      <c r="G205" s="15"/>
+      <c r="G205" s="15">
+        <v>36</v>
+      </c>
       <c r="H205" s="19"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -5807,7 +5841,9 @@
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
-      <c r="G206" s="15"/>
+      <c r="G206" s="15">
+        <v>42</v>
+      </c>
       <c r="H206" s="19"/>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -5823,7 +5859,9 @@
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
-      <c r="G207" s="15"/>
+      <c r="G207" s="15">
+        <v>49</v>
+      </c>
       <c r="H207" s="19"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -5839,7 +5877,9 @@
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
-      <c r="G208" s="15"/>
+      <c r="G208" s="15">
+        <v>16</v>
+      </c>
       <c r="H208" s="19"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -5855,7 +5895,9 @@
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
-      <c r="G209" s="15"/>
+      <c r="G209" s="15">
+        <v>42</v>
+      </c>
       <c r="H209" s="19"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -5871,7 +5913,9 @@
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
-      <c r="G210" s="15"/>
+      <c r="G210" s="15">
+        <v>43</v>
+      </c>
       <c r="H210" s="19"/>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -5887,7 +5931,9 @@
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
-      <c r="G211" s="15"/>
+      <c r="G211" s="15">
+        <v>56</v>
+      </c>
       <c r="H211" s="19"/>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -5903,7 +5949,9 @@
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
-      <c r="G212" s="15"/>
+      <c r="G212" s="15">
+        <v>45</v>
+      </c>
       <c r="H212" s="19"/>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -5919,7 +5967,9 @@
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
-      <c r="G213" s="15"/>
+      <c r="G213" s="15">
+        <v>55</v>
+      </c>
       <c r="H213" s="19"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -5935,7 +5985,9 @@
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
-      <c r="G214" s="15"/>
+      <c r="G214" s="15" t="s">
+        <v>81</v>
+      </c>
       <c r="H214" s="19"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -5951,7 +6003,9 @@
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
-      <c r="G215" s="15"/>
+      <c r="G215" s="15">
+        <v>30</v>
+      </c>
       <c r="H215" s="19"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -5967,7 +6021,9 @@
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
-      <c r="G216" s="15"/>
+      <c r="G216" s="15">
+        <v>48</v>
+      </c>
       <c r="H216" s="19"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -5983,7 +6039,9 @@
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
-      <c r="G217" s="15"/>
+      <c r="G217" s="15">
+        <v>58</v>
+      </c>
       <c r="H217" s="19"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -5999,7 +6057,9 @@
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
-      <c r="G218" s="15"/>
+      <c r="G218" s="15">
+        <v>67</v>
+      </c>
       <c r="H218" s="19"/>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -6015,7 +6075,9 @@
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
-      <c r="G219" s="15"/>
+      <c r="G219" s="15">
+        <v>59</v>
+      </c>
       <c r="H219" s="19"/>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
@@ -6031,7 +6093,9 @@
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
-      <c r="G220" s="15"/>
+      <c r="G220" s="15" t="s">
+        <v>81</v>
+      </c>
       <c r="H220" s="19"/>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -6047,7 +6111,9 @@
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
-      <c r="G221" s="15"/>
+      <c r="G221" s="15">
+        <v>41</v>
+      </c>
       <c r="H221" s="19"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
@@ -6063,7 +6129,9 @@
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
       <c r="F222" s="2"/>
-      <c r="G222" s="15"/>
+      <c r="G222" s="15">
+        <v>38</v>
+      </c>
       <c r="H222" s="19"/>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -6079,7 +6147,9 @@
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
-      <c r="G223" s="15"/>
+      <c r="G223" s="15">
+        <v>39</v>
+      </c>
       <c r="H223" s="19"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
@@ -6095,7 +6165,9 @@
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
-      <c r="G224" s="15"/>
+      <c r="G224" s="15">
+        <v>68</v>
+      </c>
       <c r="H224" s="19"/>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
@@ -6111,7 +6183,9 @@
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
-      <c r="G225" s="15"/>
+      <c r="G225" s="15">
+        <v>57</v>
+      </c>
       <c r="H225" s="19"/>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
@@ -6127,7 +6201,9 @@
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
-      <c r="G226" s="15"/>
+      <c r="G226" s="15" t="s">
+        <v>81</v>
+      </c>
       <c r="H226" s="19"/>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
@@ -6143,7 +6219,9 @@
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
-      <c r="G227" s="15"/>
+      <c r="G227" s="15">
+        <v>23</v>
+      </c>
       <c r="H227" s="19"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -6159,7 +6237,9 @@
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
-      <c r="G228" s="15"/>
+      <c r="G228" s="15">
+        <v>55</v>
+      </c>
       <c r="H228" s="19"/>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -6175,7 +6255,9 @@
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
-      <c r="G229" s="15"/>
+      <c r="G229" s="15">
+        <v>50</v>
+      </c>
       <c r="H229" s="19"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
@@ -6191,7 +6273,9 @@
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
-      <c r="G230" s="15"/>
+      <c r="G230" s="15">
+        <v>50</v>
+      </c>
       <c r="H230" s="19"/>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
@@ -6207,7 +6291,9 @@
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
-      <c r="G231" s="15"/>
+      <c r="G231" s="15">
+        <v>44</v>
+      </c>
       <c r="H231" s="19"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
@@ -6223,7 +6309,9 @@
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
-      <c r="G232" s="15"/>
+      <c r="G232" s="15">
+        <v>55</v>
+      </c>
       <c r="H232" s="19"/>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
@@ -6239,7 +6327,9 @@
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
-      <c r="G233" s="15"/>
+      <c r="G233" s="15">
+        <v>56</v>
+      </c>
       <c r="H233" s="19"/>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
@@ -6255,7 +6345,9 @@
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
-      <c r="G234" s="15"/>
+      <c r="G234" s="15">
+        <v>53</v>
+      </c>
       <c r="H234" s="19"/>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
@@ -6271,7 +6363,9 @@
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
-      <c r="G235" s="15"/>
+      <c r="G235" s="15">
+        <v>57</v>
+      </c>
       <c r="H235" s="19"/>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
@@ -6287,7 +6381,9 @@
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
-      <c r="G236" s="15"/>
+      <c r="G236" s="15">
+        <v>52</v>
+      </c>
       <c r="H236" s="19"/>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
@@ -6303,7 +6399,9 @@
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
-      <c r="G237" s="15"/>
+      <c r="G237" s="15">
+        <v>25</v>
+      </c>
       <c r="H237" s="19"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
@@ -6319,7 +6417,9 @@
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
-      <c r="G238" s="15"/>
+      <c r="G238" s="15">
+        <v>7</v>
+      </c>
       <c r="H238" s="19"/>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
@@ -6335,7 +6435,9 @@
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
-      <c r="G239" s="15"/>
+      <c r="G239" s="15">
+        <v>36</v>
+      </c>
       <c r="H239" s="19"/>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
@@ -6351,7 +6453,9 @@
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
-      <c r="G240" s="15"/>
+      <c r="G240" s="15">
+        <v>39</v>
+      </c>
       <c r="H240" s="19"/>
     </row>
     <row r="241" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -6415,6 +6519,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C7DC5809443B914698F205EDCFE14C5C" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="910dd8289e79bf7e3b2db69aaa037196">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2592cbe8-961e-4422-8c47-4737933d0fe0" xmlns:ns3="7af58a8f-2f6f-405a-b238-befdc3c227d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecb9083a17ae33be0a7009b46db9eab7" ns2:_="" ns3:_="">
     <xsd:import namespace="2592cbe8-961e-4422-8c47-4737933d0fe0"/>
@@ -6591,15 +6704,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -6607,6 +6711,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70AE5412-3087-4F96-A882-A7717BC45E52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6625,14 +6737,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
   <ds:schemaRefs>

--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30EC971-B752-4234-AF53-A6057C79772F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8279D471-9010-4314-9C66-EA3A1C196C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
@@ -2043,7 +2043,9 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="15"/>
+      <c r="G3" s="15">
+        <v>87</v>
+      </c>
       <c r="H3" s="19">
         <v>86.666666666666671</v>
       </c>
@@ -2062,7 +2064,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="15">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H4" s="19">
         <v>66.666666666666657</v>
@@ -2121,7 +2123,9 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="15"/>
+      <c r="G7" s="15">
+        <v>64</v>
+      </c>
       <c r="H7" s="19">
         <v>53.333333333333336</v>
       </c>
@@ -2139,7 +2143,9 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="15"/>
+      <c r="G8" s="15">
+        <v>77</v>
+      </c>
       <c r="H8" s="19">
         <v>73.333333333333329</v>
       </c>
@@ -2177,7 +2183,9 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="15"/>
+      <c r="G10" s="15">
+        <v>48</v>
+      </c>
       <c r="H10" s="19">
         <v>96.666666666666671</v>
       </c>
@@ -2195,7 +2203,9 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="15"/>
+      <c r="G11" s="15">
+        <v>34</v>
+      </c>
       <c r="H11" s="19">
         <v>73.333333333333329</v>
       </c>
@@ -2233,7 +2243,9 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="15"/>
+      <c r="G13" s="15">
+        <v>40</v>
+      </c>
       <c r="H13" s="19">
         <v>80</v>
       </c>
@@ -2271,7 +2283,9 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="15"/>
+      <c r="G15" s="15">
+        <v>61</v>
+      </c>
       <c r="H15" s="19">
         <v>80</v>
       </c>
@@ -2289,7 +2303,9 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="15"/>
+      <c r="G16" s="15">
+        <v>57</v>
+      </c>
       <c r="H16" s="19">
         <v>80</v>
       </c>
@@ -2307,7 +2323,9 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="15"/>
+      <c r="G17" s="15">
+        <v>79</v>
+      </c>
       <c r="H17" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -2345,7 +2363,9 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="15"/>
+      <c r="G19" s="15">
+        <v>91</v>
+      </c>
       <c r="H19" s="19">
         <v>60</v>
       </c>
@@ -2383,7 +2403,9 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="15"/>
+      <c r="G21" s="15">
+        <v>97</v>
+      </c>
       <c r="H21" s="19">
         <v>73.333333333333329</v>
       </c>
@@ -2401,7 +2423,9 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="15"/>
+      <c r="G22" s="15">
+        <v>53</v>
+      </c>
       <c r="H22" s="19">
         <v>83.333333333333343</v>
       </c>
@@ -2419,7 +2443,9 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="15"/>
+      <c r="G23" s="15">
+        <v>73</v>
+      </c>
       <c r="H23" s="19">
         <v>70</v>
       </c>
@@ -2437,7 +2463,9 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="15"/>
+      <c r="G24" s="15">
+        <v>33</v>
+      </c>
       <c r="H24" s="19">
         <v>70</v>
       </c>
@@ -2455,7 +2483,9 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="15"/>
+      <c r="G25" s="15">
+        <v>82</v>
+      </c>
       <c r="H25" s="19">
         <v>90</v>
       </c>
@@ -2473,7 +2503,9 @@
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="15"/>
+      <c r="G26" s="15">
+        <v>45</v>
+      </c>
       <c r="H26" s="19">
         <v>80</v>
       </c>
@@ -2491,7 +2523,9 @@
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="15"/>
+      <c r="G27" s="15">
+        <v>51</v>
+      </c>
       <c r="H27" s="19">
         <v>90</v>
       </c>
@@ -2509,7 +2543,9 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="15"/>
+      <c r="G28" s="15">
+        <v>54</v>
+      </c>
       <c r="H28" s="19">
         <v>96.666666666666671</v>
       </c>
@@ -2527,7 +2563,9 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="15"/>
+      <c r="G29" s="15">
+        <v>80</v>
+      </c>
       <c r="H29" s="19">
         <v>70</v>
       </c>
@@ -2545,7 +2583,9 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="15"/>
+      <c r="G30" s="15">
+        <v>74</v>
+      </c>
       <c r="H30" s="19">
         <v>96.666666666666671</v>
       </c>
@@ -2601,7 +2641,9 @@
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="15">
+        <v>74</v>
+      </c>
       <c r="H33" s="19">
         <v>70</v>
       </c>
@@ -2619,7 +2661,9 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="15"/>
+      <c r="G34" s="15">
+        <v>76</v>
+      </c>
       <c r="H34" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -2637,7 +2681,9 @@
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="15"/>
+      <c r="G35" s="15">
+        <v>66</v>
+      </c>
       <c r="H35" s="19">
         <v>93.333333333333329</v>
       </c>
@@ -2655,7 +2701,9 @@
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="15"/>
+      <c r="G36" s="15">
+        <v>37</v>
+      </c>
       <c r="H36" s="19">
         <v>80</v>
       </c>
@@ -2673,7 +2721,9 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="15"/>
+      <c r="G37" s="15">
+        <v>53</v>
+      </c>
       <c r="H37" s="19">
         <v>80</v>
       </c>
@@ -2691,7 +2741,9 @@
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="15"/>
+      <c r="G38" s="15">
+        <v>66</v>
+      </c>
       <c r="H38" s="19">
         <v>86.666666666666671</v>
       </c>
@@ -2709,7 +2761,9 @@
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="15"/>
+      <c r="G39" s="15">
+        <v>69</v>
+      </c>
       <c r="H39" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -2807,7 +2861,9 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="15"/>
+      <c r="G44" s="15">
+        <v>38</v>
+      </c>
       <c r="H44" s="19">
         <v>80</v>
       </c>
@@ -2845,7 +2901,9 @@
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="15"/>
+      <c r="G46" s="15">
+        <v>36</v>
+      </c>
       <c r="H46" s="19">
         <v>73.333333333333329</v>
       </c>
@@ -2903,7 +2961,9 @@
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="15"/>
+      <c r="G49" s="15">
+        <v>61</v>
+      </c>
       <c r="H49" s="19">
         <v>93.333333333333329</v>
       </c>
@@ -2921,7 +2981,9 @@
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="15"/>
+      <c r="G50" s="15">
+        <v>40</v>
+      </c>
       <c r="H50" s="19">
         <v>83.333333333333343</v>
       </c>
@@ -2939,7 +3001,9 @@
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="15"/>
+      <c r="G51" s="15">
+        <v>56</v>
+      </c>
       <c r="H51" s="19">
         <v>73.333333333333329</v>
       </c>
@@ -2977,7 +3041,9 @@
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
-      <c r="G53" s="15"/>
+      <c r="G53" s="15">
+        <v>57</v>
+      </c>
       <c r="H53" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -2995,7 +3061,9 @@
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="15"/>
+      <c r="G54" s="15">
+        <v>55</v>
+      </c>
       <c r="H54" s="19">
         <v>83.333333333333343</v>
       </c>
@@ -3013,7 +3081,9 @@
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="15"/>
+      <c r="G55" s="15">
+        <v>70</v>
+      </c>
       <c r="H55" s="19">
         <v>93.333333333333329</v>
       </c>
@@ -3031,7 +3101,9 @@
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
-      <c r="G56" s="15"/>
+      <c r="G56" s="15">
+        <v>44</v>
+      </c>
       <c r="H56" s="19">
         <v>93.333333333333329</v>
       </c>
@@ -3069,7 +3141,9 @@
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
-      <c r="G58" s="15"/>
+      <c r="G58" s="15">
+        <v>32</v>
+      </c>
       <c r="H58" s="19">
         <v>93.333333333333329</v>
       </c>
@@ -3087,7 +3161,9 @@
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="15"/>
+      <c r="G59" s="15">
+        <v>39</v>
+      </c>
       <c r="H59" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -3125,7 +3201,9 @@
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
-      <c r="G61" s="15"/>
+      <c r="G61" s="15">
+        <v>82</v>
+      </c>
       <c r="H61" s="19">
         <v>80</v>
       </c>
@@ -3143,7 +3221,9 @@
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
-      <c r="G62" s="15"/>
+      <c r="G62" s="15">
+        <v>68</v>
+      </c>
       <c r="H62" s="19">
         <v>70</v>
       </c>
@@ -3161,7 +3241,9 @@
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
-      <c r="G63" s="15"/>
+      <c r="G63" s="15">
+        <v>79</v>
+      </c>
       <c r="H63" s="19">
         <v>100</v>
       </c>
@@ -3179,7 +3261,9 @@
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
-      <c r="G64" s="15"/>
+      <c r="G64" s="15">
+        <v>52</v>
+      </c>
       <c r="H64" s="19">
         <v>86.666666666666671</v>
       </c>
@@ -3197,7 +3281,9 @@
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
-      <c r="G65" s="15"/>
+      <c r="G65" s="15">
+        <v>67</v>
+      </c>
       <c r="H65" s="19">
         <v>70</v>
       </c>
@@ -3215,7 +3301,9 @@
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
-      <c r="G66" s="15"/>
+      <c r="G66" s="15">
+        <v>68</v>
+      </c>
       <c r="H66" s="19">
         <v>96.666666666666671</v>
       </c>
@@ -3273,7 +3361,9 @@
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
-      <c r="G69" s="15"/>
+      <c r="G69" s="15">
+        <v>42</v>
+      </c>
       <c r="H69" s="19">
         <v>73.333333333333329</v>
       </c>
@@ -3331,7 +3421,9 @@
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="15"/>
+      <c r="G72" s="15">
+        <v>55</v>
+      </c>
       <c r="H72" s="19">
         <v>90</v>
       </c>
@@ -3349,7 +3441,9 @@
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="15"/>
+      <c r="G73" s="15">
+        <v>60</v>
+      </c>
       <c r="H73" s="19">
         <v>96.666666666666671</v>
       </c>
@@ -3427,7 +3521,9 @@
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="15"/>
+      <c r="G77" s="15">
+        <v>54</v>
+      </c>
       <c r="H77" s="19">
         <v>83.333333333333343</v>
       </c>
@@ -3505,7 +3601,9 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
-      <c r="G81" s="15"/>
+      <c r="G81" s="15">
+        <v>58</v>
+      </c>
       <c r="H81" s="19">
         <v>90</v>
       </c>
@@ -3641,7 +3739,9 @@
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
-      <c r="G88" s="15"/>
+      <c r="G88" s="15">
+        <v>69</v>
+      </c>
       <c r="H88" s="19">
         <v>80</v>
       </c>
@@ -3699,7 +3799,9 @@
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="15"/>
+      <c r="G91" s="15">
+        <v>68</v>
+      </c>
       <c r="H91" s="19">
         <v>73.333333333333329</v>
       </c>
@@ -3717,7 +3819,9 @@
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="15"/>
+      <c r="G92" s="15">
+        <v>59</v>
+      </c>
       <c r="H92" s="19">
         <v>83.333333333333343</v>
       </c>
@@ -3735,7 +3839,9 @@
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
-      <c r="G93" s="15"/>
+      <c r="G93" s="15">
+        <v>53</v>
+      </c>
       <c r="H93" s="19">
         <v>86.666666666666671</v>
       </c>
@@ -3773,7 +3879,9 @@
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
-      <c r="G95" s="15"/>
+      <c r="G95" s="15">
+        <v>55</v>
+      </c>
       <c r="H95" s="19">
         <v>90</v>
       </c>
@@ -3851,7 +3959,9 @@
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
-      <c r="G99" s="15"/>
+      <c r="G99" s="15">
+        <v>72</v>
+      </c>
       <c r="H99" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -3869,7 +3979,9 @@
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
-      <c r="G100" s="15"/>
+      <c r="G100" s="15">
+        <v>62</v>
+      </c>
       <c r="H100" s="19">
         <v>83.333333333333343</v>
       </c>
@@ -3907,7 +4019,9 @@
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
-      <c r="G102" s="15"/>
+      <c r="G102" s="15">
+        <v>74</v>
+      </c>
       <c r="H102" s="19">
         <v>93.333333333333329</v>
       </c>
@@ -3926,7 +4040,7 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="15">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H103" s="19">
         <v>60</v>
@@ -3945,7 +4059,9 @@
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
-      <c r="G104" s="15"/>
+      <c r="G104" s="15">
+        <v>84</v>
+      </c>
       <c r="H104" s="19">
         <v>80</v>
       </c>
@@ -3963,7 +4079,9 @@
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
-      <c r="G105" s="15"/>
+      <c r="G105" s="15">
+        <v>72</v>
+      </c>
       <c r="H105" s="19">
         <v>96.666666666666671</v>
       </c>
@@ -3981,7 +4099,9 @@
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
-      <c r="G106" s="15"/>
+      <c r="G106" s="15">
+        <v>35</v>
+      </c>
       <c r="H106" s="19">
         <v>83.333333333333343</v>
       </c>
@@ -4019,7 +4139,9 @@
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
-      <c r="G108" s="15"/>
+      <c r="G108" s="15">
+        <v>67</v>
+      </c>
       <c r="H108" s="19">
         <v>83.333333333333343</v>
       </c>
@@ -4057,7 +4179,9 @@
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
-      <c r="G110" s="15"/>
+      <c r="G110" s="15">
+        <v>45</v>
+      </c>
       <c r="H110" s="19">
         <v>70</v>
       </c>
@@ -4075,7 +4199,9 @@
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="15"/>
+      <c r="G111" s="15">
+        <v>9</v>
+      </c>
       <c r="H111" s="19">
         <v>70</v>
       </c>
@@ -4093,7 +4219,9 @@
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
-      <c r="G112" s="15"/>
+      <c r="G112" s="15">
+        <v>72</v>
+      </c>
       <c r="H112" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -4111,7 +4239,9 @@
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
-      <c r="G113" s="15"/>
+      <c r="G113" s="15">
+        <v>44</v>
+      </c>
       <c r="H113" s="19">
         <v>86.666666666666671</v>
       </c>
@@ -4129,7 +4259,9 @@
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
-      <c r="G114" s="15"/>
+      <c r="G114" s="15">
+        <v>56</v>
+      </c>
       <c r="H114" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -4147,7 +4279,9 @@
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
-      <c r="G115" s="15"/>
+      <c r="G115" s="15">
+        <v>75</v>
+      </c>
       <c r="H115" s="19">
         <v>70</v>
       </c>
@@ -4166,7 +4300,7 @@
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="15">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H116" s="19">
         <v>66.666666666666657</v>
@@ -4205,7 +4339,9 @@
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
-      <c r="G118" s="15"/>
+      <c r="G118" s="15">
+        <v>60</v>
+      </c>
       <c r="H118" s="19">
         <v>96.666666666666671</v>
       </c>
@@ -4223,7 +4359,9 @@
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
-      <c r="G119" s="15"/>
+      <c r="G119" s="15">
+        <v>70</v>
+      </c>
       <c r="H119" s="19">
         <v>80</v>
       </c>
@@ -4241,7 +4379,9 @@
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
-      <c r="G120" s="15"/>
+      <c r="G120" s="15">
+        <v>63</v>
+      </c>
       <c r="H120" s="19">
         <v>83.333333333333343</v>
       </c>
@@ -4279,7 +4419,9 @@
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
-      <c r="G122" s="15"/>
+      <c r="G122" s="15">
+        <v>72</v>
+      </c>
       <c r="H122" s="19">
         <v>80</v>
       </c>
@@ -4297,7 +4439,9 @@
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
-      <c r="G123" s="15"/>
+      <c r="G123" s="15">
+        <v>8</v>
+      </c>
       <c r="H123" s="19">
         <v>0</v>
       </c>
@@ -4315,7 +4459,9 @@
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
-      <c r="G124" s="15"/>
+      <c r="G124" s="15">
+        <v>70</v>
+      </c>
       <c r="H124" s="19">
         <v>86.666666666666671</v>
       </c>
@@ -4333,7 +4479,9 @@
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
-      <c r="G125" s="15"/>
+      <c r="G125" s="15">
+        <v>56</v>
+      </c>
       <c r="H125" s="19">
         <v>70</v>
       </c>
@@ -4391,7 +4539,9 @@
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
-      <c r="G128" s="15"/>
+      <c r="G128" s="15">
+        <v>52</v>
+      </c>
       <c r="H128" s="19">
         <v>70</v>
       </c>
@@ -4409,7 +4559,9 @@
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
-      <c r="G129" s="15"/>
+      <c r="G129" s="15">
+        <v>45</v>
+      </c>
       <c r="H129" s="19">
         <v>70</v>
       </c>
@@ -4427,7 +4579,9 @@
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
-      <c r="G130" s="15"/>
+      <c r="G130" s="15">
+        <v>42</v>
+      </c>
       <c r="H130" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -4445,7 +4599,9 @@
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
-      <c r="G131" s="15"/>
+      <c r="G131" s="15">
+        <v>56</v>
+      </c>
       <c r="H131" s="19">
         <v>90</v>
       </c>
@@ -4463,7 +4619,9 @@
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
-      <c r="G132" s="15"/>
+      <c r="G132" s="15">
+        <v>79</v>
+      </c>
       <c r="H132" s="19">
         <v>86.666666666666671</v>
       </c>
@@ -4481,7 +4639,9 @@
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
-      <c r="G133" s="15"/>
+      <c r="G133" s="15">
+        <v>61</v>
+      </c>
       <c r="H133" s="19">
         <v>80</v>
       </c>
@@ -4499,7 +4659,9 @@
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
-      <c r="G134" s="15"/>
+      <c r="G134" s="15">
+        <v>66</v>
+      </c>
       <c r="H134" s="19">
         <v>100</v>
       </c>
@@ -4517,7 +4679,9 @@
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
-      <c r="G135" s="15"/>
+      <c r="G135" s="15">
+        <v>37</v>
+      </c>
       <c r="H135" s="19">
         <v>80</v>
       </c>
@@ -4535,7 +4699,9 @@
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
-      <c r="G136" s="15"/>
+      <c r="G136" s="15">
+        <v>50</v>
+      </c>
       <c r="H136" s="19">
         <v>100</v>
       </c>
@@ -4553,7 +4719,9 @@
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
-      <c r="G137" s="15"/>
+      <c r="G137" s="15">
+        <v>65</v>
+      </c>
       <c r="H137" s="19">
         <v>80</v>
       </c>
@@ -4571,7 +4739,9 @@
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
-      <c r="G138" s="15"/>
+      <c r="G138" s="15">
+        <v>56</v>
+      </c>
       <c r="H138" s="19">
         <v>93.333333333333329</v>
       </c>
@@ -4607,7 +4777,9 @@
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
-      <c r="G140" s="15"/>
+      <c r="G140" s="15">
+        <v>63</v>
+      </c>
       <c r="H140" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -4645,7 +4817,9 @@
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
-      <c r="G142" s="15"/>
+      <c r="G142" s="15">
+        <v>53</v>
+      </c>
       <c r="H142" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -4683,7 +4857,9 @@
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
-      <c r="G144" s="15"/>
+      <c r="G144" s="15">
+        <v>80</v>
+      </c>
       <c r="H144" s="19">
         <v>80</v>
       </c>
@@ -4701,7 +4877,9 @@
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
-      <c r="G145" s="15"/>
+      <c r="G145" s="15">
+        <v>67</v>
+      </c>
       <c r="H145" s="19">
         <v>90</v>
       </c>
@@ -4719,7 +4897,9 @@
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
-      <c r="G146" s="15"/>
+      <c r="G146" s="15">
+        <v>70</v>
+      </c>
       <c r="H146" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -4757,7 +4937,9 @@
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
-      <c r="G148" s="15"/>
+      <c r="G148" s="15">
+        <v>38</v>
+      </c>
       <c r="H148" s="19">
         <v>70</v>
       </c>
@@ -4775,7 +4957,9 @@
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
-      <c r="G149" s="15"/>
+      <c r="G149" s="15">
+        <v>51</v>
+      </c>
       <c r="H149" s="19">
         <v>73.333333333333329</v>
       </c>
@@ -4794,7 +4978,7 @@
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="15">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H150" s="19">
         <v>60</v>
@@ -4813,7 +4997,9 @@
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
-      <c r="G151" s="15"/>
+      <c r="G151" s="15">
+        <v>55</v>
+      </c>
       <c r="H151" s="19">
         <v>73.333333333333329</v>
       </c>
@@ -4851,7 +5037,9 @@
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
-      <c r="G153" s="15"/>
+      <c r="G153" s="15">
+        <v>58</v>
+      </c>
       <c r="H153" s="19">
         <v>70</v>
       </c>
@@ -4870,7 +5058,7 @@
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="15">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H154" s="19">
         <v>20</v>
@@ -4909,7 +5097,9 @@
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
-      <c r="G156" s="15"/>
+      <c r="G156" s="15">
+        <v>90</v>
+      </c>
       <c r="H156" s="19">
         <v>93.333333333333329</v>
       </c>
@@ -4967,7 +5157,9 @@
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
-      <c r="G159" s="15"/>
+      <c r="G159" s="15">
+        <v>52</v>
+      </c>
       <c r="H159" s="19">
         <v>86.666666666666671</v>
       </c>
@@ -4985,7 +5177,9 @@
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
-      <c r="G160" s="15"/>
+      <c r="G160" s="15">
+        <v>56</v>
+      </c>
       <c r="H160" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -5023,7 +5217,9 @@
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
-      <c r="G162" s="15"/>
+      <c r="G162" s="15">
+        <v>63</v>
+      </c>
       <c r="H162" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -5102,7 +5298,7 @@
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="15">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H166" s="19">
         <v>36.666666666666664</v>
@@ -5141,7 +5337,9 @@
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
-      <c r="G168" s="15"/>
+      <c r="G168" s="15">
+        <v>63</v>
+      </c>
       <c r="H168" s="19">
         <v>50</v>
       </c>
@@ -5159,7 +5357,9 @@
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
-      <c r="G169" s="15"/>
+      <c r="G169" s="15">
+        <v>79</v>
+      </c>
       <c r="H169" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -5178,7 +5378,7 @@
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H170" s="19">
         <v>16.666666666666664</v>
@@ -5217,7 +5417,9 @@
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
-      <c r="G172" s="15"/>
+      <c r="G172" s="15">
+        <v>30</v>
+      </c>
       <c r="H172" s="19">
         <v>26.666666666666668</v>
       </c>
@@ -5255,7 +5457,9 @@
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
-      <c r="G174" s="15"/>
+      <c r="G174" s="15">
+        <v>25</v>
+      </c>
       <c r="H174" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -5313,7 +5517,9 @@
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
-      <c r="G177" s="15"/>
+      <c r="G177" s="15">
+        <v>49</v>
+      </c>
       <c r="H177" s="19">
         <v>80</v>
       </c>
@@ -5331,7 +5537,9 @@
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
-      <c r="G178" s="15"/>
+      <c r="G178" s="15">
+        <v>84</v>
+      </c>
       <c r="H178" s="19">
         <v>96.666666666666671</v>
       </c>
@@ -5349,7 +5557,9 @@
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
-      <c r="G179" s="15"/>
+      <c r="G179" s="15">
+        <v>78</v>
+      </c>
       <c r="H179" s="19">
         <v>96.666666666666671</v>
       </c>
@@ -5387,7 +5597,9 @@
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
-      <c r="G181" s="15"/>
+      <c r="G181" s="15">
+        <v>58</v>
+      </c>
       <c r="H181" s="19">
         <v>93.333333333333329</v>
       </c>
@@ -5405,7 +5617,9 @@
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
-      <c r="G182" s="15"/>
+      <c r="G182" s="15">
+        <v>34</v>
+      </c>
       <c r="H182" s="19">
         <v>93.333333333333329</v>
       </c>
@@ -5423,7 +5637,9 @@
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
-      <c r="G183" s="15"/>
+      <c r="G183" s="15">
+        <v>49</v>
+      </c>
       <c r="H183" s="19">
         <v>66.666666666666657</v>
       </c>
@@ -5461,7 +5677,9 @@
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
-      <c r="G185" s="15"/>
+      <c r="G185" s="15">
+        <v>72</v>
+      </c>
       <c r="H185" s="19">
         <v>73.333333333333329</v>
       </c>
@@ -5479,7 +5697,9 @@
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
-      <c r="G186" s="15"/>
+      <c r="G186" s="15">
+        <v>58</v>
+      </c>
       <c r="H186" s="19">
         <v>86.666666666666671</v>
       </c>
@@ -5734,7 +5954,7 @@
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="15">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H200" s="19"/>
     </row>
@@ -5770,7 +5990,7 @@
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="15">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H202" s="19"/>
     </row>
@@ -6004,7 +6224,7 @@
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
       <c r="G215" s="15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H215" s="19"/>
     </row>
@@ -6436,7 +6656,7 @@
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H239" s="19"/>
     </row>

--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8279D471-9010-4314-9C66-EA3A1C196C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B27609-1788-4300-89B8-11872D29677F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="487">
   <si>
     <t>Name</t>
   </si>
@@ -1609,7 +1609,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1654,6 +1654,12 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1975,10 +1981,10 @@
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="14" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="1"/>
@@ -2022,7 +2028,9 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="11">
+        <v>73</v>
+      </c>
       <c r="G2" s="15">
         <v>38</v>
       </c>
@@ -2042,7 +2050,9 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="F3" s="11">
+        <v>75</v>
+      </c>
       <c r="G3" s="15">
         <v>87</v>
       </c>
@@ -2062,7 +2072,9 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="F4" s="11">
+        <v>54</v>
+      </c>
       <c r="G4" s="15">
         <v>75</v>
       </c>
@@ -2082,7 +2094,9 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="11">
+        <v>60</v>
+      </c>
       <c r="G5" s="15">
         <v>46</v>
       </c>
@@ -2102,7 +2116,9 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="11">
+        <v>60</v>
+      </c>
       <c r="G6" s="15">
         <v>40</v>
       </c>
@@ -2122,7 +2138,9 @@
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="F7" s="11">
+        <v>65</v>
+      </c>
       <c r="G7" s="15">
         <v>64</v>
       </c>
@@ -2142,7 +2160,9 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="F8" s="11">
+        <v>42</v>
+      </c>
       <c r="G8" s="15">
         <v>77</v>
       </c>
@@ -2162,7 +2182,9 @@
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="F9" s="11">
+        <v>55</v>
+      </c>
       <c r="G9" s="15">
         <v>46</v>
       </c>
@@ -2182,7 +2204,9 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="F10" s="11">
+        <v>39</v>
+      </c>
       <c r="G10" s="15">
         <v>48</v>
       </c>
@@ -2202,7 +2226,9 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="F11" s="11">
+        <v>25</v>
+      </c>
       <c r="G11" s="15">
         <v>34</v>
       </c>
@@ -2222,7 +2248,9 @@
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="11">
+        <v>65</v>
+      </c>
       <c r="G12" s="15">
         <v>35</v>
       </c>
@@ -2242,7 +2270,9 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="F13" s="11">
+        <v>42</v>
+      </c>
       <c r="G13" s="15">
         <v>40</v>
       </c>
@@ -2262,7 +2292,9 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="F14" s="11">
+        <v>54</v>
+      </c>
       <c r="G14" s="15">
         <v>86</v>
       </c>
@@ -2282,7 +2314,9 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="F15" s="11">
+        <v>62</v>
+      </c>
       <c r="G15" s="15">
         <v>61</v>
       </c>
@@ -2302,7 +2336,9 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="F16" s="11">
+        <v>66</v>
+      </c>
       <c r="G16" s="15">
         <v>57</v>
       </c>
@@ -2322,7 +2358,9 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="F17" s="11">
+        <v>70</v>
+      </c>
       <c r="G17" s="15">
         <v>79</v>
       </c>
@@ -2342,7 +2380,9 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="F18" s="11">
+        <v>44</v>
+      </c>
       <c r="G18" s="15">
         <v>71</v>
       </c>
@@ -2362,7 +2402,9 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="F19" s="11">
+        <v>47</v>
+      </c>
       <c r="G19" s="15">
         <v>91</v>
       </c>
@@ -2382,7 +2424,9 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="F20" s="11">
+        <v>75</v>
+      </c>
       <c r="G20" s="15">
         <v>71</v>
       </c>
@@ -2402,7 +2446,9 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="F21" s="11">
+        <v>75</v>
+      </c>
       <c r="G21" s="15">
         <v>97</v>
       </c>
@@ -2422,7 +2468,9 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="F22" s="11">
+        <v>75</v>
+      </c>
       <c r="G22" s="15">
         <v>53</v>
       </c>
@@ -2442,7 +2490,9 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="F23" s="11">
+        <v>66</v>
+      </c>
       <c r="G23" s="15">
         <v>73</v>
       </c>
@@ -2462,7 +2512,9 @@
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="F24" s="11">
+        <v>66</v>
+      </c>
       <c r="G24" s="15">
         <v>33</v>
       </c>
@@ -2482,7 +2534,9 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
+      <c r="F25" s="11">
+        <v>63</v>
+      </c>
       <c r="G25" s="15">
         <v>82</v>
       </c>
@@ -2502,7 +2556,9 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="F26" s="11">
+        <v>55</v>
+      </c>
       <c r="G26" s="15">
         <v>45</v>
       </c>
@@ -2522,7 +2578,9 @@
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+      <c r="F27" s="11">
+        <v>75</v>
+      </c>
       <c r="G27" s="15">
         <v>51</v>
       </c>
@@ -2542,7 +2600,9 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="F28" s="11">
+        <v>66</v>
+      </c>
       <c r="G28" s="15">
         <v>54</v>
       </c>
@@ -2562,7 +2622,9 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+      <c r="F29" s="11">
+        <v>55</v>
+      </c>
       <c r="G29" s="15">
         <v>80</v>
       </c>
@@ -2582,7 +2644,9 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
+      <c r="F30" s="11">
+        <v>78</v>
+      </c>
       <c r="G30" s="15">
         <v>74</v>
       </c>
@@ -2602,8 +2666,12 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="15"/>
+      <c r="F31" s="11">
+        <v>65</v>
+      </c>
+      <c r="G31" s="15">
+        <v>38</v>
+      </c>
       <c r="H31" s="19">
         <v>20</v>
       </c>
@@ -2620,7 +2688,9 @@
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
+      <c r="F32" s="11">
+        <v>73</v>
+      </c>
       <c r="G32" s="15">
         <v>68</v>
       </c>
@@ -2640,7 +2710,9 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+      <c r="F33" s="11">
+        <v>41</v>
+      </c>
       <c r="G33" s="15">
         <v>74</v>
       </c>
@@ -2660,9 +2732,11 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+      <c r="F34" s="11">
+        <v>76</v>
+      </c>
       <c r="G34" s="15">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H34" s="19">
         <v>76.666666666666671</v>
@@ -2680,7 +2754,9 @@
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
+      <c r="F35" s="11">
+        <v>73</v>
+      </c>
       <c r="G35" s="15">
         <v>66</v>
       </c>
@@ -2700,9 +2776,11 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
+      <c r="F36" s="11">
+        <v>59</v>
+      </c>
       <c r="G36" s="15">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H36" s="19">
         <v>80</v>
@@ -2720,7 +2798,9 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
+      <c r="F37" s="11">
+        <v>78</v>
+      </c>
       <c r="G37" s="15">
         <v>53</v>
       </c>
@@ -2740,7 +2820,9 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
+      <c r="F38" s="11">
+        <v>75</v>
+      </c>
       <c r="G38" s="15">
         <v>66</v>
       </c>
@@ -2760,7 +2842,9 @@
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
+      <c r="F39" s="11">
+        <v>41</v>
+      </c>
       <c r="G39" s="15">
         <v>69</v>
       </c>
@@ -2780,7 +2864,9 @@
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="F40" s="11">
+        <v>71</v>
+      </c>
       <c r="G40" s="15">
         <v>54</v>
       </c>
@@ -2800,7 +2886,9 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
+      <c r="F41" s="11">
+        <v>62</v>
+      </c>
       <c r="G41" s="15">
         <v>34</v>
       </c>
@@ -2820,7 +2908,9 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
+      <c r="F42" s="11">
+        <v>65</v>
+      </c>
       <c r="G42" s="15">
         <v>46</v>
       </c>
@@ -2840,7 +2930,9 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="F43" s="11">
+        <v>65</v>
+      </c>
       <c r="G43" s="15">
         <v>73</v>
       </c>
@@ -2860,7 +2952,9 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
+      <c r="F44" s="11">
+        <v>57</v>
+      </c>
       <c r="G44" s="15">
         <v>38</v>
       </c>
@@ -2880,7 +2974,9 @@
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
+      <c r="F45" s="11">
+        <v>65</v>
+      </c>
       <c r="G45" s="15">
         <v>56</v>
       </c>
@@ -2900,7 +2996,9 @@
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
+      <c r="F46" s="11">
+        <v>46</v>
+      </c>
       <c r="G46" s="15">
         <v>36</v>
       </c>
@@ -2920,7 +3018,9 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
+      <c r="F47" s="11">
+        <v>44</v>
+      </c>
       <c r="G47" s="15">
         <v>51</v>
       </c>
@@ -2940,7 +3040,9 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
+      <c r="F48" s="11">
+        <v>47</v>
+      </c>
       <c r="G48" s="15">
         <v>55</v>
       </c>
@@ -2960,7 +3062,9 @@
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
+      <c r="F49" s="11">
+        <v>78</v>
+      </c>
       <c r="G49" s="15">
         <v>61</v>
       </c>
@@ -2980,7 +3084,9 @@
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
+      <c r="F50" s="11">
+        <v>42</v>
+      </c>
       <c r="G50" s="15">
         <v>40</v>
       </c>
@@ -3000,7 +3106,9 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
+      <c r="F51" s="11">
+        <v>63</v>
+      </c>
       <c r="G51" s="15">
         <v>56</v>
       </c>
@@ -3020,7 +3128,9 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
+      <c r="F52" s="11">
+        <v>73</v>
+      </c>
       <c r="G52" s="15">
         <v>56</v>
       </c>
@@ -3040,7 +3150,9 @@
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
+      <c r="F53" s="11">
+        <v>48</v>
+      </c>
       <c r="G53" s="15">
         <v>57</v>
       </c>
@@ -3060,7 +3172,9 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
+      <c r="F54" s="11">
+        <v>57</v>
+      </c>
       <c r="G54" s="15">
         <v>55</v>
       </c>
@@ -3080,7 +3194,9 @@
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
+      <c r="F55" s="11">
+        <v>70</v>
+      </c>
       <c r="G55" s="15">
         <v>70</v>
       </c>
@@ -3100,7 +3216,9 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
+      <c r="F56" s="11">
+        <v>53</v>
+      </c>
       <c r="G56" s="15">
         <v>44</v>
       </c>
@@ -3120,7 +3238,9 @@
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
+      <c r="F57" s="11">
+        <v>67</v>
+      </c>
       <c r="G57" s="15">
         <v>54</v>
       </c>
@@ -3140,7 +3260,9 @@
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
+      <c r="F58" s="11">
+        <v>73</v>
+      </c>
       <c r="G58" s="15">
         <v>32</v>
       </c>
@@ -3160,7 +3282,9 @@
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
+      <c r="F59" s="11">
+        <v>66</v>
+      </c>
       <c r="G59" s="15">
         <v>39</v>
       </c>
@@ -3180,7 +3304,9 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
+      <c r="F60" s="11">
+        <v>65</v>
+      </c>
       <c r="G60" s="15">
         <v>52</v>
       </c>
@@ -3200,7 +3326,9 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
+      <c r="F61" s="11">
+        <v>76</v>
+      </c>
       <c r="G61" s="15">
         <v>82</v>
       </c>
@@ -3220,7 +3348,9 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
+      <c r="F62" s="11">
+        <v>55</v>
+      </c>
       <c r="G62" s="15">
         <v>68</v>
       </c>
@@ -3240,7 +3370,9 @@
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
+      <c r="F63" s="11">
+        <v>70</v>
+      </c>
       <c r="G63" s="15">
         <v>79</v>
       </c>
@@ -3260,7 +3392,9 @@
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
+      <c r="F64" s="11">
+        <v>48</v>
+      </c>
       <c r="G64" s="15">
         <v>52</v>
       </c>
@@ -3280,7 +3414,9 @@
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
+      <c r="F65" s="11">
+        <v>55</v>
+      </c>
       <c r="G65" s="15">
         <v>67</v>
       </c>
@@ -3300,7 +3436,9 @@
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
+      <c r="F66" s="11">
+        <v>63</v>
+      </c>
       <c r="G66" s="15">
         <v>68</v>
       </c>
@@ -3320,7 +3458,9 @@
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
+      <c r="F67" s="11">
+        <v>47</v>
+      </c>
       <c r="G67" s="15">
         <v>49</v>
       </c>
@@ -3340,7 +3480,9 @@
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
+      <c r="F68" s="11">
+        <v>47</v>
+      </c>
       <c r="G68" s="15">
         <v>59</v>
       </c>
@@ -3360,7 +3502,9 @@
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
+      <c r="F69" s="11">
+        <v>48</v>
+      </c>
       <c r="G69" s="15">
         <v>42</v>
       </c>
@@ -3380,7 +3524,9 @@
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
+      <c r="F70" s="11">
+        <v>71</v>
+      </c>
       <c r="G70" s="15">
         <v>40</v>
       </c>
@@ -3400,7 +3546,9 @@
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
+      <c r="F71" s="11">
+        <v>44</v>
+      </c>
       <c r="G71" s="15">
         <v>50</v>
       </c>
@@ -3420,7 +3568,9 @@
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
+      <c r="F72" s="11">
+        <v>54</v>
+      </c>
       <c r="G72" s="15">
         <v>55</v>
       </c>
@@ -3440,7 +3590,9 @@
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
+      <c r="F73" s="11">
+        <v>59</v>
+      </c>
       <c r="G73" s="15">
         <v>60</v>
       </c>
@@ -3460,7 +3612,9 @@
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
+      <c r="F74" s="11">
+        <v>65</v>
+      </c>
       <c r="G74" s="15">
         <v>35</v>
       </c>
@@ -3480,7 +3634,9 @@
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
+      <c r="F75" s="11">
+        <v>71</v>
+      </c>
       <c r="G75" s="15">
         <v>48</v>
       </c>
@@ -3500,7 +3656,9 @@
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
+      <c r="F76" s="11">
+        <v>52</v>
+      </c>
       <c r="G76" s="15">
         <v>37</v>
       </c>
@@ -3520,7 +3678,9 @@
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
+      <c r="F77" s="11">
+        <v>70</v>
+      </c>
       <c r="G77" s="15">
         <v>54</v>
       </c>
@@ -3540,7 +3700,9 @@
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
+      <c r="F78" s="11">
+        <v>60</v>
+      </c>
       <c r="G78" s="15">
         <v>54</v>
       </c>
@@ -3560,7 +3722,9 @@
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
+      <c r="F79" s="11">
+        <v>55</v>
+      </c>
       <c r="G79" s="15">
         <v>42</v>
       </c>
@@ -3580,7 +3744,9 @@
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
+      <c r="F80" s="11">
+        <v>25</v>
+      </c>
       <c r="G80" s="15">
         <v>63</v>
       </c>
@@ -3600,7 +3766,9 @@
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
+      <c r="F81" s="11">
+        <v>50</v>
+      </c>
       <c r="G81" s="15">
         <v>58</v>
       </c>
@@ -3620,7 +3788,9 @@
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
+      <c r="F82" s="11">
+        <v>54</v>
+      </c>
       <c r="G82" s="15">
         <v>54</v>
       </c>
@@ -3640,7 +3810,9 @@
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
+      <c r="F83" s="11">
+        <v>67</v>
+      </c>
       <c r="G83" s="15">
         <v>67</v>
       </c>
@@ -3660,7 +3832,9 @@
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
+      <c r="F84" s="11">
+        <v>73</v>
+      </c>
       <c r="G84" s="15">
         <v>70</v>
       </c>
@@ -3680,8 +3854,12 @@
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="15"/>
+      <c r="F85" s="11">
+        <v>75</v>
+      </c>
+      <c r="G85" s="15">
+        <v>47</v>
+      </c>
       <c r="H85" s="19">
         <v>60</v>
       </c>
@@ -3698,7 +3876,9 @@
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
+      <c r="F86" s="11">
+        <v>75</v>
+      </c>
       <c r="G86" s="15">
         <v>42</v>
       </c>
@@ -3718,7 +3898,9 @@
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
+      <c r="F87" s="11">
+        <v>75</v>
+      </c>
       <c r="G87" s="15">
         <v>47</v>
       </c>
@@ -3738,7 +3920,9 @@
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
+      <c r="F88" s="11">
+        <v>76</v>
+      </c>
       <c r="G88" s="15">
         <v>69</v>
       </c>
@@ -3758,7 +3942,9 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
+      <c r="F89" s="11">
+        <v>44</v>
+      </c>
       <c r="G89" s="15">
         <v>68</v>
       </c>
@@ -3778,7 +3964,9 @@
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
+      <c r="F90" s="11">
+        <v>60</v>
+      </c>
       <c r="G90" s="15">
         <v>56</v>
       </c>
@@ -3798,7 +3986,9 @@
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
+      <c r="F91" s="11">
+        <v>75</v>
+      </c>
       <c r="G91" s="15">
         <v>68</v>
       </c>
@@ -3818,7 +4008,9 @@
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
+      <c r="F92" s="11">
+        <v>67</v>
+      </c>
       <c r="G92" s="15">
         <v>59</v>
       </c>
@@ -3838,7 +4030,9 @@
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
+      <c r="F93" s="11">
+        <v>70</v>
+      </c>
       <c r="G93" s="15">
         <v>53</v>
       </c>
@@ -3858,7 +4052,9 @@
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
+      <c r="F94" s="11">
+        <v>46</v>
+      </c>
       <c r="G94" s="15">
         <v>33</v>
       </c>
@@ -3878,7 +4074,9 @@
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
+      <c r="F95" s="11">
+        <v>62</v>
+      </c>
       <c r="G95" s="15">
         <v>55</v>
       </c>
@@ -3898,7 +4096,9 @@
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
+      <c r="F96" s="11">
+        <v>62</v>
+      </c>
       <c r="G96" s="15">
         <v>65</v>
       </c>
@@ -3918,7 +4118,9 @@
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
+      <c r="F97" s="11">
+        <v>73</v>
+      </c>
       <c r="G97" s="15">
         <v>42</v>
       </c>
@@ -3938,7 +4140,9 @@
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
+      <c r="F98" s="11">
+        <v>52</v>
+      </c>
       <c r="G98" s="15">
         <v>59</v>
       </c>
@@ -3958,7 +4162,9 @@
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
+      <c r="F99" s="11">
+        <v>62</v>
+      </c>
       <c r="G99" s="15">
         <v>72</v>
       </c>
@@ -3978,7 +4184,9 @@
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
+      <c r="F100" s="11">
+        <v>62</v>
+      </c>
       <c r="G100" s="15">
         <v>62</v>
       </c>
@@ -3998,7 +4206,9 @@
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
+      <c r="F101" s="11">
+        <v>52</v>
+      </c>
       <c r="G101" s="15">
         <v>57</v>
       </c>
@@ -4018,7 +4228,9 @@
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
+      <c r="F102" s="11">
+        <v>59</v>
+      </c>
       <c r="G102" s="15">
         <v>74</v>
       </c>
@@ -4038,7 +4250,9 @@
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
+      <c r="F103" s="11">
+        <v>52</v>
+      </c>
       <c r="G103" s="15">
         <v>36</v>
       </c>
@@ -4058,7 +4272,9 @@
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
+      <c r="F104" s="11">
+        <v>57</v>
+      </c>
       <c r="G104" s="15">
         <v>84</v>
       </c>
@@ -4078,7 +4294,9 @@
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
+      <c r="F105" s="11">
+        <v>50</v>
+      </c>
       <c r="G105" s="15">
         <v>72</v>
       </c>
@@ -4098,7 +4316,9 @@
       </c>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
+      <c r="F106" s="11">
+        <v>70</v>
+      </c>
       <c r="G106" s="15">
         <v>35</v>
       </c>
@@ -4118,7 +4338,9 @@
       </c>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
+      <c r="F107" s="11">
+        <v>65</v>
+      </c>
       <c r="G107" s="15">
         <v>57</v>
       </c>
@@ -4138,7 +4360,9 @@
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
+      <c r="F108" s="11">
+        <v>59</v>
+      </c>
       <c r="G108" s="15">
         <v>67</v>
       </c>
@@ -4158,7 +4382,9 @@
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
+      <c r="F109" s="11">
+        <v>73</v>
+      </c>
       <c r="G109" s="15">
         <v>66</v>
       </c>
@@ -4178,7 +4404,9 @@
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
+      <c r="F110" s="11">
+        <v>66</v>
+      </c>
       <c r="G110" s="15">
         <v>45</v>
       </c>
@@ -4198,7 +4426,9 @@
       </c>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
+      <c r="F111" s="11">
+        <v>41</v>
+      </c>
       <c r="G111" s="15">
         <v>9</v>
       </c>
@@ -4218,7 +4448,9 @@
       </c>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
+      <c r="F112" s="11">
+        <v>62</v>
+      </c>
       <c r="G112" s="15">
         <v>72</v>
       </c>
@@ -4238,7 +4470,9 @@
       </c>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
+      <c r="F113" s="11">
+        <v>76</v>
+      </c>
       <c r="G113" s="15">
         <v>44</v>
       </c>
@@ -4258,7 +4492,9 @@
       </c>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
+      <c r="F114" s="11">
+        <v>66</v>
+      </c>
       <c r="G114" s="15">
         <v>56</v>
       </c>
@@ -4278,7 +4514,9 @@
       </c>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
+      <c r="F115" s="11">
+        <v>75</v>
+      </c>
       <c r="G115" s="15">
         <v>75</v>
       </c>
@@ -4298,7 +4536,9 @@
       </c>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
+      <c r="F116" s="11">
+        <v>55</v>
+      </c>
       <c r="G116" s="15">
         <v>56</v>
       </c>
@@ -4318,7 +4558,9 @@
       </c>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
+      <c r="F117" s="11">
+        <v>42</v>
+      </c>
       <c r="G117" s="15">
         <v>43</v>
       </c>
@@ -4338,7 +4580,9 @@
       </c>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
+      <c r="F118" s="11">
+        <v>66</v>
+      </c>
       <c r="G118" s="15">
         <v>60</v>
       </c>
@@ -4358,7 +4602,9 @@
       </c>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
+      <c r="F119" s="11">
+        <v>75</v>
+      </c>
       <c r="G119" s="15">
         <v>70</v>
       </c>
@@ -4378,7 +4624,9 @@
       </c>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
+      <c r="F120" s="11">
+        <v>25</v>
+      </c>
       <c r="G120" s="15">
         <v>63</v>
       </c>
@@ -4398,7 +4646,9 @@
       </c>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
+      <c r="F121" s="11">
+        <v>55</v>
+      </c>
       <c r="G121" s="15">
         <v>50</v>
       </c>
@@ -4418,7 +4668,9 @@
       </c>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
+      <c r="F122" s="11">
+        <v>54</v>
+      </c>
       <c r="G122" s="15">
         <v>72</v>
       </c>
@@ -4438,7 +4690,9 @@
       </c>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
+      <c r="F123" s="20" t="s">
+        <v>81</v>
+      </c>
       <c r="G123" s="15">
         <v>8</v>
       </c>
@@ -4458,7 +4712,9 @@
       </c>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
+      <c r="F124" s="11">
+        <v>67</v>
+      </c>
       <c r="G124" s="15">
         <v>70</v>
       </c>
@@ -4478,7 +4734,9 @@
       </c>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
+      <c r="F125" s="11">
+        <v>76</v>
+      </c>
       <c r="G125" s="15">
         <v>56</v>
       </c>
@@ -4498,7 +4756,9 @@
       </c>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
+      <c r="F126" s="11">
+        <v>70</v>
+      </c>
       <c r="G126" s="15">
         <v>67</v>
       </c>
@@ -4518,7 +4778,9 @@
       </c>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
-      <c r="F127" s="2"/>
+      <c r="F127" s="11">
+        <v>70</v>
+      </c>
       <c r="G127" s="15">
         <v>56</v>
       </c>
@@ -4538,7 +4800,9 @@
       </c>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
+      <c r="F128" s="11">
+        <v>48</v>
+      </c>
       <c r="G128" s="15">
         <v>52</v>
       </c>
@@ -4558,7 +4822,9 @@
       </c>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
-      <c r="F129" s="2"/>
+      <c r="F129" s="11">
+        <v>54</v>
+      </c>
       <c r="G129" s="15">
         <v>45</v>
       </c>
@@ -4578,7 +4844,9 @@
       </c>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
-      <c r="F130" s="2"/>
+      <c r="F130" s="11">
+        <v>63</v>
+      </c>
       <c r="G130" s="15">
         <v>42</v>
       </c>
@@ -4598,7 +4866,9 @@
       </c>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
-      <c r="F131" s="2"/>
+      <c r="F131" s="11">
+        <v>53</v>
+      </c>
       <c r="G131" s="15">
         <v>56</v>
       </c>
@@ -4618,7 +4888,9 @@
       </c>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
+      <c r="F132" s="11">
+        <v>73</v>
+      </c>
       <c r="G132" s="15">
         <v>79</v>
       </c>
@@ -4638,7 +4910,9 @@
       </c>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
-      <c r="F133" s="2"/>
+      <c r="F133" s="11">
+        <v>48</v>
+      </c>
       <c r="G133" s="15">
         <v>61</v>
       </c>
@@ -4658,7 +4932,9 @@
       </c>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
+      <c r="F134" s="11">
+        <v>70</v>
+      </c>
       <c r="G134" s="15">
         <v>66</v>
       </c>
@@ -4678,7 +4954,9 @@
       </c>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
-      <c r="F135" s="2"/>
+      <c r="F135" s="11">
+        <v>66</v>
+      </c>
       <c r="G135" s="15">
         <v>37</v>
       </c>
@@ -4698,7 +4976,9 @@
       </c>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
-      <c r="F136" s="2"/>
+      <c r="F136" s="11">
+        <v>46</v>
+      </c>
       <c r="G136" s="15">
         <v>50</v>
       </c>
@@ -4718,7 +4998,9 @@
       </c>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
-      <c r="F137" s="2"/>
+      <c r="F137" s="11">
+        <v>73</v>
+      </c>
       <c r="G137" s="15">
         <v>65</v>
       </c>
@@ -4738,7 +5020,9 @@
       </c>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
-      <c r="F138" s="2"/>
+      <c r="F138" s="11">
+        <v>57</v>
+      </c>
       <c r="G138" s="15">
         <v>56</v>
       </c>
@@ -4758,8 +5042,12 @@
       </c>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
-      <c r="F139" s="2"/>
-      <c r="G139" s="15"/>
+      <c r="F139" s="11">
+        <v>73</v>
+      </c>
+      <c r="G139" s="15">
+        <v>51</v>
+      </c>
       <c r="H139" s="19">
         <v>76.666666666666671</v>
       </c>
@@ -4776,7 +5064,9 @@
       </c>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
-      <c r="F140" s="2"/>
+      <c r="F140" s="11">
+        <v>70</v>
+      </c>
       <c r="G140" s="15">
         <v>63</v>
       </c>
@@ -4796,7 +5086,9 @@
       </c>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
-      <c r="F141" s="2"/>
+      <c r="F141" s="11">
+        <v>67</v>
+      </c>
       <c r="G141" s="15">
         <v>37</v>
       </c>
@@ -4816,7 +5108,9 @@
       </c>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
-      <c r="F142" s="2"/>
+      <c r="F142" s="11">
+        <v>57</v>
+      </c>
       <c r="G142" s="15">
         <v>53</v>
       </c>
@@ -4836,7 +5130,9 @@
       </c>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
-      <c r="F143" s="2"/>
+      <c r="F143" s="11">
+        <v>54</v>
+      </c>
       <c r="G143" s="15">
         <v>66</v>
       </c>
@@ -4856,7 +5152,9 @@
       </c>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
-      <c r="F144" s="2"/>
+      <c r="F144" s="11">
+        <v>41</v>
+      </c>
       <c r="G144" s="15">
         <v>80</v>
       </c>
@@ -4876,7 +5174,9 @@
       </c>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
-      <c r="F145" s="2"/>
+      <c r="F145" s="11">
+        <v>53</v>
+      </c>
       <c r="G145" s="15">
         <v>67</v>
       </c>
@@ -4896,7 +5196,9 @@
       </c>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
-      <c r="F146" s="2"/>
+      <c r="F146" s="11">
+        <v>63</v>
+      </c>
       <c r="G146" s="15">
         <v>70</v>
       </c>
@@ -4916,7 +5218,9 @@
       </c>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
-      <c r="F147" s="2"/>
+      <c r="F147" s="11">
+        <v>55</v>
+      </c>
       <c r="G147" s="15">
         <v>26</v>
       </c>
@@ -4936,7 +5240,9 @@
       </c>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
-      <c r="F148" s="2"/>
+      <c r="F148" s="11">
+        <v>71</v>
+      </c>
       <c r="G148" s="15">
         <v>38</v>
       </c>
@@ -4956,7 +5262,9 @@
       </c>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
-      <c r="F149" s="2"/>
+      <c r="F149" s="11">
+        <v>62</v>
+      </c>
       <c r="G149" s="15">
         <v>51</v>
       </c>
@@ -4976,7 +5284,9 @@
       </c>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
-      <c r="F150" s="2"/>
+      <c r="F150" s="11">
+        <v>46</v>
+      </c>
       <c r="G150" s="15">
         <v>58</v>
       </c>
@@ -4996,7 +5306,9 @@
       </c>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
-      <c r="F151" s="2"/>
+      <c r="F151" s="11">
+        <v>50</v>
+      </c>
       <c r="G151" s="15">
         <v>55</v>
       </c>
@@ -5016,7 +5328,9 @@
       </c>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
-      <c r="F152" s="2"/>
+      <c r="F152" s="11">
+        <v>73</v>
+      </c>
       <c r="G152" s="15">
         <v>41</v>
       </c>
@@ -5036,7 +5350,9 @@
       </c>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
-      <c r="F153" s="2"/>
+      <c r="F153" s="11">
+        <v>66</v>
+      </c>
       <c r="G153" s="15">
         <v>58</v>
       </c>
@@ -5056,7 +5372,9 @@
       </c>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
-      <c r="F154" s="2"/>
+      <c r="F154" s="11">
+        <v>43</v>
+      </c>
       <c r="G154" s="15">
         <v>72</v>
       </c>
@@ -5076,7 +5394,9 @@
       </c>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
-      <c r="F155" s="2"/>
+      <c r="F155" s="11">
+        <v>50</v>
+      </c>
       <c r="G155" s="15">
         <v>55</v>
       </c>
@@ -5096,7 +5416,9 @@
       </c>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
-      <c r="F156" s="2"/>
+      <c r="F156" s="11">
+        <v>59</v>
+      </c>
       <c r="G156" s="15">
         <v>90</v>
       </c>
@@ -5116,7 +5438,9 @@
       </c>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
-      <c r="F157" s="2"/>
+      <c r="F157" s="11">
+        <v>62</v>
+      </c>
       <c r="G157" s="15">
         <v>54</v>
       </c>
@@ -5136,7 +5460,9 @@
       </c>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
-      <c r="F158" s="2"/>
+      <c r="F158" s="11">
+        <v>54</v>
+      </c>
       <c r="G158" s="15">
         <v>55</v>
       </c>
@@ -5156,7 +5482,9 @@
       </c>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
-      <c r="F159" s="2"/>
+      <c r="F159" s="11">
+        <v>75</v>
+      </c>
       <c r="G159" s="15">
         <v>52</v>
       </c>
@@ -5176,7 +5504,9 @@
       </c>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
-      <c r="F160" s="2"/>
+      <c r="F160" s="11">
+        <v>39</v>
+      </c>
       <c r="G160" s="15">
         <v>56</v>
       </c>
@@ -5196,7 +5526,9 @@
       </c>
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
-      <c r="F161" s="2"/>
+      <c r="F161" s="11">
+        <v>25</v>
+      </c>
       <c r="G161" s="15">
         <v>45</v>
       </c>
@@ -5216,7 +5548,9 @@
       </c>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
-      <c r="F162" s="2"/>
+      <c r="F162" s="11">
+        <v>25</v>
+      </c>
       <c r="G162" s="15">
         <v>63</v>
       </c>
@@ -5236,7 +5570,9 @@
       </c>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
-      <c r="F163" s="2"/>
+      <c r="F163" s="11">
+        <v>65</v>
+      </c>
       <c r="G163" s="15">
         <v>46</v>
       </c>
@@ -5256,7 +5592,9 @@
       </c>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
-      <c r="F164" s="2"/>
+      <c r="F164" s="11">
+        <v>43</v>
+      </c>
       <c r="G164" s="15">
         <v>78</v>
       </c>
@@ -5276,7 +5614,9 @@
       </c>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
-      <c r="F165" s="2"/>
+      <c r="F165" s="11">
+        <v>78</v>
+      </c>
       <c r="G165" s="15">
         <v>50</v>
       </c>
@@ -5296,7 +5636,9 @@
       </c>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
-      <c r="F166" s="2"/>
+      <c r="F166" s="11">
+        <v>71</v>
+      </c>
       <c r="G166" s="15">
         <v>64</v>
       </c>
@@ -5316,7 +5658,9 @@
       </c>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
-      <c r="F167" s="2"/>
+      <c r="F167" s="11">
+        <v>78</v>
+      </c>
       <c r="G167" s="15">
         <v>78</v>
       </c>
@@ -5336,7 +5680,9 @@
       </c>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
-      <c r="F168" s="2"/>
+      <c r="F168" s="11">
+        <v>73</v>
+      </c>
       <c r="G168" s="15">
         <v>63</v>
       </c>
@@ -5356,7 +5702,9 @@
       </c>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
-      <c r="F169" s="2"/>
+      <c r="F169" s="11">
+        <v>41</v>
+      </c>
       <c r="G169" s="15">
         <v>79</v>
       </c>
@@ -5376,7 +5724,9 @@
       </c>
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
-      <c r="F170" s="2"/>
+      <c r="F170" s="11">
+        <v>47</v>
+      </c>
       <c r="G170" s="15">
         <v>38</v>
       </c>
@@ -5396,7 +5746,9 @@
       </c>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
-      <c r="F171" s="2"/>
+      <c r="F171" s="11">
+        <v>54</v>
+      </c>
       <c r="G171" s="15">
         <v>41</v>
       </c>
@@ -5416,7 +5768,9 @@
       </c>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
-      <c r="F172" s="2"/>
+      <c r="F172" s="11">
+        <v>43</v>
+      </c>
       <c r="G172" s="15">
         <v>30</v>
       </c>
@@ -5436,7 +5790,9 @@
       </c>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
+      <c r="F173" s="11">
+        <v>60</v>
+      </c>
       <c r="G173" s="15">
         <v>48</v>
       </c>
@@ -5456,7 +5812,9 @@
       </c>
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
-      <c r="F174" s="2"/>
+      <c r="F174" s="11">
+        <v>73</v>
+      </c>
       <c r="G174" s="15">
         <v>25</v>
       </c>
@@ -5476,7 +5834,9 @@
       </c>
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
-      <c r="F175" s="2"/>
+      <c r="F175" s="11">
+        <v>75</v>
+      </c>
       <c r="G175" s="15">
         <v>29</v>
       </c>
@@ -5496,7 +5856,9 @@
       </c>
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
-      <c r="F176" s="2"/>
+      <c r="F176" s="11">
+        <v>54</v>
+      </c>
       <c r="G176" s="15">
         <v>55</v>
       </c>
@@ -5516,7 +5878,9 @@
       </c>
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
-      <c r="F177" s="2"/>
+      <c r="F177" s="11">
+        <v>42</v>
+      </c>
       <c r="G177" s="15">
         <v>49</v>
       </c>
@@ -5536,7 +5900,9 @@
       </c>
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
-      <c r="F178" s="2"/>
+      <c r="F178" s="11">
+        <v>53</v>
+      </c>
       <c r="G178" s="15">
         <v>84</v>
       </c>
@@ -5556,7 +5922,9 @@
       </c>
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
-      <c r="F179" s="2"/>
+      <c r="F179" s="11">
+        <v>53</v>
+      </c>
       <c r="G179" s="15">
         <v>78</v>
       </c>
@@ -5576,7 +5944,9 @@
       </c>
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
-      <c r="F180" s="2"/>
+      <c r="F180" s="11">
+        <v>44</v>
+      </c>
       <c r="G180" s="15">
         <v>42</v>
       </c>
@@ -5596,7 +5966,9 @@
       </c>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
-      <c r="F181" s="2"/>
+      <c r="F181" s="11">
+        <v>39</v>
+      </c>
       <c r="G181" s="15">
         <v>58</v>
       </c>
@@ -5616,7 +5988,9 @@
       </c>
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
-      <c r="F182" s="2"/>
+      <c r="F182" s="11">
+        <v>39</v>
+      </c>
       <c r="G182" s="15">
         <v>34</v>
       </c>
@@ -5636,7 +6010,9 @@
       </c>
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
-      <c r="F183" s="2"/>
+      <c r="F183" s="11">
+        <v>55</v>
+      </c>
       <c r="G183" s="15">
         <v>49</v>
       </c>
@@ -5656,7 +6032,9 @@
       </c>
       <c r="D184" s="2"/>
       <c r="E184" s="2"/>
-      <c r="F184" s="2"/>
+      <c r="F184" s="11">
+        <v>39</v>
+      </c>
       <c r="G184" s="15">
         <v>67</v>
       </c>
@@ -5676,7 +6054,9 @@
       </c>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
-      <c r="F185" s="2"/>
+      <c r="F185" s="11">
+        <v>75</v>
+      </c>
       <c r="G185" s="15">
         <v>72</v>
       </c>
@@ -5696,7 +6076,9 @@
       </c>
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
-      <c r="F186" s="2"/>
+      <c r="F186" s="11">
+        <v>62</v>
+      </c>
       <c r="G186" s="15">
         <v>58</v>
       </c>
@@ -5716,7 +6098,9 @@
       </c>
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
-      <c r="F187" s="2"/>
+      <c r="F187" s="11">
+        <v>52</v>
+      </c>
       <c r="G187" s="15">
         <v>37</v>
       </c>
@@ -5736,7 +6120,9 @@
       </c>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
-      <c r="F188" s="2"/>
+      <c r="F188" s="11">
+        <v>73</v>
+      </c>
       <c r="G188" s="15">
         <v>42</v>
       </c>
@@ -5754,7 +6140,9 @@
       </c>
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
-      <c r="F189" s="2"/>
+      <c r="F189" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G189" s="15">
         <v>55</v>
       </c>
@@ -5772,7 +6160,9 @@
       </c>
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
-      <c r="F190" s="2"/>
+      <c r="F190" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G190" s="15" t="s">
         <v>81</v>
       </c>
@@ -5790,7 +6180,9 @@
       </c>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
-      <c r="F191" s="2"/>
+      <c r="F191" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G191" s="15">
         <v>57</v>
       </c>
@@ -5808,7 +6200,9 @@
       </c>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
-      <c r="F192" s="2"/>
+      <c r="F192" s="11">
+        <v>46</v>
+      </c>
       <c r="G192" s="15">
         <v>44</v>
       </c>
@@ -5826,7 +6220,9 @@
       </c>
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
-      <c r="F193" s="2"/>
+      <c r="F193" s="11">
+        <v>47</v>
+      </c>
       <c r="G193" s="15">
         <v>44</v>
       </c>
@@ -5844,7 +6240,9 @@
       </c>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
-      <c r="F194" s="2"/>
+      <c r="F194" s="11">
+        <v>67</v>
+      </c>
       <c r="G194" s="15">
         <v>61</v>
       </c>
@@ -5862,7 +6260,9 @@
       </c>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
-      <c r="F195" s="2"/>
+      <c r="F195" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G195" s="15">
         <v>76</v>
       </c>
@@ -5880,7 +6280,9 @@
       </c>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
-      <c r="F196" s="2"/>
+      <c r="F196" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G196" s="15">
         <v>56</v>
       </c>
@@ -5898,7 +6300,9 @@
       </c>
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
-      <c r="F197" s="2"/>
+      <c r="F197" s="11">
+        <v>73</v>
+      </c>
       <c r="G197" s="15">
         <v>73</v>
       </c>
@@ -5916,7 +6320,9 @@
       </c>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
-      <c r="F198" s="2"/>
+      <c r="F198" s="11">
+        <v>60</v>
+      </c>
       <c r="G198" s="15">
         <v>42</v>
       </c>
@@ -5934,7 +6340,9 @@
       </c>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
+      <c r="F199" s="11">
+        <v>47</v>
+      </c>
       <c r="G199" s="15">
         <v>45</v>
       </c>
@@ -5952,7 +6360,9 @@
       </c>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
-      <c r="F200" s="2"/>
+      <c r="F200" s="11">
+        <v>43</v>
+      </c>
       <c r="G200" s="15">
         <v>57</v>
       </c>
@@ -5970,7 +6380,9 @@
       </c>
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
-      <c r="F201" s="2"/>
+      <c r="F201" s="11">
+        <v>47</v>
+      </c>
       <c r="G201" s="15">
         <v>37</v>
       </c>
@@ -5988,7 +6400,9 @@
       </c>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
-      <c r="F202" s="2"/>
+      <c r="F202" s="11">
+        <v>73</v>
+      </c>
       <c r="G202" s="15">
         <v>73</v>
       </c>
@@ -6006,7 +6420,9 @@
       </c>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
-      <c r="F203" s="2"/>
+      <c r="F203" s="11">
+        <v>60</v>
+      </c>
       <c r="G203" s="15">
         <v>51</v>
       </c>
@@ -6024,7 +6440,9 @@
       </c>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
+      <c r="F204" s="11">
+        <v>73</v>
+      </c>
       <c r="G204" s="15">
         <v>55</v>
       </c>
@@ -6042,7 +6460,9 @@
       </c>
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
+      <c r="F205" s="20" t="s">
+        <v>81</v>
+      </c>
       <c r="G205" s="15">
         <v>36</v>
       </c>
@@ -6060,7 +6480,9 @@
       </c>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
-      <c r="F206" s="2"/>
+      <c r="F206" s="11">
+        <v>60</v>
+      </c>
       <c r="G206" s="15">
         <v>42</v>
       </c>
@@ -6078,7 +6500,9 @@
       </c>
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
-      <c r="F207" s="2"/>
+      <c r="F207" s="20" t="s">
+        <v>81</v>
+      </c>
       <c r="G207" s="15">
         <v>49</v>
       </c>
@@ -6096,7 +6520,9 @@
       </c>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
-      <c r="F208" s="2"/>
+      <c r="F208" s="11">
+        <v>50</v>
+      </c>
       <c r="G208" s="15">
         <v>16</v>
       </c>
@@ -6114,7 +6540,9 @@
       </c>
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
-      <c r="F209" s="2"/>
+      <c r="F209" s="20" t="s">
+        <v>81</v>
+      </c>
       <c r="G209" s="15">
         <v>42</v>
       </c>
@@ -6132,7 +6560,9 @@
       </c>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
-      <c r="F210" s="2"/>
+      <c r="F210" s="11">
+        <v>60</v>
+      </c>
       <c r="G210" s="15">
         <v>43</v>
       </c>
@@ -6150,7 +6580,9 @@
       </c>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
-      <c r="F211" s="2"/>
+      <c r="F211" s="11">
+        <v>60</v>
+      </c>
       <c r="G211" s="15">
         <v>56</v>
       </c>
@@ -6168,7 +6600,9 @@
       </c>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
-      <c r="F212" s="2"/>
+      <c r="F212" s="11">
+        <v>73</v>
+      </c>
       <c r="G212" s="15">
         <v>45</v>
       </c>
@@ -6186,7 +6620,9 @@
       </c>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
-      <c r="F213" s="2"/>
+      <c r="F213" s="11">
+        <v>60</v>
+      </c>
       <c r="G213" s="15">
         <v>55</v>
       </c>
@@ -6204,7 +6640,9 @@
       </c>
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
-      <c r="F214" s="2"/>
+      <c r="F214" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G214" s="15" t="s">
         <v>81</v>
       </c>
@@ -6222,7 +6660,9 @@
       </c>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
-      <c r="F215" s="2"/>
+      <c r="F215" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G215" s="15">
         <v>28</v>
       </c>
@@ -6240,7 +6680,9 @@
       </c>
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
-      <c r="F216" s="2"/>
+      <c r="F216" s="11">
+        <v>60</v>
+      </c>
       <c r="G216" s="15">
         <v>48</v>
       </c>
@@ -6258,7 +6700,9 @@
       </c>
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
-      <c r="F217" s="2"/>
+      <c r="F217" s="11">
+        <v>67</v>
+      </c>
       <c r="G217" s="15">
         <v>58</v>
       </c>
@@ -6276,7 +6720,9 @@
       </c>
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
-      <c r="F218" s="2"/>
+      <c r="F218" s="11">
+        <v>60</v>
+      </c>
       <c r="G218" s="15">
         <v>67</v>
       </c>
@@ -6294,7 +6740,9 @@
       </c>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
-      <c r="F219" s="2"/>
+      <c r="F219" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G219" s="15">
         <v>59</v>
       </c>
@@ -6312,7 +6760,9 @@
       </c>
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
+      <c r="F220" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G220" s="15" t="s">
         <v>81</v>
       </c>
@@ -6330,7 +6780,9 @@
       </c>
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
+      <c r="F221" s="11">
+        <v>60</v>
+      </c>
       <c r="G221" s="15">
         <v>41</v>
       </c>
@@ -6348,7 +6800,9 @@
       </c>
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
+      <c r="F222" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G222" s="15">
         <v>38</v>
       </c>
@@ -6366,7 +6820,9 @@
       </c>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
+      <c r="F223" s="11">
+        <v>81</v>
+      </c>
       <c r="G223" s="15">
         <v>39</v>
       </c>
@@ -6384,7 +6840,9 @@
       </c>
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
-      <c r="F224" s="2"/>
+      <c r="F224" s="11">
+        <v>81</v>
+      </c>
       <c r="G224" s="15">
         <v>68</v>
       </c>
@@ -6402,7 +6860,9 @@
       </c>
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
-      <c r="F225" s="2"/>
+      <c r="F225" s="11">
+        <v>81</v>
+      </c>
       <c r="G225" s="15">
         <v>57</v>
       </c>
@@ -6420,7 +6880,9 @@
       </c>
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
-      <c r="F226" s="2"/>
+      <c r="F226" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G226" s="15" t="s">
         <v>81</v>
       </c>
@@ -6438,7 +6900,9 @@
       </c>
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
-      <c r="F227" s="2"/>
+      <c r="F227" s="11">
+        <v>81</v>
+      </c>
       <c r="G227" s="15">
         <v>23</v>
       </c>
@@ -6456,7 +6920,9 @@
       </c>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
-      <c r="F228" s="2"/>
+      <c r="F228" s="11">
+        <v>81</v>
+      </c>
       <c r="G228" s="15">
         <v>55</v>
       </c>
@@ -6474,7 +6940,9 @@
       </c>
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
-      <c r="F229" s="2"/>
+      <c r="F229" s="11">
+        <v>67</v>
+      </c>
       <c r="G229" s="15">
         <v>50</v>
       </c>
@@ -6492,7 +6960,9 @@
       </c>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
-      <c r="F230" s="2"/>
+      <c r="F230" s="11">
+        <v>67</v>
+      </c>
       <c r="G230" s="15">
         <v>50</v>
       </c>
@@ -6510,7 +6980,9 @@
       </c>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
+      <c r="F231" s="11">
+        <v>81</v>
+      </c>
       <c r="G231" s="15">
         <v>44</v>
       </c>
@@ -6528,7 +7000,9 @@
       </c>
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
+      <c r="F232" s="11">
+        <v>67</v>
+      </c>
       <c r="G232" s="15">
         <v>55</v>
       </c>
@@ -6546,7 +7020,9 @@
       </c>
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
-      <c r="F233" s="2"/>
+      <c r="F233" s="11">
+        <v>47</v>
+      </c>
       <c r="G233" s="15">
         <v>56</v>
       </c>
@@ -6564,7 +7040,9 @@
       </c>
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
+      <c r="F234" s="11">
+        <v>47</v>
+      </c>
       <c r="G234" s="15">
         <v>53</v>
       </c>
@@ -6582,7 +7060,9 @@
       </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
+      <c r="F235" s="11">
+        <v>60</v>
+      </c>
       <c r="G235" s="15">
         <v>57</v>
       </c>
@@ -6600,7 +7080,9 @@
       </c>
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
-      <c r="F236" s="2"/>
+      <c r="F236" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G236" s="15">
         <v>52</v>
       </c>
@@ -6618,7 +7100,9 @@
       </c>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
-      <c r="F237" s="2"/>
+      <c r="F237" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="G237" s="15">
         <v>25</v>
       </c>
@@ -6636,7 +7120,9 @@
       </c>
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
+      <c r="F238" s="11">
+        <v>43</v>
+      </c>
       <c r="G238" s="15">
         <v>7</v>
       </c>
@@ -6654,7 +7140,9 @@
       </c>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
+      <c r="F239" s="11">
+        <v>73</v>
+      </c>
       <c r="G239" s="15">
         <v>37</v>
       </c>
@@ -6672,7 +7160,9 @@
       </c>
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
-      <c r="F240" s="2"/>
+      <c r="F240" s="5" t="s">
+        <v>81</v>
+      </c>
       <c r="G240" s="15">
         <v>39</v>
       </c>
@@ -6739,15 +7229,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C7DC5809443B914698F205EDCFE14C5C" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="910dd8289e79bf7e3b2db69aaa037196">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2592cbe8-961e-4422-8c47-4737933d0fe0" xmlns:ns3="7af58a8f-2f6f-405a-b238-befdc3c227d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecb9083a17ae33be0a7009b46db9eab7" ns2:_="" ns3:_="">
     <xsd:import namespace="2592cbe8-961e-4422-8c47-4737933d0fe0"/>
@@ -6924,6 +7405,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -6931,14 +7421,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70AE5412-3087-4F96-A882-A7717BC45E52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6957,6 +7439,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
   <ds:schemaRefs>

--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B27609-1788-4300-89B8-11872D29677F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE79A12-1207-44FF-B00D-5201A1D2CBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
@@ -5090,7 +5090,7 @@
         <v>67</v>
       </c>
       <c r="G141" s="15">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H141" s="19">
         <v>66.666666666666657</v>
@@ -7229,6 +7229,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C7DC5809443B914698F205EDCFE14C5C" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="910dd8289e79bf7e3b2db69aaa037196">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2592cbe8-961e-4422-8c47-4737933d0fe0" xmlns:ns3="7af58a8f-2f6f-405a-b238-befdc3c227d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecb9083a17ae33be0a7009b46db9eab7" ns2:_="" ns3:_="">
     <xsd:import namespace="2592cbe8-961e-4422-8c47-4737933d0fe0"/>
@@ -7405,22 +7420,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70AE5412-3087-4F96-A882-A7717BC45E52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7437,21 +7454,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE79A12-1207-44FF-B00D-5201A1D2CBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395391AC-196F-46E6-8F58-D36D62694251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="487">
   <si>
     <t>Name</t>
   </si>
@@ -1609,12 +1609,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1981,5246 +1978,6202 @@
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="12" customWidth="1"/>
     <col min="4" max="4" width="9.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="14" customWidth="1"/>
+    <col min="8" max="8" width="16" style="13" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>481</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>482</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>484</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>79.5</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="11">
+      <c r="D2" s="14">
+        <v>9</v>
+      </c>
+      <c r="E2" s="14">
+        <v>62</v>
+      </c>
+      <c r="F2" s="10">
         <v>73</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="14">
         <v>38</v>
       </c>
-      <c r="H2" s="19">
+      <c r="H2" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>100</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="11">
+      <c r="D3" s="14">
+        <v>82</v>
+      </c>
+      <c r="E3" s="14">
+        <v>85</v>
+      </c>
+      <c r="F3" s="10">
         <v>75</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="14">
         <v>87</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>88</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="11">
+      <c r="D4" s="14">
+        <v>38</v>
+      </c>
+      <c r="E4" s="14">
+        <v>76</v>
+      </c>
+      <c r="F4" s="10">
         <v>54</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="14">
         <v>75</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>58</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="11">
+      <c r="D5" s="14">
+        <v>41</v>
+      </c>
+      <c r="E5" s="14">
+        <v>65</v>
+      </c>
+      <c r="F5" s="10">
         <v>60</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="14">
         <v>46</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="18">
         <v>26.666666666666668</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>92</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="11">
+      <c r="D6" s="14">
+        <v>41</v>
+      </c>
+      <c r="E6" s="14">
+        <v>66</v>
+      </c>
+      <c r="F6" s="10">
         <v>60</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="14">
         <v>40</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>43.333333333333336</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>82.5</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="11">
+      <c r="D7" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="14">
+        <v>66</v>
+      </c>
+      <c r="F7" s="10">
         <v>65</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="14">
         <v>64</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>68</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="11">
+      <c r="D8" s="14">
+        <v>83</v>
+      </c>
+      <c r="E8" s="14">
+        <v>89</v>
+      </c>
+      <c r="F8" s="10">
         <v>42</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="14">
         <v>77</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>83</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="11">
+      <c r="D9" s="14">
+        <v>40</v>
+      </c>
+      <c r="E9" s="14">
+        <v>77</v>
+      </c>
+      <c r="F9" s="10">
         <v>55</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="14">
         <v>46</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <v>67.5</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="11">
+      <c r="D10" s="14">
+        <v>27</v>
+      </c>
+      <c r="E10" s="14">
+        <v>71</v>
+      </c>
+      <c r="F10" s="10">
         <v>39</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="14">
         <v>48</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>28</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="11">
+      <c r="D11" s="14">
+        <v>26</v>
+      </c>
+      <c r="E11" s="14">
+        <v>43</v>
+      </c>
+      <c r="F11" s="10">
         <v>25</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="14">
         <v>34</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <v>82</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="11">
+      <c r="D12" s="14">
+        <v>48</v>
+      </c>
+      <c r="E12" s="14">
+        <v>94</v>
+      </c>
+      <c r="F12" s="10">
         <v>65</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="14">
         <v>35</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>80</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="11">
+      <c r="D13" s="14">
+        <v>50</v>
+      </c>
+      <c r="E13" s="14">
+        <v>71</v>
+      </c>
+      <c r="F13" s="10">
         <v>42</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="14">
         <v>40</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <v>98</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="11">
+      <c r="D14" s="14">
+        <v>56</v>
+      </c>
+      <c r="E14" s="14">
+        <v>95</v>
+      </c>
+      <c r="F14" s="10">
         <v>54</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="14">
         <v>86</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>68.5</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="11">
+      <c r="D15" s="14">
+        <v>63</v>
+      </c>
+      <c r="E15" s="14">
+        <v>69</v>
+      </c>
+      <c r="F15" s="10">
         <v>62</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="14">
         <v>61</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <v>77</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="11">
+      <c r="D16" s="14">
+        <v>79</v>
+      </c>
+      <c r="E16" s="14">
+        <v>98</v>
+      </c>
+      <c r="F16" s="10">
         <v>66</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <v>57</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <v>86.5</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="11">
+      <c r="D17" s="14">
+        <v>47</v>
+      </c>
+      <c r="E17" s="14">
+        <v>78</v>
+      </c>
+      <c r="F17" s="10">
         <v>70</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="14">
         <v>79</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <v>92</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="11">
+      <c r="D18" s="14">
+        <v>50</v>
+      </c>
+      <c r="E18" s="14">
+        <v>85</v>
+      </c>
+      <c r="F18" s="10">
         <v>44</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="14">
         <v>71</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="18">
         <v>46.666666666666664</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>98</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="11">
+      <c r="D19" s="14">
+        <v>77</v>
+      </c>
+      <c r="E19" s="14">
+        <v>87</v>
+      </c>
+      <c r="F19" s="10">
         <v>47</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="14">
         <v>91</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="10">
         <v>86</v>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="11">
+      <c r="D20" s="14">
+        <v>50</v>
+      </c>
+      <c r="E20" s="14">
+        <v>64</v>
+      </c>
+      <c r="F20" s="10">
         <v>75</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="14">
         <v>71</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <v>95</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="11">
+      <c r="D21" s="14">
+        <v>87</v>
+      </c>
+      <c r="E21" s="14">
+        <v>86</v>
+      </c>
+      <c r="F21" s="10">
         <v>75</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="14">
         <v>97</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <v>63</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="11">
+      <c r="D22" s="14">
+        <v>35</v>
+      </c>
+      <c r="E22" s="14">
+        <v>61</v>
+      </c>
+      <c r="F22" s="10">
         <v>75</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="14">
         <v>53</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>96</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="11">
+      <c r="D23" s="14">
+        <v>50</v>
+      </c>
+      <c r="E23" s="14">
+        <v>81</v>
+      </c>
+      <c r="F23" s="10">
         <v>66</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="14">
         <v>73</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <v>64</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="11">
+      <c r="D24" s="14">
+        <v>22</v>
+      </c>
+      <c r="E24" s="14">
+        <v>78</v>
+      </c>
+      <c r="F24" s="10">
         <v>66</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="14">
         <v>33</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>77.5</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="11">
+      <c r="D25" s="14">
+        <v>56</v>
+      </c>
+      <c r="E25" s="14">
+        <v>97</v>
+      </c>
+      <c r="F25" s="10">
         <v>63</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="14">
         <v>82</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <v>89</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="11">
+      <c r="D26" s="14">
         <v>55</v>
       </c>
-      <c r="G26" s="15">
+      <c r="E26" s="14">
+        <v>71</v>
+      </c>
+      <c r="F26" s="10">
+        <v>55</v>
+      </c>
+      <c r="G26" s="14">
         <v>45</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <v>85</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="11">
+      <c r="D27" s="14">
+        <v>56</v>
+      </c>
+      <c r="E27" s="14">
+        <v>82</v>
+      </c>
+      <c r="F27" s="10">
         <v>75</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="14">
         <v>51</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="10">
         <v>72</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="11">
+      <c r="D28" s="14">
+        <v>40</v>
+      </c>
+      <c r="E28" s="14">
+        <v>52</v>
+      </c>
+      <c r="F28" s="10">
         <v>66</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="14">
         <v>54</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="10">
         <v>94</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="11">
+      <c r="D29" s="14">
+        <v>62</v>
+      </c>
+      <c r="E29" s="14">
+        <v>89</v>
+      </c>
+      <c r="F29" s="10">
         <v>55</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="14">
         <v>80</v>
       </c>
-      <c r="H29" s="19">
+      <c r="H29" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="10">
         <v>99</v>
       </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="11">
+      <c r="D30" s="14">
+        <v>56</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="10">
         <v>78</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="14">
         <v>74</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="10">
         <v>77.5</v>
       </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="11">
+      <c r="D31" s="14">
+        <v>52</v>
+      </c>
+      <c r="E31" s="14">
+        <v>69</v>
+      </c>
+      <c r="F31" s="10">
         <v>65</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="14">
         <v>38</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="18">
         <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="10">
         <v>79</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="11">
+      <c r="D32" s="14">
+        <v>51</v>
+      </c>
+      <c r="E32" s="14">
+        <v>47</v>
+      </c>
+      <c r="F32" s="10">
         <v>73</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="14">
         <v>68</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <v>68</v>
       </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="11">
+      <c r="D33" s="14">
+        <v>63</v>
+      </c>
+      <c r="E33" s="14">
+        <v>81</v>
+      </c>
+      <c r="F33" s="10">
         <v>41</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="14">
         <v>74</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="10">
         <v>69.5</v>
       </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="11">
+      <c r="D34" s="14">
+        <v>52</v>
+      </c>
+      <c r="E34" s="14">
         <v>76</v>
       </c>
-      <c r="G34" s="15">
+      <c r="F34" s="10">
+        <v>76</v>
+      </c>
+      <c r="G34" s="14">
         <v>80</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <v>85</v>
       </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="11">
+      <c r="D35" s="14">
+        <v>20</v>
+      </c>
+      <c r="E35" s="14">
+        <v>75</v>
+      </c>
+      <c r="F35" s="10">
         <v>73</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="14">
         <v>66</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="10">
         <v>60</v>
       </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="11">
+      <c r="D36" s="14">
+        <v>40</v>
+      </c>
+      <c r="E36" s="14">
+        <v>64</v>
+      </c>
+      <c r="F36" s="10">
         <v>59</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="14">
         <v>39</v>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>40.5</v>
       </c>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="11">
+      <c r="D37" s="14">
+        <v>26</v>
+      </c>
+      <c r="E37" s="14">
+        <v>59</v>
+      </c>
+      <c r="F37" s="10">
         <v>78</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="14">
         <v>53</v>
       </c>
-      <c r="H37" s="19">
+      <c r="H37" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="10">
         <v>92</v>
       </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="11">
+      <c r="D38" s="14">
+        <v>45</v>
+      </c>
+      <c r="E38" s="14">
+        <v>93</v>
+      </c>
+      <c r="F38" s="10">
         <v>75</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="14">
         <v>66</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="10">
         <v>88</v>
       </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="11">
+      <c r="D39" s="14">
+        <v>37</v>
+      </c>
+      <c r="E39" s="14">
+        <v>69</v>
+      </c>
+      <c r="F39" s="10">
         <v>41</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>69</v>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="10">
         <v>85</v>
       </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="11">
+      <c r="D40" s="14">
+        <v>39</v>
+      </c>
+      <c r="E40" s="14">
+        <v>49</v>
+      </c>
+      <c r="F40" s="10">
         <v>71</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>54</v>
       </c>
-      <c r="H40" s="19">
+      <c r="H40" s="18">
         <v>46.666666666666664</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="11">
+      <c r="C41" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="14">
+        <v>29</v>
+      </c>
+      <c r="E41" s="14">
+        <v>57</v>
+      </c>
+      <c r="F41" s="10">
         <v>62</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>34</v>
       </c>
-      <c r="H41" s="19">
+      <c r="H41" s="18">
         <v>56.666666666666664</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="10">
         <v>69</v>
       </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="11">
+      <c r="D42" s="14">
+        <v>21</v>
+      </c>
+      <c r="E42" s="14">
+        <v>73</v>
+      </c>
+      <c r="F42" s="10">
         <v>65</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>46</v>
       </c>
-      <c r="H42" s="19">
+      <c r="H42" s="18">
         <v>13.333333333333334</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="10">
         <v>87.5</v>
       </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="11">
+      <c r="D43" s="14">
+        <v>74</v>
+      </c>
+      <c r="E43" s="14">
+        <v>71</v>
+      </c>
+      <c r="F43" s="10">
         <v>65</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>73</v>
       </c>
-      <c r="H43" s="19">
+      <c r="H43" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="10">
         <v>48</v>
       </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="11">
+      <c r="D44" s="14">
+        <v>48</v>
+      </c>
+      <c r="E44" s="14">
+        <v>97</v>
+      </c>
+      <c r="F44" s="10">
         <v>57</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>38</v>
       </c>
-      <c r="H44" s="19">
+      <c r="H44" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="10">
         <v>87</v>
       </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="11">
+      <c r="D45" s="14">
+        <v>66</v>
+      </c>
+      <c r="E45" s="14">
+        <v>59</v>
+      </c>
+      <c r="F45" s="10">
         <v>65</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>56</v>
       </c>
-      <c r="H45" s="19">
+      <c r="H45" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="10">
         <v>85</v>
       </c>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="11">
+      <c r="D46" s="14">
+        <v>47</v>
+      </c>
+      <c r="E46" s="14">
+        <v>73</v>
+      </c>
+      <c r="F46" s="10">
         <v>46</v>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="14">
         <v>36</v>
       </c>
-      <c r="H46" s="19">
+      <c r="H46" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="10">
         <v>91.5</v>
       </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="11">
+      <c r="D47" s="14">
+        <v>7</v>
+      </c>
+      <c r="E47" s="14">
+        <v>89</v>
+      </c>
+      <c r="F47" s="10">
         <v>44</v>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="14">
         <v>51</v>
       </c>
-      <c r="H47" s="19">
+      <c r="H47" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="10">
         <v>51</v>
       </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="11">
+      <c r="D48" s="14">
+        <v>50</v>
+      </c>
+      <c r="E48" s="14">
+        <v>89</v>
+      </c>
+      <c r="F48" s="10">
         <v>47</v>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="14">
         <v>55</v>
       </c>
-      <c r="H48" s="19">
+      <c r="H48" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="10">
         <v>88</v>
       </c>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="11">
+      <c r="D49" s="14">
+        <v>37</v>
+      </c>
+      <c r="E49" s="14">
+        <v>73</v>
+      </c>
+      <c r="F49" s="10">
         <v>78</v>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="14">
         <v>61</v>
       </c>
-      <c r="H49" s="19">
+      <c r="H49" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="10">
         <v>89</v>
       </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="11">
+      <c r="D50" s="14">
+        <v>60</v>
+      </c>
+      <c r="E50" s="14">
+        <v>94</v>
+      </c>
+      <c r="F50" s="10">
         <v>42</v>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="14">
         <v>40</v>
       </c>
-      <c r="H50" s="19">
+      <c r="H50" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="10">
         <v>88</v>
       </c>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="11">
+      <c r="D51" s="14">
+        <v>60</v>
+      </c>
+      <c r="E51" s="14">
+        <v>78</v>
+      </c>
+      <c r="F51" s="10">
         <v>63</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="14">
         <v>56</v>
       </c>
-      <c r="H51" s="19">
+      <c r="H51" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="10">
         <v>72</v>
       </c>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="11">
+      <c r="D52" s="14">
+        <v>40</v>
+      </c>
+      <c r="E52" s="14">
+        <v>71</v>
+      </c>
+      <c r="F52" s="10">
         <v>73</v>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="14">
         <v>56</v>
       </c>
-      <c r="H52" s="19">
+      <c r="H52" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="10">
         <v>81.5</v>
       </c>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="11">
+      <c r="D53" s="14">
+        <v>10</v>
+      </c>
+      <c r="E53" s="14">
+        <v>61</v>
+      </c>
+      <c r="F53" s="10">
         <v>48</v>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="14">
         <v>57</v>
       </c>
-      <c r="H53" s="19">
+      <c r="H53" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="10">
         <v>82</v>
       </c>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="11">
+      <c r="D54" s="14">
+        <v>61</v>
+      </c>
+      <c r="E54" s="14">
+        <v>96</v>
+      </c>
+      <c r="F54" s="10">
         <v>57</v>
       </c>
-      <c r="G54" s="15">
+      <c r="G54" s="14">
         <v>55</v>
       </c>
-      <c r="H54" s="19">
+      <c r="H54" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="10">
         <v>85</v>
       </c>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="11">
+      <c r="D55" s="14">
+        <v>76</v>
+      </c>
+      <c r="E55" s="14">
+        <v>91</v>
+      </c>
+      <c r="F55" s="10">
         <v>70</v>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="14">
         <v>70</v>
       </c>
-      <c r="H55" s="19">
+      <c r="H55" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="10">
         <v>91</v>
       </c>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="11">
+      <c r="D56" s="14">
+        <v>30</v>
+      </c>
+      <c r="E56" s="14">
+        <v>85</v>
+      </c>
+      <c r="F56" s="10">
         <v>53</v>
       </c>
-      <c r="G56" s="15">
+      <c r="G56" s="14">
         <v>44</v>
       </c>
-      <c r="H56" s="19">
+      <c r="H56" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="10">
         <v>42.5</v>
       </c>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="11">
+      <c r="D57" s="14">
+        <v>48</v>
+      </c>
+      <c r="E57" s="14">
+        <v>86</v>
+      </c>
+      <c r="F57" s="10">
         <v>67</v>
       </c>
-      <c r="G57" s="15">
+      <c r="G57" s="14">
         <v>54</v>
       </c>
-      <c r="H57" s="19">
+      <c r="H57" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="10">
         <v>46.5</v>
       </c>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="11">
+      <c r="D58" s="14">
+        <v>42</v>
+      </c>
+      <c r="E58" s="14">
+        <v>86</v>
+      </c>
+      <c r="F58" s="10">
         <v>73</v>
       </c>
-      <c r="G58" s="15">
+      <c r="G58" s="14">
         <v>32</v>
       </c>
-      <c r="H58" s="19">
+      <c r="H58" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="10">
         <v>72.5</v>
       </c>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="11">
+      <c r="D59" s="14">
+        <v>29</v>
+      </c>
+      <c r="E59" s="14">
+        <v>90</v>
+      </c>
+      <c r="F59" s="10">
         <v>66</v>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="14">
         <v>39</v>
       </c>
-      <c r="H59" s="19">
+      <c r="H59" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C60" s="10">
         <v>54</v>
       </c>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="11">
+      <c r="D60" s="14">
+        <v>61</v>
+      </c>
+      <c r="E60" s="14">
+        <v>79</v>
+      </c>
+      <c r="F60" s="10">
         <v>65</v>
       </c>
-      <c r="G60" s="15">
+      <c r="G60" s="14">
         <v>52</v>
       </c>
-      <c r="H60" s="19">
+      <c r="H60" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="10">
         <v>88</v>
       </c>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="11">
+      <c r="D61" s="14">
+        <v>58</v>
+      </c>
+      <c r="E61" s="14">
+        <v>77</v>
+      </c>
+      <c r="F61" s="10">
         <v>76</v>
       </c>
-      <c r="G61" s="15">
+      <c r="G61" s="14">
         <v>82</v>
       </c>
-      <c r="H61" s="19">
+      <c r="H61" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C62" s="11">
+      <c r="C62" s="10">
         <v>86.5</v>
       </c>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="11">
+      <c r="D62" s="14">
+        <v>47</v>
+      </c>
+      <c r="E62" s="14">
+        <v>79</v>
+      </c>
+      <c r="F62" s="10">
         <v>55</v>
       </c>
-      <c r="G62" s="15">
+      <c r="G62" s="14">
         <v>68</v>
       </c>
-      <c r="H62" s="19">
+      <c r="H62" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="10">
         <v>93</v>
       </c>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="11">
+      <c r="D63" s="14">
+        <v>37</v>
+      </c>
+      <c r="E63" s="14">
+        <v>91</v>
+      </c>
+      <c r="F63" s="10">
         <v>70</v>
       </c>
-      <c r="G63" s="15">
+      <c r="G63" s="14">
         <v>79</v>
       </c>
-      <c r="H63" s="19">
+      <c r="H63" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C64" s="10">
         <v>80.5</v>
       </c>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="11">
+      <c r="D64" s="14">
+        <v>84</v>
+      </c>
+      <c r="E64" s="14">
+        <v>69</v>
+      </c>
+      <c r="F64" s="10">
         <v>48</v>
       </c>
-      <c r="G64" s="15">
+      <c r="G64" s="14">
         <v>52</v>
       </c>
-      <c r="H64" s="19">
+      <c r="H64" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="10">
         <v>83.5</v>
       </c>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="11">
+      <c r="D65" s="14">
+        <v>56</v>
+      </c>
+      <c r="E65" s="14">
+        <v>58</v>
+      </c>
+      <c r="F65" s="10">
         <v>55</v>
       </c>
-      <c r="G65" s="15">
+      <c r="G65" s="14">
         <v>67</v>
       </c>
-      <c r="H65" s="19">
+      <c r="H65" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C66" s="10">
         <v>87</v>
       </c>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="11">
+      <c r="D66" s="14">
+        <v>46</v>
+      </c>
+      <c r="E66" s="14">
+        <v>81</v>
+      </c>
+      <c r="F66" s="10">
         <v>63</v>
       </c>
-      <c r="G66" s="15">
+      <c r="G66" s="14">
         <v>68</v>
       </c>
-      <c r="H66" s="19">
+      <c r="H66" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="10">
         <v>62</v>
       </c>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="11">
+      <c r="D67" s="14">
+        <v>34</v>
+      </c>
+      <c r="E67" s="14">
+        <v>58</v>
+      </c>
+      <c r="F67" s="10">
         <v>47</v>
       </c>
-      <c r="G67" s="15">
+      <c r="G67" s="14">
         <v>49</v>
       </c>
-      <c r="H67" s="19">
+      <c r="H67" s="18">
         <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="10">
         <v>61.5</v>
       </c>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="11">
+      <c r="D68" s="14">
+        <v>37</v>
+      </c>
+      <c r="E68" s="14">
+        <v>68</v>
+      </c>
+      <c r="F68" s="10">
         <v>47</v>
       </c>
-      <c r="G68" s="15">
+      <c r="G68" s="14">
         <v>59</v>
       </c>
-      <c r="H68" s="19">
+      <c r="H68" s="18">
         <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="10">
         <v>87.5</v>
       </c>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="11">
+      <c r="D69" s="14">
+        <v>32</v>
+      </c>
+      <c r="E69" s="14">
+        <v>74</v>
+      </c>
+      <c r="F69" s="10">
         <v>48</v>
       </c>
-      <c r="G69" s="15">
+      <c r="G69" s="14">
         <v>42</v>
       </c>
-      <c r="H69" s="19">
+      <c r="H69" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="10">
         <v>74</v>
       </c>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="11">
+      <c r="D70" s="14">
+        <v>37</v>
+      </c>
+      <c r="E70" s="14">
+        <v>52</v>
+      </c>
+      <c r="F70" s="10">
         <v>71</v>
       </c>
-      <c r="G70" s="15">
+      <c r="G70" s="14">
         <v>40</v>
       </c>
-      <c r="H70" s="19">
+      <c r="H70" s="18">
         <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="10">
         <v>86</v>
       </c>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="11">
+      <c r="D71" s="14">
+        <v>48</v>
+      </c>
+      <c r="E71" s="14">
+        <v>62</v>
+      </c>
+      <c r="F71" s="10">
         <v>44</v>
       </c>
-      <c r="G71" s="15">
+      <c r="G71" s="14">
         <v>50</v>
       </c>
-      <c r="H71" s="19">
+      <c r="H71" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C72" s="11">
+      <c r="C72" s="10">
         <v>83.5</v>
       </c>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="11">
+      <c r="D72" s="14">
+        <v>53</v>
+      </c>
+      <c r="E72" s="14">
+        <v>85</v>
+      </c>
+      <c r="F72" s="10">
         <v>54</v>
       </c>
-      <c r="G72" s="15">
+      <c r="G72" s="14">
         <v>55</v>
       </c>
-      <c r="H72" s="19">
+      <c r="H72" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="10">
         <v>98</v>
       </c>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="11">
+      <c r="D73" s="14">
+        <v>72</v>
+      </c>
+      <c r="E73" s="14">
+        <v>83</v>
+      </c>
+      <c r="F73" s="10">
         <v>59</v>
       </c>
-      <c r="G73" s="15">
+      <c r="G73" s="14">
         <v>60</v>
       </c>
-      <c r="H73" s="19">
+      <c r="H73" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C74" s="11">
+      <c r="C74" s="10">
         <v>66.5</v>
       </c>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="11">
+      <c r="D74" s="14">
+        <v>30</v>
+      </c>
+      <c r="E74" s="14">
+        <v>42</v>
+      </c>
+      <c r="F74" s="10">
         <v>65</v>
       </c>
-      <c r="G74" s="15">
+      <c r="G74" s="14">
         <v>35</v>
       </c>
-      <c r="H74" s="19">
+      <c r="H74" s="18">
         <v>23.333333333333332</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="10">
         <v>65</v>
       </c>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="11">
+      <c r="D75" s="14">
+        <v>55</v>
+      </c>
+      <c r="E75" s="14">
+        <v>72</v>
+      </c>
+      <c r="F75" s="10">
         <v>71</v>
       </c>
-      <c r="G75" s="15">
+      <c r="G75" s="14">
         <v>48</v>
       </c>
-      <c r="H75" s="19">
+      <c r="H75" s="18">
         <v>40</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C76" s="10">
         <v>63</v>
       </c>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="11">
+      <c r="D76" s="14">
+        <v>14</v>
+      </c>
+      <c r="E76" s="14">
+        <v>50</v>
+      </c>
+      <c r="F76" s="10">
         <v>52</v>
       </c>
-      <c r="G76" s="15">
+      <c r="G76" s="14">
         <v>37</v>
       </c>
-      <c r="H76" s="19">
+      <c r="H76" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C77" s="11">
+      <c r="C77" s="10">
         <v>64</v>
       </c>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="11">
+      <c r="D77" s="14">
+        <v>35</v>
+      </c>
+      <c r="E77" s="14">
+        <v>84</v>
+      </c>
+      <c r="F77" s="10">
         <v>70</v>
       </c>
-      <c r="G77" s="15">
+      <c r="G77" s="14">
         <v>54</v>
       </c>
-      <c r="H77" s="19">
+      <c r="H77" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C78" s="11">
+      <c r="C78" s="10">
         <v>76</v>
       </c>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="11">
+      <c r="D78" s="14">
+        <v>44</v>
+      </c>
+      <c r="E78" s="14">
+        <v>86</v>
+      </c>
+      <c r="F78" s="10">
         <v>60</v>
       </c>
-      <c r="G78" s="15">
+      <c r="G78" s="14">
         <v>54</v>
       </c>
-      <c r="H78" s="19">
+      <c r="H78" s="18">
         <v>23.333333333333332</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="10">
         <v>57.5</v>
       </c>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="11">
+      <c r="D79" s="14">
+        <v>2</v>
+      </c>
+      <c r="E79" s="14">
+        <v>77</v>
+      </c>
+      <c r="F79" s="10">
         <v>55</v>
       </c>
-      <c r="G79" s="15">
+      <c r="G79" s="14">
         <v>42</v>
       </c>
-      <c r="H79" s="19">
+      <c r="H79" s="18">
         <v>43.333333333333336</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C80" s="11">
+      <c r="C80" s="10">
         <v>71</v>
       </c>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="11">
+      <c r="D80" s="14">
+        <v>39</v>
+      </c>
+      <c r="E80" s="14">
+        <v>75</v>
+      </c>
+      <c r="F80" s="10">
         <v>25</v>
       </c>
-      <c r="G80" s="15">
+      <c r="G80" s="14">
         <v>63</v>
       </c>
-      <c r="H80" s="19">
+      <c r="H80" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="10">
         <v>72</v>
       </c>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="11">
+      <c r="D81" s="14">
+        <v>31</v>
+      </c>
+      <c r="E81" s="14">
+        <v>83</v>
+      </c>
+      <c r="F81" s="10">
         <v>50</v>
       </c>
-      <c r="G81" s="15">
+      <c r="G81" s="14">
         <v>58</v>
       </c>
-      <c r="H81" s="19">
+      <c r="H81" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C82" s="11">
+      <c r="C82" s="10">
         <v>58</v>
       </c>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="11">
+      <c r="D82" s="14">
+        <v>22</v>
+      </c>
+      <c r="E82" s="14">
+        <v>67</v>
+      </c>
+      <c r="F82" s="10">
         <v>54</v>
       </c>
-      <c r="G82" s="15">
+      <c r="G82" s="14">
         <v>54</v>
       </c>
-      <c r="H82" s="19">
+      <c r="H82" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="10">
         <v>93</v>
       </c>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="11">
+      <c r="D83" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E83" s="14">
+        <v>70</v>
+      </c>
+      <c r="F83" s="10">
         <v>67</v>
       </c>
-      <c r="G83" s="15">
+      <c r="G83" s="14">
         <v>67</v>
       </c>
-      <c r="H83" s="19">
+      <c r="H83" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C84" s="11">
+      <c r="C84" s="10">
         <v>89.5</v>
       </c>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="11">
+      <c r="D84" s="14">
+        <v>44</v>
+      </c>
+      <c r="E84" s="14">
+        <v>56</v>
+      </c>
+      <c r="F84" s="10">
         <v>73</v>
       </c>
-      <c r="G84" s="15">
+      <c r="G84" s="14">
         <v>70</v>
       </c>
-      <c r="H84" s="19">
+      <c r="H84" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="10">
         <v>69</v>
       </c>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="11">
+      <c r="D85" s="14">
+        <v>32</v>
+      </c>
+      <c r="E85" s="14">
+        <v>59</v>
+      </c>
+      <c r="F85" s="10">
         <v>75</v>
       </c>
-      <c r="G85" s="15">
+      <c r="G85" s="14">
         <v>47</v>
       </c>
-      <c r="H85" s="19">
+      <c r="H85" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="10">
         <v>40</v>
       </c>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="11">
+      <c r="D86" s="14">
+        <v>21</v>
+      </c>
+      <c r="E86" s="14">
+        <v>85</v>
+      </c>
+      <c r="F86" s="10">
         <v>75</v>
       </c>
-      <c r="G86" s="15">
+      <c r="G86" s="14">
         <v>42</v>
       </c>
-      <c r="H86" s="19">
+      <c r="H86" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="10">
         <v>79</v>
       </c>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="11">
+      <c r="D87" s="14">
+        <v>39</v>
+      </c>
+      <c r="E87" s="14">
+        <v>68</v>
+      </c>
+      <c r="F87" s="10">
         <v>75</v>
       </c>
-      <c r="G87" s="15">
+      <c r="G87" s="14">
         <v>47</v>
       </c>
-      <c r="H87" s="19">
+      <c r="H87" s="18">
         <v>43.333333333333336</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C88" s="11">
+      <c r="C88" s="10">
         <v>100</v>
       </c>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="11">
+      <c r="D88" s="14">
+        <v>71</v>
+      </c>
+      <c r="E88" s="14">
+        <v>85</v>
+      </c>
+      <c r="F88" s="10">
         <v>76</v>
       </c>
-      <c r="G88" s="15">
+      <c r="G88" s="14">
         <v>69</v>
       </c>
-      <c r="H88" s="19">
+      <c r="H88" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="10">
         <v>96.5</v>
       </c>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="11">
+      <c r="D89" s="14">
+        <v>34</v>
+      </c>
+      <c r="E89" s="14">
+        <v>96</v>
+      </c>
+      <c r="F89" s="10">
         <v>44</v>
       </c>
-      <c r="G89" s="15">
+      <c r="G89" s="14">
         <v>68</v>
       </c>
-      <c r="H89" s="19">
+      <c r="H89" s="18">
         <v>43.333333333333336</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C90" s="11">
+      <c r="C90" s="10">
         <v>81.5</v>
       </c>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="11">
+      <c r="D90" s="14">
+        <v>35</v>
+      </c>
+      <c r="E90" s="14">
+        <v>73</v>
+      </c>
+      <c r="F90" s="10">
         <v>60</v>
       </c>
-      <c r="G90" s="15">
+      <c r="G90" s="14">
         <v>56</v>
       </c>
-      <c r="H90" s="19">
+      <c r="H90" s="18">
         <v>23.333333333333332</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="10">
         <v>77</v>
       </c>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="11">
+      <c r="D91" s="14">
+        <v>40</v>
+      </c>
+      <c r="E91" s="14">
+        <v>83</v>
+      </c>
+      <c r="F91" s="10">
         <v>75</v>
       </c>
-      <c r="G91" s="15">
+      <c r="G91" s="14">
         <v>68</v>
       </c>
-      <c r="H91" s="19">
+      <c r="H91" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="10">
         <v>95.5</v>
       </c>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="11">
+      <c r="D92" s="14">
+        <v>49</v>
+      </c>
+      <c r="E92" s="14">
+        <v>77</v>
+      </c>
+      <c r="F92" s="10">
         <v>67</v>
       </c>
-      <c r="G92" s="15">
+      <c r="G92" s="14">
         <v>59</v>
       </c>
-      <c r="H92" s="19">
+      <c r="H92" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="10">
         <v>75</v>
       </c>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="11">
+      <c r="D93" s="14">
+        <v>74</v>
+      </c>
+      <c r="E93" s="14">
+        <v>76</v>
+      </c>
+      <c r="F93" s="10">
         <v>70</v>
       </c>
-      <c r="G93" s="15">
+      <c r="G93" s="14">
         <v>53</v>
       </c>
-      <c r="H93" s="19">
+      <c r="H93" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C94" s="11">
+      <c r="C94" s="10">
         <v>87</v>
       </c>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="11">
+      <c r="D94" s="14">
+        <v>37</v>
+      </c>
+      <c r="E94" s="14">
+        <v>80</v>
+      </c>
+      <c r="F94" s="10">
         <v>46</v>
       </c>
-      <c r="G94" s="15">
+      <c r="G94" s="14">
         <v>33</v>
       </c>
-      <c r="H94" s="19">
+      <c r="H94" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C95" s="11">
+      <c r="C95" s="10">
         <v>84</v>
       </c>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="11">
+      <c r="D95" s="14">
+        <v>39</v>
+      </c>
+      <c r="E95" s="14">
+        <v>76</v>
+      </c>
+      <c r="F95" s="10">
         <v>62</v>
       </c>
-      <c r="G95" s="15">
+      <c r="G95" s="14">
         <v>55</v>
       </c>
-      <c r="H95" s="19">
+      <c r="H95" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C96" s="11">
+      <c r="C96" s="10">
         <v>73</v>
       </c>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="11">
+      <c r="D96" s="14">
+        <v>54</v>
+      </c>
+      <c r="E96" s="14">
+        <v>64</v>
+      </c>
+      <c r="F96" s="10">
         <v>62</v>
       </c>
-      <c r="G96" s="15">
+      <c r="G96" s="14">
         <v>65</v>
       </c>
-      <c r="H96" s="19">
+      <c r="H96" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="10">
         <v>73</v>
       </c>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="11">
+      <c r="D97" s="14">
+        <v>39</v>
+      </c>
+      <c r="E97" s="14">
+        <v>74</v>
+      </c>
+      <c r="F97" s="10">
         <v>73</v>
       </c>
-      <c r="G97" s="15">
+      <c r="G97" s="14">
         <v>42</v>
       </c>
-      <c r="H97" s="19">
+      <c r="H97" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C98" s="11">
+      <c r="C98" s="10">
         <v>79</v>
       </c>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="11">
+      <c r="D98" s="14">
+        <v>41</v>
+      </c>
+      <c r="E98" s="14">
+        <v>60</v>
+      </c>
+      <c r="F98" s="10">
         <v>52</v>
       </c>
-      <c r="G98" s="15">
+      <c r="G98" s="14">
         <v>59</v>
       </c>
-      <c r="H98" s="19">
+      <c r="H98" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="10">
         <v>96</v>
       </c>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="11">
+      <c r="D99" s="14">
+        <v>38</v>
+      </c>
+      <c r="E99" s="14">
+        <v>79</v>
+      </c>
+      <c r="F99" s="10">
         <v>62</v>
       </c>
-      <c r="G99" s="15">
+      <c r="G99" s="14">
         <v>72</v>
       </c>
-      <c r="H99" s="19">
+      <c r="H99" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C100" s="11">
+      <c r="C100" s="10">
         <v>94.5</v>
       </c>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="11">
+      <c r="D100" s="14">
+        <v>63</v>
+      </c>
+      <c r="E100" s="14">
+        <v>92</v>
+      </c>
+      <c r="F100" s="10">
         <v>62</v>
       </c>
-      <c r="G100" s="15">
+      <c r="G100" s="14">
         <v>62</v>
       </c>
-      <c r="H100" s="19">
+      <c r="H100" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="10">
         <v>71</v>
       </c>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="11">
+      <c r="D101" s="14">
+        <v>62</v>
+      </c>
+      <c r="E101" s="14">
+        <v>69</v>
+      </c>
+      <c r="F101" s="10">
         <v>52</v>
       </c>
-      <c r="G101" s="15">
+      <c r="G101" s="14">
         <v>57</v>
       </c>
-      <c r="H101" s="19">
+      <c r="H101" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C102" s="11">
+      <c r="C102" s="10">
         <v>96</v>
       </c>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="11">
+      <c r="D102" s="14">
+        <v>79</v>
+      </c>
+      <c r="E102" s="14">
+        <v>84</v>
+      </c>
+      <c r="F102" s="10">
         <v>59</v>
       </c>
-      <c r="G102" s="15">
+      <c r="G102" s="14">
         <v>74</v>
       </c>
-      <c r="H102" s="19">
+      <c r="H102" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="6" t="s">
+      <c r="A103" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="10">
         <v>64</v>
       </c>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="11">
+      <c r="D103" s="14">
+        <v>29</v>
+      </c>
+      <c r="E103" s="14">
+        <v>74</v>
+      </c>
+      <c r="F103" s="10">
         <v>52</v>
       </c>
-      <c r="G103" s="15">
+      <c r="G103" s="14">
         <v>36</v>
       </c>
-      <c r="H103" s="19">
+      <c r="H103" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C104" s="11">
+      <c r="C104" s="10">
         <v>100</v>
       </c>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="11">
+      <c r="D104" s="14">
+        <v>58</v>
+      </c>
+      <c r="E104" s="14">
+        <v>85</v>
+      </c>
+      <c r="F104" s="10">
         <v>57</v>
       </c>
-      <c r="G104" s="15">
+      <c r="G104" s="14">
         <v>84</v>
       </c>
-      <c r="H104" s="19">
+      <c r="H104" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="6" t="s">
+      <c r="A105" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="10">
         <v>51</v>
       </c>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="11">
+      <c r="D105" s="14">
+        <v>22</v>
+      </c>
+      <c r="E105" s="14">
+        <v>95</v>
+      </c>
+      <c r="F105" s="10">
         <v>50</v>
       </c>
-      <c r="G105" s="15">
+      <c r="G105" s="14">
         <v>72</v>
       </c>
-      <c r="H105" s="19">
+      <c r="H105" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="6" t="s">
+      <c r="A106" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C106" s="11">
+      <c r="C106" s="10">
         <v>46</v>
       </c>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="11">
+      <c r="D106" s="14">
+        <v>44</v>
+      </c>
+      <c r="E106" s="14">
+        <v>82</v>
+      </c>
+      <c r="F106" s="10">
         <v>70</v>
       </c>
-      <c r="G106" s="15">
+      <c r="G106" s="14">
         <v>35</v>
       </c>
-      <c r="H106" s="19">
+      <c r="H106" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="10">
         <v>83</v>
       </c>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="11">
+      <c r="D107" s="14">
+        <v>18</v>
+      </c>
+      <c r="E107" s="14">
+        <v>62</v>
+      </c>
+      <c r="F107" s="10">
         <v>65</v>
       </c>
-      <c r="G107" s="15">
+      <c r="G107" s="14">
         <v>57</v>
       </c>
-      <c r="H107" s="19">
+      <c r="H107" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C108" s="11">
+      <c r="C108" s="10">
         <v>51</v>
       </c>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="11">
+      <c r="D108" s="14">
+        <v>41</v>
+      </c>
+      <c r="E108" s="14">
+        <v>72</v>
+      </c>
+      <c r="F108" s="10">
         <v>59</v>
       </c>
-      <c r="G108" s="15">
+      <c r="G108" s="14">
         <v>67</v>
       </c>
-      <c r="H108" s="19">
+      <c r="H108" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="10">
         <v>84</v>
       </c>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="11">
+      <c r="D109" s="14">
+        <v>43</v>
+      </c>
+      <c r="E109" s="14">
+        <v>95</v>
+      </c>
+      <c r="F109" s="10">
         <v>73</v>
       </c>
-      <c r="G109" s="15">
+      <c r="G109" s="14">
         <v>66</v>
       </c>
-      <c r="H109" s="19">
+      <c r="H109" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="10">
         <v>77</v>
       </c>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="11">
+      <c r="D110" s="14">
+        <v>33</v>
+      </c>
+      <c r="E110" s="14">
+        <v>46</v>
+      </c>
+      <c r="F110" s="10">
         <v>66</v>
       </c>
-      <c r="G110" s="15">
+      <c r="G110" s="14">
         <v>45</v>
       </c>
-      <c r="H110" s="19">
+      <c r="H110" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="10">
         <v>39.5</v>
       </c>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="11">
+      <c r="D111" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E111" s="14">
+        <v>38</v>
+      </c>
+      <c r="F111" s="10">
         <v>41</v>
       </c>
-      <c r="G111" s="15">
+      <c r="G111" s="14">
         <v>9</v>
       </c>
-      <c r="H111" s="19">
+      <c r="H111" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C112" s="11">
+      <c r="C112" s="10">
         <v>88</v>
       </c>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="11">
+      <c r="D112" s="14">
+        <v>66</v>
+      </c>
+      <c r="E112" s="14">
+        <v>76</v>
+      </c>
+      <c r="F112" s="10">
         <v>62</v>
       </c>
-      <c r="G112" s="15">
+      <c r="G112" s="14">
         <v>72</v>
       </c>
-      <c r="H112" s="19">
+      <c r="H112" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C113" s="11">
+      <c r="C113" s="10">
         <v>64</v>
       </c>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="11">
+      <c r="D113" s="14">
+        <v>25</v>
+      </c>
+      <c r="E113" s="14">
+        <v>49</v>
+      </c>
+      <c r="F113" s="10">
         <v>76</v>
       </c>
-      <c r="G113" s="15">
+      <c r="G113" s="14">
         <v>44</v>
       </c>
-      <c r="H113" s="19">
+      <c r="H113" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C114" s="11">
+      <c r="C114" s="10">
         <v>70</v>
       </c>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="11">
+      <c r="D114" s="14">
+        <v>72</v>
+      </c>
+      <c r="E114" s="14">
+        <v>53</v>
+      </c>
+      <c r="F114" s="10">
         <v>66</v>
       </c>
-      <c r="G114" s="15">
+      <c r="G114" s="14">
         <v>56</v>
       </c>
-      <c r="H114" s="19">
+      <c r="H114" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="10">
         <v>76</v>
       </c>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="11">
+      <c r="D115" s="14">
+        <v>54</v>
+      </c>
+      <c r="E115" s="14">
+        <v>84</v>
+      </c>
+      <c r="F115" s="10">
         <v>75</v>
       </c>
-      <c r="G115" s="15">
+      <c r="G115" s="14">
         <v>75</v>
       </c>
-      <c r="H115" s="19">
+      <c r="H115" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C116" s="11">
+      <c r="C116" s="10">
         <v>75</v>
       </c>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="11">
+      <c r="D116" s="14">
+        <v>51</v>
+      </c>
+      <c r="E116" s="14">
+        <v>88</v>
+      </c>
+      <c r="F116" s="10">
         <v>55</v>
       </c>
-      <c r="G116" s="15">
+      <c r="G116" s="14">
         <v>56</v>
       </c>
-      <c r="H116" s="19">
+      <c r="H116" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C117" s="11">
+      <c r="C117" s="10">
         <v>85.5</v>
       </c>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="11">
+      <c r="D117" s="14">
+        <v>45</v>
+      </c>
+      <c r="E117" s="14">
+        <v>97</v>
+      </c>
+      <c r="F117" s="10">
         <v>42</v>
       </c>
-      <c r="G117" s="15">
+      <c r="G117" s="14">
         <v>43</v>
       </c>
-      <c r="H117" s="19">
+      <c r="H117" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C118" s="11">
+      <c r="C118" s="10">
         <v>73.5</v>
       </c>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="11">
+      <c r="D118" s="14">
+        <v>71</v>
+      </c>
+      <c r="E118" s="14">
+        <v>74</v>
+      </c>
+      <c r="F118" s="10">
         <v>66</v>
       </c>
-      <c r="G118" s="15">
+      <c r="G118" s="14">
         <v>60</v>
       </c>
-      <c r="H118" s="19">
+      <c r="H118" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <v>97</v>
       </c>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="11">
+      <c r="D119" s="14">
+        <v>57</v>
+      </c>
+      <c r="E119" s="14">
+        <v>88</v>
+      </c>
+      <c r="F119" s="10">
         <v>75</v>
       </c>
-      <c r="G119" s="15">
+      <c r="G119" s="14">
         <v>70</v>
       </c>
-      <c r="H119" s="19">
+      <c r="H119" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C120" s="11">
+      <c r="C120" s="10">
         <v>84</v>
       </c>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="11">
+      <c r="D120" s="14">
+        <v>51</v>
+      </c>
+      <c r="E120" s="14">
+        <v>87</v>
+      </c>
+      <c r="F120" s="10">
         <v>25</v>
       </c>
-      <c r="G120" s="15">
+      <c r="G120" s="14">
         <v>63</v>
       </c>
-      <c r="H120" s="19">
+      <c r="H120" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C121" s="11">
+      <c r="C121" s="10">
         <v>79</v>
       </c>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="11">
+      <c r="D121" s="14">
+        <v>28</v>
+      </c>
+      <c r="E121" s="14">
+        <v>75</v>
+      </c>
+      <c r="F121" s="10">
         <v>55</v>
       </c>
-      <c r="G121" s="15">
+      <c r="G121" s="14">
         <v>50</v>
       </c>
-      <c r="H121" s="19">
+      <c r="H121" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C122" s="11">
-        <v>81</v>
-      </c>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
-      <c r="F122" s="11">
+      <c r="C122" s="10">
+        <v>81</v>
+      </c>
+      <c r="D122" s="14">
+        <v>28</v>
+      </c>
+      <c r="E122" s="14">
+        <v>91</v>
+      </c>
+      <c r="F122" s="10">
         <v>54</v>
       </c>
-      <c r="G122" s="15">
+      <c r="G122" s="14">
         <v>72</v>
       </c>
-      <c r="H122" s="19">
+      <c r="H122" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C123" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
-      <c r="F123" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="G123" s="15">
+      <c r="C123" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D123" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E123" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F123" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G123" s="14">
         <v>8</v>
       </c>
-      <c r="H123" s="19">
+      <c r="H123" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C124" s="11">
+      <c r="C124" s="10">
         <v>88</v>
       </c>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
-      <c r="F124" s="11">
+      <c r="D124" s="14">
+        <v>50</v>
+      </c>
+      <c r="E124" s="14">
+        <v>91</v>
+      </c>
+      <c r="F124" s="10">
         <v>67</v>
       </c>
-      <c r="G124" s="15">
+      <c r="G124" s="14">
         <v>70</v>
       </c>
-      <c r="H124" s="19">
+      <c r="H124" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="10">
         <v>96</v>
       </c>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
-      <c r="F125" s="11">
+      <c r="D125" s="14">
+        <v>65</v>
+      </c>
+      <c r="E125" s="14">
+        <v>77</v>
+      </c>
+      <c r="F125" s="10">
         <v>76</v>
       </c>
-      <c r="G125" s="15">
+      <c r="G125" s="14">
         <v>56</v>
       </c>
-      <c r="H125" s="19">
+      <c r="H125" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="6" t="s">
+      <c r="A126" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C126" s="11">
+      <c r="C126" s="10">
         <v>90</v>
       </c>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
-      <c r="F126" s="11">
+      <c r="D126" s="14">
+        <v>49</v>
+      </c>
+      <c r="E126" s="14">
+        <v>91</v>
+      </c>
+      <c r="F126" s="10">
         <v>70</v>
       </c>
-      <c r="G126" s="15">
+      <c r="G126" s="14">
         <v>67</v>
       </c>
-      <c r="H126" s="19">
+      <c r="H126" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="10">
         <v>51.5</v>
       </c>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
-      <c r="F127" s="11">
+      <c r="D127" s="14">
+        <v>35</v>
+      </c>
+      <c r="E127" s="14">
+        <v>72</v>
+      </c>
+      <c r="F127" s="10">
         <v>70</v>
       </c>
-      <c r="G127" s="15">
+      <c r="G127" s="14">
         <v>56</v>
       </c>
-      <c r="H127" s="19">
+      <c r="H127" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C128" s="11">
+      <c r="C128" s="10">
         <v>87.5</v>
       </c>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
-      <c r="F128" s="11">
+      <c r="D128" s="14">
+        <v>31</v>
+      </c>
+      <c r="E128" s="14">
+        <v>81</v>
+      </c>
+      <c r="F128" s="10">
         <v>48</v>
       </c>
-      <c r="G128" s="15">
+      <c r="G128" s="14">
         <v>52</v>
       </c>
-      <c r="H128" s="19">
+      <c r="H128" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="6" t="s">
+      <c r="A129" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="10">
         <v>70</v>
       </c>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
-      <c r="F129" s="11">
+      <c r="D129" s="14">
+        <v>40</v>
+      </c>
+      <c r="E129" s="14">
+        <v>78</v>
+      </c>
+      <c r="F129" s="10">
         <v>54</v>
       </c>
-      <c r="G129" s="15">
+      <c r="G129" s="14">
         <v>45</v>
       </c>
-      <c r="H129" s="19">
+      <c r="H129" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="6" t="s">
+      <c r="A130" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C130" s="11">
+      <c r="C130" s="10">
         <v>54.5</v>
       </c>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
-      <c r="F130" s="11">
+      <c r="D130" s="14">
+        <v>28</v>
+      </c>
+      <c r="E130" s="14">
+        <v>81</v>
+      </c>
+      <c r="F130" s="10">
         <v>63</v>
       </c>
-      <c r="G130" s="15">
+      <c r="G130" s="14">
         <v>42</v>
       </c>
-      <c r="H130" s="19">
+      <c r="H130" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="6" t="s">
+      <c r="A131" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C131" s="11">
+      <c r="C131" s="10">
         <v>79</v>
       </c>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
-      <c r="F131" s="11">
+      <c r="D131" s="14">
+        <v>45</v>
+      </c>
+      <c r="E131" s="14">
+        <v>91</v>
+      </c>
+      <c r="F131" s="10">
         <v>53</v>
       </c>
-      <c r="G131" s="15">
+      <c r="G131" s="14">
         <v>56</v>
       </c>
-      <c r="H131" s="19">
+      <c r="H131" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="6" t="s">
+      <c r="A132" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C132" s="11">
+      <c r="C132" s="10">
         <v>91</v>
       </c>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-      <c r="F132" s="11">
+      <c r="D132" s="14">
+        <v>56</v>
+      </c>
+      <c r="E132" s="14">
+        <v>92</v>
+      </c>
+      <c r="F132" s="10">
         <v>73</v>
       </c>
-      <c r="G132" s="15">
+      <c r="G132" s="14">
         <v>79</v>
       </c>
-      <c r="H132" s="19">
+      <c r="H132" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="10">
         <v>50</v>
       </c>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
-      <c r="F133" s="11">
+      <c r="D133" s="14">
+        <v>22</v>
+      </c>
+      <c r="E133" s="14">
+        <v>68</v>
+      </c>
+      <c r="F133" s="10">
         <v>48</v>
       </c>
-      <c r="G133" s="15">
+      <c r="G133" s="14">
         <v>61</v>
       </c>
-      <c r="H133" s="19">
+      <c r="H133" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="6" t="s">
+      <c r="A134" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C134" s="11">
+      <c r="C134" s="10">
         <v>86</v>
       </c>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
-      <c r="F134" s="11">
+      <c r="D134" s="14">
+        <v>51</v>
+      </c>
+      <c r="E134" s="14">
+        <v>80</v>
+      </c>
+      <c r="F134" s="10">
         <v>70</v>
       </c>
-      <c r="G134" s="15">
+      <c r="G134" s="14">
         <v>66</v>
       </c>
-      <c r="H134" s="19">
+      <c r="H134" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="6" t="s">
+      <c r="A135" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="10">
         <v>57</v>
       </c>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
-      <c r="F135" s="11">
+      <c r="D135" s="14">
+        <v>26</v>
+      </c>
+      <c r="E135" s="14">
+        <v>80</v>
+      </c>
+      <c r="F135" s="10">
         <v>66</v>
       </c>
-      <c r="G135" s="15">
+      <c r="G135" s="14">
         <v>37</v>
       </c>
-      <c r="H135" s="19">
+      <c r="H135" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="6" t="s">
+      <c r="A136" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C136" s="11">
+      <c r="C136" s="10">
         <v>59.5</v>
       </c>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
-      <c r="F136" s="11">
+      <c r="D136" s="14">
+        <v>20</v>
+      </c>
+      <c r="E136" s="14">
+        <v>87</v>
+      </c>
+      <c r="F136" s="10">
         <v>46</v>
       </c>
-      <c r="G136" s="15">
+      <c r="G136" s="14">
         <v>50</v>
       </c>
-      <c r="H136" s="19">
+      <c r="H136" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="6" t="s">
+      <c r="A137" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="10">
         <v>85</v>
       </c>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2"/>
-      <c r="F137" s="11">
+      <c r="D137" s="14">
+        <v>59</v>
+      </c>
+      <c r="E137" s="14">
+        <v>61</v>
+      </c>
+      <c r="F137" s="10">
         <v>73</v>
       </c>
-      <c r="G137" s="15">
+      <c r="G137" s="14">
         <v>65</v>
       </c>
-      <c r="H137" s="19">
+      <c r="H137" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="6" t="s">
+      <c r="A138" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C138" s="11">
+      <c r="C138" s="10">
         <v>73</v>
       </c>
-      <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
-      <c r="F138" s="11">
+      <c r="D138" s="14">
         <v>57</v>
       </c>
-      <c r="G138" s="15">
+      <c r="E138" s="14">
+        <v>75</v>
+      </c>
+      <c r="F138" s="10">
+        <v>57</v>
+      </c>
+      <c r="G138" s="14">
         <v>56</v>
       </c>
-      <c r="H138" s="19">
+      <c r="H138" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="6" t="s">
+      <c r="A139" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="10">
         <v>61</v>
       </c>
-      <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
-      <c r="F139" s="11">
+      <c r="D139" s="14">
+        <v>32</v>
+      </c>
+      <c r="E139" s="14">
+        <v>69</v>
+      </c>
+      <c r="F139" s="10">
         <v>73</v>
       </c>
-      <c r="G139" s="15">
+      <c r="G139" s="14">
         <v>51</v>
       </c>
-      <c r="H139" s="19">
+      <c r="H139" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="6" t="s">
+      <c r="A140" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C140" s="11">
+      <c r="C140" s="10">
         <v>90.5</v>
       </c>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
-      <c r="F140" s="11">
+      <c r="D140" s="14">
+        <v>90</v>
+      </c>
+      <c r="E140" s="14">
+        <v>84</v>
+      </c>
+      <c r="F140" s="10">
         <v>70</v>
       </c>
-      <c r="G140" s="15">
+      <c r="G140" s="14">
         <v>63</v>
       </c>
-      <c r="H140" s="19">
+      <c r="H140" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="6" t="s">
+      <c r="A141" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C141" s="11">
+      <c r="C141" s="10">
         <v>96.5</v>
       </c>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
-      <c r="F141" s="11">
+      <c r="D141" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E141" s="14">
+        <v>80</v>
+      </c>
+      <c r="F141" s="10">
         <v>67</v>
       </c>
-      <c r="G141" s="15">
+      <c r="G141" s="14">
         <v>41</v>
       </c>
-      <c r="H141" s="19">
+      <c r="H141" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="6" t="s">
+      <c r="A142" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C142" s="11">
+      <c r="C142" s="10">
         <v>88.5</v>
       </c>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
-      <c r="F142" s="11">
+      <c r="D142" s="14">
+        <v>30</v>
+      </c>
+      <c r="E142" s="14">
+        <v>87</v>
+      </c>
+      <c r="F142" s="10">
         <v>57</v>
       </c>
-      <c r="G142" s="15">
+      <c r="G142" s="14">
         <v>53</v>
       </c>
-      <c r="H142" s="19">
+      <c r="H142" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="6" t="s">
+      <c r="A143" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C143" s="11">
+      <c r="C143" s="10">
         <v>84</v>
       </c>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
-      <c r="F143" s="11">
+      <c r="D143" s="14">
+        <v>41</v>
+      </c>
+      <c r="E143" s="14">
+        <v>75</v>
+      </c>
+      <c r="F143" s="10">
         <v>54</v>
       </c>
-      <c r="G143" s="15">
+      <c r="G143" s="14">
         <v>66</v>
       </c>
-      <c r="H143" s="19">
+      <c r="H143" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="6" t="s">
+      <c r="A144" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C144" s="11">
+      <c r="C144" s="10">
         <v>96</v>
       </c>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
-      <c r="F144" s="11">
+      <c r="D144" s="14">
+        <v>68</v>
+      </c>
+      <c r="E144" s="14">
+        <v>73</v>
+      </c>
+      <c r="F144" s="10">
         <v>41</v>
       </c>
-      <c r="G144" s="15">
+      <c r="G144" s="14">
         <v>80</v>
       </c>
-      <c r="H144" s="19">
+      <c r="H144" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="6" t="s">
+      <c r="A145" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C145" s="11">
+      <c r="C145" s="10">
         <v>85</v>
       </c>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
-      <c r="F145" s="11">
+      <c r="D145" s="14">
+        <v>39</v>
+      </c>
+      <c r="E145" s="14">
+        <v>78</v>
+      </c>
+      <c r="F145" s="10">
         <v>53</v>
       </c>
-      <c r="G145" s="15">
+      <c r="G145" s="14">
         <v>67</v>
       </c>
-      <c r="H145" s="19">
+      <c r="H145" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="6" t="s">
+      <c r="A146" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C146" s="11">
+      <c r="C146" s="10">
         <v>100</v>
       </c>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
-      <c r="F146" s="11">
+      <c r="D146" s="14">
+        <v>52</v>
+      </c>
+      <c r="E146" s="14">
+        <v>98</v>
+      </c>
+      <c r="F146" s="10">
         <v>63</v>
       </c>
-      <c r="G146" s="15">
+      <c r="G146" s="14">
         <v>70</v>
       </c>
-      <c r="H146" s="19">
+      <c r="H146" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="6" t="s">
+      <c r="A147" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C147" s="11">
+      <c r="C147" s="10">
         <v>61.5</v>
       </c>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
-      <c r="F147" s="11">
+      <c r="D147" s="14">
+        <v>38</v>
+      </c>
+      <c r="E147" s="14">
+        <v>87</v>
+      </c>
+      <c r="F147" s="10">
         <v>55</v>
       </c>
-      <c r="G147" s="15">
+      <c r="G147" s="14">
         <v>26</v>
       </c>
-      <c r="H147" s="19">
+      <c r="H147" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="6" t="s">
+      <c r="A148" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C148" s="11">
+      <c r="C148" s="10">
         <v>70</v>
       </c>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
-      <c r="F148" s="11">
+      <c r="D148" s="14">
+        <v>46</v>
+      </c>
+      <c r="E148" s="14">
+        <v>89</v>
+      </c>
+      <c r="F148" s="10">
         <v>71</v>
       </c>
-      <c r="G148" s="15">
+      <c r="G148" s="14">
         <v>38</v>
       </c>
-      <c r="H148" s="19">
+      <c r="H148" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="6" t="s">
+      <c r="A149" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C149" s="11">
+      <c r="C149" s="10">
         <v>79</v>
       </c>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
-      <c r="F149" s="11">
+      <c r="D149" s="14">
+        <v>29</v>
+      </c>
+      <c r="E149" s="14">
+        <v>64</v>
+      </c>
+      <c r="F149" s="10">
         <v>62</v>
       </c>
-      <c r="G149" s="15">
+      <c r="G149" s="14">
         <v>51</v>
       </c>
-      <c r="H149" s="19">
+      <c r="H149" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="6" t="s">
+      <c r="A150" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C150" s="11">
+      <c r="C150" s="10">
         <v>89</v>
       </c>
-      <c r="D150" s="2"/>
-      <c r="E150" s="2"/>
-      <c r="F150" s="11">
+      <c r="D150" s="14">
+        <v>68</v>
+      </c>
+      <c r="E150" s="14">
+        <v>100</v>
+      </c>
+      <c r="F150" s="10">
         <v>46</v>
       </c>
-      <c r="G150" s="15">
+      <c r="G150" s="14">
         <v>58</v>
       </c>
-      <c r="H150" s="19">
+      <c r="H150" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="6" t="s">
+      <c r="A151" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C151" s="11">
+      <c r="C151" s="10">
         <v>86</v>
       </c>
-      <c r="D151" s="2"/>
-      <c r="E151" s="2"/>
-      <c r="F151" s="11">
+      <c r="D151" s="14">
+        <v>44</v>
+      </c>
+      <c r="E151" s="14">
+        <v>64</v>
+      </c>
+      <c r="F151" s="10">
         <v>50</v>
       </c>
-      <c r="G151" s="15">
+      <c r="G151" s="14">
         <v>55</v>
       </c>
-      <c r="H151" s="19">
+      <c r="H151" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="6" t="s">
+      <c r="A152" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B152" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C152" s="11">
+      <c r="C152" s="10">
         <v>61</v>
       </c>
-      <c r="D152" s="2"/>
-      <c r="E152" s="2"/>
-      <c r="F152" s="11">
+      <c r="D152" s="14">
+        <v>33</v>
+      </c>
+      <c r="E152" s="14">
         <v>73</v>
       </c>
-      <c r="G152" s="15">
+      <c r="F152" s="10">
+        <v>73</v>
+      </c>
+      <c r="G152" s="14">
         <v>41</v>
       </c>
-      <c r="H152" s="19">
+      <c r="H152" s="18">
         <v>46.666666666666664</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="6" t="s">
+      <c r="A153" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C153" s="11">
+      <c r="C153" s="10">
         <v>89.5</v>
       </c>
-      <c r="D153" s="2"/>
-      <c r="E153" s="2"/>
-      <c r="F153" s="11">
+      <c r="D153" s="14">
+        <v>33</v>
+      </c>
+      <c r="E153" s="14">
+        <v>77</v>
+      </c>
+      <c r="F153" s="10">
         <v>66</v>
       </c>
-      <c r="G153" s="15">
+      <c r="G153" s="14">
         <v>58</v>
       </c>
-      <c r="H153" s="19">
+      <c r="H153" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="6" t="s">
+      <c r="A154" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C154" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D154" s="2"/>
-      <c r="E154" s="2"/>
-      <c r="F154" s="11">
+      <c r="C154" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D154" s="14">
+        <v>38</v>
+      </c>
+      <c r="E154" s="14">
+        <v>76</v>
+      </c>
+      <c r="F154" s="10">
         <v>43</v>
       </c>
-      <c r="G154" s="15">
+      <c r="G154" s="14">
         <v>72</v>
       </c>
-      <c r="H154" s="19">
+      <c r="H154" s="18">
         <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="6" t="s">
+      <c r="A155" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C155" s="11">
+      <c r="C155" s="10">
         <v>57.5</v>
       </c>
-      <c r="D155" s="2"/>
-      <c r="E155" s="2"/>
-      <c r="F155" s="11">
+      <c r="D155" s="14">
+        <v>45</v>
+      </c>
+      <c r="E155" s="14">
+        <v>78</v>
+      </c>
+      <c r="F155" s="10">
         <v>50</v>
       </c>
-      <c r="G155" s="15">
+      <c r="G155" s="14">
         <v>55</v>
       </c>
-      <c r="H155" s="19">
+      <c r="H155" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="6" t="s">
+      <c r="A156" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C156" s="11">
+      <c r="C156" s="10">
         <v>84</v>
       </c>
-      <c r="D156" s="2"/>
-      <c r="E156" s="2"/>
-      <c r="F156" s="11">
+      <c r="D156" s="14">
+        <v>77</v>
+      </c>
+      <c r="E156" s="14">
+        <v>81</v>
+      </c>
+      <c r="F156" s="10">
         <v>59</v>
       </c>
-      <c r="G156" s="15">
+      <c r="G156" s="14">
         <v>90</v>
       </c>
-      <c r="H156" s="19">
+      <c r="H156" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="6" t="s">
+      <c r="A157" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C157" s="11">
-        <v>81</v>
-      </c>
-      <c r="D157" s="2"/>
-      <c r="E157" s="2"/>
-      <c r="F157" s="11">
+      <c r="C157" s="10">
+        <v>81</v>
+      </c>
+      <c r="D157" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E157" s="14">
+        <v>59</v>
+      </c>
+      <c r="F157" s="10">
         <v>62</v>
       </c>
-      <c r="G157" s="15">
+      <c r="G157" s="14">
         <v>54</v>
       </c>
-      <c r="H157" s="19">
+      <c r="H157" s="18">
         <v>56.666666666666664</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="6" t="s">
+      <c r="A158" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C158" s="11">
+      <c r="C158" s="10">
         <v>100</v>
       </c>
-      <c r="D158" s="2"/>
-      <c r="E158" s="2"/>
-      <c r="F158" s="11">
+      <c r="D158" s="14">
+        <v>50</v>
+      </c>
+      <c r="E158" s="14">
+        <v>88</v>
+      </c>
+      <c r="F158" s="10">
         <v>54</v>
       </c>
-      <c r="G158" s="15">
+      <c r="G158" s="14">
         <v>55</v>
       </c>
-      <c r="H158" s="19">
+      <c r="H158" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="6" t="s">
+      <c r="A159" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C159" s="11">
+      <c r="C159" s="10">
         <v>46</v>
       </c>
-      <c r="D159" s="2"/>
-      <c r="E159" s="2"/>
-      <c r="F159" s="11">
+      <c r="D159" s="14">
+        <v>45</v>
+      </c>
+      <c r="E159" s="14">
+        <v>68</v>
+      </c>
+      <c r="F159" s="10">
         <v>75</v>
       </c>
-      <c r="G159" s="15">
+      <c r="G159" s="14">
         <v>52</v>
       </c>
-      <c r="H159" s="19">
+      <c r="H159" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="6" t="s">
+      <c r="A160" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C160" s="11">
+      <c r="C160" s="10">
         <v>79</v>
       </c>
-      <c r="D160" s="2"/>
-      <c r="E160" s="2"/>
-      <c r="F160" s="11">
+      <c r="D160" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E160" s="14">
+        <v>72</v>
+      </c>
+      <c r="F160" s="10">
         <v>39</v>
       </c>
-      <c r="G160" s="15">
+      <c r="G160" s="14">
         <v>56</v>
       </c>
-      <c r="H160" s="19">
+      <c r="H160" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="6" t="s">
+      <c r="A161" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C161" s="11">
+      <c r="C161" s="10">
         <v>73.5</v>
       </c>
-      <c r="D161" s="2"/>
-      <c r="E161" s="2"/>
-      <c r="F161" s="11">
+      <c r="D161" s="14">
+        <v>48</v>
+      </c>
+      <c r="E161" s="14">
+        <v>69</v>
+      </c>
+      <c r="F161" s="10">
         <v>25</v>
       </c>
-      <c r="G161" s="15">
+      <c r="G161" s="14">
         <v>45</v>
       </c>
-      <c r="H161" s="19">
+      <c r="H161" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="6" t="s">
+      <c r="A162" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B162" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C162" s="11">
+      <c r="C162" s="10">
         <v>92</v>
       </c>
-      <c r="D162" s="2"/>
-      <c r="E162" s="2"/>
-      <c r="F162" s="11">
+      <c r="D162" s="14">
+        <v>53</v>
+      </c>
+      <c r="E162" s="14">
+        <v>72</v>
+      </c>
+      <c r="F162" s="10">
         <v>25</v>
       </c>
-      <c r="G162" s="15">
+      <c r="G162" s="14">
         <v>63</v>
       </c>
-      <c r="H162" s="19">
+      <c r="H162" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="6" t="s">
+      <c r="A163" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C163" s="11">
+      <c r="C163" s="10">
         <v>78</v>
       </c>
-      <c r="D163" s="2"/>
-      <c r="E163" s="2"/>
-      <c r="F163" s="11">
+      <c r="D163" s="14">
+        <v>26</v>
+      </c>
+      <c r="E163" s="14">
+        <v>81</v>
+      </c>
+      <c r="F163" s="10">
         <v>65</v>
       </c>
-      <c r="G163" s="15">
+      <c r="G163" s="14">
         <v>46</v>
       </c>
-      <c r="H163" s="19">
+      <c r="H163" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="6" t="s">
+      <c r="A164" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C164" s="11">
+      <c r="C164" s="10">
         <v>79</v>
       </c>
-      <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
-      <c r="F164" s="11">
+      <c r="D164" s="14">
+        <v>41</v>
+      </c>
+      <c r="E164" s="14">
+        <v>70</v>
+      </c>
+      <c r="F164" s="10">
         <v>43</v>
       </c>
-      <c r="G164" s="15">
+      <c r="G164" s="14">
         <v>78</v>
       </c>
-      <c r="H164" s="19">
+      <c r="H164" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="6" t="s">
+      <c r="A165" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C165" s="11">
+      <c r="C165" s="10">
         <v>59.5</v>
       </c>
-      <c r="D165" s="2"/>
-      <c r="E165" s="2"/>
-      <c r="F165" s="11">
+      <c r="D165" s="14">
+        <v>29</v>
+      </c>
+      <c r="E165" s="14">
+        <v>72</v>
+      </c>
+      <c r="F165" s="10">
         <v>78</v>
       </c>
-      <c r="G165" s="15">
+      <c r="G165" s="14">
         <v>50</v>
       </c>
-      <c r="H165" s="19">
+      <c r="H165" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="6" t="s">
+      <c r="A166" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C166" s="11">
+      <c r="C166" s="10">
         <v>74.5</v>
       </c>
-      <c r="D166" s="2"/>
-      <c r="E166" s="2"/>
-      <c r="F166" s="11">
+      <c r="D166" s="14">
+        <v>61</v>
+      </c>
+      <c r="E166" s="14">
+        <v>82</v>
+      </c>
+      <c r="F166" s="10">
         <v>71</v>
       </c>
-      <c r="G166" s="15">
+      <c r="G166" s="14">
         <v>64</v>
       </c>
-      <c r="H166" s="19">
+      <c r="H166" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="6" t="s">
+      <c r="A167" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C167" s="11">
+      <c r="C167" s="10">
         <v>84</v>
       </c>
-      <c r="D167" s="2"/>
-      <c r="E167" s="2"/>
-      <c r="F167" s="11">
+      <c r="D167" s="14">
+        <v>66</v>
+      </c>
+      <c r="E167" s="14">
+        <v>68</v>
+      </c>
+      <c r="F167" s="10">
         <v>78</v>
       </c>
-      <c r="G167" s="15">
+      <c r="G167" s="14">
         <v>78</v>
       </c>
-      <c r="H167" s="19">
+      <c r="H167" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="6" t="s">
+      <c r="A168" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C168" s="11">
+      <c r="C168" s="10">
         <v>76.5</v>
       </c>
-      <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
-      <c r="F168" s="11">
+      <c r="D168" s="14">
+        <v>36</v>
+      </c>
+      <c r="E168" s="14">
+        <v>79</v>
+      </c>
+      <c r="F168" s="10">
         <v>73</v>
       </c>
-      <c r="G168" s="15">
+      <c r="G168" s="14">
         <v>63</v>
       </c>
-      <c r="H168" s="19">
+      <c r="H168" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="6" t="s">
+      <c r="A169" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C169" s="11">
+      <c r="C169" s="10">
         <v>93</v>
       </c>
-      <c r="D169" s="2"/>
-      <c r="E169" s="2"/>
-      <c r="F169" s="11">
+      <c r="D169" s="14">
+        <v>80</v>
+      </c>
+      <c r="E169" s="14">
+        <v>90</v>
+      </c>
+      <c r="F169" s="10">
         <v>41</v>
       </c>
-      <c r="G169" s="15">
+      <c r="G169" s="14">
         <v>79</v>
       </c>
-      <c r="H169" s="19">
+      <c r="H169" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="6" t="s">
+      <c r="A170" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C170" s="11">
+      <c r="C170" s="10">
         <v>58.5</v>
       </c>
-      <c r="D170" s="2"/>
-      <c r="E170" s="2"/>
-      <c r="F170" s="11">
+      <c r="D170" s="14">
+        <v>23</v>
+      </c>
+      <c r="E170" s="14">
+        <v>78</v>
+      </c>
+      <c r="F170" s="10">
         <v>47</v>
       </c>
-      <c r="G170" s="15">
+      <c r="G170" s="14">
         <v>38</v>
       </c>
-      <c r="H170" s="19">
+      <c r="H170" s="18">
         <v>16.666666666666664</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="6" t="s">
+      <c r="A171" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C171" s="11">
+      <c r="C171" s="10">
         <v>47</v>
       </c>
-      <c r="D171" s="2"/>
-      <c r="E171" s="2"/>
-      <c r="F171" s="11">
+      <c r="D171" s="14">
+        <v>27</v>
+      </c>
+      <c r="E171" s="14">
+        <v>70</v>
+      </c>
+      <c r="F171" s="10">
         <v>54</v>
       </c>
-      <c r="G171" s="15">
+      <c r="G171" s="14">
         <v>41</v>
       </c>
-      <c r="H171" s="19">
+      <c r="H171" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="6" t="s">
+      <c r="A172" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="B172" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C172" s="11">
+      <c r="C172" s="10">
         <v>65</v>
       </c>
-      <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
-      <c r="F172" s="11">
+      <c r="D172" s="14">
+        <v>31</v>
+      </c>
+      <c r="E172" s="14">
+        <v>55</v>
+      </c>
+      <c r="F172" s="10">
         <v>43</v>
       </c>
-      <c r="G172" s="15">
+      <c r="G172" s="14">
         <v>30</v>
       </c>
-      <c r="H172" s="19">
+      <c r="H172" s="18">
         <v>26.666666666666668</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="6" t="s">
+      <c r="A173" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C173" s="11">
+      <c r="C173" s="10">
         <v>83.5</v>
       </c>
-      <c r="D173" s="2"/>
-      <c r="E173" s="2"/>
-      <c r="F173" s="11">
+      <c r="D173" s="14">
+        <v>43</v>
+      </c>
+      <c r="E173" s="14">
+        <v>96</v>
+      </c>
+      <c r="F173" s="10">
         <v>60</v>
       </c>
-      <c r="G173" s="15">
+      <c r="G173" s="14">
         <v>48</v>
       </c>
-      <c r="H173" s="19">
+      <c r="H173" s="18">
         <v>16.666666666666664</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="6" t="s">
+      <c r="A174" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B174" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C174" s="11">
+      <c r="C174" s="10">
         <v>41</v>
       </c>
-      <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
-      <c r="F174" s="11">
+      <c r="D174" s="14">
+        <v>37</v>
+      </c>
+      <c r="E174" s="14">
+        <v>71</v>
+      </c>
+      <c r="F174" s="10">
         <v>73</v>
       </c>
-      <c r="G174" s="15">
+      <c r="G174" s="14">
         <v>25</v>
       </c>
-      <c r="H174" s="19">
+      <c r="H174" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="6" t="s">
+      <c r="A175" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C175" s="11">
+      <c r="C175" s="10">
         <v>37</v>
       </c>
-      <c r="D175" s="2"/>
-      <c r="E175" s="2"/>
-      <c r="F175" s="11">
+      <c r="D175" s="14">
+        <v>50</v>
+      </c>
+      <c r="E175" s="14">
         <v>75</v>
       </c>
-      <c r="G175" s="15">
+      <c r="F175" s="10">
+        <v>75</v>
+      </c>
+      <c r="G175" s="14">
         <v>29</v>
       </c>
-      <c r="H175" s="19">
+      <c r="H175" s="18">
         <v>26.666666666666668</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="6" t="s">
+      <c r="A176" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C176" s="11">
+      <c r="C176" s="10">
         <v>65.5</v>
       </c>
-      <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
-      <c r="F176" s="11">
+      <c r="D176" s="14">
         <v>54</v>
       </c>
-      <c r="G176" s="15">
+      <c r="E176" s="14">
+        <v>62</v>
+      </c>
+      <c r="F176" s="10">
+        <v>54</v>
+      </c>
+      <c r="G176" s="14">
         <v>55</v>
       </c>
-      <c r="H176" s="19">
+      <c r="H176" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="6" t="s">
+      <c r="A177" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C177" s="11">
+      <c r="C177" s="10">
         <v>46.5</v>
       </c>
-      <c r="D177" s="2"/>
-      <c r="E177" s="2"/>
-      <c r="F177" s="11">
+      <c r="D177" s="14">
+        <v>32</v>
+      </c>
+      <c r="E177" s="14">
+        <v>79</v>
+      </c>
+      <c r="F177" s="10">
         <v>42</v>
       </c>
-      <c r="G177" s="15">
+      <c r="G177" s="14">
         <v>49</v>
       </c>
-      <c r="H177" s="19">
+      <c r="H177" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="6" t="s">
+      <c r="A178" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="B178" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C178" s="11">
+      <c r="C178" s="10">
         <v>91</v>
       </c>
-      <c r="D178" s="2"/>
-      <c r="E178" s="2"/>
-      <c r="F178" s="11">
+      <c r="D178" s="14">
+        <v>54</v>
+      </c>
+      <c r="E178" s="14">
+        <v>81</v>
+      </c>
+      <c r="F178" s="10">
         <v>53</v>
       </c>
-      <c r="G178" s="15">
+      <c r="G178" s="14">
         <v>84</v>
       </c>
-      <c r="H178" s="19">
+      <c r="H178" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="6" t="s">
+      <c r="A179" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="B179" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C179" s="11">
+      <c r="C179" s="10">
         <v>85</v>
       </c>
-      <c r="D179" s="2"/>
-      <c r="E179" s="2"/>
-      <c r="F179" s="11">
+      <c r="D179" s="14">
+        <v>76</v>
+      </c>
+      <c r="E179" s="14">
+        <v>90</v>
+      </c>
+      <c r="F179" s="10">
         <v>53</v>
       </c>
-      <c r="G179" s="15">
+      <c r="G179" s="14">
         <v>78</v>
       </c>
-      <c r="H179" s="19">
+      <c r="H179" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="6" t="s">
+      <c r="A180" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="B180" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C180" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D180" s="2"/>
-      <c r="E180" s="2"/>
-      <c r="F180" s="11">
+      <c r="C180" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D180" s="14">
+        <v>50</v>
+      </c>
+      <c r="E180" s="14">
+        <v>48</v>
+      </c>
+      <c r="F180" s="10">
         <v>44</v>
       </c>
-      <c r="G180" s="15">
+      <c r="G180" s="14">
         <v>42</v>
       </c>
-      <c r="H180" s="19">
+      <c r="H180" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" s="6" t="s">
+      <c r="A181" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B181" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C181" s="11">
-        <v>81</v>
-      </c>
-      <c r="D181" s="2"/>
-      <c r="E181" s="2"/>
-      <c r="F181" s="11">
+      <c r="C181" s="10">
+        <v>81</v>
+      </c>
+      <c r="D181" s="14">
+        <v>40</v>
+      </c>
+      <c r="E181" s="14">
+        <v>78</v>
+      </c>
+      <c r="F181" s="10">
         <v>39</v>
       </c>
-      <c r="G181" s="15">
+      <c r="G181" s="14">
         <v>58</v>
       </c>
-      <c r="H181" s="19">
+      <c r="H181" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="6" t="s">
+      <c r="A182" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="B182" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C182" s="11">
+      <c r="C182" s="10">
         <v>58.5</v>
       </c>
-      <c r="D182" s="2"/>
-      <c r="E182" s="2"/>
-      <c r="F182" s="11">
+      <c r="D182" s="14">
+        <v>61</v>
+      </c>
+      <c r="E182" s="14">
+        <v>66</v>
+      </c>
+      <c r="F182" s="10">
         <v>39</v>
       </c>
-      <c r="G182" s="15">
+      <c r="G182" s="14">
         <v>34</v>
       </c>
-      <c r="H182" s="19">
+      <c r="H182" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="6" t="s">
+      <c r="A183" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C183" s="11">
+      <c r="C183" s="10">
         <v>94.5</v>
       </c>
-      <c r="D183" s="2"/>
-      <c r="E183" s="2"/>
-      <c r="F183" s="11">
+      <c r="D183" s="14">
+        <v>54</v>
+      </c>
+      <c r="E183" s="14">
+        <v>93</v>
+      </c>
+      <c r="F183" s="10">
         <v>55</v>
       </c>
-      <c r="G183" s="15">
+      <c r="G183" s="14">
         <v>49</v>
       </c>
-      <c r="H183" s="19">
+      <c r="H183" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="6" t="s">
+      <c r="A184" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B184" s="3" t="s">
+      <c r="B184" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C184" s="11">
+      <c r="C184" s="10">
         <v>72</v>
       </c>
-      <c r="D184" s="2"/>
-      <c r="E184" s="2"/>
-      <c r="F184" s="11">
+      <c r="D184" s="14">
+        <v>70</v>
+      </c>
+      <c r="E184" s="14">
+        <v>76</v>
+      </c>
+      <c r="F184" s="10">
         <v>39</v>
       </c>
-      <c r="G184" s="15">
+      <c r="G184" s="14">
         <v>67</v>
       </c>
-      <c r="H184" s="19">
+      <c r="H184" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="6" t="s">
+      <c r="A185" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C185" s="11">
+      <c r="C185" s="10">
         <v>85</v>
       </c>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
-      <c r="F185" s="11">
+      <c r="D185" s="14">
+        <v>58</v>
+      </c>
+      <c r="E185" s="14">
+        <v>65</v>
+      </c>
+      <c r="F185" s="10">
         <v>75</v>
       </c>
-      <c r="G185" s="15">
+      <c r="G185" s="14">
         <v>72</v>
       </c>
-      <c r="H185" s="19">
+      <c r="H185" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="6" t="s">
+      <c r="A186" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C186" s="11">
+      <c r="C186" s="10">
         <v>99</v>
       </c>
-      <c r="D186" s="2"/>
-      <c r="E186" s="2"/>
-      <c r="F186" s="11">
+      <c r="D186" s="14">
+        <v>52</v>
+      </c>
+      <c r="E186" s="14">
+        <v>74</v>
+      </c>
+      <c r="F186" s="10">
         <v>62</v>
       </c>
-      <c r="G186" s="15">
+      <c r="G186" s="14">
         <v>58</v>
       </c>
-      <c r="H186" s="19">
+      <c r="H186" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="6" t="s">
+      <c r="A187" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C187" s="11">
+      <c r="C187" s="10">
         <v>44</v>
       </c>
-      <c r="D187" s="2"/>
-      <c r="E187" s="2"/>
-      <c r="F187" s="11">
+      <c r="D187" s="14">
+        <v>57</v>
+      </c>
+      <c r="E187" s="14">
+        <v>58</v>
+      </c>
+      <c r="F187" s="10">
         <v>52</v>
       </c>
-      <c r="G187" s="15">
+      <c r="G187" s="14">
         <v>37</v>
       </c>
-      <c r="H187" s="19">
+      <c r="H187" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="6" t="s">
+      <c r="A188" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="B188" s="3" t="s">
+      <c r="B188" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C188" s="11">
+      <c r="C188" s="10">
         <v>91.5</v>
       </c>
-      <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
-      <c r="F188" s="11">
+      <c r="D188" s="14">
+        <v>14</v>
+      </c>
+      <c r="E188" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F188" s="10">
         <v>73</v>
       </c>
-      <c r="G188" s="15">
+      <c r="G188" s="14">
         <v>42</v>
       </c>
-      <c r="H188" s="19"/>
+      <c r="H188" s="18"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="8" t="s">
+      <c r="A189" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B189" s="7" t="s">
+      <c r="B189" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="C189" s="11">
+      <c r="C189" s="10">
         <v>86</v>
       </c>
-      <c r="D189" s="2"/>
-      <c r="E189" s="2"/>
-      <c r="F189" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G189" s="15">
+      <c r="D189" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E189" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F189" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G189" s="14">
         <v>55</v>
       </c>
-      <c r="H189" s="19"/>
+      <c r="H189" s="18"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="8" t="s">
+      <c r="A190" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B190" s="7" t="s">
+      <c r="B190" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="C190" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D190" s="2"/>
-      <c r="E190" s="2"/>
-      <c r="F190" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G190" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="H190" s="19"/>
+      <c r="C190" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D190" s="14">
+        <v>31</v>
+      </c>
+      <c r="E190" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F190" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G190" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H190" s="18"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="8" t="s">
+      <c r="A191" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B191" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="C191" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D191" s="2"/>
-      <c r="E191" s="2"/>
-      <c r="F191" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G191" s="15">
+      <c r="C191" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D191" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E191" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F191" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G191" s="14">
         <v>57</v>
       </c>
-      <c r="H191" s="19"/>
+      <c r="H191" s="18"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="8" t="s">
+      <c r="A192" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="B192" s="7" t="s">
+      <c r="B192" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="11">
+      <c r="C192" s="10">
         <v>86.5</v>
       </c>
-      <c r="D192" s="2"/>
-      <c r="E192" s="2"/>
-      <c r="F192" s="11">
+      <c r="D192" s="14">
+        <v>23</v>
+      </c>
+      <c r="E192" s="14">
+        <v>68</v>
+      </c>
+      <c r="F192" s="10">
         <v>46</v>
       </c>
-      <c r="G192" s="15">
+      <c r="G192" s="14">
         <v>44</v>
       </c>
-      <c r="H192" s="19"/>
+      <c r="H192" s="18"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="8" t="s">
+      <c r="A193" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="B193" s="7" t="s">
+      <c r="B193" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="C193" s="11">
+      <c r="C193" s="10">
         <v>88.5</v>
       </c>
-      <c r="D193" s="2"/>
-      <c r="E193" s="2"/>
-      <c r="F193" s="11">
+      <c r="D193" s="14">
+        <v>21</v>
+      </c>
+      <c r="E193" s="14">
+        <v>64</v>
+      </c>
+      <c r="F193" s="10">
         <v>47</v>
       </c>
-      <c r="G193" s="15">
+      <c r="G193" s="14">
         <v>44</v>
       </c>
-      <c r="H193" s="19"/>
+      <c r="H193" s="18"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="8" t="s">
+      <c r="A194" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="B194" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="C194" s="11">
+      <c r="C194" s="10">
         <v>93</v>
       </c>
-      <c r="D194" s="2"/>
-      <c r="E194" s="2"/>
-      <c r="F194" s="11">
+      <c r="D194" s="14">
+        <v>86</v>
+      </c>
+      <c r="E194" s="14">
+        <v>73</v>
+      </c>
+      <c r="F194" s="10">
         <v>67</v>
       </c>
-      <c r="G194" s="15">
+      <c r="G194" s="14">
         <v>61</v>
       </c>
-      <c r="H194" s="19"/>
+      <c r="H194" s="18"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="8" t="s">
+      <c r="A195" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="B195" s="7" t="s">
+      <c r="B195" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="C195" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D195" s="2"/>
-      <c r="E195" s="2"/>
-      <c r="F195" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G195" s="15">
+      <c r="C195" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D195" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E195" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F195" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G195" s="14">
         <v>76</v>
       </c>
-      <c r="H195" s="19"/>
+      <c r="H195" s="18"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="8" t="s">
+      <c r="A196" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="B196" s="7" t="s">
+      <c r="B196" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="C196" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
-      <c r="F196" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G196" s="15">
+      <c r="C196" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D196" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E196" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F196" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G196" s="14">
         <v>56</v>
       </c>
-      <c r="H196" s="19"/>
+      <c r="H196" s="18"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="8" t="s">
+      <c r="A197" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="B197" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="C197" s="11">
+      <c r="C197" s="10">
         <v>87</v>
       </c>
-      <c r="D197" s="2"/>
-      <c r="E197" s="2"/>
-      <c r="F197" s="11">
+      <c r="D197" s="14">
+        <v>16</v>
+      </c>
+      <c r="E197" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F197" s="10">
         <v>73</v>
       </c>
-      <c r="G197" s="15">
+      <c r="G197" s="14">
         <v>73</v>
       </c>
-      <c r="H197" s="19"/>
+      <c r="H197" s="18"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="8" t="s">
+      <c r="A198" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B198" s="7" t="s">
+      <c r="B198" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="C198" s="11">
+      <c r="C198" s="10">
         <v>100</v>
       </c>
-      <c r="D198" s="2"/>
-      <c r="E198" s="2"/>
-      <c r="F198" s="11">
+      <c r="D198" s="14">
+        <v>37</v>
+      </c>
+      <c r="E198" s="14">
+        <v>62</v>
+      </c>
+      <c r="F198" s="10">
         <v>60</v>
       </c>
-      <c r="G198" s="15">
+      <c r="G198" s="14">
         <v>42</v>
       </c>
-      <c r="H198" s="19"/>
+      <c r="H198" s="18"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="8" t="s">
+      <c r="A199" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="B199" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="C199" s="11">
+      <c r="C199" s="10">
         <v>69</v>
       </c>
-      <c r="D199" s="2"/>
-      <c r="E199" s="2"/>
-      <c r="F199" s="11">
+      <c r="D199" s="14">
+        <v>42</v>
+      </c>
+      <c r="E199" s="14">
+        <v>78</v>
+      </c>
+      <c r="F199" s="10">
         <v>47</v>
       </c>
-      <c r="G199" s="15">
+      <c r="G199" s="14">
         <v>45</v>
       </c>
-      <c r="H199" s="19"/>
+      <c r="H199" s="18"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="8" t="s">
+      <c r="A200" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="B200" s="7" t="s">
+      <c r="B200" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C200" s="11">
+      <c r="C200" s="10">
         <v>83</v>
       </c>
-      <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="11">
+      <c r="D200" s="14">
+        <v>35</v>
+      </c>
+      <c r="E200" s="14">
+        <v>71</v>
+      </c>
+      <c r="F200" s="10">
         <v>43</v>
       </c>
-      <c r="G200" s="15">
+      <c r="G200" s="14">
         <v>57</v>
       </c>
-      <c r="H200" s="19"/>
+      <c r="H200" s="18"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="8" t="s">
+      <c r="A201" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B201" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="C201" s="11">
+      <c r="C201" s="10">
         <v>57</v>
       </c>
-      <c r="D201" s="2"/>
-      <c r="E201" s="2"/>
-      <c r="F201" s="11">
+      <c r="D201" s="14">
+        <v>29</v>
+      </c>
+      <c r="E201" s="14">
+        <v>43</v>
+      </c>
+      <c r="F201" s="10">
         <v>47</v>
       </c>
-      <c r="G201" s="15">
+      <c r="G201" s="14">
         <v>37</v>
       </c>
-      <c r="H201" s="19"/>
+      <c r="H201" s="18"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="8" t="s">
+      <c r="A202" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B202" s="7" t="s">
+      <c r="B202" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="C202" s="11">
+      <c r="C202" s="10">
         <v>100</v>
       </c>
-      <c r="D202" s="2"/>
-      <c r="E202" s="2"/>
-      <c r="F202" s="11">
+      <c r="D202" s="14">
+        <v>28</v>
+      </c>
+      <c r="E202" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F202" s="10">
         <v>73</v>
       </c>
-      <c r="G202" s="15">
+      <c r="G202" s="14">
         <v>73</v>
       </c>
-      <c r="H202" s="19"/>
+      <c r="H202" s="18"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" s="8" t="s">
+      <c r="A203" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="B203" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="C203" s="11">
+      <c r="C203" s="10">
         <v>68.5</v>
       </c>
-      <c r="D203" s="2"/>
-      <c r="E203" s="2"/>
-      <c r="F203" s="11">
+      <c r="D203" s="14">
+        <v>69</v>
+      </c>
+      <c r="E203" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F203" s="10">
         <v>60</v>
       </c>
-      <c r="G203" s="15">
+      <c r="G203" s="14">
         <v>51</v>
       </c>
-      <c r="H203" s="19"/>
+      <c r="H203" s="18"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="8" t="s">
+      <c r="A204" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="B204" s="7" t="s">
+      <c r="B204" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="C204" s="11">
+      <c r="C204" s="10">
         <v>52.5</v>
       </c>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="11">
+      <c r="D204" s="14">
+        <v>24</v>
+      </c>
+      <c r="E204" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F204" s="10">
         <v>73</v>
       </c>
-      <c r="G204" s="15">
+      <c r="G204" s="14">
         <v>55</v>
       </c>
-      <c r="H204" s="19"/>
+      <c r="H204" s="18"/>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A205" s="8" t="s">
+      <c r="A205" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="B205" s="7" t="s">
+      <c r="B205" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="C205" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="G205" s="15">
+      <c r="C205" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D205" s="14">
+        <v>15</v>
+      </c>
+      <c r="E205" s="14">
+        <v>66</v>
+      </c>
+      <c r="F205" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G205" s="14">
         <v>36</v>
       </c>
-      <c r="H205" s="19"/>
+      <c r="H205" s="18"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="8" t="s">
+      <c r="A206" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="B206" s="7" t="s">
+      <c r="B206" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="C206" s="11">
+      <c r="C206" s="10">
         <v>83.5</v>
       </c>
-      <c r="D206" s="2"/>
-      <c r="E206" s="2"/>
-      <c r="F206" s="11">
+      <c r="D206" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E206" s="14">
+        <v>86</v>
+      </c>
+      <c r="F206" s="10">
         <v>60</v>
       </c>
-      <c r="G206" s="15">
+      <c r="G206" s="14">
         <v>42</v>
       </c>
-      <c r="H206" s="19"/>
+      <c r="H206" s="18"/>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A207" s="8" t="s">
+      <c r="A207" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="B207" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="C207" s="11">
+      <c r="C207" s="10">
         <v>72.5</v>
       </c>
-      <c r="D207" s="2"/>
-      <c r="E207" s="2"/>
-      <c r="F207" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="G207" s="15">
+      <c r="D207" s="14">
+        <v>60</v>
+      </c>
+      <c r="E207" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F207" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G207" s="14">
         <v>49</v>
       </c>
-      <c r="H207" s="19"/>
+      <c r="H207" s="18"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A208" s="8" t="s">
+      <c r="A208" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B208" s="7" t="s">
+      <c r="B208" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="C208" s="11">
+      <c r="C208" s="10">
         <v>31.5</v>
       </c>
-      <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
-      <c r="F208" s="11">
+      <c r="D208" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E208" s="14">
+        <v>49</v>
+      </c>
+      <c r="F208" s="10">
         <v>50</v>
       </c>
-      <c r="G208" s="15">
+      <c r="G208" s="14">
         <v>16</v>
       </c>
-      <c r="H208" s="19"/>
+      <c r="H208" s="18"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209" s="8" t="s">
+      <c r="A209" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B209" s="7" t="s">
+      <c r="B209" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="C209" s="11">
+      <c r="C209" s="10">
         <v>53</v>
       </c>
-      <c r="D209" s="2"/>
-      <c r="E209" s="2"/>
-      <c r="F209" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="G209" s="15">
+      <c r="D209" s="14">
+        <v>11</v>
+      </c>
+      <c r="E209" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F209" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G209" s="14">
         <v>42</v>
       </c>
-      <c r="H209" s="19"/>
+      <c r="H209" s="18"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A210" s="8" t="s">
+      <c r="A210" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="B210" s="7" t="s">
+      <c r="B210" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="C210" s="11">
+      <c r="C210" s="10">
         <v>66</v>
       </c>
-      <c r="D210" s="2"/>
-      <c r="E210" s="2"/>
-      <c r="F210" s="11">
+      <c r="D210" s="14">
+        <v>33</v>
+      </c>
+      <c r="E210" s="14">
+        <v>41</v>
+      </c>
+      <c r="F210" s="10">
         <v>60</v>
       </c>
-      <c r="G210" s="15">
+      <c r="G210" s="14">
         <v>43</v>
       </c>
-      <c r="H210" s="19"/>
+      <c r="H210" s="18"/>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211" s="8" t="s">
+      <c r="A211" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B211" s="7" t="s">
+      <c r="B211" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="C211" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D211" s="2"/>
-      <c r="E211" s="2"/>
-      <c r="F211" s="11">
+      <c r="C211" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D211" s="14">
         <v>60</v>
       </c>
-      <c r="G211" s="15">
+      <c r="E211" s="14">
+        <v>69</v>
+      </c>
+      <c r="F211" s="10">
+        <v>60</v>
+      </c>
+      <c r="G211" s="14">
         <v>56</v>
       </c>
-      <c r="H211" s="19"/>
+      <c r="H211" s="18"/>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A212" s="8" t="s">
+      <c r="A212" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B212" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="C212" s="11">
+      <c r="C212" s="10">
         <v>65</v>
       </c>
-      <c r="D212" s="2"/>
-      <c r="E212" s="2"/>
-      <c r="F212" s="11">
+      <c r="D212" s="14">
+        <v>38</v>
+      </c>
+      <c r="E212" s="14">
+        <v>34</v>
+      </c>
+      <c r="F212" s="10">
         <v>73</v>
       </c>
-      <c r="G212" s="15">
+      <c r="G212" s="14">
         <v>45</v>
       </c>
-      <c r="H212" s="19"/>
+      <c r="H212" s="18"/>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A213" s="8" t="s">
+      <c r="A213" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="B213" s="7" t="s">
+      <c r="B213" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="C213" s="11">
+      <c r="C213" s="10">
         <v>65</v>
       </c>
-      <c r="D213" s="2"/>
-      <c r="E213" s="2"/>
-      <c r="F213" s="11">
+      <c r="D213" s="14">
+        <v>21</v>
+      </c>
+      <c r="E213" s="14">
         <v>60</v>
       </c>
-      <c r="G213" s="15">
+      <c r="F213" s="10">
+        <v>60</v>
+      </c>
+      <c r="G213" s="14">
         <v>55</v>
       </c>
-      <c r="H213" s="19"/>
+      <c r="H213" s="18"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A214" s="8" t="s">
+      <c r="A214" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B214" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="C214" s="11">
+      <c r="C214" s="10">
         <v>84</v>
       </c>
-      <c r="D214" s="2"/>
-      <c r="E214" s="2"/>
-      <c r="F214" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G214" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="H214" s="19"/>
+      <c r="D214" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E214" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F214" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G214" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H214" s="18"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A215" s="8" t="s">
+      <c r="A215" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="B215" s="7" t="s">
+      <c r="B215" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="C215" s="11">
+      <c r="C215" s="10">
         <v>44</v>
       </c>
-      <c r="D215" s="2"/>
-      <c r="E215" s="2"/>
-      <c r="F215" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G215" s="15">
+      <c r="D215" s="14">
+        <v>33</v>
+      </c>
+      <c r="E215" s="14">
+        <v>55</v>
+      </c>
+      <c r="F215" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G215" s="14">
         <v>28</v>
       </c>
-      <c r="H215" s="19"/>
+      <c r="H215" s="18"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216" s="8" t="s">
+      <c r="A216" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="B216" s="7" t="s">
+      <c r="B216" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="C216" s="11">
+      <c r="C216" s="10">
         <v>84.5</v>
       </c>
-      <c r="D216" s="2"/>
-      <c r="E216" s="2"/>
-      <c r="F216" s="11">
+      <c r="D216" s="14">
+        <v>39</v>
+      </c>
+      <c r="E216" s="14">
+        <v>66</v>
+      </c>
+      <c r="F216" s="10">
         <v>60</v>
       </c>
-      <c r="G216" s="15">
+      <c r="G216" s="14">
         <v>48</v>
       </c>
-      <c r="H216" s="19"/>
+      <c r="H216" s="18"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="8" t="s">
+      <c r="A217" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="B217" s="7" t="s">
+      <c r="B217" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="C217" s="11">
+      <c r="C217" s="10">
         <v>90</v>
       </c>
-      <c r="D217" s="2"/>
-      <c r="E217" s="2"/>
-      <c r="F217" s="11">
+      <c r="D217" s="14">
+        <v>29</v>
+      </c>
+      <c r="E217" s="14">
+        <v>38</v>
+      </c>
+      <c r="F217" s="10">
         <v>67</v>
       </c>
-      <c r="G217" s="15">
+      <c r="G217" s="14">
         <v>58</v>
       </c>
-      <c r="H217" s="19"/>
+      <c r="H217" s="18"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218" s="8" t="s">
+      <c r="A218" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="B218" s="7" t="s">
+      <c r="B218" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="C218" s="11">
+      <c r="C218" s="10">
         <v>78</v>
       </c>
-      <c r="D218" s="2"/>
-      <c r="E218" s="2"/>
-      <c r="F218" s="11">
+      <c r="D218" s="14">
+        <v>41</v>
+      </c>
+      <c r="E218" s="14">
         <v>60</v>
       </c>
-      <c r="G218" s="15">
+      <c r="F218" s="10">
+        <v>60</v>
+      </c>
+      <c r="G218" s="14">
         <v>67</v>
       </c>
-      <c r="H218" s="19"/>
+      <c r="H218" s="18"/>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A219" s="8" t="s">
+      <c r="A219" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="B219" s="7" t="s">
+      <c r="B219" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="C219" s="11">
+      <c r="C219" s="10">
         <v>69</v>
       </c>
-      <c r="D219" s="2"/>
-      <c r="E219" s="2"/>
-      <c r="F219" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G219" s="15">
+      <c r="D219" s="14">
+        <v>44</v>
+      </c>
+      <c r="E219" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F219" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G219" s="14">
         <v>59</v>
       </c>
-      <c r="H219" s="19"/>
+      <c r="H219" s="18"/>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A220" s="8" t="s">
+      <c r="A220" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B220" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="C220" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
-      <c r="F220" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G220" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="H220" s="19"/>
+      <c r="C220" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D220" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E220" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F220" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G220" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H220" s="18"/>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A221" s="8" t="s">
+      <c r="A221" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="B221" s="7" t="s">
+      <c r="B221" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="C221" s="11">
+      <c r="C221" s="10">
         <v>79</v>
       </c>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
-      <c r="F221" s="11">
+      <c r="D221" s="14">
+        <v>17</v>
+      </c>
+      <c r="E221" s="14">
+        <v>46</v>
+      </c>
+      <c r="F221" s="10">
         <v>60</v>
       </c>
-      <c r="G221" s="15">
+      <c r="G221" s="14">
         <v>41</v>
       </c>
-      <c r="H221" s="19"/>
+      <c r="H221" s="18"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A222" s="8" t="s">
+      <c r="A222" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B222" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="C222" s="11">
+      <c r="C222" s="10">
         <v>54</v>
       </c>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-      <c r="F222" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G222" s="15">
+      <c r="D222" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E222" s="14">
+        <v>82</v>
+      </c>
+      <c r="F222" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G222" s="14">
         <v>38</v>
       </c>
-      <c r="H222" s="19"/>
+      <c r="H222" s="18"/>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223" s="8" t="s">
+      <c r="A223" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="B223" s="7" t="s">
+      <c r="B223" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="C223" s="11">
+      <c r="C223" s="10">
         <v>60</v>
       </c>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
-      <c r="F223" s="11">
-        <v>81</v>
-      </c>
-      <c r="G223" s="15">
+      <c r="D223" s="14">
+        <v>42</v>
+      </c>
+      <c r="E223" s="14">
+        <v>61</v>
+      </c>
+      <c r="F223" s="10">
+        <v>81</v>
+      </c>
+      <c r="G223" s="14">
         <v>39</v>
       </c>
-      <c r="H223" s="19"/>
+      <c r="H223" s="18"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A224" s="8" t="s">
+      <c r="A224" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B224" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="C224" s="11">
+      <c r="C224" s="10">
         <v>38.5</v>
       </c>
-      <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
-      <c r="F224" s="11">
-        <v>81</v>
-      </c>
-      <c r="G224" s="15">
+      <c r="D224" s="14">
+        <v>47</v>
+      </c>
+      <c r="E224" s="14">
+        <v>59</v>
+      </c>
+      <c r="F224" s="10">
+        <v>81</v>
+      </c>
+      <c r="G224" s="14">
         <v>68</v>
       </c>
-      <c r="H224" s="19"/>
+      <c r="H224" s="18"/>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A225" s="8" t="s">
+      <c r="A225" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="B225" s="7" t="s">
+      <c r="B225" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="C225" s="11">
+      <c r="C225" s="10">
         <v>89</v>
       </c>
-      <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
-      <c r="F225" s="11">
-        <v>81</v>
-      </c>
-      <c r="G225" s="15">
+      <c r="D225" s="14">
+        <v>44</v>
+      </c>
+      <c r="E225" s="14">
+        <v>48</v>
+      </c>
+      <c r="F225" s="10">
+        <v>81</v>
+      </c>
+      <c r="G225" s="14">
         <v>57</v>
       </c>
-      <c r="H225" s="19"/>
+      <c r="H225" s="18"/>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A226" s="8" t="s">
+      <c r="A226" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B226" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="C226" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D226" s="2"/>
-      <c r="E226" s="2"/>
-      <c r="F226" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G226" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="H226" s="19"/>
+      <c r="C226" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D226" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E226" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F226" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G226" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H226" s="18"/>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A227" s="8" t="s">
+      <c r="A227" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="B227" s="7" t="s">
+      <c r="B227" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="C227" s="11">
+      <c r="C227" s="10">
         <v>35</v>
       </c>
-      <c r="D227" s="2"/>
-      <c r="E227" s="2"/>
-      <c r="F227" s="11">
-        <v>81</v>
-      </c>
-      <c r="G227" s="15">
+      <c r="D227" s="14">
+        <v>24</v>
+      </c>
+      <c r="E227" s="14">
+        <v>69</v>
+      </c>
+      <c r="F227" s="10">
+        <v>81</v>
+      </c>
+      <c r="G227" s="14">
         <v>23</v>
       </c>
-      <c r="H227" s="19"/>
+      <c r="H227" s="18"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A228" s="8" t="s">
+      <c r="A228" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="B228" s="7" t="s">
+      <c r="B228" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="C228" s="11">
+      <c r="C228" s="10">
         <v>69</v>
       </c>
-      <c r="D228" s="2"/>
-      <c r="E228" s="2"/>
-      <c r="F228" s="11">
-        <v>81</v>
-      </c>
-      <c r="G228" s="15">
+      <c r="D228" s="14">
+        <v>9</v>
+      </c>
+      <c r="E228" s="14">
+        <v>93</v>
+      </c>
+      <c r="F228" s="10">
+        <v>81</v>
+      </c>
+      <c r="G228" s="14">
         <v>55</v>
       </c>
-      <c r="H228" s="19"/>
+      <c r="H228" s="18"/>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A229" s="8" t="s">
+      <c r="A229" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B229" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="C229" s="11">
+      <c r="C229" s="10">
         <v>62.5</v>
       </c>
-      <c r="D229" s="2"/>
-      <c r="E229" s="2"/>
-      <c r="F229" s="11">
+      <c r="D229" s="14">
+        <v>22</v>
+      </c>
+      <c r="E229" s="14">
+        <v>53</v>
+      </c>
+      <c r="F229" s="10">
         <v>67</v>
       </c>
-      <c r="G229" s="15">
+      <c r="G229" s="14">
         <v>50</v>
       </c>
-      <c r="H229" s="19"/>
+      <c r="H229" s="18"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A230" s="8" t="s">
+      <c r="A230" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="B230" s="7" t="s">
+      <c r="B230" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="C230" s="11">
+      <c r="C230" s="10">
         <v>65</v>
       </c>
-      <c r="D230" s="2"/>
-      <c r="E230" s="2"/>
-      <c r="F230" s="11">
+      <c r="D230" s="14">
+        <v>48</v>
+      </c>
+      <c r="E230" s="14">
+        <v>69</v>
+      </c>
+      <c r="F230" s="10">
         <v>67</v>
       </c>
-      <c r="G230" s="15">
+      <c r="G230" s="14">
         <v>50</v>
       </c>
-      <c r="H230" s="19"/>
+      <c r="H230" s="18"/>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A231" s="8" t="s">
+      <c r="A231" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B231" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="C231" s="11">
+      <c r="C231" s="10">
         <v>49.5</v>
       </c>
-      <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-      <c r="F231" s="11">
-        <v>81</v>
-      </c>
-      <c r="G231" s="15">
+      <c r="D231" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E231" s="14">
+        <v>18</v>
+      </c>
+      <c r="F231" s="10">
+        <v>81</v>
+      </c>
+      <c r="G231" s="14">
         <v>44</v>
       </c>
-      <c r="H231" s="19"/>
+      <c r="H231" s="18"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A232" s="8" t="s">
+      <c r="A232" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="B232" s="7" t="s">
+      <c r="B232" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="C232" s="11">
+      <c r="C232" s="10">
         <v>85</v>
       </c>
-      <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
-      <c r="F232" s="11">
+      <c r="D232" s="14">
+        <v>23</v>
+      </c>
+      <c r="E232" s="14">
+        <v>69</v>
+      </c>
+      <c r="F232" s="10">
         <v>67</v>
       </c>
-      <c r="G232" s="15">
+      <c r="G232" s="14">
         <v>55</v>
       </c>
-      <c r="H232" s="19"/>
+      <c r="H232" s="18"/>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A233" s="8" t="s">
+      <c r="A233" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B233" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="C233" s="11">
+      <c r="C233" s="10">
         <v>77.5</v>
       </c>
-      <c r="D233" s="2"/>
-      <c r="E233" s="2"/>
-      <c r="F233" s="11">
+      <c r="D233" s="14">
+        <v>34</v>
+      </c>
+      <c r="E233" s="14">
+        <v>61</v>
+      </c>
+      <c r="F233" s="10">
         <v>47</v>
       </c>
-      <c r="G233" s="15">
+      <c r="G233" s="14">
         <v>56</v>
       </c>
-      <c r="H233" s="19"/>
+      <c r="H233" s="18"/>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A234" s="8" t="s">
+      <c r="A234" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="C234" s="11">
+      <c r="C234" s="10">
         <v>57</v>
       </c>
-      <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
-      <c r="F234" s="11">
+      <c r="D234" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E234" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F234" s="10">
         <v>47</v>
       </c>
-      <c r="G234" s="15">
+      <c r="G234" s="14">
         <v>53</v>
       </c>
-      <c r="H234" s="19"/>
+      <c r="H234" s="18"/>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A235" s="8" t="s">
+      <c r="A235" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="B235" s="7" t="s">
+      <c r="B235" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="C235" s="11">
+      <c r="C235" s="10">
         <v>92.5</v>
       </c>
-      <c r="D235" s="2"/>
-      <c r="E235" s="2"/>
-      <c r="F235" s="11">
+      <c r="D235" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E235" s="14">
+        <v>86</v>
+      </c>
+      <c r="F235" s="10">
         <v>60</v>
       </c>
-      <c r="G235" s="15">
+      <c r="G235" s="14">
         <v>57</v>
       </c>
-      <c r="H235" s="19"/>
+      <c r="H235" s="18"/>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A236" s="8" t="s">
+      <c r="A236" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="B236" s="7" t="s">
+      <c r="B236" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="C236" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D236" s="2"/>
-      <c r="E236" s="2"/>
-      <c r="F236" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G236" s="15">
+      <c r="C236" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D236" s="14">
+        <v>54</v>
+      </c>
+      <c r="E236" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F236" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G236" s="14">
         <v>52</v>
       </c>
-      <c r="H236" s="19"/>
+      <c r="H236" s="18"/>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A237" s="8" t="s">
+      <c r="A237" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="B237" s="4" t="s">
+      <c r="B237" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C237" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D237" s="2"/>
-      <c r="E237" s="2"/>
-      <c r="F237" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G237" s="15">
+      <c r="C237" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D237" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E237" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F237" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G237" s="14">
         <v>25</v>
       </c>
-      <c r="H237" s="19"/>
+      <c r="H237" s="18"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A238" s="8" t="s">
+      <c r="A238" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="B238" s="4" t="s">
+      <c r="B238" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C238" s="11">
+      <c r="C238" s="10">
         <v>30</v>
       </c>
-      <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
-      <c r="F238" s="11">
+      <c r="D238" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E238" s="14">
+        <v>34</v>
+      </c>
+      <c r="F238" s="10">
         <v>43</v>
       </c>
-      <c r="G238" s="15">
+      <c r="G238" s="14">
         <v>7</v>
       </c>
-      <c r="H238" s="19"/>
+      <c r="H238" s="18"/>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A239" s="8" t="s">
+      <c r="A239" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="B239" s="4" t="s">
+      <c r="B239" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="C239" s="11">
+      <c r="C239" s="10">
         <v>74</v>
       </c>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
-      <c r="F239" s="11">
+      <c r="D239" s="14">
+        <v>17</v>
+      </c>
+      <c r="E239" s="14">
+        <v>31</v>
+      </c>
+      <c r="F239" s="10">
         <v>73</v>
       </c>
-      <c r="G239" s="15">
+      <c r="G239" s="14">
         <v>37</v>
       </c>
-      <c r="H239" s="19"/>
+      <c r="H239" s="18"/>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A240" s="8" t="s">
+      <c r="A240" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="B240" s="9" t="s">
+      <c r="B240" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="C240" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-      <c r="F240" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G240" s="15">
+      <c r="C240" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D240" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E240" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G240" s="14">
         <v>39</v>
       </c>
-      <c r="H240" s="19"/>
+      <c r="H240" s="18"/>
     </row>
     <row r="241" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A241" s="10"/>
-      <c r="B241" s="10"/>
-      <c r="C241" s="12"/>
-      <c r="D241" s="10"/>
-      <c r="E241" s="10"/>
-      <c r="F241" s="10"/>
-      <c r="G241" s="10"/>
+      <c r="A241" s="9"/>
+      <c r="B241" s="9"/>
+      <c r="C241" s="11"/>
+      <c r="D241" s="9"/>
+      <c r="E241" s="9"/>
+      <c r="F241" s="9"/>
+      <c r="G241" s="9"/>
     </row>
     <row r="242" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A242" s="10"/>
-      <c r="B242" s="10"/>
-      <c r="C242" s="12"/>
-      <c r="D242" s="10"/>
-      <c r="E242" s="10"/>
-      <c r="F242" s="10"/>
-      <c r="G242" s="10"/>
+      <c r="A242" s="9"/>
+      <c r="B242" s="9"/>
+      <c r="C242" s="11"/>
+      <c r="D242" s="9"/>
+      <c r="E242" s="9"/>
+      <c r="F242" s="9"/>
+      <c r="G242" s="9"/>
     </row>
     <row r="243" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A243" s="10"/>
-      <c r="B243" s="10"/>
-      <c r="C243" s="12"/>
-      <c r="D243" s="10"/>
-      <c r="E243" s="10"/>
-      <c r="F243" s="10"/>
-      <c r="G243" s="10"/>
+      <c r="A243" s="9"/>
+      <c r="B243" s="9"/>
+      <c r="C243" s="11"/>
+      <c r="D243" s="9"/>
+      <c r="E243" s="9"/>
+      <c r="F243" s="9"/>
+      <c r="G243" s="9"/>
     </row>
     <row r="244" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A244" s="10"/>
-      <c r="B244" s="10"/>
-      <c r="C244" s="12"/>
-      <c r="D244" s="10"/>
-      <c r="E244" s="10"/>
-      <c r="F244" s="10"/>
-      <c r="G244" s="10"/>
+      <c r="A244" s="9"/>
+      <c r="B244" s="9"/>
+      <c r="C244" s="11"/>
+      <c r="D244" s="9"/>
+      <c r="E244" s="9"/>
+      <c r="F244" s="9"/>
+      <c r="G244" s="9"/>
     </row>
     <row r="245" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A245" s="10"/>
-      <c r="B245" s="10"/>
-      <c r="C245" s="12"/>
-      <c r="D245" s="10"/>
-      <c r="E245" s="10"/>
-      <c r="F245" s="10"/>
-      <c r="G245" s="10"/>
+      <c r="A245" s="9"/>
+      <c r="B245" s="9"/>
+      <c r="C245" s="11"/>
+      <c r="D245" s="9"/>
+      <c r="E245" s="9"/>
+      <c r="F245" s="9"/>
+      <c r="G245" s="9"/>
     </row>
     <row r="246" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A246" s="10"/>
-      <c r="B246" s="10"/>
-      <c r="C246" s="12"/>
-      <c r="D246" s="10"/>
-      <c r="E246" s="10"/>
-      <c r="F246" s="10"/>
-      <c r="G246" s="10"/>
+      <c r="A246" s="9"/>
+      <c r="B246" s="9"/>
+      <c r="C246" s="11"/>
+      <c r="D246" s="9"/>
+      <c r="E246" s="9"/>
+      <c r="F246" s="9"/>
+      <c r="G246" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7229,18 +8182,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7421,18 +8374,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395391AC-196F-46E6-8F58-D36D62694251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA812DB2-5092-42A2-927D-830ECDEBF7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="487">
   <si>
     <t>Name</t>
   </si>
@@ -2153,8 +2153,8 @@
       <c r="C7" s="10">
         <v>82.5</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>81</v>
+      <c r="D7" s="14">
+        <v>73</v>
       </c>
       <c r="E7" s="14">
         <v>66</v>
@@ -3034,8 +3034,8 @@
       <c r="B41" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>81</v>
+      <c r="C41" s="10">
+        <v>39</v>
       </c>
       <c r="D41" s="14">
         <v>29</v>
@@ -4129,8 +4129,8 @@
       <c r="C83" s="10">
         <v>93</v>
       </c>
-      <c r="D83" s="14" t="s">
-        <v>81</v>
+      <c r="D83" s="14">
+        <v>61</v>
       </c>
       <c r="E83" s="14">
         <v>70</v>
@@ -4857,8 +4857,8 @@
       <c r="C111" s="10">
         <v>39.5</v>
       </c>
-      <c r="D111" s="14" t="s">
-        <v>81</v>
+      <c r="D111" s="14">
+        <v>41</v>
       </c>
       <c r="E111" s="14">
         <v>38</v>
@@ -5637,8 +5637,8 @@
       <c r="C141" s="10">
         <v>96.5</v>
       </c>
-      <c r="D141" s="14" t="s">
-        <v>81</v>
+      <c r="D141" s="14">
+        <v>49</v>
       </c>
       <c r="E141" s="14">
         <v>80</v>
@@ -5972,8 +5972,8 @@
       <c r="B154" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C154" s="10" t="s">
-        <v>81</v>
+      <c r="C154" s="10">
+        <v>82</v>
       </c>
       <c r="D154" s="14">
         <v>38</v>
@@ -6053,8 +6053,8 @@
       <c r="C157" s="10">
         <v>81</v>
       </c>
-      <c r="D157" s="14" t="s">
-        <v>81</v>
+      <c r="D157" s="14">
+        <v>92</v>
       </c>
       <c r="E157" s="14">
         <v>59</v>
@@ -6131,8 +6131,8 @@
       <c r="C160" s="10">
         <v>79</v>
       </c>
-      <c r="D160" s="14" t="s">
-        <v>81</v>
+      <c r="D160" s="14">
+        <v>79</v>
       </c>
       <c r="E160" s="14">
         <v>72</v>
@@ -7291,8 +7291,8 @@
       <c r="C206" s="10">
         <v>83.5</v>
       </c>
-      <c r="D206" s="14" t="s">
-        <v>81</v>
+      <c r="D206" s="14">
+        <v>59</v>
       </c>
       <c r="E206" s="14">
         <v>86</v>
@@ -7339,8 +7339,8 @@
       <c r="C208" s="10">
         <v>31.5</v>
       </c>
-      <c r="D208" s="14" t="s">
-        <v>81</v>
+      <c r="D208" s="14">
+        <v>39</v>
       </c>
       <c r="E208" s="14">
         <v>49</v>
@@ -7408,8 +7408,8 @@
       <c r="B211" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="C211" s="10" t="s">
-        <v>81</v>
+      <c r="C211" s="10">
+        <v>96</v>
       </c>
       <c r="D211" s="14">
         <v>60</v>
@@ -7891,8 +7891,8 @@
       <c r="C231" s="10">
         <v>49.5</v>
       </c>
-      <c r="D231" s="14" t="s">
-        <v>81</v>
+      <c r="D231" s="14">
+        <v>75</v>
       </c>
       <c r="E231" s="14">
         <v>18</v>
@@ -7987,8 +7987,8 @@
       <c r="C235" s="10">
         <v>92.5</v>
       </c>
-      <c r="D235" s="14" t="s">
-        <v>81</v>
+      <c r="D235" s="14">
+        <v>78</v>
       </c>
       <c r="E235" s="14">
         <v>86</v>
@@ -8182,18 +8182,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8374,18 +8374,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA812DB2-5092-42A2-927D-830ECDEBF7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9309FDF-E708-4A52-AC9C-AC1F5BBFF629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
@@ -2030,7 +2030,7 @@
         <v>62</v>
       </c>
       <c r="F2" s="10">
-        <v>73</v>
+        <v>43.8</v>
       </c>
       <c r="G2" s="14">
         <v>38</v>
@@ -2056,7 +2056,7 @@
         <v>85</v>
       </c>
       <c r="F3" s="10">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G3" s="14">
         <v>87</v>
@@ -2082,7 +2082,7 @@
         <v>76</v>
       </c>
       <c r="F4" s="10">
-        <v>54</v>
+        <v>32.4</v>
       </c>
       <c r="G4" s="14">
         <v>75</v>
@@ -2108,7 +2108,7 @@
         <v>65</v>
       </c>
       <c r="F5" s="10">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G5" s="14">
         <v>46</v>
@@ -2134,7 +2134,7 @@
         <v>66</v>
       </c>
       <c r="F6" s="10">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G6" s="14">
         <v>40</v>
@@ -2160,7 +2160,7 @@
         <v>66</v>
       </c>
       <c r="F7" s="10">
-        <v>65</v>
+        <v>38.999999999999993</v>
       </c>
       <c r="G7" s="14">
         <v>64</v>
@@ -2186,7 +2186,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="10">
-        <v>42</v>
+        <v>42.199999999999996</v>
       </c>
       <c r="G8" s="14">
         <v>77</v>
@@ -2212,7 +2212,7 @@
         <v>77</v>
       </c>
       <c r="F9" s="10">
-        <v>55</v>
+        <v>48.800000000000004</v>
       </c>
       <c r="G9" s="14">
         <v>46</v>
@@ -2238,7 +2238,7 @@
         <v>71</v>
       </c>
       <c r="F10" s="10">
-        <v>39</v>
+        <v>38.4</v>
       </c>
       <c r="G10" s="14">
         <v>48</v>
@@ -2264,7 +2264,7 @@
         <v>43</v>
       </c>
       <c r="F11" s="10">
-        <v>25</v>
+        <v>27.200000000000003</v>
       </c>
       <c r="G11" s="14">
         <v>34</v>
@@ -2290,7 +2290,7 @@
         <v>94</v>
       </c>
       <c r="F12" s="10">
-        <v>65</v>
+        <v>50.79999999999999</v>
       </c>
       <c r="G12" s="14">
         <v>35</v>
@@ -2316,7 +2316,7 @@
         <v>71</v>
       </c>
       <c r="F13" s="10">
-        <v>42</v>
+        <v>59.199999999999996</v>
       </c>
       <c r="G13" s="14">
         <v>40</v>
@@ -2342,7 +2342,7 @@
         <v>95</v>
       </c>
       <c r="F14" s="10">
-        <v>54</v>
+        <v>32.4</v>
       </c>
       <c r="G14" s="14">
         <v>86</v>
@@ -2368,7 +2368,7 @@
         <v>69</v>
       </c>
       <c r="F15" s="10">
-        <v>62</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="G15" s="14">
         <v>61</v>
@@ -2394,7 +2394,7 @@
         <v>98</v>
       </c>
       <c r="F16" s="10">
-        <v>66</v>
+        <v>56.999999999999993</v>
       </c>
       <c r="G16" s="14">
         <v>57</v>
@@ -2420,7 +2420,7 @@
         <v>78</v>
       </c>
       <c r="F17" s="10">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G17" s="14">
         <v>79</v>
@@ -2446,7 +2446,7 @@
         <v>85</v>
       </c>
       <c r="F18" s="10">
-        <v>44</v>
+        <v>26.400000000000002</v>
       </c>
       <c r="G18" s="14">
         <v>71</v>
@@ -2472,7 +2472,7 @@
         <v>87</v>
       </c>
       <c r="F19" s="10">
-        <v>47</v>
+        <v>36.599999999999994</v>
       </c>
       <c r="G19" s="14">
         <v>91</v>
@@ -2498,7 +2498,7 @@
         <v>64</v>
       </c>
       <c r="F20" s="10">
-        <v>75</v>
+        <v>68.399999999999991</v>
       </c>
       <c r="G20" s="14">
         <v>71</v>
@@ -2524,7 +2524,7 @@
         <v>86</v>
       </c>
       <c r="F21" s="10">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G21" s="14">
         <v>97</v>
@@ -2550,7 +2550,7 @@
         <v>61</v>
       </c>
       <c r="F22" s="10">
-        <v>75</v>
+        <v>52.6</v>
       </c>
       <c r="G22" s="14">
         <v>53</v>
@@ -2576,7 +2576,7 @@
         <v>81</v>
       </c>
       <c r="F23" s="10">
-        <v>66</v>
+        <v>69.199999999999989</v>
       </c>
       <c r="G23" s="14">
         <v>73</v>
@@ -2602,7 +2602,7 @@
         <v>78</v>
       </c>
       <c r="F24" s="10">
-        <v>66</v>
+        <v>69.199999999999989</v>
       </c>
       <c r="G24" s="14">
         <v>33</v>
@@ -2628,7 +2628,7 @@
         <v>97</v>
       </c>
       <c r="F25" s="10">
-        <v>63</v>
+        <v>66.8</v>
       </c>
       <c r="G25" s="14">
         <v>82</v>
@@ -2654,7 +2654,7 @@
         <v>71</v>
       </c>
       <c r="F26" s="10">
-        <v>55</v>
+        <v>45.2</v>
       </c>
       <c r="G26" s="14">
         <v>45</v>
@@ -2680,7 +2680,7 @@
         <v>82</v>
       </c>
       <c r="F27" s="10">
-        <v>75</v>
+        <v>57.4</v>
       </c>
       <c r="G27" s="14">
         <v>51</v>
@@ -2706,7 +2706,7 @@
         <v>52</v>
       </c>
       <c r="F28" s="10">
-        <v>66</v>
+        <v>52.800000000000004</v>
       </c>
       <c r="G28" s="14">
         <v>54</v>
@@ -2732,7 +2732,7 @@
         <v>89</v>
       </c>
       <c r="F29" s="10">
-        <v>55</v>
+        <v>48.800000000000004</v>
       </c>
       <c r="G29" s="14">
         <v>80</v>
@@ -2758,7 +2758,7 @@
         <v>60</v>
       </c>
       <c r="F30" s="10">
-        <v>78</v>
+        <v>77.999999999999986</v>
       </c>
       <c r="G30" s="14">
         <v>74</v>
@@ -2784,7 +2784,7 @@
         <v>69</v>
       </c>
       <c r="F31" s="10">
-        <v>65</v>
+        <v>50.79999999999999</v>
       </c>
       <c r="G31" s="14">
         <v>38</v>
@@ -2810,7 +2810,7 @@
         <v>47</v>
       </c>
       <c r="F32" s="10">
-        <v>73</v>
+        <v>43.8</v>
       </c>
       <c r="G32" s="14">
         <v>68</v>
@@ -2836,7 +2836,7 @@
         <v>81</v>
       </c>
       <c r="F33" s="10">
-        <v>41</v>
+        <v>24.6</v>
       </c>
       <c r="G33" s="14">
         <v>74</v>
@@ -2862,7 +2862,7 @@
         <v>76</v>
       </c>
       <c r="F34" s="10">
-        <v>76</v>
+        <v>62.8</v>
       </c>
       <c r="G34" s="14">
         <v>80</v>
@@ -2888,7 +2888,7 @@
         <v>75</v>
       </c>
       <c r="F35" s="10">
-        <v>73</v>
+        <v>60.199999999999996</v>
       </c>
       <c r="G35" s="14">
         <v>66</v>
@@ -2914,7 +2914,7 @@
         <v>64</v>
       </c>
       <c r="F36" s="10">
-        <v>59</v>
+        <v>49.8</v>
       </c>
       <c r="G36" s="14">
         <v>39</v>
@@ -2940,7 +2940,7 @@
         <v>59</v>
       </c>
       <c r="F37" s="10">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="G37" s="14">
         <v>53</v>
@@ -2966,7 +2966,7 @@
         <v>93</v>
       </c>
       <c r="F38" s="10">
-        <v>75</v>
+        <v>56.8</v>
       </c>
       <c r="G38" s="14">
         <v>66</v>
@@ -2992,7 +2992,7 @@
         <v>69</v>
       </c>
       <c r="F39" s="10">
-        <v>41</v>
+        <v>24.6</v>
       </c>
       <c r="G39" s="14">
         <v>69</v>
@@ -3018,7 +3018,7 @@
         <v>49</v>
       </c>
       <c r="F40" s="10">
-        <v>71</v>
+        <v>42.6</v>
       </c>
       <c r="G40" s="14">
         <v>54</v>
@@ -3044,7 +3044,7 @@
         <v>57</v>
       </c>
       <c r="F41" s="10">
-        <v>62</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="G41" s="14">
         <v>34</v>
@@ -3070,7 +3070,7 @@
         <v>73</v>
       </c>
       <c r="F42" s="10">
-        <v>65</v>
+        <v>38.999999999999993</v>
       </c>
       <c r="G42" s="14">
         <v>46</v>
@@ -3096,7 +3096,7 @@
         <v>71</v>
       </c>
       <c r="F43" s="10">
-        <v>65</v>
+        <v>53.999999999999993</v>
       </c>
       <c r="G43" s="14">
         <v>73</v>
@@ -3122,7 +3122,7 @@
         <v>97</v>
       </c>
       <c r="F44" s="10">
-        <v>57</v>
+        <v>34.199999999999996</v>
       </c>
       <c r="G44" s="14">
         <v>38</v>
@@ -3148,7 +3148,7 @@
         <v>59</v>
       </c>
       <c r="F45" s="10">
-        <v>65</v>
+        <v>55.999999999999993</v>
       </c>
       <c r="G45" s="14">
         <v>56</v>
@@ -3174,7 +3174,7 @@
         <v>73</v>
       </c>
       <c r="F46" s="10">
-        <v>46</v>
+        <v>42.4</v>
       </c>
       <c r="G46" s="14">
         <v>36</v>
@@ -3200,7 +3200,7 @@
         <v>89</v>
       </c>
       <c r="F47" s="10">
-        <v>44</v>
+        <v>26.400000000000002</v>
       </c>
       <c r="G47" s="14">
         <v>51</v>
@@ -3226,7 +3226,7 @@
         <v>89</v>
       </c>
       <c r="F48" s="10">
-        <v>47</v>
+        <v>45.199999999999996</v>
       </c>
       <c r="G48" s="14">
         <v>55</v>
@@ -3252,7 +3252,7 @@
         <v>73</v>
       </c>
       <c r="F49" s="10">
-        <v>78</v>
+        <v>77.999999999999986</v>
       </c>
       <c r="G49" s="14">
         <v>61</v>
@@ -3278,7 +3278,7 @@
         <v>94</v>
       </c>
       <c r="F50" s="10">
-        <v>42</v>
+        <v>59.599999999999994</v>
       </c>
       <c r="G50" s="14">
         <v>40</v>
@@ -3304,7 +3304,7 @@
         <v>78</v>
       </c>
       <c r="F51" s="10">
-        <v>63</v>
+        <v>67.800000000000011</v>
       </c>
       <c r="G51" s="14">
         <v>56</v>
@@ -3330,7 +3330,7 @@
         <v>71</v>
       </c>
       <c r="F52" s="10">
-        <v>73</v>
+        <v>57.199999999999982</v>
       </c>
       <c r="G52" s="14">
         <v>56</v>
@@ -3356,7 +3356,7 @@
         <v>61</v>
       </c>
       <c r="F53" s="10">
-        <v>48</v>
+        <v>28.800000000000004</v>
       </c>
       <c r="G53" s="14">
         <v>57</v>
@@ -3382,7 +3382,7 @@
         <v>96</v>
       </c>
       <c r="F54" s="10">
-        <v>57</v>
+        <v>47.2</v>
       </c>
       <c r="G54" s="14">
         <v>55</v>
@@ -3408,7 +3408,7 @@
         <v>91</v>
       </c>
       <c r="F55" s="10">
-        <v>70</v>
+        <v>77.199999999999989</v>
       </c>
       <c r="G55" s="14">
         <v>70</v>
@@ -3434,7 +3434,7 @@
         <v>85</v>
       </c>
       <c r="F56" s="10">
-        <v>53</v>
+        <v>54.599999999999994</v>
       </c>
       <c r="G56" s="14">
         <v>44</v>
@@ -3460,7 +3460,7 @@
         <v>86</v>
       </c>
       <c r="F57" s="10">
-        <v>67</v>
+        <v>73.799999999999983</v>
       </c>
       <c r="G57" s="14">
         <v>54</v>
@@ -3486,7 +3486,7 @@
         <v>86</v>
       </c>
       <c r="F58" s="10">
-        <v>73</v>
+        <v>77.600000000000009</v>
       </c>
       <c r="G58" s="14">
         <v>32</v>
@@ -3512,7 +3512,7 @@
         <v>90</v>
       </c>
       <c r="F59" s="10">
-        <v>66</v>
+        <v>66.600000000000009</v>
       </c>
       <c r="G59" s="14">
         <v>39</v>
@@ -3538,7 +3538,7 @@
         <v>79</v>
       </c>
       <c r="F60" s="10">
-        <v>65</v>
+        <v>52.999999999999993</v>
       </c>
       <c r="G60" s="14">
         <v>52</v>
@@ -3564,7 +3564,7 @@
         <v>77</v>
       </c>
       <c r="F61" s="10">
-        <v>76</v>
+        <v>56.000000000000007</v>
       </c>
       <c r="G61" s="14">
         <v>82</v>
@@ -3590,7 +3590,7 @@
         <v>79</v>
       </c>
       <c r="F62" s="10">
-        <v>55</v>
+        <v>40.599999999999994</v>
       </c>
       <c r="G62" s="14">
         <v>68</v>
@@ -3616,7 +3616,7 @@
         <v>91</v>
       </c>
       <c r="F63" s="10">
-        <v>70</v>
+        <v>79.199999999999989</v>
       </c>
       <c r="G63" s="14">
         <v>79</v>
@@ -3642,7 +3642,7 @@
         <v>69</v>
       </c>
       <c r="F64" s="10">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G64" s="14">
         <v>52</v>
@@ -3668,7 +3668,7 @@
         <v>58</v>
       </c>
       <c r="F65" s="10">
-        <v>55</v>
+        <v>44.800000000000004</v>
       </c>
       <c r="G65" s="14">
         <v>67</v>
@@ -3694,7 +3694,7 @@
         <v>81</v>
       </c>
       <c r="F66" s="10">
-        <v>63</v>
+        <v>62.8</v>
       </c>
       <c r="G66" s="14">
         <v>68</v>
@@ -3720,7 +3720,7 @@
         <v>58</v>
       </c>
       <c r="F67" s="10">
-        <v>47</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="G67" s="14">
         <v>49</v>
@@ -3746,7 +3746,7 @@
         <v>68</v>
       </c>
       <c r="F68" s="10">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G68" s="14">
         <v>59</v>
@@ -3772,7 +3772,7 @@
         <v>74</v>
       </c>
       <c r="F69" s="10">
-        <v>48</v>
+        <v>47.6</v>
       </c>
       <c r="G69" s="14">
         <v>42</v>
@@ -3798,7 +3798,7 @@
         <v>52</v>
       </c>
       <c r="F70" s="10">
-        <v>71</v>
+        <v>42.6</v>
       </c>
       <c r="G70" s="14">
         <v>40</v>
@@ -3824,7 +3824,7 @@
         <v>62</v>
       </c>
       <c r="F71" s="10">
-        <v>44</v>
+        <v>26.400000000000002</v>
       </c>
       <c r="G71" s="14">
         <v>50</v>
@@ -3850,7 +3850,7 @@
         <v>85</v>
       </c>
       <c r="F72" s="10">
-        <v>54</v>
+        <v>32.4</v>
       </c>
       <c r="G72" s="14">
         <v>55</v>
@@ -3876,7 +3876,7 @@
         <v>83</v>
       </c>
       <c r="F73" s="10">
-        <v>59</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="G73" s="14">
         <v>60</v>
@@ -3902,7 +3902,7 @@
         <v>42</v>
       </c>
       <c r="F74" s="10">
-        <v>65</v>
+        <v>38.999999999999993</v>
       </c>
       <c r="G74" s="14">
         <v>35</v>
@@ -3928,7 +3928,7 @@
         <v>72</v>
       </c>
       <c r="F75" s="10">
-        <v>71</v>
+        <v>42.6</v>
       </c>
       <c r="G75" s="14">
         <v>48</v>
@@ -3954,7 +3954,7 @@
         <v>50</v>
       </c>
       <c r="F76" s="10">
-        <v>52</v>
+        <v>31.2</v>
       </c>
       <c r="G76" s="14">
         <v>37</v>
@@ -3980,7 +3980,7 @@
         <v>84</v>
       </c>
       <c r="F77" s="10">
-        <v>70</v>
+        <v>59.199999999999996</v>
       </c>
       <c r="G77" s="14">
         <v>54</v>
@@ -4006,7 +4006,7 @@
         <v>86</v>
       </c>
       <c r="F78" s="10">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G78" s="14">
         <v>54</v>
@@ -4032,7 +4032,7 @@
         <v>77</v>
       </c>
       <c r="F79" s="10">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="G79" s="14">
         <v>42</v>
@@ -4058,7 +4058,7 @@
         <v>75</v>
       </c>
       <c r="F80" s="10">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="G80" s="14">
         <v>63</v>
@@ -4084,7 +4084,7 @@
         <v>83</v>
       </c>
       <c r="F81" s="10">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G81" s="14">
         <v>58</v>
@@ -4110,7 +4110,7 @@
         <v>67</v>
       </c>
       <c r="F82" s="10">
-        <v>54</v>
+        <v>32.4</v>
       </c>
       <c r="G82" s="14">
         <v>54</v>
@@ -4136,7 +4136,7 @@
         <v>70</v>
       </c>
       <c r="F83" s="10">
-        <v>67</v>
+        <v>40.199999999999996</v>
       </c>
       <c r="G83" s="14">
         <v>67</v>
@@ -4162,7 +4162,7 @@
         <v>56</v>
       </c>
       <c r="F84" s="10">
-        <v>73</v>
+        <v>43.8</v>
       </c>
       <c r="G84" s="14">
         <v>70</v>
@@ -4188,7 +4188,7 @@
         <v>59</v>
       </c>
       <c r="F85" s="10">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G85" s="14">
         <v>47</v>
@@ -4214,7 +4214,7 @@
         <v>85</v>
       </c>
       <c r="F86" s="10">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G86" s="14">
         <v>42</v>
@@ -4240,7 +4240,7 @@
         <v>68</v>
       </c>
       <c r="F87" s="10">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G87" s="14">
         <v>47</v>
@@ -4266,7 +4266,7 @@
         <v>85</v>
       </c>
       <c r="F88" s="10">
-        <v>76</v>
+        <v>58.20000000000001</v>
       </c>
       <c r="G88" s="14">
         <v>69</v>
@@ -4292,7 +4292,7 @@
         <v>96</v>
       </c>
       <c r="F89" s="10">
-        <v>44</v>
+        <v>26.400000000000002</v>
       </c>
       <c r="G89" s="14">
         <v>68</v>
@@ -4318,7 +4318,7 @@
         <v>73</v>
       </c>
       <c r="F90" s="10">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G90" s="14">
         <v>56</v>
@@ -4344,7 +4344,7 @@
         <v>83</v>
       </c>
       <c r="F91" s="10">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G91" s="14">
         <v>68</v>
@@ -4370,7 +4370,7 @@
         <v>77</v>
       </c>
       <c r="F92" s="10">
-        <v>67</v>
+        <v>73.799999999999983</v>
       </c>
       <c r="G92" s="14">
         <v>59</v>
@@ -4396,7 +4396,7 @@
         <v>76</v>
       </c>
       <c r="F93" s="10">
-        <v>70</v>
+        <v>56.400000000000006</v>
       </c>
       <c r="G93" s="14">
         <v>53</v>
@@ -4422,7 +4422,7 @@
         <v>80</v>
       </c>
       <c r="F94" s="10">
-        <v>46</v>
+        <v>59.599999999999994</v>
       </c>
       <c r="G94" s="14">
         <v>33</v>
@@ -4448,7 +4448,7 @@
         <v>76</v>
       </c>
       <c r="F95" s="10">
-        <v>62</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="G95" s="14">
         <v>55</v>
@@ -4474,7 +4474,7 @@
         <v>64</v>
       </c>
       <c r="F96" s="10">
-        <v>62</v>
+        <v>51.2</v>
       </c>
       <c r="G96" s="14">
         <v>65</v>
@@ -4500,7 +4500,7 @@
         <v>74</v>
       </c>
       <c r="F97" s="10">
-        <v>73</v>
+        <v>57.199999999999982</v>
       </c>
       <c r="G97" s="14">
         <v>42</v>
@@ -4526,7 +4526,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="10">
-        <v>52</v>
+        <v>31.2</v>
       </c>
       <c r="G98" s="14">
         <v>59</v>
@@ -4552,7 +4552,7 @@
         <v>79</v>
       </c>
       <c r="F99" s="10">
-        <v>62</v>
+        <v>56.000000000000007</v>
       </c>
       <c r="G99" s="14">
         <v>72</v>
@@ -4578,7 +4578,7 @@
         <v>92</v>
       </c>
       <c r="F100" s="10">
-        <v>62</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="G100" s="14">
         <v>62</v>
@@ -4604,7 +4604,7 @@
         <v>69</v>
       </c>
       <c r="F101" s="10">
-        <v>52</v>
+        <v>31.2</v>
       </c>
       <c r="G101" s="14">
         <v>57</v>
@@ -4630,7 +4630,7 @@
         <v>84</v>
       </c>
       <c r="F102" s="10">
-        <v>59</v>
+        <v>44.599999999999994</v>
       </c>
       <c r="G102" s="14">
         <v>74</v>
@@ -4656,7 +4656,7 @@
         <v>74</v>
       </c>
       <c r="F103" s="10">
-        <v>52</v>
+        <v>31.2</v>
       </c>
       <c r="G103" s="14">
         <v>36</v>
@@ -4682,7 +4682,7 @@
         <v>85</v>
       </c>
       <c r="F104" s="10">
-        <v>57</v>
+        <v>51.4</v>
       </c>
       <c r="G104" s="14">
         <v>84</v>
@@ -4708,7 +4708,7 @@
         <v>95</v>
       </c>
       <c r="F105" s="10">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G105" s="14">
         <v>72</v>
@@ -4734,7 +4734,7 @@
         <v>82</v>
       </c>
       <c r="F106" s="10">
-        <v>70</v>
+        <v>57.8</v>
       </c>
       <c r="G106" s="14">
         <v>35</v>
@@ -4760,7 +4760,7 @@
         <v>62</v>
       </c>
       <c r="F107" s="10">
-        <v>65</v>
+        <v>38.999999999999993</v>
       </c>
       <c r="G107" s="14">
         <v>57</v>
@@ -4786,7 +4786,7 @@
         <v>72</v>
       </c>
       <c r="F108" s="10">
-        <v>59</v>
+        <v>49.8</v>
       </c>
       <c r="G108" s="14">
         <v>67</v>
@@ -4812,7 +4812,7 @@
         <v>95</v>
       </c>
       <c r="F109" s="10">
-        <v>73</v>
+        <v>43.8</v>
       </c>
       <c r="G109" s="14">
         <v>66</v>
@@ -4838,7 +4838,7 @@
         <v>46</v>
       </c>
       <c r="F110" s="10">
-        <v>66</v>
+        <v>55.999999999999993</v>
       </c>
       <c r="G110" s="14">
         <v>45</v>
@@ -4864,7 +4864,7 @@
         <v>38</v>
       </c>
       <c r="F111" s="10">
-        <v>41</v>
+        <v>24.6</v>
       </c>
       <c r="G111" s="14">
         <v>9</v>
@@ -4890,7 +4890,7 @@
         <v>76</v>
       </c>
       <c r="F112" s="10">
-        <v>62</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="G112" s="14">
         <v>72</v>
@@ -4916,7 +4916,7 @@
         <v>49</v>
       </c>
       <c r="F113" s="10">
-        <v>76</v>
+        <v>45.6</v>
       </c>
       <c r="G113" s="14">
         <v>44</v>
@@ -4942,7 +4942,7 @@
         <v>53</v>
       </c>
       <c r="F114" s="10">
-        <v>66</v>
+        <v>47.199999999999989</v>
       </c>
       <c r="G114" s="14">
         <v>56</v>
@@ -4968,7 +4968,7 @@
         <v>84</v>
       </c>
       <c r="F115" s="10">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G115" s="14">
         <v>75</v>
@@ -4994,7 +4994,7 @@
         <v>88</v>
       </c>
       <c r="F116" s="10">
-        <v>55</v>
+        <v>48.800000000000004</v>
       </c>
       <c r="G116" s="14">
         <v>56</v>
@@ -5020,7 +5020,7 @@
         <v>97</v>
       </c>
       <c r="F117" s="10">
-        <v>42</v>
+        <v>59.599999999999994</v>
       </c>
       <c r="G117" s="14">
         <v>43</v>
@@ -5046,7 +5046,7 @@
         <v>74</v>
       </c>
       <c r="F118" s="10">
-        <v>66</v>
+        <v>52.800000000000004</v>
       </c>
       <c r="G118" s="14">
         <v>60</v>
@@ -5072,7 +5072,7 @@
         <v>88</v>
       </c>
       <c r="F119" s="10">
-        <v>75</v>
+        <v>68.399999999999991</v>
       </c>
       <c r="G119" s="14">
         <v>70</v>
@@ -5098,7 +5098,7 @@
         <v>87</v>
       </c>
       <c r="F120" s="10">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="G120" s="14">
         <v>63</v>
@@ -5124,7 +5124,7 @@
         <v>75</v>
       </c>
       <c r="F121" s="10">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="G121" s="14">
         <v>50</v>
@@ -5150,7 +5150,7 @@
         <v>91</v>
       </c>
       <c r="F122" s="10">
-        <v>54</v>
+        <v>47.199999999999989</v>
       </c>
       <c r="G122" s="14">
         <v>72</v>
@@ -5175,7 +5175,7 @@
       <c r="E123" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F123" s="19" t="s">
+      <c r="F123" s="10" t="s">
         <v>81</v>
       </c>
       <c r="G123" s="14">
@@ -5202,7 +5202,7 @@
         <v>91</v>
       </c>
       <c r="F124" s="10">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G124" s="14">
         <v>70</v>
@@ -5228,7 +5228,7 @@
         <v>77</v>
       </c>
       <c r="F125" s="10">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="G125" s="14">
         <v>56</v>
@@ -5254,7 +5254,7 @@
         <v>91</v>
       </c>
       <c r="F126" s="10">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="G126" s="14">
         <v>67</v>
@@ -5280,7 +5280,7 @@
         <v>72</v>
       </c>
       <c r="F127" s="10">
-        <v>70</v>
+        <v>57.8</v>
       </c>
       <c r="G127" s="14">
         <v>56</v>
@@ -5306,7 +5306,7 @@
         <v>81</v>
       </c>
       <c r="F128" s="10">
-        <v>48</v>
+        <v>28.800000000000004</v>
       </c>
       <c r="G128" s="14">
         <v>52</v>
@@ -5332,7 +5332,7 @@
         <v>78</v>
       </c>
       <c r="F129" s="10">
-        <v>54</v>
+        <v>32.4</v>
       </c>
       <c r="G129" s="14">
         <v>45</v>
@@ -5358,7 +5358,7 @@
         <v>81</v>
       </c>
       <c r="F130" s="10">
-        <v>63</v>
+        <v>71.8</v>
       </c>
       <c r="G130" s="14">
         <v>42</v>
@@ -5384,7 +5384,7 @@
         <v>91</v>
       </c>
       <c r="F131" s="10">
-        <v>53</v>
+        <v>60.199999999999996</v>
       </c>
       <c r="G131" s="14">
         <v>56</v>
@@ -5410,7 +5410,7 @@
         <v>92</v>
       </c>
       <c r="F132" s="10">
-        <v>73</v>
+        <v>43.8</v>
       </c>
       <c r="G132" s="14">
         <v>79</v>
@@ -5436,7 +5436,7 @@
         <v>68</v>
       </c>
       <c r="F133" s="10">
-        <v>48</v>
+        <v>46.199999999999996</v>
       </c>
       <c r="G133" s="14">
         <v>61</v>
@@ -5462,7 +5462,7 @@
         <v>80</v>
       </c>
       <c r="F134" s="10">
-        <v>70</v>
+        <v>79.199999999999989</v>
       </c>
       <c r="G134" s="14">
         <v>66</v>
@@ -5488,7 +5488,7 @@
         <v>80</v>
       </c>
       <c r="F135" s="10">
-        <v>66</v>
+        <v>62.4</v>
       </c>
       <c r="G135" s="14">
         <v>37</v>
@@ -5514,7 +5514,7 @@
         <v>87</v>
       </c>
       <c r="F136" s="10">
-        <v>46</v>
+        <v>61.599999999999987</v>
       </c>
       <c r="G136" s="14">
         <v>50</v>
@@ -5540,7 +5540,7 @@
         <v>61</v>
       </c>
       <c r="F137" s="10">
-        <v>73</v>
+        <v>58.20000000000001</v>
       </c>
       <c r="G137" s="14">
         <v>65</v>
@@ -5566,7 +5566,7 @@
         <v>75</v>
       </c>
       <c r="F138" s="10">
-        <v>57</v>
+        <v>49.4</v>
       </c>
       <c r="G138" s="14">
         <v>56</v>
@@ -5592,7 +5592,7 @@
         <v>69</v>
       </c>
       <c r="F139" s="10">
-        <v>73</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="G139" s="14">
         <v>51</v>
@@ -5618,7 +5618,7 @@
         <v>84</v>
       </c>
       <c r="F140" s="10">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G140" s="14">
         <v>63</v>
@@ -5644,7 +5644,7 @@
         <v>80</v>
       </c>
       <c r="F141" s="10">
-        <v>67</v>
+        <v>40.199999999999996</v>
       </c>
       <c r="G141" s="14">
         <v>41</v>
@@ -5670,7 +5670,7 @@
         <v>87</v>
       </c>
       <c r="F142" s="10">
-        <v>57</v>
+        <v>47.2</v>
       </c>
       <c r="G142" s="14">
         <v>53</v>
@@ -5696,7 +5696,7 @@
         <v>75</v>
       </c>
       <c r="F143" s="10">
-        <v>54</v>
+        <v>32.4</v>
       </c>
       <c r="G143" s="14">
         <v>66</v>
@@ -5722,7 +5722,7 @@
         <v>73</v>
       </c>
       <c r="F144" s="10">
-        <v>41</v>
+        <v>24.6</v>
       </c>
       <c r="G144" s="14">
         <v>80</v>
@@ -5748,7 +5748,7 @@
         <v>78</v>
       </c>
       <c r="F145" s="10">
-        <v>53</v>
+        <v>60.199999999999996</v>
       </c>
       <c r="G145" s="14">
         <v>67</v>
@@ -5774,7 +5774,7 @@
         <v>98</v>
       </c>
       <c r="F146" s="10">
-        <v>63</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="G146" s="14">
         <v>70</v>
@@ -5800,7 +5800,7 @@
         <v>87</v>
       </c>
       <c r="F147" s="10">
-        <v>55</v>
+        <v>45.2</v>
       </c>
       <c r="G147" s="14">
         <v>26</v>
@@ -5826,7 +5826,7 @@
         <v>89</v>
       </c>
       <c r="F148" s="10">
-        <v>71</v>
+        <v>56.600000000000009</v>
       </c>
       <c r="G148" s="14">
         <v>38</v>
@@ -5852,7 +5852,7 @@
         <v>64</v>
       </c>
       <c r="F149" s="10">
-        <v>62</v>
+        <v>52.2</v>
       </c>
       <c r="G149" s="14">
         <v>51</v>
@@ -5878,7 +5878,7 @@
         <v>100</v>
       </c>
       <c r="F150" s="10">
-        <v>46</v>
+        <v>46.8</v>
       </c>
       <c r="G150" s="14">
         <v>58</v>
@@ -5904,7 +5904,7 @@
         <v>64</v>
       </c>
       <c r="F151" s="10">
-        <v>50</v>
+        <v>61.6</v>
       </c>
       <c r="G151" s="14">
         <v>55</v>
@@ -5930,7 +5930,7 @@
         <v>73</v>
       </c>
       <c r="F152" s="10">
-        <v>73</v>
+        <v>43.8</v>
       </c>
       <c r="G152" s="14">
         <v>41</v>
@@ -5956,7 +5956,7 @@
         <v>77</v>
       </c>
       <c r="F153" s="10">
-        <v>66</v>
+        <v>52.800000000000004</v>
       </c>
       <c r="G153" s="14">
         <v>58</v>
@@ -5982,7 +5982,7 @@
         <v>76</v>
       </c>
       <c r="F154" s="10">
-        <v>43</v>
+        <v>25.799999999999994</v>
       </c>
       <c r="G154" s="14">
         <v>72</v>
@@ -6008,7 +6008,7 @@
         <v>78</v>
       </c>
       <c r="F155" s="10">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G155" s="14">
         <v>55</v>
@@ -6034,7 +6034,7 @@
         <v>81</v>
       </c>
       <c r="F156" s="10">
-        <v>59</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="G156" s="14">
         <v>90</v>
@@ -6060,7 +6060,7 @@
         <v>59</v>
       </c>
       <c r="F157" s="10">
-        <v>62</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="G157" s="14">
         <v>54</v>
@@ -6086,7 +6086,7 @@
         <v>88</v>
       </c>
       <c r="F158" s="10">
-        <v>54</v>
+        <v>32.4</v>
       </c>
       <c r="G158" s="14">
         <v>55</v>
@@ -6112,7 +6112,7 @@
         <v>68</v>
       </c>
       <c r="F159" s="10">
-        <v>75</v>
+        <v>52.6</v>
       </c>
       <c r="G159" s="14">
         <v>52</v>
@@ -6138,7 +6138,7 @@
         <v>72</v>
       </c>
       <c r="F160" s="10">
-        <v>39</v>
+        <v>38.4</v>
       </c>
       <c r="G160" s="14">
         <v>56</v>
@@ -6164,7 +6164,7 @@
         <v>69</v>
       </c>
       <c r="F161" s="10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G161" s="14">
         <v>45</v>
@@ -6190,7 +6190,7 @@
         <v>72</v>
       </c>
       <c r="F162" s="10">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="G162" s="14">
         <v>63</v>
@@ -6216,7 +6216,7 @@
         <v>81</v>
       </c>
       <c r="F163" s="10">
-        <v>65</v>
+        <v>53.999999999999993</v>
       </c>
       <c r="G163" s="14">
         <v>46</v>
@@ -6242,7 +6242,7 @@
         <v>70</v>
       </c>
       <c r="F164" s="10">
-        <v>43</v>
+        <v>25.799999999999994</v>
       </c>
       <c r="G164" s="14">
         <v>78</v>
@@ -6268,7 +6268,7 @@
         <v>72</v>
       </c>
       <c r="F165" s="10">
-        <v>78</v>
+        <v>46.8</v>
       </c>
       <c r="G165" s="14">
         <v>50</v>
@@ -6294,7 +6294,7 @@
         <v>82</v>
       </c>
       <c r="F166" s="10">
-        <v>71</v>
+        <v>42.6</v>
       </c>
       <c r="G166" s="14">
         <v>64</v>
@@ -6320,7 +6320,7 @@
         <v>68</v>
       </c>
       <c r="F167" s="10">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G167" s="14">
         <v>78</v>
@@ -6346,7 +6346,7 @@
         <v>79</v>
       </c>
       <c r="F168" s="10">
-        <v>73</v>
+        <v>43.8</v>
       </c>
       <c r="G168" s="14">
         <v>63</v>
@@ -6372,7 +6372,7 @@
         <v>90</v>
       </c>
       <c r="F169" s="10">
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="G169" s="14">
         <v>79</v>
@@ -6398,7 +6398,7 @@
         <v>78</v>
       </c>
       <c r="F170" s="10">
-        <v>47</v>
+        <v>36.599999999999994</v>
       </c>
       <c r="G170" s="14">
         <v>38</v>
@@ -6424,7 +6424,7 @@
         <v>70</v>
       </c>
       <c r="F171" s="10">
-        <v>54</v>
+        <v>47.599999999999994</v>
       </c>
       <c r="G171" s="14">
         <v>41</v>
@@ -6450,7 +6450,7 @@
         <v>55</v>
       </c>
       <c r="F172" s="10">
-        <v>43</v>
+        <v>25.799999999999994</v>
       </c>
       <c r="G172" s="14">
         <v>30</v>
@@ -6476,7 +6476,7 @@
         <v>96</v>
       </c>
       <c r="F173" s="10">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G173" s="14">
         <v>48</v>
@@ -6502,7 +6502,7 @@
         <v>71</v>
       </c>
       <c r="F174" s="10">
-        <v>73</v>
+        <v>56.199999999999996</v>
       </c>
       <c r="G174" s="14">
         <v>25</v>
@@ -6528,7 +6528,7 @@
         <v>75</v>
       </c>
       <c r="F175" s="10">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G175" s="14">
         <v>29</v>
@@ -6554,7 +6554,7 @@
         <v>62</v>
       </c>
       <c r="F176" s="10">
-        <v>54</v>
+        <v>45.4</v>
       </c>
       <c r="G176" s="14">
         <v>55</v>
@@ -6580,7 +6580,7 @@
         <v>79</v>
       </c>
       <c r="F177" s="10">
-        <v>42</v>
+        <v>51.800000000000004</v>
       </c>
       <c r="G177" s="14">
         <v>49</v>
@@ -6606,7 +6606,7 @@
         <v>81</v>
       </c>
       <c r="F178" s="10">
-        <v>53</v>
+        <v>60.999999999999986</v>
       </c>
       <c r="G178" s="14">
         <v>84</v>
@@ -6632,7 +6632,7 @@
         <v>90</v>
       </c>
       <c r="F179" s="10">
-        <v>53</v>
+        <v>60.999999999999986</v>
       </c>
       <c r="G179" s="14">
         <v>78</v>
@@ -6658,7 +6658,7 @@
         <v>48</v>
       </c>
       <c r="F180" s="10">
-        <v>44</v>
+        <v>26.400000000000002</v>
       </c>
       <c r="G180" s="14">
         <v>42</v>
@@ -6684,7 +6684,7 @@
         <v>78</v>
       </c>
       <c r="F181" s="10">
-        <v>39</v>
+        <v>23.4</v>
       </c>
       <c r="G181" s="14">
         <v>58</v>
@@ -6710,7 +6710,7 @@
         <v>66</v>
       </c>
       <c r="F182" s="10">
-        <v>39</v>
+        <v>33.800000000000004</v>
       </c>
       <c r="G182" s="14">
         <v>34</v>
@@ -6736,7 +6736,7 @@
         <v>93</v>
       </c>
       <c r="F183" s="10">
-        <v>55</v>
+        <v>59.600000000000009</v>
       </c>
       <c r="G183" s="14">
         <v>49</v>
@@ -6762,7 +6762,7 @@
         <v>76</v>
       </c>
       <c r="F184" s="10">
-        <v>39</v>
+        <v>52.6</v>
       </c>
       <c r="G184" s="14">
         <v>67</v>
@@ -6788,7 +6788,7 @@
         <v>65</v>
       </c>
       <c r="F185" s="10">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G185" s="14">
         <v>72</v>
@@ -6814,7 +6814,7 @@
         <v>74</v>
       </c>
       <c r="F186" s="10">
-        <v>62</v>
+        <v>49.599999999999994</v>
       </c>
       <c r="G186" s="14">
         <v>58</v>
@@ -6840,7 +6840,7 @@
         <v>58</v>
       </c>
       <c r="F187" s="10">
-        <v>52</v>
+        <v>39.599999999999994</v>
       </c>
       <c r="G187" s="14">
         <v>37</v>
@@ -6866,7 +6866,7 @@
         <v>81</v>
       </c>
       <c r="F188" s="10">
-        <v>73</v>
+        <v>43.8</v>
       </c>
       <c r="G188" s="14">
         <v>42</v>
@@ -8182,18 +8182,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8374,18 +8374,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theva\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F862BD5-6CDF-4A44-BF04-5DE8AF0F5E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9309FDF-E708-4A52-AC9C-AC1F5BBFF629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="487">
   <si>
     <t>Name</t>
   </si>
@@ -1580,7 +1580,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1603,46 +1603,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1672,12 +1641,22 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1698,9 +1677,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1738,7 +1717,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1844,7 +1823,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1986,7 +1965,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1999,4237 +1978,6202 @@
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="17" customWidth="1"/>
+    <col min="8" max="8" width="16" style="13" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>481</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>482</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="16" t="s">
         <v>484</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="17" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>79.5</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="17">
+      <c r="D2" s="14">
+        <v>9</v>
+      </c>
+      <c r="E2" s="14">
+        <v>62</v>
+      </c>
+      <c r="F2" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="G2" s="14">
+        <v>38</v>
+      </c>
+      <c r="H2" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>100</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="17">
+      <c r="D3" s="14">
+        <v>82</v>
+      </c>
+      <c r="E3" s="14">
+        <v>85</v>
+      </c>
+      <c r="F3" s="10">
+        <v>45</v>
+      </c>
+      <c r="G3" s="14">
+        <v>87</v>
+      </c>
+      <c r="H3" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>88</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="17">
+      <c r="D4" s="14">
+        <v>38</v>
+      </c>
+      <c r="E4" s="14">
+        <v>76</v>
+      </c>
+      <c r="F4" s="10">
+        <v>32.4</v>
+      </c>
+      <c r="G4" s="14">
+        <v>75</v>
+      </c>
+      <c r="H4" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>58</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="17">
+      <c r="D5" s="14">
+        <v>41</v>
+      </c>
+      <c r="E5" s="14">
+        <v>65</v>
+      </c>
+      <c r="F5" s="10">
+        <v>36</v>
+      </c>
+      <c r="G5" s="14">
+        <v>46</v>
+      </c>
+      <c r="H5" s="18">
         <v>26.666666666666668</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>92</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="17">
+      <c r="D6" s="14">
+        <v>41</v>
+      </c>
+      <c r="E6" s="14">
+        <v>66</v>
+      </c>
+      <c r="F6" s="10">
+        <v>36</v>
+      </c>
+      <c r="G6" s="14">
+        <v>40</v>
+      </c>
+      <c r="H6" s="18">
         <v>43.333333333333336</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>82.5</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="17">
+      <c r="D7" s="14">
+        <v>73</v>
+      </c>
+      <c r="E7" s="14">
+        <v>66</v>
+      </c>
+      <c r="F7" s="10">
+        <v>38.999999999999993</v>
+      </c>
+      <c r="G7" s="14">
+        <v>64</v>
+      </c>
+      <c r="H7" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>68</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="17">
+      <c r="D8" s="14">
+        <v>83</v>
+      </c>
+      <c r="E8" s="14">
+        <v>89</v>
+      </c>
+      <c r="F8" s="10">
+        <v>42.199999999999996</v>
+      </c>
+      <c r="G8" s="14">
+        <v>77</v>
+      </c>
+      <c r="H8" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>83</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="17">
+      <c r="D9" s="14">
+        <v>40</v>
+      </c>
+      <c r="E9" s="14">
+        <v>77</v>
+      </c>
+      <c r="F9" s="10">
+        <v>48.800000000000004</v>
+      </c>
+      <c r="G9" s="14">
+        <v>46</v>
+      </c>
+      <c r="H9" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <v>67.5</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="17">
+      <c r="D10" s="14">
+        <v>27</v>
+      </c>
+      <c r="E10" s="14">
+        <v>71</v>
+      </c>
+      <c r="F10" s="10">
+        <v>38.4</v>
+      </c>
+      <c r="G10" s="14">
+        <v>48</v>
+      </c>
+      <c r="H10" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>28</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="17">
+      <c r="D11" s="14">
+        <v>26</v>
+      </c>
+      <c r="E11" s="14">
+        <v>43</v>
+      </c>
+      <c r="F11" s="10">
+        <v>27.200000000000003</v>
+      </c>
+      <c r="G11" s="14">
+        <v>34</v>
+      </c>
+      <c r="H11" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <v>82</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="17">
+      <c r="D12" s="14">
+        <v>48</v>
+      </c>
+      <c r="E12" s="14">
+        <v>94</v>
+      </c>
+      <c r="F12" s="10">
+        <v>50.79999999999999</v>
+      </c>
+      <c r="G12" s="14">
+        <v>35</v>
+      </c>
+      <c r="H12" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>80</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="17">
+      <c r="D13" s="14">
+        <v>50</v>
+      </c>
+      <c r="E13" s="14">
+        <v>71</v>
+      </c>
+      <c r="F13" s="10">
+        <v>59.199999999999996</v>
+      </c>
+      <c r="G13" s="14">
+        <v>40</v>
+      </c>
+      <c r="H13" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <v>98</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="17">
+      <c r="D14" s="14">
+        <v>56</v>
+      </c>
+      <c r="E14" s="14">
+        <v>95</v>
+      </c>
+      <c r="F14" s="10">
+        <v>32.4</v>
+      </c>
+      <c r="G14" s="14">
+        <v>86</v>
+      </c>
+      <c r="H14" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>68.5</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="17">
+      <c r="D15" s="14">
+        <v>63</v>
+      </c>
+      <c r="E15" s="14">
+        <v>69</v>
+      </c>
+      <c r="F15" s="10">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="G15" s="14">
+        <v>61</v>
+      </c>
+      <c r="H15" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <v>77</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="17">
+      <c r="D16" s="14">
+        <v>79</v>
+      </c>
+      <c r="E16" s="14">
+        <v>98</v>
+      </c>
+      <c r="F16" s="10">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="G16" s="14">
+        <v>57</v>
+      </c>
+      <c r="H16" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <v>86.5</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="17">
+      <c r="D17" s="14">
+        <v>47</v>
+      </c>
+      <c r="E17" s="14">
+        <v>78</v>
+      </c>
+      <c r="F17" s="10">
+        <v>42</v>
+      </c>
+      <c r="G17" s="14">
+        <v>79</v>
+      </c>
+      <c r="H17" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <v>92</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="17">
+      <c r="D18" s="14">
+        <v>50</v>
+      </c>
+      <c r="E18" s="14">
+        <v>85</v>
+      </c>
+      <c r="F18" s="10">
+        <v>26.400000000000002</v>
+      </c>
+      <c r="G18" s="14">
+        <v>71</v>
+      </c>
+      <c r="H18" s="18">
         <v>46.666666666666664</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>98</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="17">
+      <c r="D19" s="14">
+        <v>77</v>
+      </c>
+      <c r="E19" s="14">
+        <v>87</v>
+      </c>
+      <c r="F19" s="10">
+        <v>36.599999999999994</v>
+      </c>
+      <c r="G19" s="14">
+        <v>91</v>
+      </c>
+      <c r="H19" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="10">
         <v>86</v>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="17">
+      <c r="D20" s="14">
+        <v>50</v>
+      </c>
+      <c r="E20" s="14">
+        <v>64</v>
+      </c>
+      <c r="F20" s="10">
+        <v>68.399999999999991</v>
+      </c>
+      <c r="G20" s="14">
+        <v>71</v>
+      </c>
+      <c r="H20" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <v>95</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="17">
+      <c r="D21" s="14">
+        <v>87</v>
+      </c>
+      <c r="E21" s="14">
+        <v>86</v>
+      </c>
+      <c r="F21" s="10">
+        <v>68</v>
+      </c>
+      <c r="G21" s="14">
+        <v>97</v>
+      </c>
+      <c r="H21" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <v>63</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="17">
+      <c r="D22" s="14">
+        <v>35</v>
+      </c>
+      <c r="E22" s="14">
+        <v>61</v>
+      </c>
+      <c r="F22" s="10">
+        <v>52.6</v>
+      </c>
+      <c r="G22" s="14">
+        <v>53</v>
+      </c>
+      <c r="H22" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>96</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="17">
+      <c r="D23" s="14">
+        <v>50</v>
+      </c>
+      <c r="E23" s="14">
+        <v>81</v>
+      </c>
+      <c r="F23" s="10">
+        <v>69.199999999999989</v>
+      </c>
+      <c r="G23" s="14">
+        <v>73</v>
+      </c>
+      <c r="H23" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <v>64</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="17">
+      <c r="D24" s="14">
+        <v>22</v>
+      </c>
+      <c r="E24" s="14">
+        <v>78</v>
+      </c>
+      <c r="F24" s="10">
+        <v>69.199999999999989</v>
+      </c>
+      <c r="G24" s="14">
+        <v>33</v>
+      </c>
+      <c r="H24" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>77.5</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="17">
+      <c r="D25" s="14">
+        <v>56</v>
+      </c>
+      <c r="E25" s="14">
+        <v>97</v>
+      </c>
+      <c r="F25" s="10">
+        <v>66.8</v>
+      </c>
+      <c r="G25" s="14">
+        <v>82</v>
+      </c>
+      <c r="H25" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <v>89</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="17">
+      <c r="D26" s="14">
+        <v>55</v>
+      </c>
+      <c r="E26" s="14">
+        <v>71</v>
+      </c>
+      <c r="F26" s="10">
+        <v>45.2</v>
+      </c>
+      <c r="G26" s="14">
+        <v>45</v>
+      </c>
+      <c r="H26" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <v>85</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="17">
+      <c r="D27" s="14">
+        <v>56</v>
+      </c>
+      <c r="E27" s="14">
+        <v>82</v>
+      </c>
+      <c r="F27" s="10">
+        <v>57.4</v>
+      </c>
+      <c r="G27" s="14">
+        <v>51</v>
+      </c>
+      <c r="H27" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="10">
         <v>72</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="17">
+      <c r="D28" s="14">
+        <v>40</v>
+      </c>
+      <c r="E28" s="14">
+        <v>52</v>
+      </c>
+      <c r="F28" s="10">
+        <v>52.800000000000004</v>
+      </c>
+      <c r="G28" s="14">
+        <v>54</v>
+      </c>
+      <c r="H28" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="10">
         <v>94</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="17">
+      <c r="D29" s="14">
+        <v>62</v>
+      </c>
+      <c r="E29" s="14">
+        <v>89</v>
+      </c>
+      <c r="F29" s="10">
+        <v>48.800000000000004</v>
+      </c>
+      <c r="G29" s="14">
+        <v>80</v>
+      </c>
+      <c r="H29" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="10">
         <v>99</v>
       </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="17">
+      <c r="D30" s="14">
+        <v>56</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="10">
+        <v>77.999999999999986</v>
+      </c>
+      <c r="G30" s="14">
+        <v>74</v>
+      </c>
+      <c r="H30" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="10">
         <v>77.5</v>
       </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="17">
+      <c r="D31" s="14">
+        <v>52</v>
+      </c>
+      <c r="E31" s="14">
+        <v>69</v>
+      </c>
+      <c r="F31" s="10">
+        <v>50.79999999999999</v>
+      </c>
+      <c r="G31" s="14">
+        <v>38</v>
+      </c>
+      <c r="H31" s="18">
         <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="10">
         <v>79</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="17">
+      <c r="D32" s="14">
+        <v>51</v>
+      </c>
+      <c r="E32" s="14">
+        <v>47</v>
+      </c>
+      <c r="F32" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="G32" s="14">
+        <v>68</v>
+      </c>
+      <c r="H32" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <v>68</v>
       </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="17">
+      <c r="D33" s="14">
+        <v>63</v>
+      </c>
+      <c r="E33" s="14">
+        <v>81</v>
+      </c>
+      <c r="F33" s="10">
+        <v>24.6</v>
+      </c>
+      <c r="G33" s="14">
+        <v>74</v>
+      </c>
+      <c r="H33" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="10">
         <v>69.5</v>
       </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="17">
+      <c r="D34" s="14">
+        <v>52</v>
+      </c>
+      <c r="E34" s="14">
+        <v>76</v>
+      </c>
+      <c r="F34" s="10">
+        <v>62.8</v>
+      </c>
+      <c r="G34" s="14">
+        <v>80</v>
+      </c>
+      <c r="H34" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <v>85</v>
       </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="17">
+      <c r="D35" s="14">
+        <v>20</v>
+      </c>
+      <c r="E35" s="14">
+        <v>75</v>
+      </c>
+      <c r="F35" s="10">
+        <v>60.199999999999996</v>
+      </c>
+      <c r="G35" s="14">
+        <v>66</v>
+      </c>
+      <c r="H35" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="10">
         <v>60</v>
       </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="17">
+      <c r="D36" s="14">
+        <v>40</v>
+      </c>
+      <c r="E36" s="14">
+        <v>64</v>
+      </c>
+      <c r="F36" s="10">
+        <v>49.8</v>
+      </c>
+      <c r="G36" s="14">
+        <v>39</v>
+      </c>
+      <c r="H36" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>40.5</v>
       </c>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="17">
+      <c r="D37" s="14">
+        <v>26</v>
+      </c>
+      <c r="E37" s="14">
+        <v>59</v>
+      </c>
+      <c r="F37" s="10">
+        <v>59</v>
+      </c>
+      <c r="G37" s="14">
+        <v>53</v>
+      </c>
+      <c r="H37" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="10">
         <v>92</v>
       </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="17">
+      <c r="D38" s="14">
+        <v>45</v>
+      </c>
+      <c r="E38" s="14">
+        <v>93</v>
+      </c>
+      <c r="F38" s="10">
+        <v>56.8</v>
+      </c>
+      <c r="G38" s="14">
+        <v>66</v>
+      </c>
+      <c r="H38" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="10">
         <v>88</v>
       </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="17">
+      <c r="D39" s="14">
+        <v>37</v>
+      </c>
+      <c r="E39" s="14">
+        <v>69</v>
+      </c>
+      <c r="F39" s="10">
+        <v>24.6</v>
+      </c>
+      <c r="G39" s="14">
+        <v>69</v>
+      </c>
+      <c r="H39" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="10">
         <v>85</v>
       </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="17">
+      <c r="D40" s="14">
+        <v>39</v>
+      </c>
+      <c r="E40" s="14">
+        <v>49</v>
+      </c>
+      <c r="F40" s="10">
+        <v>42.6</v>
+      </c>
+      <c r="G40" s="14">
+        <v>54</v>
+      </c>
+      <c r="H40" s="18">
         <v>46.666666666666664</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="17">
+      <c r="C41" s="10">
+        <v>39</v>
+      </c>
+      <c r="D41" s="14">
+        <v>29</v>
+      </c>
+      <c r="E41" s="14">
+        <v>57</v>
+      </c>
+      <c r="F41" s="10">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="G41" s="14">
+        <v>34</v>
+      </c>
+      <c r="H41" s="18">
         <v>56.666666666666664</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="10">
         <v>69</v>
       </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="17">
+      <c r="D42" s="14">
+        <v>21</v>
+      </c>
+      <c r="E42" s="14">
+        <v>73</v>
+      </c>
+      <c r="F42" s="10">
+        <v>38.999999999999993</v>
+      </c>
+      <c r="G42" s="14">
+        <v>46</v>
+      </c>
+      <c r="H42" s="18">
         <v>13.333333333333334</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="10">
         <v>87.5</v>
       </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="17">
+      <c r="D43" s="14">
+        <v>74</v>
+      </c>
+      <c r="E43" s="14">
+        <v>71</v>
+      </c>
+      <c r="F43" s="10">
+        <v>53.999999999999993</v>
+      </c>
+      <c r="G43" s="14">
+        <v>73</v>
+      </c>
+      <c r="H43" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="10">
         <v>48</v>
       </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="17">
+      <c r="D44" s="14">
+        <v>48</v>
+      </c>
+      <c r="E44" s="14">
+        <v>97</v>
+      </c>
+      <c r="F44" s="10">
+        <v>34.199999999999996</v>
+      </c>
+      <c r="G44" s="14">
+        <v>38</v>
+      </c>
+      <c r="H44" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="10">
         <v>87</v>
       </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="17">
+      <c r="D45" s="14">
+        <v>66</v>
+      </c>
+      <c r="E45" s="14">
+        <v>59</v>
+      </c>
+      <c r="F45" s="10">
+        <v>55.999999999999993</v>
+      </c>
+      <c r="G45" s="14">
+        <v>56</v>
+      </c>
+      <c r="H45" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="10">
         <v>85</v>
       </c>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="17">
+      <c r="D46" s="14">
+        <v>47</v>
+      </c>
+      <c r="E46" s="14">
+        <v>73</v>
+      </c>
+      <c r="F46" s="10">
+        <v>42.4</v>
+      </c>
+      <c r="G46" s="14">
+        <v>36</v>
+      </c>
+      <c r="H46" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="10">
         <v>91.5</v>
       </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="17">
+      <c r="D47" s="14">
+        <v>7</v>
+      </c>
+      <c r="E47" s="14">
+        <v>89</v>
+      </c>
+      <c r="F47" s="10">
+        <v>26.400000000000002</v>
+      </c>
+      <c r="G47" s="14">
+        <v>51</v>
+      </c>
+      <c r="H47" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="10">
         <v>51</v>
       </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="17">
+      <c r="D48" s="14">
+        <v>50</v>
+      </c>
+      <c r="E48" s="14">
+        <v>89</v>
+      </c>
+      <c r="F48" s="10">
+        <v>45.199999999999996</v>
+      </c>
+      <c r="G48" s="14">
+        <v>55</v>
+      </c>
+      <c r="H48" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="10">
         <v>88</v>
       </c>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="17">
+      <c r="D49" s="14">
+        <v>37</v>
+      </c>
+      <c r="E49" s="14">
+        <v>73</v>
+      </c>
+      <c r="F49" s="10">
+        <v>77.999999999999986</v>
+      </c>
+      <c r="G49" s="14">
+        <v>61</v>
+      </c>
+      <c r="H49" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="10">
         <v>89</v>
       </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="17">
+      <c r="D50" s="14">
+        <v>60</v>
+      </c>
+      <c r="E50" s="14">
+        <v>94</v>
+      </c>
+      <c r="F50" s="10">
+        <v>59.599999999999994</v>
+      </c>
+      <c r="G50" s="14">
+        <v>40</v>
+      </c>
+      <c r="H50" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="10">
         <v>88</v>
       </c>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="17">
+      <c r="D51" s="14">
+        <v>60</v>
+      </c>
+      <c r="E51" s="14">
+        <v>78</v>
+      </c>
+      <c r="F51" s="10">
+        <v>67.800000000000011</v>
+      </c>
+      <c r="G51" s="14">
+        <v>56</v>
+      </c>
+      <c r="H51" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="10">
         <v>72</v>
       </c>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="17">
+      <c r="D52" s="14">
+        <v>40</v>
+      </c>
+      <c r="E52" s="14">
+        <v>71</v>
+      </c>
+      <c r="F52" s="10">
+        <v>57.199999999999982</v>
+      </c>
+      <c r="G52" s="14">
+        <v>56</v>
+      </c>
+      <c r="H52" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="10">
         <v>81.5</v>
       </c>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="17">
+      <c r="D53" s="14">
+        <v>10</v>
+      </c>
+      <c r="E53" s="14">
+        <v>61</v>
+      </c>
+      <c r="F53" s="10">
+        <v>28.800000000000004</v>
+      </c>
+      <c r="G53" s="14">
+        <v>57</v>
+      </c>
+      <c r="H53" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="10">
         <v>82</v>
       </c>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="17">
+      <c r="D54" s="14">
+        <v>61</v>
+      </c>
+      <c r="E54" s="14">
+        <v>96</v>
+      </c>
+      <c r="F54" s="10">
+        <v>47.2</v>
+      </c>
+      <c r="G54" s="14">
+        <v>55</v>
+      </c>
+      <c r="H54" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="10">
         <v>85</v>
       </c>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="17">
+      <c r="D55" s="14">
+        <v>76</v>
+      </c>
+      <c r="E55" s="14">
+        <v>91</v>
+      </c>
+      <c r="F55" s="10">
+        <v>77.199999999999989</v>
+      </c>
+      <c r="G55" s="14">
+        <v>70</v>
+      </c>
+      <c r="H55" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="10">
         <v>91</v>
       </c>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="17">
+      <c r="D56" s="14">
+        <v>30</v>
+      </c>
+      <c r="E56" s="14">
+        <v>85</v>
+      </c>
+      <c r="F56" s="10">
+        <v>54.599999999999994</v>
+      </c>
+      <c r="G56" s="14">
+        <v>44</v>
+      </c>
+      <c r="H56" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="10">
         <v>42.5</v>
       </c>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="17">
+      <c r="D57" s="14">
+        <v>48</v>
+      </c>
+      <c r="E57" s="14">
+        <v>86</v>
+      </c>
+      <c r="F57" s="10">
+        <v>73.799999999999983</v>
+      </c>
+      <c r="G57" s="14">
+        <v>54</v>
+      </c>
+      <c r="H57" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="10">
         <v>46.5</v>
       </c>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="17">
+      <c r="D58" s="14">
+        <v>42</v>
+      </c>
+      <c r="E58" s="14">
+        <v>86</v>
+      </c>
+      <c r="F58" s="10">
+        <v>77.600000000000009</v>
+      </c>
+      <c r="G58" s="14">
+        <v>32</v>
+      </c>
+      <c r="H58" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="10">
         <v>72.5</v>
       </c>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="17">
+      <c r="D59" s="14">
+        <v>29</v>
+      </c>
+      <c r="E59" s="14">
+        <v>90</v>
+      </c>
+      <c r="F59" s="10">
+        <v>66.600000000000009</v>
+      </c>
+      <c r="G59" s="14">
+        <v>39</v>
+      </c>
+      <c r="H59" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C60" s="10">
         <v>54</v>
       </c>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="17">
+      <c r="D60" s="14">
+        <v>61</v>
+      </c>
+      <c r="E60" s="14">
+        <v>79</v>
+      </c>
+      <c r="F60" s="10">
+        <v>52.999999999999993</v>
+      </c>
+      <c r="G60" s="14">
+        <v>52</v>
+      </c>
+      <c r="H60" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="10">
         <v>88</v>
       </c>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="17">
+      <c r="D61" s="14">
+        <v>58</v>
+      </c>
+      <c r="E61" s="14">
+        <v>77</v>
+      </c>
+      <c r="F61" s="10">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="G61" s="14">
+        <v>82</v>
+      </c>
+      <c r="H61" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C62" s="11">
+      <c r="C62" s="10">
         <v>86.5</v>
       </c>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="17">
+      <c r="D62" s="14">
+        <v>47</v>
+      </c>
+      <c r="E62" s="14">
+        <v>79</v>
+      </c>
+      <c r="F62" s="10">
+        <v>40.599999999999994</v>
+      </c>
+      <c r="G62" s="14">
+        <v>68</v>
+      </c>
+      <c r="H62" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="10">
         <v>93</v>
       </c>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="17">
+      <c r="D63" s="14">
+        <v>37</v>
+      </c>
+      <c r="E63" s="14">
+        <v>91</v>
+      </c>
+      <c r="F63" s="10">
+        <v>79.199999999999989</v>
+      </c>
+      <c r="G63" s="14">
+        <v>79</v>
+      </c>
+      <c r="H63" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C64" s="10">
         <v>80.5</v>
       </c>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="17">
+      <c r="D64" s="14">
+        <v>84</v>
+      </c>
+      <c r="E64" s="14">
+        <v>69</v>
+      </c>
+      <c r="F64" s="10">
+        <v>39</v>
+      </c>
+      <c r="G64" s="14">
+        <v>52</v>
+      </c>
+      <c r="H64" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="10">
         <v>83.5</v>
       </c>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="17">
+      <c r="D65" s="14">
+        <v>56</v>
+      </c>
+      <c r="E65" s="14">
+        <v>58</v>
+      </c>
+      <c r="F65" s="10">
+        <v>44.800000000000004</v>
+      </c>
+      <c r="G65" s="14">
+        <v>67</v>
+      </c>
+      <c r="H65" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C66" s="10">
         <v>87</v>
       </c>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="17">
+      <c r="D66" s="14">
+        <v>46</v>
+      </c>
+      <c r="E66" s="14">
+        <v>81</v>
+      </c>
+      <c r="F66" s="10">
+        <v>62.8</v>
+      </c>
+      <c r="G66" s="14">
+        <v>68</v>
+      </c>
+      <c r="H66" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="10">
         <v>62</v>
       </c>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="17">
+      <c r="D67" s="14">
+        <v>34</v>
+      </c>
+      <c r="E67" s="14">
+        <v>58</v>
+      </c>
+      <c r="F67" s="10">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="G67" s="14">
+        <v>49</v>
+      </c>
+      <c r="H67" s="18">
         <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="10">
         <v>61.5</v>
       </c>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="17">
+      <c r="D68" s="14">
+        <v>37</v>
+      </c>
+      <c r="E68" s="14">
+        <v>68</v>
+      </c>
+      <c r="F68" s="10">
+        <v>40</v>
+      </c>
+      <c r="G68" s="14">
+        <v>59</v>
+      </c>
+      <c r="H68" s="18">
         <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="10">
         <v>87.5</v>
       </c>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="17">
+      <c r="D69" s="14">
+        <v>32</v>
+      </c>
+      <c r="E69" s="14">
+        <v>74</v>
+      </c>
+      <c r="F69" s="10">
+        <v>47.6</v>
+      </c>
+      <c r="G69" s="14">
+        <v>42</v>
+      </c>
+      <c r="H69" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="10">
         <v>74</v>
       </c>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="17">
+      <c r="D70" s="14">
+        <v>37</v>
+      </c>
+      <c r="E70" s="14">
+        <v>52</v>
+      </c>
+      <c r="F70" s="10">
+        <v>42.6</v>
+      </c>
+      <c r="G70" s="14">
+        <v>40</v>
+      </c>
+      <c r="H70" s="18">
         <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="10">
         <v>86</v>
       </c>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="17">
+      <c r="D71" s="14">
+        <v>48</v>
+      </c>
+      <c r="E71" s="14">
+        <v>62</v>
+      </c>
+      <c r="F71" s="10">
+        <v>26.400000000000002</v>
+      </c>
+      <c r="G71" s="14">
+        <v>50</v>
+      </c>
+      <c r="H71" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C72" s="11">
+      <c r="C72" s="10">
         <v>83.5</v>
       </c>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="17">
+      <c r="D72" s="14">
+        <v>53</v>
+      </c>
+      <c r="E72" s="14">
+        <v>85</v>
+      </c>
+      <c r="F72" s="10">
+        <v>32.4</v>
+      </c>
+      <c r="G72" s="14">
+        <v>55</v>
+      </c>
+      <c r="H72" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="10">
         <v>98</v>
       </c>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="17">
+      <c r="D73" s="14">
+        <v>72</v>
+      </c>
+      <c r="E73" s="14">
+        <v>83</v>
+      </c>
+      <c r="F73" s="10">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="G73" s="14">
+        <v>60</v>
+      </c>
+      <c r="H73" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C74" s="11">
+      <c r="C74" s="10">
         <v>66.5</v>
       </c>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="17">
+      <c r="D74" s="14">
+        <v>30</v>
+      </c>
+      <c r="E74" s="14">
+        <v>42</v>
+      </c>
+      <c r="F74" s="10">
+        <v>38.999999999999993</v>
+      </c>
+      <c r="G74" s="14">
+        <v>35</v>
+      </c>
+      <c r="H74" s="18">
         <v>23.333333333333332</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="10">
         <v>65</v>
       </c>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="17">
+      <c r="D75" s="14">
+        <v>55</v>
+      </c>
+      <c r="E75" s="14">
+        <v>72</v>
+      </c>
+      <c r="F75" s="10">
+        <v>42.6</v>
+      </c>
+      <c r="G75" s="14">
+        <v>48</v>
+      </c>
+      <c r="H75" s="18">
         <v>40</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C76" s="10">
         <v>63</v>
       </c>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="17">
+      <c r="D76" s="14">
+        <v>14</v>
+      </c>
+      <c r="E76" s="14">
         <v>50</v>
       </c>
+      <c r="F76" s="10">
+        <v>31.2</v>
+      </c>
+      <c r="G76" s="14">
+        <v>37</v>
+      </c>
+      <c r="H76" s="18">
+        <v>50</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C77" s="11">
+      <c r="C77" s="10">
         <v>64</v>
       </c>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="17">
+      <c r="D77" s="14">
+        <v>35</v>
+      </c>
+      <c r="E77" s="14">
+        <v>84</v>
+      </c>
+      <c r="F77" s="10">
+        <v>59.199999999999996</v>
+      </c>
+      <c r="G77" s="14">
+        <v>54</v>
+      </c>
+      <c r="H77" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C78" s="11">
+      <c r="C78" s="10">
         <v>76</v>
       </c>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="17">
+      <c r="D78" s="14">
+        <v>44</v>
+      </c>
+      <c r="E78" s="14">
+        <v>86</v>
+      </c>
+      <c r="F78" s="10">
+        <v>36</v>
+      </c>
+      <c r="G78" s="14">
+        <v>54</v>
+      </c>
+      <c r="H78" s="18">
         <v>23.333333333333332</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="10">
         <v>57.5</v>
       </c>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="17">
+      <c r="D79" s="14">
+        <v>2</v>
+      </c>
+      <c r="E79" s="14">
+        <v>77</v>
+      </c>
+      <c r="F79" s="10">
+        <v>33</v>
+      </c>
+      <c r="G79" s="14">
+        <v>42</v>
+      </c>
+      <c r="H79" s="18">
         <v>43.333333333333336</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C80" s="11">
+      <c r="C80" s="10">
         <v>71</v>
       </c>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="17">
+      <c r="D80" s="14">
+        <v>39</v>
+      </c>
+      <c r="E80" s="14">
+        <v>75</v>
+      </c>
+      <c r="F80" s="10">
+        <v>25.6</v>
+      </c>
+      <c r="G80" s="14">
+        <v>63</v>
+      </c>
+      <c r="H80" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="10">
         <v>72</v>
       </c>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="17">
+      <c r="D81" s="14">
+        <v>31</v>
+      </c>
+      <c r="E81" s="14">
+        <v>83</v>
+      </c>
+      <c r="F81" s="10">
+        <v>46</v>
+      </c>
+      <c r="G81" s="14">
+        <v>58</v>
+      </c>
+      <c r="H81" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C82" s="11">
+      <c r="C82" s="10">
         <v>58</v>
       </c>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="17">
+      <c r="D82" s="14">
+        <v>22</v>
+      </c>
+      <c r="E82" s="14">
+        <v>67</v>
+      </c>
+      <c r="F82" s="10">
+        <v>32.4</v>
+      </c>
+      <c r="G82" s="14">
+        <v>54</v>
+      </c>
+      <c r="H82" s="18">
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="10">
         <v>93</v>
       </c>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="17">
+      <c r="D83" s="14">
+        <v>61</v>
+      </c>
+      <c r="E83" s="14">
+        <v>70</v>
+      </c>
+      <c r="F83" s="10">
+        <v>40.199999999999996</v>
+      </c>
+      <c r="G83" s="14">
+        <v>67</v>
+      </c>
+      <c r="H83" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C84" s="11">
+      <c r="C84" s="10">
         <v>89.5</v>
       </c>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="17">
+      <c r="D84" s="14">
+        <v>44</v>
+      </c>
+      <c r="E84" s="14">
+        <v>56</v>
+      </c>
+      <c r="F84" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="G84" s="14">
+        <v>70</v>
+      </c>
+      <c r="H84" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="10">
         <v>69</v>
       </c>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="17">
+      <c r="D85" s="14">
+        <v>32</v>
+      </c>
+      <c r="E85" s="14">
+        <v>59</v>
+      </c>
+      <c r="F85" s="10">
+        <v>45</v>
+      </c>
+      <c r="G85" s="14">
+        <v>47</v>
+      </c>
+      <c r="H85" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="10">
         <v>40</v>
       </c>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="17">
+      <c r="D86" s="14">
+        <v>21</v>
+      </c>
+      <c r="E86" s="14">
+        <v>85</v>
+      </c>
+      <c r="F86" s="10">
+        <v>45</v>
+      </c>
+      <c r="G86" s="14">
+        <v>42</v>
+      </c>
+      <c r="H86" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="10">
         <v>79</v>
       </c>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="17">
+      <c r="D87" s="14">
+        <v>39</v>
+      </c>
+      <c r="E87" s="14">
+        <v>68</v>
+      </c>
+      <c r="F87" s="10">
+        <v>45</v>
+      </c>
+      <c r="G87" s="14">
+        <v>47</v>
+      </c>
+      <c r="H87" s="18">
         <v>43.333333333333336</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C88" s="11">
+      <c r="C88" s="10">
         <v>100</v>
       </c>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="17">
+      <c r="D88" s="14">
+        <v>71</v>
+      </c>
+      <c r="E88" s="14">
+        <v>85</v>
+      </c>
+      <c r="F88" s="10">
+        <v>58.20000000000001</v>
+      </c>
+      <c r="G88" s="14">
+        <v>69</v>
+      </c>
+      <c r="H88" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="10">
         <v>96.5</v>
       </c>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="17">
+      <c r="D89" s="14">
+        <v>34</v>
+      </c>
+      <c r="E89" s="14">
+        <v>96</v>
+      </c>
+      <c r="F89" s="10">
+        <v>26.400000000000002</v>
+      </c>
+      <c r="G89" s="14">
+        <v>68</v>
+      </c>
+      <c r="H89" s="18">
         <v>43.333333333333336</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C90" s="11">
+      <c r="C90" s="10">
         <v>81.5</v>
       </c>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="17">
+      <c r="D90" s="14">
+        <v>35</v>
+      </c>
+      <c r="E90" s="14">
+        <v>73</v>
+      </c>
+      <c r="F90" s="10">
+        <v>36</v>
+      </c>
+      <c r="G90" s="14">
+        <v>56</v>
+      </c>
+      <c r="H90" s="18">
         <v>23.333333333333332</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="10">
         <v>77</v>
       </c>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="17">
+      <c r="D91" s="14">
+        <v>40</v>
+      </c>
+      <c r="E91" s="14">
+        <v>83</v>
+      </c>
+      <c r="F91" s="10">
+        <v>45</v>
+      </c>
+      <c r="G91" s="14">
+        <v>68</v>
+      </c>
+      <c r="H91" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="10">
         <v>95.5</v>
       </c>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="17">
+      <c r="D92" s="14">
+        <v>49</v>
+      </c>
+      <c r="E92" s="14">
+        <v>77</v>
+      </c>
+      <c r="F92" s="10">
+        <v>73.799999999999983</v>
+      </c>
+      <c r="G92" s="14">
+        <v>59</v>
+      </c>
+      <c r="H92" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="10">
         <v>75</v>
       </c>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="17">
+      <c r="D93" s="14">
+        <v>74</v>
+      </c>
+      <c r="E93" s="14">
+        <v>76</v>
+      </c>
+      <c r="F93" s="10">
+        <v>56.400000000000006</v>
+      </c>
+      <c r="G93" s="14">
+        <v>53</v>
+      </c>
+      <c r="H93" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C94" s="11">
+      <c r="C94" s="10">
         <v>87</v>
       </c>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="17">
+      <c r="D94" s="14">
+        <v>37</v>
+      </c>
+      <c r="E94" s="14">
+        <v>80</v>
+      </c>
+      <c r="F94" s="10">
+        <v>59.599999999999994</v>
+      </c>
+      <c r="G94" s="14">
+        <v>33</v>
+      </c>
+      <c r="H94" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C95" s="11">
+      <c r="C95" s="10">
         <v>84</v>
       </c>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="17">
+      <c r="D95" s="14">
+        <v>39</v>
+      </c>
+      <c r="E95" s="14">
+        <v>76</v>
+      </c>
+      <c r="F95" s="10">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="G95" s="14">
+        <v>55</v>
+      </c>
+      <c r="H95" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C96" s="11">
+      <c r="C96" s="10">
         <v>73</v>
       </c>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="17">
+      <c r="D96" s="14">
+        <v>54</v>
+      </c>
+      <c r="E96" s="14">
+        <v>64</v>
+      </c>
+      <c r="F96" s="10">
+        <v>51.2</v>
+      </c>
+      <c r="G96" s="14">
+        <v>65</v>
+      </c>
+      <c r="H96" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="10">
         <v>73</v>
       </c>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="17">
+      <c r="D97" s="14">
+        <v>39</v>
+      </c>
+      <c r="E97" s="14">
+        <v>74</v>
+      </c>
+      <c r="F97" s="10">
+        <v>57.199999999999982</v>
+      </c>
+      <c r="G97" s="14">
+        <v>42</v>
+      </c>
+      <c r="H97" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C98" s="11">
+      <c r="C98" s="10">
         <v>79</v>
       </c>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="17">
+      <c r="D98" s="14">
+        <v>41</v>
+      </c>
+      <c r="E98" s="14">
+        <v>60</v>
+      </c>
+      <c r="F98" s="10">
+        <v>31.2</v>
+      </c>
+      <c r="G98" s="14">
+        <v>59</v>
+      </c>
+      <c r="H98" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="10">
         <v>96</v>
       </c>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="17">
+      <c r="D99" s="14">
+        <v>38</v>
+      </c>
+      <c r="E99" s="14">
+        <v>79</v>
+      </c>
+      <c r="F99" s="10">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="G99" s="14">
+        <v>72</v>
+      </c>
+      <c r="H99" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C100" s="11">
+      <c r="C100" s="10">
         <v>94.5</v>
       </c>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="17">
+      <c r="D100" s="14">
+        <v>63</v>
+      </c>
+      <c r="E100" s="14">
+        <v>92</v>
+      </c>
+      <c r="F100" s="10">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="G100" s="14">
+        <v>62</v>
+      </c>
+      <c r="H100" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="10">
         <v>71</v>
       </c>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="17">
+      <c r="D101" s="14">
+        <v>62</v>
+      </c>
+      <c r="E101" s="14">
+        <v>69</v>
+      </c>
+      <c r="F101" s="10">
+        <v>31.2</v>
+      </c>
+      <c r="G101" s="14">
+        <v>57</v>
+      </c>
+      <c r="H101" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C102" s="11">
+      <c r="C102" s="10">
         <v>96</v>
       </c>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="17">
+      <c r="D102" s="14">
+        <v>79</v>
+      </c>
+      <c r="E102" s="14">
+        <v>84</v>
+      </c>
+      <c r="F102" s="10">
+        <v>44.599999999999994</v>
+      </c>
+      <c r="G102" s="14">
+        <v>74</v>
+      </c>
+      <c r="H102" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="6" t="s">
+      <c r="A103" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="10">
         <v>64</v>
       </c>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="17">
+      <c r="D103" s="14">
+        <v>29</v>
+      </c>
+      <c r="E103" s="14">
+        <v>74</v>
+      </c>
+      <c r="F103" s="10">
+        <v>31.2</v>
+      </c>
+      <c r="G103" s="14">
+        <v>36</v>
+      </c>
+      <c r="H103" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C104" s="11">
+      <c r="C104" s="10">
         <v>100</v>
       </c>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="17">
+      <c r="D104" s="14">
+        <v>58</v>
+      </c>
+      <c r="E104" s="14">
+        <v>85</v>
+      </c>
+      <c r="F104" s="10">
+        <v>51.4</v>
+      </c>
+      <c r="G104" s="14">
+        <v>84</v>
+      </c>
+      <c r="H104" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="6" t="s">
+      <c r="A105" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="10">
         <v>51</v>
       </c>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="17">
+      <c r="D105" s="14">
+        <v>22</v>
+      </c>
+      <c r="E105" s="14">
+        <v>95</v>
+      </c>
+      <c r="F105" s="10">
+        <v>46</v>
+      </c>
+      <c r="G105" s="14">
+        <v>72</v>
+      </c>
+      <c r="H105" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="6" t="s">
+      <c r="A106" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C106" s="11">
+      <c r="C106" s="10">
         <v>46</v>
       </c>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="17">
+      <c r="D106" s="14">
+        <v>44</v>
+      </c>
+      <c r="E106" s="14">
+        <v>82</v>
+      </c>
+      <c r="F106" s="10">
+        <v>57.8</v>
+      </c>
+      <c r="G106" s="14">
+        <v>35</v>
+      </c>
+      <c r="H106" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="10">
         <v>83</v>
       </c>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="17">
+      <c r="D107" s="14">
+        <v>18</v>
+      </c>
+      <c r="E107" s="14">
+        <v>62</v>
+      </c>
+      <c r="F107" s="10">
+        <v>38.999999999999993</v>
+      </c>
+      <c r="G107" s="14">
+        <v>57</v>
+      </c>
+      <c r="H107" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C108" s="11">
+      <c r="C108" s="10">
         <v>51</v>
       </c>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="17">
+      <c r="D108" s="14">
+        <v>41</v>
+      </c>
+      <c r="E108" s="14">
+        <v>72</v>
+      </c>
+      <c r="F108" s="10">
+        <v>49.8</v>
+      </c>
+      <c r="G108" s="14">
+        <v>67</v>
+      </c>
+      <c r="H108" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="10">
         <v>84</v>
       </c>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="17">
+      <c r="D109" s="14">
+        <v>43</v>
+      </c>
+      <c r="E109" s="14">
+        <v>95</v>
+      </c>
+      <c r="F109" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="G109" s="14">
+        <v>66</v>
+      </c>
+      <c r="H109" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="10">
         <v>77</v>
       </c>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="17">
+      <c r="D110" s="14">
+        <v>33</v>
+      </c>
+      <c r="E110" s="14">
+        <v>46</v>
+      </c>
+      <c r="F110" s="10">
+        <v>55.999999999999993</v>
+      </c>
+      <c r="G110" s="14">
+        <v>45</v>
+      </c>
+      <c r="H110" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="10">
         <v>39.5</v>
       </c>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="17">
+      <c r="D111" s="14">
+        <v>41</v>
+      </c>
+      <c r="E111" s="14">
+        <v>38</v>
+      </c>
+      <c r="F111" s="10">
+        <v>24.6</v>
+      </c>
+      <c r="G111" s="14">
+        <v>9</v>
+      </c>
+      <c r="H111" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C112" s="11">
+      <c r="C112" s="10">
         <v>88</v>
       </c>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="17">
+      <c r="D112" s="14">
+        <v>66</v>
+      </c>
+      <c r="E112" s="14">
+        <v>76</v>
+      </c>
+      <c r="F112" s="10">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="G112" s="14">
+        <v>72</v>
+      </c>
+      <c r="H112" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C113" s="11">
+      <c r="C113" s="10">
         <v>64</v>
       </c>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-      <c r="H113" s="17">
+      <c r="D113" s="14">
+        <v>25</v>
+      </c>
+      <c r="E113" s="14">
+        <v>49</v>
+      </c>
+      <c r="F113" s="10">
+        <v>45.6</v>
+      </c>
+      <c r="G113" s="14">
+        <v>44</v>
+      </c>
+      <c r="H113" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C114" s="11">
+      <c r="C114" s="10">
         <v>70</v>
       </c>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="17">
+      <c r="D114" s="14">
+        <v>72</v>
+      </c>
+      <c r="E114" s="14">
+        <v>53</v>
+      </c>
+      <c r="F114" s="10">
+        <v>47.199999999999989</v>
+      </c>
+      <c r="G114" s="14">
+        <v>56</v>
+      </c>
+      <c r="H114" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="10">
         <v>76</v>
       </c>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="17">
+      <c r="D115" s="14">
+        <v>54</v>
+      </c>
+      <c r="E115" s="14">
+        <v>84</v>
+      </c>
+      <c r="F115" s="10">
+        <v>60</v>
+      </c>
+      <c r="G115" s="14">
+        <v>75</v>
+      </c>
+      <c r="H115" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C116" s="11">
+      <c r="C116" s="10">
         <v>75</v>
       </c>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="17">
+      <c r="D116" s="14">
+        <v>51</v>
+      </c>
+      <c r="E116" s="14">
+        <v>88</v>
+      </c>
+      <c r="F116" s="10">
+        <v>48.800000000000004</v>
+      </c>
+      <c r="G116" s="14">
+        <v>56</v>
+      </c>
+      <c r="H116" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C117" s="11">
+      <c r="C117" s="10">
         <v>85.5</v>
       </c>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="17">
+      <c r="D117" s="14">
+        <v>45</v>
+      </c>
+      <c r="E117" s="14">
+        <v>97</v>
+      </c>
+      <c r="F117" s="10">
+        <v>59.599999999999994</v>
+      </c>
+      <c r="G117" s="14">
+        <v>43</v>
+      </c>
+      <c r="H117" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C118" s="11">
+      <c r="C118" s="10">
         <v>73.5</v>
       </c>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="17">
+      <c r="D118" s="14">
+        <v>71</v>
+      </c>
+      <c r="E118" s="14">
+        <v>74</v>
+      </c>
+      <c r="F118" s="10">
+        <v>52.800000000000004</v>
+      </c>
+      <c r="G118" s="14">
+        <v>60</v>
+      </c>
+      <c r="H118" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <v>97</v>
       </c>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-      <c r="H119" s="17">
+      <c r="D119" s="14">
+        <v>57</v>
+      </c>
+      <c r="E119" s="14">
+        <v>88</v>
+      </c>
+      <c r="F119" s="10">
+        <v>68.399999999999991</v>
+      </c>
+      <c r="G119" s="14">
+        <v>70</v>
+      </c>
+      <c r="H119" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C120" s="11">
+      <c r="C120" s="10">
         <v>84</v>
       </c>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-      <c r="H120" s="17">
+      <c r="D120" s="14">
+        <v>51</v>
+      </c>
+      <c r="E120" s="14">
+        <v>87</v>
+      </c>
+      <c r="F120" s="10">
+        <v>25.6</v>
+      </c>
+      <c r="G120" s="14">
+        <v>63</v>
+      </c>
+      <c r="H120" s="18">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C121" s="11">
+      <c r="C121" s="10">
         <v>79</v>
       </c>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="17">
+      <c r="D121" s="14">
+        <v>28</v>
+      </c>
+      <c r="E121" s="14">
+        <v>75</v>
+      </c>
+      <c r="F121" s="10">
+        <v>33</v>
+      </c>
+      <c r="G121" s="14">
+        <v>50</v>
+      </c>
+      <c r="H121" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C122" s="11">
-        <v>81</v>
-      </c>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-      <c r="H122" s="17">
+      <c r="C122" s="10">
+        <v>81</v>
+      </c>
+      <c r="D122" s="14">
+        <v>28</v>
+      </c>
+      <c r="E122" s="14">
+        <v>91</v>
+      </c>
+      <c r="F122" s="10">
+        <v>47.199999999999989</v>
+      </c>
+      <c r="G122" s="14">
+        <v>72</v>
+      </c>
+      <c r="H122" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C123" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-      <c r="H123" s="17">
+      <c r="C123" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D123" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E123" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F123" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G123" s="14">
+        <v>8</v>
+      </c>
+      <c r="H123" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C124" s="11">
+      <c r="C124" s="10">
         <v>88</v>
       </c>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-      <c r="H124" s="17">
+      <c r="D124" s="14">
+        <v>50</v>
+      </c>
+      <c r="E124" s="14">
+        <v>91</v>
+      </c>
+      <c r="F124" s="10">
+        <v>73</v>
+      </c>
+      <c r="G124" s="14">
+        <v>70</v>
+      </c>
+      <c r="H124" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="10">
         <v>96</v>
       </c>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-      <c r="H125" s="17">
+      <c r="D125" s="14">
+        <v>65</v>
+      </c>
+      <c r="E125" s="14">
+        <v>77</v>
+      </c>
+      <c r="F125" s="10">
+        <v>60</v>
+      </c>
+      <c r="G125" s="14">
+        <v>56</v>
+      </c>
+      <c r="H125" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="6" t="s">
+      <c r="A126" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C126" s="11">
+      <c r="C126" s="10">
         <v>90</v>
       </c>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-      <c r="H126" s="17">
+      <c r="D126" s="14">
+        <v>49</v>
+      </c>
+      <c r="E126" s="14">
+        <v>91</v>
+      </c>
+      <c r="F126" s="10">
+        <v>76.2</v>
+      </c>
+      <c r="G126" s="14">
+        <v>67</v>
+      </c>
+      <c r="H126" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="10">
         <v>51.5</v>
       </c>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-      <c r="H127" s="17">
+      <c r="D127" s="14">
+        <v>35</v>
+      </c>
+      <c r="E127" s="14">
+        <v>72</v>
+      </c>
+      <c r="F127" s="10">
+        <v>57.8</v>
+      </c>
+      <c r="G127" s="14">
+        <v>56</v>
+      </c>
+      <c r="H127" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C128" s="11">
+      <c r="C128" s="10">
         <v>87.5</v>
       </c>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-      <c r="H128" s="17">
+      <c r="D128" s="14">
+        <v>31</v>
+      </c>
+      <c r="E128" s="14">
+        <v>81</v>
+      </c>
+      <c r="F128" s="10">
+        <v>28.800000000000004</v>
+      </c>
+      <c r="G128" s="14">
+        <v>52</v>
+      </c>
+      <c r="H128" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="6" t="s">
+      <c r="A129" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="10">
         <v>70</v>
       </c>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-      <c r="H129" s="17">
+      <c r="D129" s="14">
+        <v>40</v>
+      </c>
+      <c r="E129" s="14">
+        <v>78</v>
+      </c>
+      <c r="F129" s="10">
+        <v>32.4</v>
+      </c>
+      <c r="G129" s="14">
+        <v>45</v>
+      </c>
+      <c r="H129" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="6" t="s">
+      <c r="A130" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C130" s="11">
+      <c r="C130" s="10">
         <v>54.5</v>
       </c>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
-      <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-      <c r="H130" s="17">
+      <c r="D130" s="14">
+        <v>28</v>
+      </c>
+      <c r="E130" s="14">
+        <v>81</v>
+      </c>
+      <c r="F130" s="10">
+        <v>71.8</v>
+      </c>
+      <c r="G130" s="14">
+        <v>42</v>
+      </c>
+      <c r="H130" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="6" t="s">
+      <c r="A131" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C131" s="11">
+      <c r="C131" s="10">
         <v>79</v>
       </c>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-      <c r="H131" s="17">
+      <c r="D131" s="14">
+        <v>45</v>
+      </c>
+      <c r="E131" s="14">
+        <v>91</v>
+      </c>
+      <c r="F131" s="10">
+        <v>60.199999999999996</v>
+      </c>
+      <c r="G131" s="14">
+        <v>56</v>
+      </c>
+      <c r="H131" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="6" t="s">
+      <c r="A132" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C132" s="11">
+      <c r="C132" s="10">
         <v>91</v>
       </c>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-      <c r="H132" s="17">
+      <c r="D132" s="14">
+        <v>56</v>
+      </c>
+      <c r="E132" s="14">
+        <v>92</v>
+      </c>
+      <c r="F132" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="G132" s="14">
+        <v>79</v>
+      </c>
+      <c r="H132" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="10">
         <v>50</v>
       </c>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-      <c r="H133" s="17">
+      <c r="D133" s="14">
+        <v>22</v>
+      </c>
+      <c r="E133" s="14">
+        <v>68</v>
+      </c>
+      <c r="F133" s="10">
+        <v>46.199999999999996</v>
+      </c>
+      <c r="G133" s="14">
+        <v>61</v>
+      </c>
+      <c r="H133" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="6" t="s">
+      <c r="A134" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C134" s="11">
+      <c r="C134" s="10">
         <v>86</v>
       </c>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-      <c r="H134" s="17">
+      <c r="D134" s="14">
+        <v>51</v>
+      </c>
+      <c r="E134" s="14">
+        <v>80</v>
+      </c>
+      <c r="F134" s="10">
+        <v>79.199999999999989</v>
+      </c>
+      <c r="G134" s="14">
+        <v>66</v>
+      </c>
+      <c r="H134" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="6" t="s">
+      <c r="A135" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="10">
         <v>57</v>
       </c>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-      <c r="H135" s="17">
+      <c r="D135" s="14">
+        <v>26</v>
+      </c>
+      <c r="E135" s="14">
         <v>80</v>
       </c>
+      <c r="F135" s="10">
+        <v>62.4</v>
+      </c>
+      <c r="G135" s="14">
+        <v>37</v>
+      </c>
+      <c r="H135" s="18">
+        <v>80</v>
+      </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="6" t="s">
+      <c r="A136" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C136" s="11">
+      <c r="C136" s="10">
         <v>59.5</v>
       </c>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
-      <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-      <c r="H136" s="17">
+      <c r="D136" s="14">
+        <v>20</v>
+      </c>
+      <c r="E136" s="14">
+        <v>87</v>
+      </c>
+      <c r="F136" s="10">
+        <v>61.599999999999987</v>
+      </c>
+      <c r="G136" s="14">
+        <v>50</v>
+      </c>
+      <c r="H136" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="6" t="s">
+      <c r="A137" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="10">
         <v>85</v>
       </c>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2"/>
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-      <c r="H137" s="17">
+      <c r="D137" s="14">
+        <v>59</v>
+      </c>
+      <c r="E137" s="14">
+        <v>61</v>
+      </c>
+      <c r="F137" s="10">
+        <v>58.20000000000001</v>
+      </c>
+      <c r="G137" s="14">
+        <v>65</v>
+      </c>
+      <c r="H137" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="6" t="s">
+      <c r="A138" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C138" s="11">
+      <c r="C138" s="10">
         <v>73</v>
       </c>
-      <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-      <c r="H138" s="17">
+      <c r="D138" s="14">
+        <v>57</v>
+      </c>
+      <c r="E138" s="14">
+        <v>75</v>
+      </c>
+      <c r="F138" s="10">
+        <v>49.4</v>
+      </c>
+      <c r="G138" s="14">
+        <v>56</v>
+      </c>
+      <c r="H138" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="6" t="s">
+      <c r="A139" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="10">
         <v>61</v>
       </c>
-      <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
-      <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-      <c r="H139" s="17">
+      <c r="D139" s="14">
+        <v>32</v>
+      </c>
+      <c r="E139" s="14">
+        <v>69</v>
+      </c>
+      <c r="F139" s="10">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="G139" s="14">
+        <v>51</v>
+      </c>
+      <c r="H139" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="6" t="s">
+      <c r="A140" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C140" s="11">
+      <c r="C140" s="10">
         <v>90.5</v>
       </c>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-      <c r="H140" s="17">
+      <c r="D140" s="14">
+        <v>90</v>
+      </c>
+      <c r="E140" s="14">
+        <v>84</v>
+      </c>
+      <c r="F140" s="10">
+        <v>42</v>
+      </c>
+      <c r="G140" s="14">
+        <v>63</v>
+      </c>
+      <c r="H140" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="6" t="s">
+      <c r="A141" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C141" s="11">
+      <c r="C141" s="10">
         <v>96.5</v>
       </c>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
-      <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
-      <c r="H141" s="17">
+      <c r="D141" s="14">
+        <v>49</v>
+      </c>
+      <c r="E141" s="14">
+        <v>80</v>
+      </c>
+      <c r="F141" s="10">
+        <v>40.199999999999996</v>
+      </c>
+      <c r="G141" s="14">
+        <v>41</v>
+      </c>
+      <c r="H141" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="6" t="s">
+      <c r="A142" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C142" s="11">
+      <c r="C142" s="10">
         <v>88.5</v>
       </c>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-      <c r="H142" s="17">
+      <c r="D142" s="14">
+        <v>30</v>
+      </c>
+      <c r="E142" s="14">
+        <v>87</v>
+      </c>
+      <c r="F142" s="10">
+        <v>47.2</v>
+      </c>
+      <c r="G142" s="14">
+        <v>53</v>
+      </c>
+      <c r="H142" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="6" t="s">
+      <c r="A143" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C143" s="11">
+      <c r="C143" s="10">
         <v>84</v>
       </c>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
-      <c r="F143" s="2"/>
-      <c r="G143" s="2"/>
-      <c r="H143" s="17">
+      <c r="D143" s="14">
+        <v>41</v>
+      </c>
+      <c r="E143" s="14">
+        <v>75</v>
+      </c>
+      <c r="F143" s="10">
+        <v>32.4</v>
+      </c>
+      <c r="G143" s="14">
+        <v>66</v>
+      </c>
+      <c r="H143" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="6" t="s">
+      <c r="A144" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C144" s="11">
+      <c r="C144" s="10">
         <v>96</v>
       </c>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
-      <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-      <c r="H144" s="17">
+      <c r="D144" s="14">
+        <v>68</v>
+      </c>
+      <c r="E144" s="14">
+        <v>73</v>
+      </c>
+      <c r="F144" s="10">
+        <v>24.6</v>
+      </c>
+      <c r="G144" s="14">
         <v>80</v>
       </c>
+      <c r="H144" s="18">
+        <v>80</v>
+      </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="6" t="s">
+      <c r="A145" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C145" s="11">
+      <c r="C145" s="10">
         <v>85</v>
       </c>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
-      <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-      <c r="H145" s="17">
+      <c r="D145" s="14">
+        <v>39</v>
+      </c>
+      <c r="E145" s="14">
+        <v>78</v>
+      </c>
+      <c r="F145" s="10">
+        <v>60.199999999999996</v>
+      </c>
+      <c r="G145" s="14">
+        <v>67</v>
+      </c>
+      <c r="H145" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="6" t="s">
+      <c r="A146" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C146" s="11">
+      <c r="C146" s="10">
         <v>100</v>
       </c>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
-      <c r="F146" s="2"/>
-      <c r="G146" s="2"/>
-      <c r="H146" s="17">
+      <c r="D146" s="14">
+        <v>52</v>
+      </c>
+      <c r="E146" s="14">
+        <v>98</v>
+      </c>
+      <c r="F146" s="10">
+        <v>72.600000000000009</v>
+      </c>
+      <c r="G146" s="14">
+        <v>70</v>
+      </c>
+      <c r="H146" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="6" t="s">
+      <c r="A147" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C147" s="11">
+      <c r="C147" s="10">
         <v>61.5</v>
       </c>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
-      <c r="F147" s="2"/>
-      <c r="G147" s="2"/>
-      <c r="H147" s="17">
+      <c r="D147" s="14">
+        <v>38</v>
+      </c>
+      <c r="E147" s="14">
+        <v>87</v>
+      </c>
+      <c r="F147" s="10">
+        <v>45.2</v>
+      </c>
+      <c r="G147" s="14">
+        <v>26</v>
+      </c>
+      <c r="H147" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="6" t="s">
+      <c r="A148" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C148" s="11">
+      <c r="C148" s="10">
         <v>70</v>
       </c>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
-      <c r="F148" s="2"/>
-      <c r="G148" s="2"/>
-      <c r="H148" s="17">
+      <c r="D148" s="14">
+        <v>46</v>
+      </c>
+      <c r="E148" s="14">
+        <v>89</v>
+      </c>
+      <c r="F148" s="10">
+        <v>56.600000000000009</v>
+      </c>
+      <c r="G148" s="14">
+        <v>38</v>
+      </c>
+      <c r="H148" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="6" t="s">
+      <c r="A149" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C149" s="11">
+      <c r="C149" s="10">
         <v>79</v>
       </c>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
-      <c r="F149" s="2"/>
-      <c r="G149" s="2"/>
-      <c r="H149" s="17">
+      <c r="D149" s="14">
+        <v>29</v>
+      </c>
+      <c r="E149" s="14">
+        <v>64</v>
+      </c>
+      <c r="F149" s="10">
+        <v>52.2</v>
+      </c>
+      <c r="G149" s="14">
+        <v>51</v>
+      </c>
+      <c r="H149" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="6" t="s">
+      <c r="A150" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C150" s="11">
+      <c r="C150" s="10">
         <v>89</v>
       </c>
-      <c r="D150" s="2"/>
-      <c r="E150" s="2"/>
-      <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-      <c r="H150" s="17">
+      <c r="D150" s="14">
+        <v>68</v>
+      </c>
+      <c r="E150" s="14">
+        <v>100</v>
+      </c>
+      <c r="F150" s="10">
+        <v>46.8</v>
+      </c>
+      <c r="G150" s="14">
+        <v>58</v>
+      </c>
+      <c r="H150" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="6" t="s">
+      <c r="A151" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C151" s="11">
+      <c r="C151" s="10">
         <v>86</v>
       </c>
-      <c r="D151" s="2"/>
-      <c r="E151" s="2"/>
-      <c r="F151" s="2"/>
-      <c r="G151" s="2"/>
-      <c r="H151" s="17">
+      <c r="D151" s="14">
+        <v>44</v>
+      </c>
+      <c r="E151" s="14">
+        <v>64</v>
+      </c>
+      <c r="F151" s="10">
+        <v>61.6</v>
+      </c>
+      <c r="G151" s="14">
+        <v>55</v>
+      </c>
+      <c r="H151" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="6" t="s">
+      <c r="A152" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B152" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C152" s="11">
+      <c r="C152" s="10">
         <v>61</v>
       </c>
-      <c r="D152" s="2"/>
-      <c r="E152" s="2"/>
-      <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-      <c r="H152" s="17">
+      <c r="D152" s="14">
+        <v>33</v>
+      </c>
+      <c r="E152" s="14">
+        <v>73</v>
+      </c>
+      <c r="F152" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="G152" s="14">
+        <v>41</v>
+      </c>
+      <c r="H152" s="18">
         <v>46.666666666666664</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="6" t="s">
+      <c r="A153" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C153" s="11">
+      <c r="C153" s="10">
         <v>89.5</v>
       </c>
-      <c r="D153" s="2"/>
-      <c r="E153" s="2"/>
-      <c r="F153" s="2"/>
-      <c r="G153" s="2"/>
-      <c r="H153" s="17">
+      <c r="D153" s="14">
+        <v>33</v>
+      </c>
+      <c r="E153" s="14">
+        <v>77</v>
+      </c>
+      <c r="F153" s="10">
+        <v>52.800000000000004</v>
+      </c>
+      <c r="G153" s="14">
+        <v>58</v>
+      </c>
+      <c r="H153" s="18">
         <v>70</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="6" t="s">
+      <c r="A154" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C154" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D154" s="2"/>
-      <c r="E154" s="2"/>
-      <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-      <c r="H154" s="17">
+      <c r="C154" s="10">
+        <v>82</v>
+      </c>
+      <c r="D154" s="14">
+        <v>38</v>
+      </c>
+      <c r="E154" s="14">
+        <v>76</v>
+      </c>
+      <c r="F154" s="10">
+        <v>25.799999999999994</v>
+      </c>
+      <c r="G154" s="14">
+        <v>72</v>
+      </c>
+      <c r="H154" s="18">
         <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="6" t="s">
+      <c r="A155" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C155" s="11">
+      <c r="C155" s="10">
         <v>57.5</v>
       </c>
-      <c r="D155" s="2"/>
-      <c r="E155" s="2"/>
-      <c r="F155" s="2"/>
-      <c r="G155" s="2"/>
-      <c r="H155" s="17">
+      <c r="D155" s="14">
+        <v>45</v>
+      </c>
+      <c r="E155" s="14">
+        <v>78</v>
+      </c>
+      <c r="F155" s="10">
+        <v>30</v>
+      </c>
+      <c r="G155" s="14">
+        <v>55</v>
+      </c>
+      <c r="H155" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="6" t="s">
+      <c r="A156" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C156" s="11">
+      <c r="C156" s="10">
         <v>84</v>
       </c>
-      <c r="D156" s="2"/>
-      <c r="E156" s="2"/>
-      <c r="F156" s="2"/>
-      <c r="G156" s="2"/>
-      <c r="H156" s="17">
+      <c r="D156" s="14">
+        <v>77</v>
+      </c>
+      <c r="E156" s="14">
+        <v>81</v>
+      </c>
+      <c r="F156" s="10">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="G156" s="14">
+        <v>90</v>
+      </c>
+      <c r="H156" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="6" t="s">
+      <c r="A157" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C157" s="11">
-        <v>81</v>
-      </c>
-      <c r="D157" s="2"/>
-      <c r="E157" s="2"/>
-      <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-      <c r="H157" s="17">
+      <c r="C157" s="10">
+        <v>81</v>
+      </c>
+      <c r="D157" s="14">
+        <v>92</v>
+      </c>
+      <c r="E157" s="14">
+        <v>59</v>
+      </c>
+      <c r="F157" s="10">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="G157" s="14">
+        <v>54</v>
+      </c>
+      <c r="H157" s="18">
         <v>56.666666666666664</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="6" t="s">
+      <c r="A158" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C158" s="11">
+      <c r="C158" s="10">
         <v>100</v>
       </c>
-      <c r="D158" s="2"/>
-      <c r="E158" s="2"/>
-      <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
-      <c r="H158" s="17">
+      <c r="D158" s="14">
+        <v>50</v>
+      </c>
+      <c r="E158" s="14">
+        <v>88</v>
+      </c>
+      <c r="F158" s="10">
+        <v>32.4</v>
+      </c>
+      <c r="G158" s="14">
+        <v>55</v>
+      </c>
+      <c r="H158" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="6" t="s">
+      <c r="A159" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C159" s="11">
+      <c r="C159" s="10">
         <v>46</v>
       </c>
-      <c r="D159" s="2"/>
-      <c r="E159" s="2"/>
-      <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-      <c r="H159" s="17">
+      <c r="D159" s="14">
+        <v>45</v>
+      </c>
+      <c r="E159" s="14">
+        <v>68</v>
+      </c>
+      <c r="F159" s="10">
+        <v>52.6</v>
+      </c>
+      <c r="G159" s="14">
+        <v>52</v>
+      </c>
+      <c r="H159" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="6" t="s">
+      <c r="A160" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C160" s="11">
+      <c r="C160" s="10">
         <v>79</v>
       </c>
-      <c r="D160" s="2"/>
-      <c r="E160" s="2"/>
-      <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-      <c r="H160" s="17">
+      <c r="D160" s="14">
+        <v>79</v>
+      </c>
+      <c r="E160" s="14">
+        <v>72</v>
+      </c>
+      <c r="F160" s="10">
+        <v>38.4</v>
+      </c>
+      <c r="G160" s="14">
+        <v>56</v>
+      </c>
+      <c r="H160" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="6" t="s">
+      <c r="A161" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C161" s="11">
+      <c r="C161" s="10">
         <v>73.5</v>
       </c>
-      <c r="D161" s="2"/>
-      <c r="E161" s="2"/>
-      <c r="F161" s="2"/>
-      <c r="G161" s="2"/>
-      <c r="H161" s="17">
+      <c r="D161" s="14">
+        <v>48</v>
+      </c>
+      <c r="E161" s="14">
+        <v>69</v>
+      </c>
+      <c r="F161" s="10">
+        <v>15</v>
+      </c>
+      <c r="G161" s="14">
+        <v>45</v>
+      </c>
+      <c r="H161" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="6" t="s">
+      <c r="A162" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B162" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C162" s="11">
+      <c r="C162" s="10">
         <v>92</v>
       </c>
-      <c r="D162" s="2"/>
-      <c r="E162" s="2"/>
-      <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-      <c r="H162" s="17">
+      <c r="D162" s="14">
+        <v>53</v>
+      </c>
+      <c r="E162" s="14">
+        <v>72</v>
+      </c>
+      <c r="F162" s="10">
+        <v>25.6</v>
+      </c>
+      <c r="G162" s="14">
+        <v>63</v>
+      </c>
+      <c r="H162" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="6" t="s">
+      <c r="A163" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C163" s="11">
+      <c r="C163" s="10">
         <v>78</v>
       </c>
-      <c r="D163" s="2"/>
-      <c r="E163" s="2"/>
-      <c r="F163" s="2"/>
-      <c r="G163" s="2"/>
-      <c r="H163" s="17">
+      <c r="D163" s="14">
+        <v>26</v>
+      </c>
+      <c r="E163" s="14">
+        <v>81</v>
+      </c>
+      <c r="F163" s="10">
+        <v>53.999999999999993</v>
+      </c>
+      <c r="G163" s="14">
+        <v>46</v>
+      </c>
+      <c r="H163" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="6" t="s">
+      <c r="A164" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C164" s="11">
+      <c r="C164" s="10">
         <v>79</v>
       </c>
-      <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
-      <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-      <c r="H164" s="17">
+      <c r="D164" s="14">
+        <v>41</v>
+      </c>
+      <c r="E164" s="14">
+        <v>70</v>
+      </c>
+      <c r="F164" s="10">
+        <v>25.799999999999994</v>
+      </c>
+      <c r="G164" s="14">
+        <v>78</v>
+      </c>
+      <c r="H164" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="6" t="s">
+      <c r="A165" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C165" s="11">
+      <c r="C165" s="10">
         <v>59.5</v>
       </c>
-      <c r="D165" s="2"/>
-      <c r="E165" s="2"/>
-      <c r="F165" s="2"/>
-      <c r="G165" s="2"/>
-      <c r="H165" s="17">
+      <c r="D165" s="14">
+        <v>29</v>
+      </c>
+      <c r="E165" s="14">
+        <v>72</v>
+      </c>
+      <c r="F165" s="10">
+        <v>46.8</v>
+      </c>
+      <c r="G165" s="14">
+        <v>50</v>
+      </c>
+      <c r="H165" s="18">
         <v>63.333333333333329</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="6" t="s">
+      <c r="A166" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C166" s="11">
+      <c r="C166" s="10">
         <v>74.5</v>
       </c>
-      <c r="D166" s="2"/>
-      <c r="E166" s="2"/>
-      <c r="F166" s="2"/>
-      <c r="G166" s="2"/>
-      <c r="H166" s="17">
+      <c r="D166" s="14">
+        <v>61</v>
+      </c>
+      <c r="E166" s="14">
+        <v>82</v>
+      </c>
+      <c r="F166" s="10">
+        <v>42.6</v>
+      </c>
+      <c r="G166" s="14">
+        <v>64</v>
+      </c>
+      <c r="H166" s="18">
         <v>36.666666666666664</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="6" t="s">
+      <c r="A167" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C167" s="11">
+      <c r="C167" s="10">
         <v>84</v>
       </c>
-      <c r="D167" s="2"/>
-      <c r="E167" s="2"/>
-      <c r="F167" s="2"/>
-      <c r="G167" s="2"/>
-      <c r="H167" s="17">
+      <c r="D167" s="14">
+        <v>66</v>
+      </c>
+      <c r="E167" s="14">
+        <v>68</v>
+      </c>
+      <c r="F167" s="10">
+        <v>81</v>
+      </c>
+      <c r="G167" s="14">
+        <v>78</v>
+      </c>
+      <c r="H167" s="18">
         <v>90</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="6" t="s">
+      <c r="A168" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C168" s="11">
+      <c r="C168" s="10">
         <v>76.5</v>
       </c>
-      <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
-      <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
-      <c r="H168" s="17">
+      <c r="D168" s="14">
+        <v>36</v>
+      </c>
+      <c r="E168" s="14">
+        <v>79</v>
+      </c>
+      <c r="F168" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="G168" s="14">
+        <v>63</v>
+      </c>
+      <c r="H168" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="6" t="s">
+      <c r="A169" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C169" s="11">
+      <c r="C169" s="10">
         <v>93</v>
       </c>
-      <c r="D169" s="2"/>
-      <c r="E169" s="2"/>
-      <c r="F169" s="2"/>
-      <c r="G169" s="2"/>
-      <c r="H169" s="17">
+      <c r="D169" s="14">
+        <v>80</v>
+      </c>
+      <c r="E169" s="14">
+        <v>90</v>
+      </c>
+      <c r="F169" s="10">
+        <v>41.6</v>
+      </c>
+      <c r="G169" s="14">
+        <v>79</v>
+      </c>
+      <c r="H169" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="6" t="s">
+      <c r="A170" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C170" s="11">
+      <c r="C170" s="10">
         <v>58.5</v>
       </c>
-      <c r="D170" s="2"/>
-      <c r="E170" s="2"/>
-      <c r="F170" s="2"/>
-      <c r="G170" s="2"/>
-      <c r="H170" s="17">
+      <c r="D170" s="14">
+        <v>23</v>
+      </c>
+      <c r="E170" s="14">
+        <v>78</v>
+      </c>
+      <c r="F170" s="10">
+        <v>36.599999999999994</v>
+      </c>
+      <c r="G170" s="14">
+        <v>38</v>
+      </c>
+      <c r="H170" s="18">
         <v>16.666666666666664</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="6" t="s">
+      <c r="A171" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C171" s="11">
+      <c r="C171" s="10">
         <v>47</v>
       </c>
-      <c r="D171" s="2"/>
-      <c r="E171" s="2"/>
-      <c r="F171" s="2"/>
-      <c r="G171" s="2"/>
-      <c r="H171" s="17">
+      <c r="D171" s="14">
+        <v>27</v>
+      </c>
+      <c r="E171" s="14">
+        <v>70</v>
+      </c>
+      <c r="F171" s="10">
+        <v>47.599999999999994</v>
+      </c>
+      <c r="G171" s="14">
+        <v>41</v>
+      </c>
+      <c r="H171" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="6" t="s">
+      <c r="A172" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="B172" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C172" s="11">
+      <c r="C172" s="10">
         <v>65</v>
       </c>
-      <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
-      <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
-      <c r="H172" s="17">
+      <c r="D172" s="14">
+        <v>31</v>
+      </c>
+      <c r="E172" s="14">
+        <v>55</v>
+      </c>
+      <c r="F172" s="10">
+        <v>25.799999999999994</v>
+      </c>
+      <c r="G172" s="14">
+        <v>30</v>
+      </c>
+      <c r="H172" s="18">
         <v>26.666666666666668</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="6" t="s">
+      <c r="A173" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C173" s="11">
+      <c r="C173" s="10">
         <v>83.5</v>
       </c>
-      <c r="D173" s="2"/>
-      <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-      <c r="H173" s="17">
+      <c r="D173" s="14">
+        <v>43</v>
+      </c>
+      <c r="E173" s="14">
+        <v>96</v>
+      </c>
+      <c r="F173" s="10">
+        <v>36</v>
+      </c>
+      <c r="G173" s="14">
+        <v>48</v>
+      </c>
+      <c r="H173" s="18">
         <v>16.666666666666664</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="6" t="s">
+      <c r="A174" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B174" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C174" s="11">
+      <c r="C174" s="10">
         <v>41</v>
       </c>
-      <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
-      <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-      <c r="H174" s="17">
+      <c r="D174" s="14">
+        <v>37</v>
+      </c>
+      <c r="E174" s="14">
+        <v>71</v>
+      </c>
+      <c r="F174" s="10">
+        <v>56.199999999999996</v>
+      </c>
+      <c r="G174" s="14">
+        <v>25</v>
+      </c>
+      <c r="H174" s="18">
         <v>76.666666666666671</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="6" t="s">
+      <c r="A175" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C175" s="11">
+      <c r="C175" s="10">
         <v>37</v>
       </c>
-      <c r="D175" s="2"/>
-      <c r="E175" s="2"/>
-      <c r="F175" s="2"/>
-      <c r="G175" s="2"/>
-      <c r="H175" s="17">
+      <c r="D175" s="14">
+        <v>50</v>
+      </c>
+      <c r="E175" s="14">
+        <v>75</v>
+      </c>
+      <c r="F175" s="10">
+        <v>45</v>
+      </c>
+      <c r="G175" s="14">
+        <v>29</v>
+      </c>
+      <c r="H175" s="18">
         <v>26.666666666666668</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="6" t="s">
+      <c r="A176" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C176" s="11">
+      <c r="C176" s="10">
         <v>65.5</v>
       </c>
-      <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
-      <c r="F176" s="2"/>
-      <c r="G176" s="2"/>
-      <c r="H176" s="17">
+      <c r="D176" s="14">
+        <v>54</v>
+      </c>
+      <c r="E176" s="14">
+        <v>62</v>
+      </c>
+      <c r="F176" s="10">
+        <v>45.4</v>
+      </c>
+      <c r="G176" s="14">
+        <v>55</v>
+      </c>
+      <c r="H176" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="6" t="s">
+      <c r="A177" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C177" s="11">
+      <c r="C177" s="10">
         <v>46.5</v>
       </c>
-      <c r="D177" s="2"/>
-      <c r="E177" s="2"/>
-      <c r="F177" s="2"/>
-      <c r="G177" s="2"/>
-      <c r="H177" s="17">
+      <c r="D177" s="14">
+        <v>32</v>
+      </c>
+      <c r="E177" s="14">
+        <v>79</v>
+      </c>
+      <c r="F177" s="10">
+        <v>51.800000000000004</v>
+      </c>
+      <c r="G177" s="14">
+        <v>49</v>
+      </c>
+      <c r="H177" s="18">
         <v>80</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="6" t="s">
+      <c r="A178" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="B178" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C178" s="11">
+      <c r="C178" s="10">
         <v>91</v>
       </c>
-      <c r="D178" s="2"/>
-      <c r="E178" s="2"/>
-      <c r="F178" s="2"/>
-      <c r="G178" s="2"/>
-      <c r="H178" s="17">
+      <c r="D178" s="14">
+        <v>54</v>
+      </c>
+      <c r="E178" s="14">
+        <v>81</v>
+      </c>
+      <c r="F178" s="10">
+        <v>60.999999999999986</v>
+      </c>
+      <c r="G178" s="14">
+        <v>84</v>
+      </c>
+      <c r="H178" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="6" t="s">
+      <c r="A179" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="B179" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C179" s="11">
+      <c r="C179" s="10">
         <v>85</v>
       </c>
-      <c r="D179" s="2"/>
-      <c r="E179" s="2"/>
-      <c r="F179" s="2"/>
-      <c r="G179" s="2"/>
-      <c r="H179" s="17">
+      <c r="D179" s="14">
+        <v>76</v>
+      </c>
+      <c r="E179" s="14">
+        <v>90</v>
+      </c>
+      <c r="F179" s="10">
+        <v>60.999999999999986</v>
+      </c>
+      <c r="G179" s="14">
+        <v>78</v>
+      </c>
+      <c r="H179" s="18">
         <v>96.666666666666671</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="6" t="s">
+      <c r="A180" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="B180" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C180" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D180" s="2"/>
-      <c r="E180" s="2"/>
-      <c r="F180" s="2"/>
-      <c r="G180" s="2"/>
-      <c r="H180" s="17">
+      <c r="C180" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D180" s="14">
+        <v>50</v>
+      </c>
+      <c r="E180" s="14">
+        <v>48</v>
+      </c>
+      <c r="F180" s="10">
+        <v>26.400000000000002</v>
+      </c>
+      <c r="G180" s="14">
+        <v>42</v>
+      </c>
+      <c r="H180" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" s="6" t="s">
+      <c r="A181" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B181" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C181" s="11">
-        <v>81</v>
-      </c>
-      <c r="D181" s="2"/>
-      <c r="E181" s="2"/>
-      <c r="F181" s="2"/>
-      <c r="G181" s="2"/>
-      <c r="H181" s="17">
+      <c r="C181" s="10">
+        <v>81</v>
+      </c>
+      <c r="D181" s="14">
+        <v>40</v>
+      </c>
+      <c r="E181" s="14">
+        <v>78</v>
+      </c>
+      <c r="F181" s="10">
+        <v>23.4</v>
+      </c>
+      <c r="G181" s="14">
+        <v>58</v>
+      </c>
+      <c r="H181" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="6" t="s">
+      <c r="A182" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="B182" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C182" s="11">
+      <c r="C182" s="10">
         <v>58.5</v>
       </c>
-      <c r="D182" s="2"/>
-      <c r="E182" s="2"/>
-      <c r="F182" s="2"/>
-      <c r="G182" s="2"/>
-      <c r="H182" s="17">
+      <c r="D182" s="14">
+        <v>61</v>
+      </c>
+      <c r="E182" s="14">
+        <v>66</v>
+      </c>
+      <c r="F182" s="10">
+        <v>33.800000000000004</v>
+      </c>
+      <c r="G182" s="14">
+        <v>34</v>
+      </c>
+      <c r="H182" s="18">
         <v>93.333333333333329</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="6" t="s">
+      <c r="A183" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C183" s="11">
+      <c r="C183" s="10">
         <v>94.5</v>
       </c>
-      <c r="D183" s="2"/>
-      <c r="E183" s="2"/>
-      <c r="F183" s="2"/>
-      <c r="G183" s="2"/>
-      <c r="H183" s="17">
+      <c r="D183" s="14">
+        <v>54</v>
+      </c>
+      <c r="E183" s="14">
+        <v>93</v>
+      </c>
+      <c r="F183" s="10">
+        <v>59.600000000000009</v>
+      </c>
+      <c r="G183" s="14">
+        <v>49</v>
+      </c>
+      <c r="H183" s="18">
         <v>66.666666666666657</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="6" t="s">
+      <c r="A184" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B184" s="3" t="s">
+      <c r="B184" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C184" s="11">
+      <c r="C184" s="10">
         <v>72</v>
       </c>
-      <c r="D184" s="2"/>
-      <c r="E184" s="2"/>
-      <c r="F184" s="2"/>
-      <c r="G184" s="2"/>
-      <c r="H184" s="17">
+      <c r="D184" s="14">
+        <v>70</v>
+      </c>
+      <c r="E184" s="14">
+        <v>76</v>
+      </c>
+      <c r="F184" s="10">
+        <v>52.6</v>
+      </c>
+      <c r="G184" s="14">
+        <v>67</v>
+      </c>
+      <c r="H184" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="6" t="s">
+      <c r="A185" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C185" s="11">
+      <c r="C185" s="10">
         <v>85</v>
       </c>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
-      <c r="F185" s="2"/>
-      <c r="G185" s="2"/>
-      <c r="H185" s="17">
+      <c r="D185" s="14">
+        <v>58</v>
+      </c>
+      <c r="E185" s="14">
+        <v>65</v>
+      </c>
+      <c r="F185" s="10">
+        <v>45</v>
+      </c>
+      <c r="G185" s="14">
+        <v>72</v>
+      </c>
+      <c r="H185" s="18">
         <v>73.333333333333329</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="6" t="s">
+      <c r="A186" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C186" s="11">
+      <c r="C186" s="10">
         <v>99</v>
       </c>
-      <c r="D186" s="2"/>
-      <c r="E186" s="2"/>
-      <c r="F186" s="2"/>
-      <c r="G186" s="2"/>
-      <c r="H186" s="17">
+      <c r="D186" s="14">
+        <v>52</v>
+      </c>
+      <c r="E186" s="14">
+        <v>74</v>
+      </c>
+      <c r="F186" s="10">
+        <v>49.599999999999994</v>
+      </c>
+      <c r="G186" s="14">
+        <v>58</v>
+      </c>
+      <c r="H186" s="18">
         <v>86.666666666666671</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="6" t="s">
+      <c r="A187" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C187" s="11">
+      <c r="C187" s="10">
         <v>44</v>
       </c>
-      <c r="D187" s="2"/>
-      <c r="E187" s="2"/>
-      <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-      <c r="H187" s="17">
+      <c r="D187" s="14">
+        <v>57</v>
+      </c>
+      <c r="E187" s="14">
+        <v>58</v>
+      </c>
+      <c r="F187" s="10">
+        <v>39.599999999999994</v>
+      </c>
+      <c r="G187" s="14">
+        <v>37</v>
+      </c>
+      <c r="H187" s="18">
         <v>50</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="6" t="s">
+      <c r="A188" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="B188" s="3" t="s">
+      <c r="B188" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C188" s="11">
+      <c r="C188" s="10">
         <v>91.5</v>
       </c>
-      <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
-      <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
+      <c r="D188" s="14">
+        <v>14</v>
+      </c>
+      <c r="E188" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F188" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="G188" s="14">
+        <v>42</v>
+      </c>
+      <c r="H188" s="18"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="8" t="s">
+      <c r="A189" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B189" s="7" t="s">
+      <c r="B189" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="C189" s="11">
+      <c r="C189" s="10">
         <v>86</v>
       </c>
-      <c r="D189" s="2"/>
-      <c r="E189" s="2"/>
-      <c r="F189" s="2"/>
-      <c r="G189" s="2"/>
+      <c r="D189" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E189" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F189" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G189" s="14">
+        <v>55</v>
+      </c>
+      <c r="H189" s="18"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="8" t="s">
+      <c r="A190" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B190" s="7" t="s">
+      <c r="B190" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="C190" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D190" s="2"/>
-      <c r="E190" s="2"/>
-      <c r="F190" s="2"/>
-      <c r="G190" s="2"/>
+      <c r="C190" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D190" s="14">
+        <v>31</v>
+      </c>
+      <c r="E190" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F190" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G190" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H190" s="18"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="8" t="s">
+      <c r="A191" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B191" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="C191" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D191" s="2"/>
-      <c r="E191" s="2"/>
-      <c r="F191" s="2"/>
-      <c r="G191" s="2"/>
+      <c r="C191" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D191" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E191" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F191" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G191" s="14">
+        <v>57</v>
+      </c>
+      <c r="H191" s="18"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="8" t="s">
+      <c r="A192" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="B192" s="7" t="s">
+      <c r="B192" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="11">
+      <c r="C192" s="10">
         <v>86.5</v>
       </c>
-      <c r="D192" s="2"/>
-      <c r="E192" s="2"/>
-      <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A193" s="8" t="s">
+      <c r="D192" s="14">
+        <v>23</v>
+      </c>
+      <c r="E192" s="14">
+        <v>68</v>
+      </c>
+      <c r="F192" s="10">
+        <v>46</v>
+      </c>
+      <c r="G192" s="14">
+        <v>44</v>
+      </c>
+      <c r="H192" s="18"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="B193" s="7" t="s">
+      <c r="B193" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="C193" s="11">
+      <c r="C193" s="10">
         <v>88.5</v>
       </c>
-      <c r="D193" s="2"/>
-      <c r="E193" s="2"/>
-      <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A194" s="8" t="s">
+      <c r="D193" s="14">
+        <v>21</v>
+      </c>
+      <c r="E193" s="14">
+        <v>64</v>
+      </c>
+      <c r="F193" s="10">
+        <v>47</v>
+      </c>
+      <c r="G193" s="14">
+        <v>44</v>
+      </c>
+      <c r="H193" s="18"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="B194" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="C194" s="11">
+      <c r="C194" s="10">
         <v>93</v>
       </c>
-      <c r="D194" s="2"/>
-      <c r="E194" s="2"/>
-      <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A195" s="8" t="s">
+      <c r="D194" s="14">
+        <v>86</v>
+      </c>
+      <c r="E194" s="14">
+        <v>73</v>
+      </c>
+      <c r="F194" s="10">
+        <v>67</v>
+      </c>
+      <c r="G194" s="14">
+        <v>61</v>
+      </c>
+      <c r="H194" s="18"/>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="B195" s="7" t="s">
+      <c r="B195" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="C195" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D195" s="2"/>
-      <c r="E195" s="2"/>
-      <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A196" s="8" t="s">
+      <c r="C195" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D195" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E195" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F195" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G195" s="14">
+        <v>76</v>
+      </c>
+      <c r="H195" s="18"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="B196" s="7" t="s">
+      <c r="B196" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="C196" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
-      <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A197" s="8" t="s">
+      <c r="C196" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D196" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E196" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F196" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G196" s="14">
+        <v>56</v>
+      </c>
+      <c r="H196" s="18"/>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="B197" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="C197" s="11">
+      <c r="C197" s="10">
         <v>87</v>
       </c>
-      <c r="D197" s="2"/>
-      <c r="E197" s="2"/>
-      <c r="F197" s="2"/>
-      <c r="G197" s="2"/>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A198" s="8" t="s">
+      <c r="D197" s="14">
+        <v>16</v>
+      </c>
+      <c r="E197" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F197" s="10">
+        <v>73</v>
+      </c>
+      <c r="G197" s="14">
+        <v>73</v>
+      </c>
+      <c r="H197" s="18"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B198" s="7" t="s">
+      <c r="B198" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="C198" s="11">
+      <c r="C198" s="10">
         <v>100</v>
       </c>
-      <c r="D198" s="2"/>
-      <c r="E198" s="2"/>
-      <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A199" s="8" t="s">
+      <c r="D198" s="14">
+        <v>37</v>
+      </c>
+      <c r="E198" s="14">
+        <v>62</v>
+      </c>
+      <c r="F198" s="10">
+        <v>60</v>
+      </c>
+      <c r="G198" s="14">
+        <v>42</v>
+      </c>
+      <c r="H198" s="18"/>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="B199" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="C199" s="11">
+      <c r="C199" s="10">
         <v>69</v>
       </c>
-      <c r="D199" s="2"/>
-      <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A200" s="8" t="s">
+      <c r="D199" s="14">
+        <v>42</v>
+      </c>
+      <c r="E199" s="14">
+        <v>78</v>
+      </c>
+      <c r="F199" s="10">
+        <v>47</v>
+      </c>
+      <c r="G199" s="14">
+        <v>45</v>
+      </c>
+      <c r="H199" s="18"/>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="B200" s="7" t="s">
+      <c r="B200" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C200" s="11">
+      <c r="C200" s="10">
         <v>83</v>
       </c>
-      <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A201" s="8" t="s">
+      <c r="D200" s="14">
+        <v>35</v>
+      </c>
+      <c r="E200" s="14">
+        <v>71</v>
+      </c>
+      <c r="F200" s="10">
+        <v>43</v>
+      </c>
+      <c r="G200" s="14">
+        <v>57</v>
+      </c>
+      <c r="H200" s="18"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B201" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="C201" s="11">
+      <c r="C201" s="10">
         <v>57</v>
       </c>
-      <c r="D201" s="2"/>
-      <c r="E201" s="2"/>
-      <c r="F201" s="2"/>
-      <c r="G201" s="2"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A202" s="8" t="s">
+      <c r="D201" s="14">
+        <v>29</v>
+      </c>
+      <c r="E201" s="14">
+        <v>43</v>
+      </c>
+      <c r="F201" s="10">
+        <v>47</v>
+      </c>
+      <c r="G201" s="14">
+        <v>37</v>
+      </c>
+      <c r="H201" s="18"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B202" s="7" t="s">
+      <c r="B202" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="C202" s="11">
+      <c r="C202" s="10">
         <v>100</v>
       </c>
-      <c r="D202" s="2"/>
-      <c r="E202" s="2"/>
-      <c r="F202" s="2"/>
-      <c r="G202" s="2"/>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A203" s="8" t="s">
+      <c r="D202" s="14">
+        <v>28</v>
+      </c>
+      <c r="E202" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F202" s="10">
+        <v>73</v>
+      </c>
+      <c r="G202" s="14">
+        <v>73</v>
+      </c>
+      <c r="H202" s="18"/>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="B203" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="C203" s="11">
+      <c r="C203" s="10">
         <v>68.5</v>
       </c>
-      <c r="D203" s="2"/>
-      <c r="E203" s="2"/>
-      <c r="F203" s="2"/>
-      <c r="G203" s="2"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A204" s="8" t="s">
+      <c r="D203" s="14">
+        <v>69</v>
+      </c>
+      <c r="E203" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F203" s="10">
+        <v>60</v>
+      </c>
+      <c r="G203" s="14">
+        <v>51</v>
+      </c>
+      <c r="H203" s="18"/>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="B204" s="7" t="s">
+      <c r="B204" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="C204" s="11">
+      <c r="C204" s="10">
         <v>52.5</v>
       </c>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A205" s="8" t="s">
+      <c r="D204" s="14">
+        <v>24</v>
+      </c>
+      <c r="E204" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F204" s="10">
+        <v>73</v>
+      </c>
+      <c r="G204" s="14">
+        <v>55</v>
+      </c>
+      <c r="H204" s="18"/>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="B205" s="7" t="s">
+      <c r="B205" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="C205" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A206" s="8" t="s">
+      <c r="C205" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D205" s="14">
+        <v>15</v>
+      </c>
+      <c r="E205" s="14">
+        <v>66</v>
+      </c>
+      <c r="F205" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G205" s="14">
+        <v>36</v>
+      </c>
+      <c r="H205" s="18"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="B206" s="7" t="s">
+      <c r="B206" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="C206" s="11">
+      <c r="C206" s="10">
         <v>83.5</v>
       </c>
-      <c r="D206" s="2"/>
-      <c r="E206" s="2"/>
-      <c r="F206" s="2"/>
-      <c r="G206" s="2"/>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A207" s="8" t="s">
+      <c r="D206" s="14">
+        <v>59</v>
+      </c>
+      <c r="E206" s="14">
+        <v>86</v>
+      </c>
+      <c r="F206" s="10">
+        <v>60</v>
+      </c>
+      <c r="G206" s="14">
+        <v>42</v>
+      </c>
+      <c r="H206" s="18"/>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="B207" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="C207" s="11">
+      <c r="C207" s="10">
         <v>72.5</v>
       </c>
-      <c r="D207" s="2"/>
-      <c r="E207" s="2"/>
-      <c r="F207" s="2"/>
-      <c r="G207" s="2"/>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A208" s="8" t="s">
+      <c r="D207" s="14">
+        <v>60</v>
+      </c>
+      <c r="E207" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F207" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G207" s="14">
+        <v>49</v>
+      </c>
+      <c r="H207" s="18"/>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B208" s="7" t="s">
+      <c r="B208" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="C208" s="11">
+      <c r="C208" s="10">
         <v>31.5</v>
       </c>
-      <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
-      <c r="F208" s="2"/>
-      <c r="G208" s="2"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A209" s="8" t="s">
+      <c r="D208" s="14">
+        <v>39</v>
+      </c>
+      <c r="E208" s="14">
+        <v>49</v>
+      </c>
+      <c r="F208" s="10">
+        <v>50</v>
+      </c>
+      <c r="G208" s="14">
+        <v>16</v>
+      </c>
+      <c r="H208" s="18"/>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B209" s="7" t="s">
+      <c r="B209" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="C209" s="11">
+      <c r="C209" s="10">
         <v>53</v>
       </c>
-      <c r="D209" s="2"/>
-      <c r="E209" s="2"/>
-      <c r="F209" s="2"/>
-      <c r="G209" s="2"/>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A210" s="8" t="s">
+      <c r="D209" s="14">
+        <v>11</v>
+      </c>
+      <c r="E209" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F209" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G209" s="14">
+        <v>42</v>
+      </c>
+      <c r="H209" s="18"/>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="B210" s="7" t="s">
+      <c r="B210" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="C210" s="11">
+      <c r="C210" s="10">
         <v>66</v>
       </c>
-      <c r="D210" s="2"/>
-      <c r="E210" s="2"/>
-      <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A211" s="8" t="s">
+      <c r="D210" s="14">
+        <v>33</v>
+      </c>
+      <c r="E210" s="14">
+        <v>41</v>
+      </c>
+      <c r="F210" s="10">
+        <v>60</v>
+      </c>
+      <c r="G210" s="14">
+        <v>43</v>
+      </c>
+      <c r="H210" s="18"/>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B211" s="7" t="s">
+      <c r="B211" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="C211" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D211" s="2"/>
-      <c r="E211" s="2"/>
-      <c r="F211" s="2"/>
-      <c r="G211" s="2"/>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A212" s="8" t="s">
+      <c r="C211" s="10">
+        <v>96</v>
+      </c>
+      <c r="D211" s="14">
+        <v>60</v>
+      </c>
+      <c r="E211" s="14">
+        <v>69</v>
+      </c>
+      <c r="F211" s="10">
+        <v>60</v>
+      </c>
+      <c r="G211" s="14">
+        <v>56</v>
+      </c>
+      <c r="H211" s="18"/>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B212" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="C212" s="11">
+      <c r="C212" s="10">
         <v>65</v>
       </c>
-      <c r="D212" s="2"/>
-      <c r="E212" s="2"/>
-      <c r="F212" s="2"/>
-      <c r="G212" s="2"/>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A213" s="8" t="s">
+      <c r="D212" s="14">
+        <v>38</v>
+      </c>
+      <c r="E212" s="14">
+        <v>34</v>
+      </c>
+      <c r="F212" s="10">
+        <v>73</v>
+      </c>
+      <c r="G212" s="14">
+        <v>45</v>
+      </c>
+      <c r="H212" s="18"/>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="B213" s="7" t="s">
+      <c r="B213" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="C213" s="11">
+      <c r="C213" s="10">
         <v>65</v>
       </c>
-      <c r="D213" s="2"/>
-      <c r="E213" s="2"/>
-      <c r="F213" s="2"/>
-      <c r="G213" s="2"/>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A214" s="8" t="s">
+      <c r="D213" s="14">
+        <v>21</v>
+      </c>
+      <c r="E213" s="14">
+        <v>60</v>
+      </c>
+      <c r="F213" s="10">
+        <v>60</v>
+      </c>
+      <c r="G213" s="14">
+        <v>55</v>
+      </c>
+      <c r="H213" s="18"/>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B214" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="C214" s="11">
+      <c r="C214" s="10">
         <v>84</v>
       </c>
-      <c r="D214" s="2"/>
-      <c r="E214" s="2"/>
-      <c r="F214" s="2"/>
-      <c r="G214" s="2"/>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A215" s="8" t="s">
+      <c r="D214" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E214" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F214" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G214" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H214" s="18"/>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="B215" s="7" t="s">
+      <c r="B215" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="C215" s="11">
+      <c r="C215" s="10">
         <v>44</v>
       </c>
-      <c r="D215" s="2"/>
-      <c r="E215" s="2"/>
-      <c r="F215" s="2"/>
-      <c r="G215" s="2"/>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A216" s="8" t="s">
+      <c r="D215" s="14">
+        <v>33</v>
+      </c>
+      <c r="E215" s="14">
+        <v>55</v>
+      </c>
+      <c r="F215" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G215" s="14">
+        <v>28</v>
+      </c>
+      <c r="H215" s="18"/>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="B216" s="7" t="s">
+      <c r="B216" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="C216" s="11">
+      <c r="C216" s="10">
         <v>84.5</v>
       </c>
-      <c r="D216" s="2"/>
-      <c r="E216" s="2"/>
-      <c r="F216" s="2"/>
-      <c r="G216" s="2"/>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A217" s="8" t="s">
+      <c r="D216" s="14">
+        <v>39</v>
+      </c>
+      <c r="E216" s="14">
+        <v>66</v>
+      </c>
+      <c r="F216" s="10">
+        <v>60</v>
+      </c>
+      <c r="G216" s="14">
+        <v>48</v>
+      </c>
+      <c r="H216" s="18"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="B217" s="7" t="s">
+      <c r="B217" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="C217" s="11">
+      <c r="C217" s="10">
         <v>90</v>
       </c>
-      <c r="D217" s="2"/>
-      <c r="E217" s="2"/>
-      <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A218" s="8" t="s">
+      <c r="D217" s="14">
+        <v>29</v>
+      </c>
+      <c r="E217" s="14">
+        <v>38</v>
+      </c>
+      <c r="F217" s="10">
+        <v>67</v>
+      </c>
+      <c r="G217" s="14">
+        <v>58</v>
+      </c>
+      <c r="H217" s="18"/>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="B218" s="7" t="s">
+      <c r="B218" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="C218" s="11">
+      <c r="C218" s="10">
         <v>78</v>
       </c>
-      <c r="D218" s="2"/>
-      <c r="E218" s="2"/>
-      <c r="F218" s="2"/>
-      <c r="G218" s="2"/>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A219" s="8" t="s">
+      <c r="D218" s="14">
+        <v>41</v>
+      </c>
+      <c r="E218" s="14">
+        <v>60</v>
+      </c>
+      <c r="F218" s="10">
+        <v>60</v>
+      </c>
+      <c r="G218" s="14">
+        <v>67</v>
+      </c>
+      <c r="H218" s="18"/>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="B219" s="7" t="s">
+      <c r="B219" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="C219" s="11">
+      <c r="C219" s="10">
         <v>69</v>
       </c>
-      <c r="D219" s="2"/>
-      <c r="E219" s="2"/>
-      <c r="F219" s="2"/>
-      <c r="G219" s="2"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A220" s="8" t="s">
+      <c r="D219" s="14">
+        <v>44</v>
+      </c>
+      <c r="E219" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F219" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G219" s="14">
+        <v>59</v>
+      </c>
+      <c r="H219" s="18"/>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B220" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="C220" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
-      <c r="G220" s="2"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A221" s="8" t="s">
+      <c r="C220" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D220" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E220" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F220" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G220" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H220" s="18"/>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="B221" s="7" t="s">
+      <c r="B221" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="C221" s="11">
+      <c r="C221" s="10">
         <v>79</v>
       </c>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
-      <c r="G221" s="2"/>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A222" s="8" t="s">
+      <c r="D221" s="14">
+        <v>17</v>
+      </c>
+      <c r="E221" s="14">
+        <v>46</v>
+      </c>
+      <c r="F221" s="10">
+        <v>60</v>
+      </c>
+      <c r="G221" s="14">
+        <v>41</v>
+      </c>
+      <c r="H221" s="18"/>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B222" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="C222" s="11">
+      <c r="C222" s="10">
         <v>54</v>
       </c>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
-      <c r="G222" s="2"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A223" s="8" t="s">
+      <c r="D222" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E222" s="14">
+        <v>82</v>
+      </c>
+      <c r="F222" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G222" s="14">
+        <v>38</v>
+      </c>
+      <c r="H222" s="18"/>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="B223" s="7" t="s">
+      <c r="B223" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="C223" s="11">
+      <c r="C223" s="10">
         <v>60</v>
       </c>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A224" s="8" t="s">
+      <c r="D223" s="14">
+        <v>42</v>
+      </c>
+      <c r="E223" s="14">
+        <v>61</v>
+      </c>
+      <c r="F223" s="10">
+        <v>81</v>
+      </c>
+      <c r="G223" s="14">
+        <v>39</v>
+      </c>
+      <c r="H223" s="18"/>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B224" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="C224" s="11">
+      <c r="C224" s="10">
         <v>38.5</v>
       </c>
-      <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
-      <c r="F224" s="2"/>
-      <c r="G224" s="2"/>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A225" s="8" t="s">
+      <c r="D224" s="14">
+        <v>47</v>
+      </c>
+      <c r="E224" s="14">
+        <v>59</v>
+      </c>
+      <c r="F224" s="10">
+        <v>81</v>
+      </c>
+      <c r="G224" s="14">
+        <v>68</v>
+      </c>
+      <c r="H224" s="18"/>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="B225" s="7" t="s">
+      <c r="B225" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="C225" s="11">
+      <c r="C225" s="10">
         <v>89</v>
       </c>
-      <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
-      <c r="F225" s="2"/>
-      <c r="G225" s="2"/>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A226" s="8" t="s">
+      <c r="D225" s="14">
+        <v>44</v>
+      </c>
+      <c r="E225" s="14">
+        <v>48</v>
+      </c>
+      <c r="F225" s="10">
+        <v>81</v>
+      </c>
+      <c r="G225" s="14">
+        <v>57</v>
+      </c>
+      <c r="H225" s="18"/>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B226" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="C226" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D226" s="2"/>
-      <c r="E226" s="2"/>
-      <c r="F226" s="2"/>
-      <c r="G226" s="2"/>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A227" s="8" t="s">
+      <c r="C226" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D226" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E226" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F226" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G226" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H226" s="18"/>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="B227" s="7" t="s">
+      <c r="B227" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="C227" s="11">
+      <c r="C227" s="10">
         <v>35</v>
       </c>
-      <c r="D227" s="2"/>
-      <c r="E227" s="2"/>
-      <c r="F227" s="2"/>
-      <c r="G227" s="2"/>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A228" s="8" t="s">
+      <c r="D227" s="14">
+        <v>24</v>
+      </c>
+      <c r="E227" s="14">
+        <v>69</v>
+      </c>
+      <c r="F227" s="10">
+        <v>81</v>
+      </c>
+      <c r="G227" s="14">
+        <v>23</v>
+      </c>
+      <c r="H227" s="18"/>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="B228" s="7" t="s">
+      <c r="B228" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="C228" s="11">
+      <c r="C228" s="10">
         <v>69</v>
       </c>
-      <c r="D228" s="2"/>
-      <c r="E228" s="2"/>
-      <c r="F228" s="2"/>
-      <c r="G228" s="2"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A229" s="8" t="s">
+      <c r="D228" s="14">
+        <v>9</v>
+      </c>
+      <c r="E228" s="14">
+        <v>93</v>
+      </c>
+      <c r="F228" s="10">
+        <v>81</v>
+      </c>
+      <c r="G228" s="14">
+        <v>55</v>
+      </c>
+      <c r="H228" s="18"/>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B229" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="C229" s="11">
+      <c r="C229" s="10">
         <v>62.5</v>
       </c>
-      <c r="D229" s="2"/>
-      <c r="E229" s="2"/>
-      <c r="F229" s="2"/>
-      <c r="G229" s="2"/>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A230" s="8" t="s">
+      <c r="D229" s="14">
+        <v>22</v>
+      </c>
+      <c r="E229" s="14">
+        <v>53</v>
+      </c>
+      <c r="F229" s="10">
+        <v>67</v>
+      </c>
+      <c r="G229" s="14">
+        <v>50</v>
+      </c>
+      <c r="H229" s="18"/>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="B230" s="7" t="s">
+      <c r="B230" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="C230" s="11">
+      <c r="C230" s="10">
         <v>65</v>
       </c>
-      <c r="D230" s="2"/>
-      <c r="E230" s="2"/>
-      <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A231" s="8" t="s">
+      <c r="D230" s="14">
+        <v>48</v>
+      </c>
+      <c r="E230" s="14">
+        <v>69</v>
+      </c>
+      <c r="F230" s="10">
+        <v>67</v>
+      </c>
+      <c r="G230" s="14">
+        <v>50</v>
+      </c>
+      <c r="H230" s="18"/>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B231" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="C231" s="11">
+      <c r="C231" s="10">
         <v>49.5</v>
       </c>
-      <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
-      <c r="G231" s="2"/>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A232" s="8" t="s">
+      <c r="D231" s="14">
+        <v>75</v>
+      </c>
+      <c r="E231" s="14">
+        <v>18</v>
+      </c>
+      <c r="F231" s="10">
+        <v>81</v>
+      </c>
+      <c r="G231" s="14">
+        <v>44</v>
+      </c>
+      <c r="H231" s="18"/>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="B232" s="7" t="s">
+      <c r="B232" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="C232" s="11">
+      <c r="C232" s="10">
         <v>85</v>
       </c>
-      <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
-      <c r="G232" s="2"/>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A233" s="8" t="s">
+      <c r="D232" s="14">
+        <v>23</v>
+      </c>
+      <c r="E232" s="14">
+        <v>69</v>
+      </c>
+      <c r="F232" s="10">
+        <v>67</v>
+      </c>
+      <c r="G232" s="14">
+        <v>55</v>
+      </c>
+      <c r="H232" s="18"/>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B233" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="C233" s="11">
+      <c r="C233" s="10">
         <v>77.5</v>
       </c>
-      <c r="D233" s="2"/>
-      <c r="E233" s="2"/>
-      <c r="F233" s="2"/>
-      <c r="G233" s="2"/>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A234" s="8" t="s">
+      <c r="D233" s="14">
+        <v>34</v>
+      </c>
+      <c r="E233" s="14">
+        <v>61</v>
+      </c>
+      <c r="F233" s="10">
+        <v>47</v>
+      </c>
+      <c r="G233" s="14">
+        <v>56</v>
+      </c>
+      <c r="H233" s="18"/>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="C234" s="11">
+      <c r="C234" s="10">
         <v>57</v>
       </c>
-      <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A235" s="8" t="s">
+      <c r="D234" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E234" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F234" s="10">
+        <v>47</v>
+      </c>
+      <c r="G234" s="14">
+        <v>53</v>
+      </c>
+      <c r="H234" s="18"/>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="B235" s="7" t="s">
+      <c r="B235" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="C235" s="11">
+      <c r="C235" s="10">
         <v>92.5</v>
       </c>
-      <c r="D235" s="2"/>
-      <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A236" s="8" t="s">
+      <c r="D235" s="14">
+        <v>78</v>
+      </c>
+      <c r="E235" s="14">
+        <v>86</v>
+      </c>
+      <c r="F235" s="10">
+        <v>60</v>
+      </c>
+      <c r="G235" s="14">
+        <v>57</v>
+      </c>
+      <c r="H235" s="18"/>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="B236" s="7" t="s">
+      <c r="B236" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="C236" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D236" s="2"/>
-      <c r="E236" s="2"/>
-      <c r="F236" s="2"/>
-      <c r="G236" s="2"/>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A237" s="8" t="s">
+      <c r="C236" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D236" s="14">
+        <v>54</v>
+      </c>
+      <c r="E236" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F236" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G236" s="14">
+        <v>52</v>
+      </c>
+      <c r="H236" s="18"/>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="B237" s="4" t="s">
+      <c r="B237" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C237" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D237" s="2"/>
-      <c r="E237" s="2"/>
-      <c r="F237" s="2"/>
-      <c r="G237" s="2"/>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A238" s="8" t="s">
+      <c r="C237" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D237" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E237" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F237" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G237" s="14">
+        <v>25</v>
+      </c>
+      <c r="H237" s="18"/>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="B238" s="4" t="s">
+      <c r="B238" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C238" s="11">
+      <c r="C238" s="10">
         <v>30</v>
       </c>
-      <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A239" s="8" t="s">
+      <c r="D238" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E238" s="14">
+        <v>34</v>
+      </c>
+      <c r="F238" s="10">
+        <v>43</v>
+      </c>
+      <c r="G238" s="14">
+        <v>7</v>
+      </c>
+      <c r="H238" s="18"/>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="B239" s="4" t="s">
+      <c r="B239" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="C239" s="11">
+      <c r="C239" s="10">
         <v>74</v>
       </c>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A240" s="8" t="s">
+      <c r="D239" s="14">
+        <v>17</v>
+      </c>
+      <c r="E239" s="14">
+        <v>31</v>
+      </c>
+      <c r="F239" s="10">
+        <v>73</v>
+      </c>
+      <c r="G239" s="14">
+        <v>37</v>
+      </c>
+      <c r="H239" s="18"/>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="B240" s="9" t="s">
+      <c r="B240" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="C240" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-      <c r="F240" s="2"/>
-      <c r="G240" s="2"/>
+      <c r="C240" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D240" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E240" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G240" s="14">
+        <v>39</v>
+      </c>
+      <c r="H240" s="18"/>
     </row>
     <row r="241" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A241" s="10"/>
-      <c r="B241" s="10"/>
-      <c r="C241" s="12"/>
-      <c r="D241" s="10"/>
-      <c r="E241" s="10"/>
-      <c r="F241" s="10"/>
-      <c r="G241" s="10"/>
+      <c r="A241" s="9"/>
+      <c r="B241" s="9"/>
+      <c r="C241" s="11"/>
+      <c r="D241" s="9"/>
+      <c r="E241" s="9"/>
+      <c r="F241" s="9"/>
+      <c r="G241" s="9"/>
     </row>
     <row r="242" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A242" s="10"/>
-      <c r="B242" s="10"/>
-      <c r="C242" s="12"/>
-      <c r="D242" s="10"/>
-      <c r="E242" s="10"/>
-      <c r="F242" s="10"/>
-      <c r="G242" s="10"/>
+      <c r="A242" s="9"/>
+      <c r="B242" s="9"/>
+      <c r="C242" s="11"/>
+      <c r="D242" s="9"/>
+      <c r="E242" s="9"/>
+      <c r="F242" s="9"/>
+      <c r="G242" s="9"/>
     </row>
     <row r="243" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A243" s="10"/>
-      <c r="B243" s="10"/>
-      <c r="C243" s="12"/>
-      <c r="D243" s="10"/>
-      <c r="E243" s="10"/>
-      <c r="F243" s="10"/>
-      <c r="G243" s="10"/>
+      <c r="A243" s="9"/>
+      <c r="B243" s="9"/>
+      <c r="C243" s="11"/>
+      <c r="D243" s="9"/>
+      <c r="E243" s="9"/>
+      <c r="F243" s="9"/>
+      <c r="G243" s="9"/>
     </row>
     <row r="244" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A244" s="10"/>
-      <c r="B244" s="10"/>
-      <c r="C244" s="12"/>
-      <c r="D244" s="10"/>
-      <c r="E244" s="10"/>
-      <c r="F244" s="10"/>
-      <c r="G244" s="10"/>
+      <c r="A244" s="9"/>
+      <c r="B244" s="9"/>
+      <c r="C244" s="11"/>
+      <c r="D244" s="9"/>
+      <c r="E244" s="9"/>
+      <c r="F244" s="9"/>
+      <c r="G244" s="9"/>
     </row>
     <row r="245" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A245" s="10"/>
-      <c r="B245" s="10"/>
-      <c r="C245" s="12"/>
-      <c r="D245" s="10"/>
-      <c r="E245" s="10"/>
-      <c r="F245" s="10"/>
-      <c r="G245" s="10"/>
+      <c r="A245" s="9"/>
+      <c r="B245" s="9"/>
+      <c r="C245" s="11"/>
+      <c r="D245" s="9"/>
+      <c r="E245" s="9"/>
+      <c r="F245" s="9"/>
+      <c r="G245" s="9"/>
     </row>
     <row r="246" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A246" s="10"/>
-      <c r="B246" s="10"/>
-      <c r="C246" s="12"/>
-      <c r="D246" s="10"/>
-      <c r="E246" s="10"/>
-      <c r="F246" s="10"/>
-      <c r="G246" s="10"/>
+      <c r="A246" s="9"/>
+      <c r="B246" s="9"/>
+      <c r="C246" s="11"/>
+      <c r="D246" s="9"/>
+      <c r="E246" s="9"/>
+      <c r="F246" s="9"/>
+      <c r="G246" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6238,6 +8182,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C7DC5809443B914698F205EDCFE14C5C" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="910dd8289e79bf7e3b2db69aaa037196">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2592cbe8-961e-4422-8c47-4737933d0fe0" xmlns:ns3="7af58a8f-2f6f-405a-b238-befdc3c227d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecb9083a17ae33be0a7009b46db9eab7" ns2:_="" ns3:_="">
     <xsd:import namespace="2592cbe8-961e-4422-8c47-4737933d0fe0"/>
@@ -6414,22 +8373,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70AE5412-3087-4F96-A882-A7717BC45E52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6446,21 +8407,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MC3010_E24.xlsx
+++ b/MC3010_E24.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9309FDF-E708-4A52-AC9C-AC1F5BBFF629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF69D146-09B5-4438-A54C-601AC5280C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C7CD7951-09B0-4C7C-879A-E2D1E2A563F4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="487">
   <si>
     <t>Name</t>
   </si>
@@ -2029,8 +2029,8 @@
       <c r="E2" s="14">
         <v>62</v>
       </c>
-      <c r="F2" s="10">
-        <v>43.8</v>
+      <c r="F2" s="14">
+        <v>73</v>
       </c>
       <c r="G2" s="14">
         <v>38</v>
@@ -2055,8 +2055,8 @@
       <c r="E3" s="14">
         <v>85</v>
       </c>
-      <c r="F3" s="10">
-        <v>45</v>
+      <c r="F3" s="14">
+        <v>75</v>
       </c>
       <c r="G3" s="14">
         <v>87</v>
@@ -2081,8 +2081,8 @@
       <c r="E4" s="14">
         <v>76</v>
       </c>
-      <c r="F4" s="10">
-        <v>32.4</v>
+      <c r="F4" s="14">
+        <v>54</v>
       </c>
       <c r="G4" s="14">
         <v>75</v>
@@ -2107,8 +2107,8 @@
       <c r="E5" s="14">
         <v>65</v>
       </c>
-      <c r="F5" s="10">
-        <v>36</v>
+      <c r="F5" s="14">
+        <v>60</v>
       </c>
       <c r="G5" s="14">
         <v>46</v>
@@ -2133,8 +2133,8 @@
       <c r="E6" s="14">
         <v>66</v>
       </c>
-      <c r="F6" s="10">
-        <v>36</v>
+      <c r="F6" s="14">
+        <v>60</v>
       </c>
       <c r="G6" s="14">
         <v>40</v>
@@ -2159,8 +2159,8 @@
       <c r="E7" s="14">
         <v>66</v>
       </c>
-      <c r="F7" s="10">
-        <v>38.999999999999993</v>
+      <c r="F7" s="14">
+        <v>65</v>
       </c>
       <c r="G7" s="14">
         <v>64</v>
@@ -2185,8 +2185,8 @@
       <c r="E8" s="14">
         <v>89</v>
       </c>
-      <c r="F8" s="10">
-        <v>42.199999999999996</v>
+      <c r="F8" s="14">
+        <v>85</v>
       </c>
       <c r="G8" s="14">
         <v>77</v>
@@ -2211,8 +2211,8 @@
       <c r="E9" s="14">
         <v>77</v>
       </c>
-      <c r="F9" s="10">
-        <v>48.800000000000004</v>
+      <c r="F9" s="14">
+        <v>79</v>
       </c>
       <c r="G9" s="14">
         <v>46</v>
@@ -2237,8 +2237,8 @@
       <c r="E10" s="14">
         <v>71</v>
       </c>
-      <c r="F10" s="10">
-        <v>38.4</v>
+      <c r="F10" s="14">
+        <v>75</v>
       </c>
       <c r="G10" s="14">
         <v>48</v>
@@ -2263,8 +2263,8 @@
       <c r="E11" s="14">
         <v>43</v>
       </c>
-      <c r="F11" s="10">
-        <v>27.200000000000003</v>
+      <c r="F11" s="14">
+        <v>61</v>
       </c>
       <c r="G11" s="14">
         <v>34</v>
@@ -2289,8 +2289,8 @@
       <c r="E12" s="14">
         <v>94</v>
       </c>
-      <c r="F12" s="10">
-        <v>50.79999999999999</v>
+      <c r="F12" s="14">
+        <v>65</v>
       </c>
       <c r="G12" s="14">
         <v>35</v>
@@ -2315,8 +2315,8 @@
       <c r="E13" s="14">
         <v>71</v>
       </c>
-      <c r="F13" s="10">
-        <v>59.199999999999996</v>
+      <c r="F13" s="14">
+        <v>86</v>
       </c>
       <c r="G13" s="14">
         <v>40</v>
@@ -2341,8 +2341,8 @@
       <c r="E14" s="14">
         <v>95</v>
       </c>
-      <c r="F14" s="10">
-        <v>32.4</v>
+      <c r="F14" s="14">
+        <v>54</v>
       </c>
       <c r="G14" s="14">
         <v>86</v>
@@ -2367,8 +2367,8 @@
       <c r="E15" s="14">
         <v>69</v>
       </c>
-      <c r="F15" s="10">
-        <v>70.599999999999994</v>
+      <c r="F15" s="14">
+        <v>86</v>
       </c>
       <c r="G15" s="14">
         <v>61</v>
@@ -2393,8 +2393,8 @@
       <c r="E16" s="14">
         <v>98</v>
       </c>
-      <c r="F16" s="10">
-        <v>56.999999999999993</v>
+      <c r="F16" s="14">
+        <v>87</v>
       </c>
       <c r="G16" s="14">
         <v>57</v>
@@ -2419,8 +2419,8 @@
       <c r="E17" s="14">
         <v>78</v>
       </c>
-      <c r="F17" s="10">
-        <v>42</v>
+      <c r="F17" s="14">
+        <v>70</v>
       </c>
       <c r="G17" s="14">
         <v>79</v>
@@ -2445,8 +2445,8 @@
       <c r="E18" s="14">
         <v>85</v>
       </c>
-      <c r="F18" s="10">
-        <v>26.400000000000002</v>
+      <c r="F18" s="14">
+        <v>44</v>
       </c>
       <c r="G18" s="14">
         <v>71</v>
@@ -2471,8 +2471,8 @@
       <c r="E19" s="14">
         <v>87</v>
       </c>
-      <c r="F19" s="10">
-        <v>36.599999999999994</v>
+      <c r="F19" s="14">
+        <v>47</v>
       </c>
       <c r="G19" s="14">
         <v>91</v>
@@ -2497,8 +2497,8 @@
       <c r="E20" s="14">
         <v>64</v>
       </c>
-      <c r="F20" s="10">
-        <v>68.399999999999991</v>
+      <c r="F20" s="14">
+        <v>75</v>
       </c>
       <c r="G20" s="14">
         <v>71</v>
@@ -2523,8 +2523,8 @@
       <c r="E21" s="14">
         <v>86</v>
       </c>
-      <c r="F21" s="10">
-        <v>68</v>
+      <c r="F21" s="14">
+        <v>75</v>
       </c>
       <c r="G21" s="14">
         <v>97</v>
@@ -2549,8 +2549,8 @@
       <c r="E22" s="14">
         <v>61</v>
       </c>
-      <c r="F22" s="10">
-        <v>52.6</v>
+      <c r="F22" s="14">
+        <v>75</v>
       </c>
       <c r="G22" s="14">
         <v>53</v>
@@ -2575,8 +2575,8 @@
       <c r="E23" s="14">
         <v>81</v>
       </c>
-      <c r="F23" s="10">
-        <v>69.199999999999989</v>
+      <c r="F23" s="14">
+        <v>87</v>
       </c>
       <c r="G23" s="14">
         <v>73</v>
@@ -2601,8 +2601,8 @@
       <c r="E24" s="14">
         <v>78</v>
       </c>
-      <c r="F24" s="10">
-        <v>69.199999999999989</v>
+      <c r="F24" s="14">
+        <v>87</v>
       </c>
       <c r="G24" s="14">
         <v>33</v>
@@ -2627,8 +2627,8 @@
       <c r="E25" s="14">
         <v>97</v>
       </c>
-      <c r="F25" s="10">
-        <v>66.8</v>
+      <c r="F25" s="14">
+        <v>84</v>
       </c>
       <c r="G25" s="14">
         <v>82</v>
@@ -2653,8 +2653,8 @@
       <c r="E26" s="14">
         <v>71</v>
       </c>
-      <c r="F26" s="10">
-        <v>45.2</v>
+      <c r="F26" s="14">
+        <v>61</v>
       </c>
       <c r="G26" s="14">
         <v>45</v>
@@ -2679,8 +2679,8 @@
       <c r="E27" s="14">
         <v>82</v>
       </c>
-      <c r="F27" s="10">
-        <v>57.4</v>
+      <c r="F27" s="14">
+        <v>75</v>
       </c>
       <c r="G27" s="14">
         <v>51</v>
@@ -2705,8 +2705,8 @@
       <c r="E28" s="14">
         <v>52</v>
       </c>
-      <c r="F28" s="10">
-        <v>52.800000000000004</v>
+      <c r="F28" s="14">
+        <v>66</v>
       </c>
       <c r="G28" s="14">
         <v>54</v>
@@ -2731,8 +2731,8 @@
       <c r="E29" s="14">
         <v>89</v>
       </c>
-      <c r="F29" s="10">
-        <v>48.800000000000004</v>
+      <c r="F29" s="14">
+        <v>79</v>
       </c>
       <c r="G29" s="14">
         <v>80</v>
@@ -2757,8 +2757,8 @@
       <c r="E30" s="14">
         <v>60</v>
       </c>
-      <c r="F30" s="10">
-        <v>77.999999999999986</v>
+      <c r="F30" s="14">
+        <v>82</v>
       </c>
       <c r="G30" s="14">
         <v>74</v>
@@ -2783,8 +2783,8 @@
       <c r="E31" s="14">
         <v>69</v>
       </c>
-      <c r="F31" s="10">
-        <v>50.79999999999999</v>
+      <c r="F31" s="14">
+        <v>65</v>
       </c>
       <c r="G31" s="14">
         <v>38</v>
@@ -2809,8 +2809,8 @@
       <c r="E32" s="14">
         <v>47</v>
       </c>
-      <c r="F32" s="10">
-        <v>43.8</v>
+      <c r="F32" s="14">
+        <v>73</v>
       </c>
       <c r="G32" s="14">
         <v>68</v>
@@ -2835,8 +2835,8 @@
       <c r="E33" s="14">
         <v>81</v>
       </c>
-      <c r="F33" s="10">
-        <v>24.6</v>
+      <c r="F33" s="14">
+        <v>41</v>
       </c>
       <c r="G33" s="14">
         <v>74</v>
@@ -2861,8 +2861,8 @@
       <c r="E34" s="14">
         <v>76</v>
       </c>
-      <c r="F34" s="10">
-        <v>62.8</v>
+      <c r="F34" s="14">
+        <v>86</v>
       </c>
       <c r="G34" s="14">
         <v>80</v>
@@ -2887,8 +2887,8 @@
       <c r="E35" s="14">
         <v>75</v>
       </c>
-      <c r="F35" s="10">
-        <v>60.199999999999996</v>
+      <c r="F35" s="14">
+        <v>82</v>
       </c>
       <c r="G35" s="14">
         <v>66</v>
@@ -2913,8 +2913,8 @@
       <c r="E36" s="14">
         <v>64</v>
       </c>
-      <c r="F36" s="10">
-        <v>49.8</v>
+      <c r="F36" s="14">
+        <v>72</v>
       </c>
       <c r="G36" s="14">
         <v>39</v>
@@ -2939,8 +2939,8 @@
       <c r="E37" s="14">
         <v>59</v>
       </c>
-      <c r="F37" s="10">
-        <v>59</v>
+      <c r="F37" s="14">
+        <v>78</v>
       </c>
       <c r="G37" s="14">
         <v>53</v>
@@ -2965,8 +2965,8 @@
       <c r="E38" s="14">
         <v>93</v>
       </c>
-      <c r="F38" s="10">
-        <v>56.8</v>
+      <c r="F38" s="14">
+        <v>75</v>
       </c>
       <c r="G38" s="14">
         <v>66</v>
@@ -2991,8 +2991,8 @@
       <c r="E39" s="14">
         <v>69</v>
       </c>
-      <c r="F39" s="10">
-        <v>24.6</v>
+      <c r="F39" s="14">
+        <v>41</v>
       </c>
       <c r="G39" s="14">
         <v>69</v>
@@ -3017,8 +3017,8 @@
       <c r="E40" s="14">
         <v>49</v>
       </c>
-      <c r="F40" s="10">
-        <v>42.6</v>
+      <c r="F40" s="14">
+        <v>71</v>
       </c>
       <c r="G40" s="14">
         <v>54</v>
@@ -3043,8 +3043,8 @@
       <c r="E41" s="14">
         <v>57</v>
       </c>
-      <c r="F41" s="10">
-        <v>37.200000000000003</v>
+      <c r="F41" s="14">
+        <v>62</v>
       </c>
       <c r="G41" s="14">
         <v>34</v>
@@ -3069,8 +3069,8 @@
       <c r="E42" s="14">
         <v>73</v>
       </c>
-      <c r="F42" s="10">
-        <v>38.999999999999993</v>
+      <c r="F42" s="14">
+        <v>65</v>
       </c>
       <c r="G42" s="14">
         <v>46</v>
@@ -3095,8 +3095,8 @@
       <c r="E43" s="14">
         <v>71</v>
       </c>
-      <c r="F43" s="10">
-        <v>53.999999999999993</v>
+      <c r="F43" s="14">
+        <v>75</v>
       </c>
       <c r="G43" s="14">
         <v>73</v>
@@ -3121,8 +3121,8 @@
       <c r="E44" s="14">
         <v>97</v>
       </c>
-      <c r="F44" s="10">
-        <v>34.199999999999996</v>
+      <c r="F44" s="14">
+        <v>57</v>
       </c>
       <c r="G44" s="14">
         <v>38</v>
@@ -3147,8 +3147,8 @@
       <c r="E45" s="14">
         <v>59</v>
       </c>
-      <c r="F45" s="10">
-        <v>55.999999999999993</v>
+      <c r="F45" s="14">
+        <v>85</v>
       </c>
       <c r="G45" s="14">
         <v>56</v>
@@ -3173,8 +3173,8 @@
       <c r="E46" s="14">
         <v>73</v>
       </c>
-      <c r="F46" s="10">
-        <v>42.4</v>
+      <c r="F46" s="14">
+        <v>74</v>
       </c>
       <c r="G46" s="14">
         <v>36</v>
@@ -3199,8 +3199,8 @@
       <c r="E47" s="14">
         <v>89</v>
       </c>
-      <c r="F47" s="10">
-        <v>26.400000000000002</v>
+      <c r="F47" s="14">
+        <v>44</v>
       </c>
       <c r="G47" s="14">
         <v>51</v>
@@ -3225,8 +3225,8 @@
       <c r="E48" s="14">
         <v>89</v>
       </c>
-      <c r="F48" s="10">
-        <v>45.199999999999996</v>
+      <c r="F48" s="14">
+        <v>85</v>
       </c>
       <c r="G48" s="14">
         <v>55</v>
@@ -3251,8 +3251,8 @@
       <c r="E49" s="14">
         <v>73</v>
       </c>
-      <c r="F49" s="10">
-        <v>77.999999999999986</v>
+      <c r="F49" s="14">
+        <v>82</v>
       </c>
       <c r="G49" s="14">
         <v>61</v>
@@ -3277,8 +3277,8 @@
       <c r="E50" s="14">
         <v>94</v>
       </c>
-      <c r="F50" s="10">
-        <v>59.599999999999994</v>
+      <c r="F50" s="14">
+        <v>87</v>
       </c>
       <c r="G50" s="14">
         <v>40</v>
@@ -3303,8 +3303,8 @@
       <c r="E51" s="14">
         <v>78</v>
       </c>
-      <c r="F51" s="10">
-        <v>67.800000000000011</v>
+      <c r="F51" s="14">
+        <v>78</v>
       </c>
       <c r="G51" s="14">
         <v>56</v>
@@ -3329,8 +3329,8 @@
       <c r="E52" s="14">
         <v>71</v>
       </c>
-      <c r="F52" s="10">
-        <v>57.199999999999982</v>
+      <c r="F52" s="14">
+        <v>73</v>
       </c>
       <c r="G52" s="14">
         <v>56</v>
@@ -3355,8 +3355,8 @@
       <c r="E53" s="14">
         <v>61</v>
       </c>
-      <c r="F53" s="10">
-        <v>28.800000000000004</v>
+      <c r="F53" s="14">
+        <v>48</v>
       </c>
       <c r="G53" s="14">
         <v>57</v>
@@ -3381,8 +3381,8 @@
       <c r="E54" s="14">
         <v>96</v>
       </c>
-      <c r="F54" s="10">
-        <v>47.2</v>
+      <c r="F54" s="14">
+        <v>65</v>
       </c>
       <c r="G54" s="14">
         <v>55</v>
@@ -3407,8 +3407,8 @@
       <c r="E55" s="14">
         <v>91</v>
       </c>
-      <c r="F55" s="10">
-        <v>77.199999999999989</v>
+      <c r="F55" s="14">
+        <v>94</v>
       </c>
       <c r="G55" s="14">
         <v>70</v>
@@ -3433,8 +3433,8 @@
       <c r="E56" s="14">
         <v>85</v>
       </c>
-      <c r="F56" s="10">
-        <v>54.599999999999994</v>
+      <c r="F56" s="14">
+        <v>62</v>
       </c>
       <c r="G56" s="14">
         <v>44</v>
@@ -3459,8 +3459,8 @@
       <c r="E57" s="14">
         <v>86</v>
       </c>
-      <c r="F57" s="10">
-        <v>73.799999999999983</v>
+      <c r="F57" s="14">
+        <v>86</v>
       </c>
       <c r="G57" s="14">
         <v>54</v>
@@ -3485,8 +3485,8 @@
       <c r="E58" s="14">
         <v>86</v>
       </c>
-      <c r="F58" s="10">
-        <v>77.600000000000009</v>
+      <c r="F58" s="14">
+        <v>87</v>
       </c>
       <c r="G58" s="14">
         <v>32</v>
@@ -3511,8 +3511,8 @@
       <c r="E59" s="14">
         <v>90</v>
       </c>
-      <c r="F59" s="10">
-        <v>66.600000000000009</v>
+      <c r="F59" s="14">
+        <v>74</v>
       </c>
       <c r="G59" s="14">
         <v>39</v>
@@ -3537,8 +3537,8 @@
       <c r="E60" s="14">
         <v>79</v>
       </c>
-      <c r="F60" s="10">
-        <v>52.999999999999993</v>
+      <c r="F60" s="14">
+        <v>70</v>
       </c>
       <c r="G60" s="14">
         <v>52</v>
@@ -3563,8 +3563,8 @@
       <c r="E61" s="14">
         <v>77</v>
       </c>
-      <c r="F61" s="10">
-        <v>56.000000000000007</v>
+      <c r="F61" s="14">
+        <v>76</v>
       </c>
       <c r="G61" s="14">
         <v>82</v>
@@ -3589,8 +3589,8 @@
       <c r="E62" s="14">
         <v>79</v>
       </c>
-      <c r="F62" s="10">
-        <v>40.599999999999994</v>
+      <c r="F62" s="14">
+        <v>55</v>
       </c>
       <c r="G62" s="14">
         <v>68</v>
@@ -3615,8 +3615,8 @@
       <c r="E63" s="14">
         <v>91</v>
       </c>
-      <c r="F63" s="10">
-        <v>79.199999999999989</v>
+      <c r="F63" s="14">
+        <v>94</v>
       </c>
       <c r="G63" s="14">
         <v>79</v>
@@ -3641,8 +3641,8 @@
       <c r="E64" s="14">
         <v>69</v>
       </c>
-      <c r="F64" s="10">
-        <v>39</v>
+      <c r="F64" s="14">
+        <v>51</v>
       </c>
       <c r="G64" s="14">
         <v>52</v>
@@ -3667,8 +3667,8 @@
       <c r="E65" s="14">
         <v>58</v>
       </c>
-      <c r="F65" s="10">
-        <v>44.800000000000004</v>
+      <c r="F65" s="14">
+        <v>59</v>
       </c>
       <c r="G65" s="14">
         <v>67</v>
@@ -3693,8 +3693,8 @@
       <c r="E66" s="14">
         <v>81</v>
       </c>
-      <c r="F66" s="10">
-        <v>62.8</v>
+      <c r="F66" s="14">
+        <v>87</v>
       </c>
       <c r="G66" s="14">
         <v>68</v>
@@ -3719,8 +3719,8 @@
       <c r="E67" s="14">
         <v>58</v>
       </c>
-      <c r="F67" s="10">
-        <v>40.799999999999997</v>
+      <c r="F67" s="14">
+        <v>63</v>
       </c>
       <c r="G67" s="14">
         <v>49</v>
@@ -3745,8 +3745,8 @@
       <c r="E68" s="14">
         <v>68</v>
       </c>
-      <c r="F68" s="10">
-        <v>40</v>
+      <c r="F68" s="14">
+        <v>59</v>
       </c>
       <c r="G68" s="14">
         <v>59</v>
@@ -3771,8 +3771,8 @@
       <c r="E69" s="14">
         <v>74</v>
       </c>
-      <c r="F69" s="10">
-        <v>47.6</v>
+      <c r="F69" s="14">
+        <v>94</v>
       </c>
       <c r="G69" s="14">
         <v>42</v>
@@ -3797,8 +3797,8 @@
       <c r="E70" s="14">
         <v>52</v>
       </c>
-      <c r="F70" s="10">
-        <v>42.6</v>
+      <c r="F70" s="14">
+        <v>71</v>
       </c>
       <c r="G70" s="14">
         <v>40</v>
@@ -3823,8 +3823,8 @@
       <c r="E71" s="14">
         <v>62</v>
       </c>
-      <c r="F71" s="10">
-        <v>26.400000000000002</v>
+      <c r="F71" s="14">
+        <v>44</v>
       </c>
       <c r="G71" s="14">
         <v>50</v>
@@ -3849,8 +3849,8 @@
       <c r="E72" s="14">
         <v>85</v>
       </c>
-      <c r="F72" s="10">
-        <v>32.4</v>
+      <c r="F72" s="14">
+        <v>54</v>
       </c>
       <c r="G72" s="14">
         <v>55</v>
@@ -3875,8 +3875,8 @@
       <c r="E73" s="14">
         <v>83</v>
       </c>
-      <c r="F73" s="10">
-        <v>55.000000000000007</v>
+      <c r="F73" s="14">
+        <v>59</v>
       </c>
       <c r="G73" s="14">
         <v>60</v>
@@ -3901,8 +3901,8 @@
       <c r="E74" s="14">
         <v>42</v>
       </c>
-      <c r="F74" s="10">
-        <v>38.999999999999993</v>
+      <c r="F74" s="14">
+        <v>65</v>
       </c>
       <c r="G74" s="14">
         <v>35</v>
@@ -3927,8 +3927,8 @@
       <c r="E75" s="14">
         <v>72</v>
       </c>
-      <c r="F75" s="10">
-        <v>42.6</v>
+      <c r="F75" s="14">
+        <v>71</v>
       </c>
       <c r="G75" s="14">
         <v>48</v>
@@ -3953,8 +3953,8 @@
       <c r="E76" s="14">
         <v>50</v>
       </c>
-      <c r="F76" s="10">
-        <v>31.2</v>
+      <c r="F76" s="14">
+        <v>52</v>
       </c>
       <c r="G76" s="14">
         <v>37</v>
@@ -3979,8 +3979,8 @@
       <c r="E77" s="14">
         <v>84</v>
       </c>
-      <c r="F77" s="10">
-        <v>59.199999999999996</v>
+      <c r="F77" s="14">
+        <v>86</v>
       </c>
       <c r="G77" s="14">
         <v>54</v>
@@ -4005,8 +4005,8 @@
       <c r="E78" s="14">
         <v>86</v>
       </c>
-      <c r="F78" s="10">
-        <v>36</v>
+      <c r="F78" s="14">
+        <v>60</v>
       </c>
       <c r="G78" s="14">
         <v>54</v>
@@ -4031,8 +4031,8 @@
       <c r="E79" s="14">
         <v>77</v>
       </c>
-      <c r="F79" s="10">
-        <v>33</v>
+      <c r="F79" s="14">
+        <v>55</v>
       </c>
       <c r="G79" s="14">
         <v>42</v>
@@ -4057,8 +4057,8 @@
       <c r="E80" s="14">
         <v>75</v>
       </c>
-      <c r="F80" s="10">
-        <v>25.6</v>
+      <c r="F80" s="14">
+        <v>53</v>
       </c>
       <c r="G80" s="14">
         <v>63</v>
@@ -4083,8 +4083,8 @@
       <c r="E81" s="14">
         <v>83</v>
       </c>
-      <c r="F81" s="10">
-        <v>46</v>
+      <c r="F81" s="14">
+        <v>80</v>
       </c>
       <c r="G81" s="14">
         <v>58</v>
@@ -4109,8 +4109,8 @@
       <c r="E82" s="14">
         <v>67</v>
       </c>
-      <c r="F82" s="10">
-        <v>32.4</v>
+      <c r="F82" s="14">
+        <v>54</v>
       </c>
       <c r="G82" s="14">
         <v>54</v>
@@ -4135,8 +4135,8 @@
       <c r="E83" s="14">
         <v>70</v>
       </c>
-      <c r="F83" s="10">
-        <v>40.199999999999996</v>
+      <c r="F83" s="14">
+        <v>67</v>
       </c>
       <c r="G83" s="14">
         <v>67</v>
@@ -4161,8 +4161,8 @@
       <c r="E84" s="14">
         <v>56</v>
       </c>
-      <c r="F84" s="10">
-        <v>43.8</v>
+      <c r="F84" s="14">
+        <v>73</v>
       </c>
       <c r="G84" s="14">
         <v>70</v>
@@ -4187,8 +4187,8 @@
       <c r="E85" s="14">
         <v>59</v>
       </c>
-      <c r="F85" s="10">
-        <v>45</v>
+      <c r="F85" s="14">
+        <v>75</v>
       </c>
       <c r="G85" s="14">
         <v>47</v>
@@ -4213,8 +4213,8 @@
       <c r="E86" s="14">
         <v>85</v>
       </c>
-      <c r="F86" s="10">
-        <v>45</v>
+      <c r="F86" s="14">
+        <v>75</v>
       </c>
       <c r="G86" s="14">
         <v>42</v>
@@ -4239,8 +4239,8 @@
       <c r="E87" s="14">
         <v>68</v>
       </c>
-      <c r="F87" s="10">
-        <v>45</v>
+      <c r="F87" s="14">
+        <v>75</v>
       </c>
       <c r="G87" s="14">
         <v>47</v>
@@ -4265,8 +4265,8 @@
       <c r="E88" s="14">
         <v>85</v>
       </c>
-      <c r="F88" s="10">
-        <v>58.20000000000001</v>
+      <c r="F88" s="14">
+        <v>76</v>
       </c>
       <c r="G88" s="14">
         <v>69</v>
@@ -4291,8 +4291,8 @@
       <c r="E89" s="14">
         <v>96</v>
       </c>
-      <c r="F89" s="10">
-        <v>26.400000000000002</v>
+      <c r="F89" s="14">
+        <v>44</v>
       </c>
       <c r="G89" s="14">
         <v>68</v>
@@ -4317,8 +4317,8 @@
       <c r="E90" s="14">
         <v>73</v>
       </c>
-      <c r="F90" s="10">
-        <v>36</v>
+      <c r="F90" s="14">
+        <v>60</v>
       </c>
       <c r="G90" s="14">
         <v>56</v>
@@ -4343,8 +4343,8 @@
       <c r="E91" s="14">
         <v>83</v>
       </c>
-      <c r="F91" s="10">
-        <v>45</v>
+      <c r="F91" s="14">
+        <v>75</v>
       </c>
       <c r="G91" s="14">
         <v>68</v>
@@ -4369,8 +4369,8 @@
       <c r="E92" s="14">
         <v>77</v>
       </c>
-      <c r="F92" s="10">
-        <v>73.799999999999983</v>
+      <c r="F92" s="14">
+        <v>86</v>
       </c>
       <c r="G92" s="14">
         <v>59</v>
@@ -4395,8 +4395,8 @@
       <c r="E93" s="14">
         <v>76</v>
       </c>
-      <c r="F93" s="10">
-        <v>56.400000000000006</v>
+      <c r="F93" s="14">
+        <v>72</v>
       </c>
       <c r="G93" s="14">
         <v>53</v>
@@ -4421,8 +4421,8 @@
       <c r="E94" s="14">
         <v>80</v>
       </c>
-      <c r="F94" s="10">
-        <v>59.599999999999994</v>
+      <c r="F94" s="14">
+        <v>86</v>
       </c>
       <c r="G94" s="14">
         <v>33</v>
@@ -4447,8 +4447,8 @@
       <c r="E95" s="14">
         <v>76</v>
       </c>
-      <c r="F95" s="10">
-        <v>37.200000000000003</v>
+      <c r="F95" s="14">
+        <v>62</v>
       </c>
       <c r="G95" s="14">
         <v>55</v>
@@ -4473,8 +4473,8 @@
       <c r="E96" s="14">
         <v>64</v>
       </c>
-      <c r="F96" s="10">
-        <v>51.2</v>
+      <c r="F96" s="14">
+        <v>70</v>
       </c>
       <c r="G96" s="14">
         <v>65</v>
@@ -4499,8 +4499,8 @@
       <c r="E97" s="14">
         <v>74</v>
       </c>
-      <c r="F97" s="10">
-        <v>57.199999999999982</v>
+      <c r="F97" s="14">
+        <v>73</v>
       </c>
       <c r="G97" s="14">
         <v>42</v>
@@ -4525,8 +4525,8 @@
       <c r="E98" s="14">
         <v>60</v>
       </c>
-      <c r="F98" s="10">
-        <v>31.2</v>
+      <c r="F98" s="14">
+        <v>52</v>
       </c>
       <c r="G98" s="14">
         <v>59</v>
@@ -4551,8 +4551,8 @@
       <c r="E99" s="14">
         <v>79</v>
       </c>
-      <c r="F99" s="10">
-        <v>56.000000000000007</v>
+      <c r="F99" s="14">
+        <v>94</v>
       </c>
       <c r="G99" s="14">
         <v>72</v>
@@ -4577,8 +4577,8 @@
       <c r="E100" s="14">
         <v>92</v>
       </c>
-      <c r="F100" s="10">
-        <v>37.200000000000003</v>
+      <c r="F100" s="14">
+        <v>62</v>
       </c>
       <c r="G100" s="14">
         <v>62</v>
@@ -4603,8 +4603,8 @@
       <c r="E101" s="14">
         <v>69</v>
       </c>
-      <c r="F101" s="10">
-        <v>31.2</v>
+      <c r="F101" s="14">
+        <v>52</v>
       </c>
       <c r="G101" s="14">
         <v>57</v>
@@ -4629,8 +4629,8 @@
       <c r="E102" s="14">
         <v>84</v>
       </c>
-      <c r="F102" s="10">
-        <v>44.599999999999994</v>
+      <c r="F102" s="14">
+        <v>59</v>
       </c>
       <c r="G102" s="14">
         <v>74</v>
@@ -4655,8 +4655,8 @@
       <c r="E103" s="14">
         <v>74</v>
       </c>
-      <c r="F103" s="10">
-        <v>31.2</v>
+      <c r="F103" s="14">
+        <v>52</v>
       </c>
       <c r="G103" s="14">
         <v>36</v>
@@ -4681,8 +4681,8 @@
       <c r="E104" s="14">
         <v>85</v>
       </c>
-      <c r="F104" s="10">
-        <v>51.4</v>
+      <c r="F104" s="14">
+        <v>86</v>
       </c>
       <c r="G104" s="14">
         <v>84</v>
@@ -4707,8 +4707,8 @@
       <c r="E105" s="14">
         <v>95</v>
       </c>
-      <c r="F105" s="10">
-        <v>46</v>
+      <c r="F105" s="14">
+        <v>80</v>
       </c>
       <c r="G105" s="14">
         <v>72</v>
@@ -4733,8 +4733,8 @@
       <c r="E106" s="14">
         <v>82</v>
       </c>
-      <c r="F106" s="10">
-        <v>57.8</v>
+      <c r="F106" s="14">
+        <v>79</v>
       </c>
       <c r="G106" s="14">
         <v>35</v>
@@ -4759,8 +4759,8 @@
       <c r="E107" s="14">
         <v>62</v>
       </c>
-      <c r="F107" s="10">
-        <v>38.999999999999993</v>
+      <c r="F107" s="14">
+        <v>65</v>
       </c>
       <c r="G107" s="14">
         <v>57</v>
@@ -4785,8 +4785,8 @@
       <c r="E108" s="14">
         <v>72</v>
       </c>
-      <c r="F108" s="10">
-        <v>49.8</v>
+      <c r="F108" s="14">
+        <v>72</v>
       </c>
       <c r="G108" s="14">
         <v>67</v>
@@ -4811,8 +4811,8 @@
       <c r="E109" s="14">
         <v>95</v>
       </c>
-      <c r="F109" s="10">
-        <v>43.8</v>
+      <c r="F109" s="14">
+        <v>73</v>
       </c>
       <c r="G109" s="14">
         <v>66</v>
@@ -4837,8 +4837,8 @@
       <c r="E110" s="14">
         <v>46</v>
       </c>
-      <c r="F110" s="10">
-        <v>55.999999999999993</v>
+      <c r="F110" s="14">
+        <v>82</v>
       </c>
       <c r="G110" s="14">
         <v>45</v>
@@ -4863,8 +4863,8 @@
       <c r="E111" s="14">
         <v>38</v>
       </c>
-      <c r="F111" s="10">
-        <v>24.6</v>
+      <c r="F111" s="14">
+        <v>41</v>
       </c>
       <c r="G111" s="14">
         <v>9</v>
@@ -4889,8 +4889,8 @@
       <c r="E112" s="14">
         <v>76</v>
       </c>
-      <c r="F112" s="10">
-        <v>37.200000000000003</v>
+      <c r="F112" s="14">
+        <v>62</v>
       </c>
       <c r="G112" s="14">
         <v>72</v>
@@ -4915,8 +4915,8 @@
       <c r="E113" s="14">
         <v>49</v>
       </c>
-      <c r="F113" s="10">
-        <v>45.6</v>
+      <c r="F113" s="14">
+        <v>76</v>
       </c>
       <c r="G113" s="14">
         <v>44</v>
@@ -4941,8 +4941,8 @@
       <c r="E114" s="14">
         <v>53</v>
       </c>
-      <c r="F114" s="10">
-        <v>47.199999999999989</v>
+      <c r="F114" s="14">
+        <v>66</v>
       </c>
       <c r="G114" s="14">
         <v>56</v>
@@ -4967,8 +4967,8 @@
       <c r="E115" s="14">
         <v>84</v>
       </c>
-      <c r="F115" s="10">
-        <v>60</v>
+      <c r="F115" s="14">
+        <v>75</v>
       </c>
       <c r="G115" s="14">
         <v>75</v>
@@ -4993,8 +4993,8 @@
       <c r="E116" s="14">
         <v>88</v>
       </c>
-      <c r="F116" s="10">
-        <v>48.800000000000004</v>
+      <c r="F116" s="14">
+        <v>79</v>
       </c>
       <c r="G116" s="14">
         <v>56</v>
@@ -5019,8 +5019,8 @@
       <c r="E117" s="14">
         <v>97</v>
       </c>
-      <c r="F117" s="10">
-        <v>59.599999999999994</v>
+      <c r="F117" s="14">
+        <v>87</v>
       </c>
       <c r="G117" s="14">
         <v>43</v>
@@ -5045,8 +5045,8 @@
       <c r="E118" s="14">
         <v>74</v>
       </c>
-      <c r="F118" s="10">
-        <v>52.800000000000004</v>
+      <c r="F118" s="14">
+        <v>66</v>
       </c>
       <c r="G118" s="14">
         <v>60</v>
@@ -5071,8 +5071,8 @@
       <c r="E119" s="14">
         <v>88</v>
       </c>
-      <c r="F119" s="10">
-        <v>68.399999999999991</v>
+      <c r="F119" s="14">
+        <v>75</v>
       </c>
       <c r="G119" s="14">
         <v>70</v>
@@ -5097,8 +5097,8 @@
       <c r="E120" s="14">
         <v>87</v>
       </c>
-      <c r="F120" s="10">
-        <v>25.6</v>
+      <c r="F120" s="14">
+        <v>53</v>
       </c>
       <c r="G120" s="14">
         <v>63</v>
@@ -5123,8 +5123,8 @@
       <c r="E121" s="14">
         <v>75</v>
       </c>
-      <c r="F121" s="10">
-        <v>33</v>
+      <c r="F121" s="14">
+        <v>55</v>
       </c>
       <c r="G121" s="14">
         <v>50</v>
@@ -5149,8 +5149,8 @@
       <c r="E122" s="14">
         <v>91</v>
       </c>
-      <c r="F122" s="10">
-        <v>47.199999999999989</v>
+      <c r="F122" s="14">
+        <v>74</v>
       </c>
       <c r="G122" s="14">
         <v>72</v>
@@ -5175,8 +5175,8 @@
       <c r="E123" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F123" s="10" t="s">
-        <v>81</v>
+      <c r="F123" s="14">
+        <v>0</v>
       </c>
       <c r="G123" s="14">
         <v>8</v>
@@ -5201,8 +5201,8 @@
       <c r="E124" s="14">
         <v>91</v>
       </c>
-      <c r="F124" s="10">
-        <v>73</v>
+      <c r="F124" s="14">
+        <v>82</v>
       </c>
       <c r="G124" s="14">
         <v>70</v>
@@ -5227,8 +5227,8 @@
       <c r="E125" s="14">
         <v>77</v>
       </c>
-      <c r="F125" s="10">
-        <v>60</v>
+      <c r="F125" s="14">
+        <v>76</v>
       </c>
       <c r="G125" s="14">
         <v>56</v>
@@ -5253,8 +5253,8 @@
       <c r="E126" s="14">
         <v>91</v>
       </c>
-      <c r="F126" s="10">
-        <v>76.2</v>
+      <c r="F126" s="14">
+        <v>92</v>
       </c>
       <c r="G126" s="14">
         <v>67</v>
@@ -5279,8 +5279,8 @@
       <c r="E127" s="14">
         <v>72</v>
       </c>
-      <c r="F127" s="10">
-        <v>57.8</v>
+      <c r="F127" s="14">
+        <v>79</v>
       </c>
       <c r="G127" s="14">
         <v>56</v>
@@ -5305,8 +5305,8 @@
       <c r="E128" s="14">
         <v>81</v>
       </c>
-      <c r="F128" s="10">
-        <v>28.800000000000004</v>
+      <c r="F128" s="14">
+        <v>48</v>
       </c>
       <c r="G128" s="14">
         <v>52</v>
@@ -5331,8 +5331,8 @@
       <c r="E129" s="14">
         <v>78</v>
       </c>
-      <c r="F129" s="10">
-        <v>32.4</v>
+      <c r="F129" s="14">
+        <v>54</v>
       </c>
       <c r="G129" s="14">
         <v>45</v>
@@ -5357,8 +5357,8 @@
       <c r="E130" s="14">
         <v>81</v>
       </c>
-      <c r="F130" s="10">
-        <v>71.8</v>
+      <c r="F130" s="14">
+        <v>86</v>
       </c>
       <c r="G130" s="14">
         <v>42</v>
@@ -5383,8 +5383,8 @@
       <c r="E131" s="14">
         <v>91</v>
       </c>
-      <c r="F131" s="10">
-        <v>60.199999999999996</v>
+      <c r="F131" s="14">
+        <v>81</v>
       </c>
       <c r="G131" s="14">
         <v>56</v>
@@ -5409,8 +5409,8 @@
       <c r="E132" s="14">
         <v>92</v>
       </c>
-      <c r="F132" s="10">
-        <v>43.8</v>
+      <c r="F132" s="14">
+        <v>73</v>
       </c>
       <c r="G132" s="14">
         <v>79</v>
@@ -5435,8 +5435,8 @@
       <c r="E133" s="14">
         <v>68</v>
       </c>
-      <c r="F133" s="10">
-        <v>46.199999999999996</v>
+      <c r="F133" s="14">
+        <v>87</v>
       </c>
       <c r="G133" s="14">
         <v>61</v>
@@ -5461,8 +5461,8 @@
       <c r="E134" s="14">
         <v>80</v>
       </c>
-      <c r="F134" s="10">
-        <v>79.199999999999989</v>
+      <c r="F134" s="14">
+        <v>94</v>
       </c>
       <c r="G134" s="14">
         <v>66</v>
@@ -5487,8 +5487,8 @@
       <c r="E135" s="14">
         <v>80</v>
       </c>
-      <c r="F135" s="10">
-        <v>62.4</v>
+      <c r="F135" s="14">
+        <v>66</v>
       </c>
       <c r="G135" s="14">
         <v>37</v>
@@ -5513,8 +5513,8 @@
       <c r="E136" s="14">
         <v>87</v>
       </c>
-      <c r="F136" s="10">
-        <v>61.599999999999987</v>
+      <c r="F136" s="14">
+        <v>94</v>
       </c>
       <c r="G136" s="14">
         <v>50</v>
@@ -5539,8 +5539,8 @@
       <c r="E137" s="14">
         <v>61</v>
       </c>
-      <c r="F137" s="10">
-        <v>58.20000000000001</v>
+      <c r="F137" s="14">
+        <v>73</v>
       </c>
       <c r="G137" s="14">
         <v>65</v>
@@ -5565,8 +5565,8 @@
       <c r="E138" s="14">
         <v>75</v>
       </c>
-      <c r="F138" s="10">
-        <v>49.4</v>
+      <c r="F138" s="14">
+        <v>76</v>
       </c>
       <c r="G138" s="14">
         <v>56</v>
@@ -5591,8 +5591,8 @@
       <c r="E139" s="14">
         <v>69</v>
       </c>
-      <c r="F139" s="10">
-        <v>73.599999999999994</v>
+      <c r="F139" s="14">
+        <v>87</v>
       </c>
       <c r="G139" s="14">
         <v>51</v>
@@ -5617,8 +5617,8 @@
       <c r="E140" s="14">
         <v>84</v>
       </c>
-      <c r="F140" s="10">
-        <v>42</v>
+      <c r="F140" s="14">
+        <v>70</v>
       </c>
       <c r="G140" s="14">
         <v>63</v>
@@ -5643,8 +5643,8 @@
       <c r="E141" s="14">
         <v>80</v>
       </c>
-      <c r="F141" s="10">
-        <v>40.199999999999996</v>
+      <c r="F141" s="14">
+        <v>67</v>
       </c>
       <c r="G141" s="14">
         <v>41</v>
@@ -5669,8 +5669,8 @@
       <c r="E142" s="14">
         <v>87</v>
       </c>
-      <c r="F142" s="10">
-        <v>47.2</v>
+      <c r="F142" s="14">
+        <v>65</v>
       </c>
       <c r="G142" s="14">
         <v>53</v>
@@ -5695,8 +5695,8 @@
       <c r="E143" s="14">
         <v>75</v>
       </c>
-      <c r="F143" s="10">
-        <v>32.4</v>
+      <c r="F143" s="14">
+        <v>54</v>
       </c>
       <c r="G143" s="14">
         <v>66</v>
@@ -5721,8 +5721,8 @@
       <c r="E144" s="14">
         <v>73</v>
       </c>
-      <c r="F144" s="10">
-        <v>24.6</v>
+      <c r="F144" s="14">
+        <v>41</v>
       </c>
       <c r="G144" s="14">
         <v>80</v>
@@ -5747,8 +5747,8 @@
       <c r="E145" s="14">
         <v>78</v>
       </c>
-      <c r="F145" s="10">
-        <v>60.199999999999996</v>
+      <c r="F145" s="14">
+        <v>81</v>
       </c>
       <c r="G145" s="14">
         <v>67</v>
@@ -5773,8 +5773,8 @@
       <c r="E146" s="14">
         <v>98</v>
       </c>
-      <c r="F146" s="10">
-        <v>72.600000000000009</v>
+      <c r="F146" s="14">
+        <v>96</v>
       </c>
       <c r="G146" s="14">
         <v>70</v>
@@ -5799,8 +5799,8 @@
       <c r="E147" s="14">
         <v>87</v>
       </c>
-      <c r="F147" s="10">
-        <v>45.2</v>
+      <c r="F147" s="14">
+        <v>61</v>
       </c>
       <c r="G147" s="14">
         <v>26</v>
@@ -5825,8 +5825,8 @@
       <c r="E148" s="14">
         <v>89</v>
       </c>
-      <c r="F148" s="10">
-        <v>56.600000000000009</v>
+      <c r="F148" s="14">
+        <v>71</v>
       </c>
       <c r="G148" s="14">
         <v>38</v>
@@ -5851,8 +5851,8 @@
       <c r="E149" s="14">
         <v>64</v>
       </c>
-      <c r="F149" s="10">
-        <v>52.2</v>
+      <c r="F149" s="14">
+        <v>75</v>
       </c>
       <c r="G149" s="14">
         <v>51</v>
@@ -5877,8 +5877,8 @@
       <c r="E150" s="14">
         <v>100</v>
       </c>
-      <c r="F150" s="10">
-        <v>46.8</v>
+      <c r="F150" s="14">
+        <v>96</v>
       </c>
       <c r="G150" s="14">
         <v>58</v>
@@ -5903,8 +5903,8 @@
       <c r="E151" s="14">
         <v>64</v>
       </c>
-      <c r="F151" s="10">
-        <v>61.6</v>
+      <c r="F151" s="14">
+        <v>80</v>
       </c>
       <c r="G151" s="14">
         <v>55</v>
@@ -5929,8 +5929,8 @@
       <c r="E152" s="14">
         <v>73</v>
       </c>
-      <c r="F152" s="10">
-        <v>43.8</v>
+      <c r="F152" s="14">
+        <v>73</v>
       </c>
       <c r="G152" s="14">
         <v>41</v>
@@ -5955,8 +5955,8 @@
       <c r="E153" s="14">
         <v>77</v>
       </c>
-      <c r="F153" s="10">
-        <v>52.800000000000004</v>
+      <c r="F153" s="14">
+        <v>66</v>
       </c>
       <c r="G153" s="14">
         <v>58</v>
@@ -5981,8 +5981,8 @@
       <c r="E154" s="14">
         <v>76</v>
       </c>
-      <c r="F154" s="10">
-        <v>25.799999999999994</v>
+      <c r="F154" s="14">
+        <v>43</v>
       </c>
       <c r="G154" s="14">
         <v>72</v>
@@ -6007,8 +6007,8 @@
       <c r="E155" s="14">
         <v>78</v>
       </c>
-      <c r="F155" s="10">
-        <v>30</v>
+      <c r="F155" s="14">
+        <v>50</v>
       </c>
       <c r="G155" s="14">
         <v>55</v>
@@ -6033,8 +6033,8 @@
       <c r="E156" s="14">
         <v>81</v>
       </c>
-      <c r="F156" s="10">
-        <v>55.000000000000007</v>
+      <c r="F156" s="14">
+        <v>59</v>
       </c>
       <c r="G156" s="14">
         <v>90</v>
@@ -6059,8 +6059,8 @@
       <c r="E157" s="14">
         <v>59</v>
       </c>
-      <c r="F157" s="10">
-        <v>37.200000000000003</v>
+      <c r="F157" s="14">
+        <v>62</v>
       </c>
       <c r="G157" s="14">
         <v>54</v>
@@ -6085,8 +6085,8 @@
       <c r="E158" s="14">
         <v>88</v>
       </c>
-      <c r="F158" s="10">
-        <v>32.4</v>
+      <c r="F158" s="14">
+        <v>54</v>
       </c>
       <c r="G158" s="14">
         <v>55</v>
@@ -6111,8 +6111,8 @@
       <c r="E159" s="14">
         <v>68</v>
       </c>
-      <c r="F159" s="10">
-        <v>52.6</v>
+      <c r="F159" s="14">
+        <v>75</v>
       </c>
       <c r="G159" s="14">
         <v>52</v>
@@ -6137,8 +6137,8 @@
       <c r="E160" s="14">
         <v>72</v>
       </c>
-      <c r="F160" s="10">
-        <v>38.4</v>
+      <c r="F160" s="14">
+        <v>75</v>
       </c>
       <c r="G160" s="14">
         <v>56</v>
@@ -6163,8 +6163,8 @@
       <c r="E161" s="14">
         <v>69</v>
       </c>
-      <c r="F161" s="10">
-        <v>15</v>
+      <c r="F161" s="14">
+        <v>25</v>
       </c>
       <c r="G161" s="14">
         <v>45</v>
@@ -6189,8 +6189,8 @@
       <c r="E162" s="14">
         <v>72</v>
       </c>
-      <c r="F162" s="10">
-        <v>25.6</v>
+      <c r="F162" s="14">
+        <v>53</v>
       </c>
       <c r="G162" s="14">
         <v>63</v>
@@ -6215,8 +6215,8 @@
       <c r="E163" s="14">
         <v>81</v>
       </c>
-      <c r="F163" s="10">
-        <v>53.999999999999993</v>
+      <c r="F163" s="14">
+        <v>75</v>
       </c>
       <c r="G163" s="14">
         <v>46</v>
@@ -6241,8 +6241,8 @@
       <c r="E164" s="14">
         <v>70</v>
       </c>
-      <c r="F164" s="10">
-        <v>25.799999999999994</v>
+      <c r="F164" s="14">
+        <v>43</v>
       </c>
       <c r="G164" s="14">
         <v>78</v>
@@ -6267,8 +6267,8 @@
       <c r="E165" s="14">
         <v>72</v>
       </c>
-      <c r="F165" s="10">
-        <v>46.8</v>
+      <c r="F165" s="14">
+        <v>78</v>
       </c>
       <c r="G165" s="14">
         <v>50</v>
@@ -6293,8 +6293,8 @@
       <c r="E166" s="14">
         <v>82</v>
       </c>
-      <c r="F166" s="10">
-        <v>42.6</v>
+      <c r="F166" s="14">
+        <v>71</v>
       </c>
       <c r="G166" s="14">
         <v>64</v>
@@ -6319,8 +6319,8 @@
       <c r="E167" s="14">
         <v>68</v>
       </c>
-      <c r="F167" s="10">
-        <v>81</v>
+      <c r="F167" s="14">
+        <v>96</v>
       </c>
       <c r="G167" s="14">
         <v>78</v>
@@ -6345,8 +6345,8 @@
       <c r="E168" s="14">
         <v>79</v>
       </c>
-      <c r="F168" s="10">
-        <v>43.8</v>
+      <c r="F168" s="14">
+        <v>73</v>
       </c>
       <c r="G168" s="14">
         <v>63</v>
@@ -6371,8 +6371,8 @@
       <c r="E169" s="14">
         <v>90</v>
       </c>
-      <c r="F169" s="10">
-        <v>41.6</v>
+      <c r="F169" s="14">
+        <v>85</v>
       </c>
       <c r="G169" s="14">
         <v>79</v>
@@ -6397,8 +6397,8 @@
       <c r="E170" s="14">
         <v>78</v>
       </c>
-      <c r="F170" s="10">
-        <v>36.599999999999994</v>
+      <c r="F170" s="14">
+        <v>47</v>
       </c>
       <c r="G170" s="14">
         <v>38</v>
@@ -6423,8 +6423,8 @@
       <c r="E171" s="14">
         <v>70</v>
       </c>
-      <c r="F171" s="10">
-        <v>47.599999999999994</v>
+      <c r="F171" s="14">
+        <v>76</v>
       </c>
       <c r="G171" s="14">
         <v>41</v>
@@ -6449,8 +6449,8 @@
       <c r="E172" s="14">
         <v>55</v>
       </c>
-      <c r="F172" s="10">
-        <v>25.799999999999994</v>
+      <c r="F172" s="14">
+        <v>43</v>
       </c>
       <c r="G172" s="14">
         <v>30</v>
@@ -6475,8 +6475,8 @@
       <c r="E173" s="14">
         <v>96</v>
       </c>
-      <c r="F173" s="10">
-        <v>36</v>
+      <c r="F173" s="14">
+        <v>60</v>
       </c>
       <c r="G173" s="14">
         <v>48</v>
@@ -6501,8 +6501,8 @@
       <c r="E174" s="14">
         <v>71</v>
       </c>
-      <c r="F174" s="10">
-        <v>56.199999999999996</v>
+      <c r="F174" s="14">
+        <v>73</v>
       </c>
       <c r="G174" s="14">
         <v>25</v>
@@ -6527,8 +6527,8 @@
       <c r="E175" s="14">
         <v>75</v>
       </c>
-      <c r="F175" s="10">
-        <v>45</v>
+      <c r="F175" s="14">
+        <v>75</v>
       </c>
       <c r="G175" s="14">
         <v>29</v>
@@ -6553,8 +6553,8 @@
       <c r="E176" s="14">
         <v>62</v>
       </c>
-      <c r="F176" s="10">
-        <v>45.4</v>
+      <c r="F176" s="14">
+        <v>65</v>
       </c>
       <c r="G176" s="14">
         <v>55</v>
@@ -6579,8 +6579,8 @@
       <c r="E177" s="14">
         <v>79</v>
       </c>
-      <c r="F177" s="10">
-        <v>51.800000000000004</v>
+      <c r="F177" s="14">
+        <v>82</v>
       </c>
       <c r="G177" s="14">
         <v>49</v>
@@ -6605,8 +6605,8 @@
       <c r="E178" s="14">
         <v>81</v>
       </c>
-      <c r="F178" s="10">
-        <v>60.999999999999986</v>
+      <c r="F178" s="14">
+        <v>78</v>
       </c>
       <c r="G178" s="14">
         <v>84</v>
@@ -6631,8 +6631,8 @@
       <c r="E179" s="14">
         <v>90</v>
       </c>
-      <c r="F179" s="10">
-        <v>60.999999999999986</v>
+      <c r="F179" s="14">
+        <v>78</v>
       </c>
       <c r="G179" s="14">
         <v>78</v>
@@ -6657,8 +6657,8 @@
       <c r="E180" s="14">
         <v>48</v>
       </c>
-      <c r="F180" s="10">
-        <v>26.400000000000002</v>
+      <c r="F180" s="14">
+        <v>44</v>
       </c>
       <c r="G180" s="14">
         <v>42</v>
@@ -6683,8 +6683,8 @@
       <c r="E181" s="14">
         <v>78</v>
       </c>
-      <c r="F181" s="10">
-        <v>23.4</v>
+      <c r="F181" s="14">
+        <v>39</v>
       </c>
       <c r="G181" s="14">
         <v>58</v>
@@ -6709,8 +6709,8 @@
       <c r="E182" s="14">
         <v>66</v>
       </c>
-      <c r="F182" s="10">
-        <v>33.800000000000004</v>
+      <c r="F182" s="14">
+        <v>52</v>
       </c>
       <c r="G182" s="14">
         <v>34</v>
@@ -6735,8 +6735,8 @@
       <c r="E183" s="14">
         <v>93</v>
       </c>
-      <c r="F183" s="10">
-        <v>59.600000000000009</v>
+      <c r="F183" s="14">
+        <v>82</v>
       </c>
       <c r="G183" s="14">
         <v>49</v>
@@ -6761,8 +6761,8 @@
       <c r="E184" s="14">
         <v>76</v>
       </c>
-      <c r="F184" s="10">
-        <v>52.6</v>
+      <c r="F184" s="14">
+        <v>78</v>
       </c>
       <c r="G184" s="14">
         <v>67</v>
@@ -6787,8 +6787,8 @@
       <c r="E185" s="14">
         <v>65</v>
       </c>
-      <c r="F185" s="10">
-        <v>45</v>
+      <c r="F185" s="14">
+        <v>75</v>
       </c>
       <c r="G185" s="14">
         <v>72</v>
@@ -6813,8 +6813,8 @@
       <c r="E186" s="14">
         <v>74</v>
       </c>
-      <c r="F186" s="10">
-        <v>49.599999999999994</v>
+      <c r="F186" s="14">
+        <v>62</v>
       </c>
       <c r="G186" s="14">
         <v>58</v>
@@ -6839,8 +6839,8 @@
       <c r="E187" s="14">
         <v>58</v>
       </c>
-      <c r="F187" s="10">
-        <v>39.599999999999994</v>
+      <c r="F187" s="14">
+        <v>52</v>
       </c>
       <c r="G187" s="14">
         <v>37</v>
@@ -6865,8 +6865,8 @@
       <c r="E188" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F188" s="10">
-        <v>43.8</v>
+      <c r="F188" s="14">
+        <v>73</v>
       </c>
       <c r="G188" s="14">
         <v>42</v>
@@ -8182,18 +8182,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8374,18 +8374,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6B50D8-0F8B-403E-8859-669A61D04BDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEDF697-907A-42E5-892A-657C1A2ED37C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
